--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\python\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC2F136-2D4F-4C09-9EE6-29BDA8F88293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989FB45E-C548-4CD8-A12E-2343B8EFF2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4577" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4579" uniqueCount="730">
   <si>
     <t>mCODE Profile Name</t>
   </si>
@@ -13163,6 +13163,9 @@
       <c r="J506" s="3" t="s">
         <v>308</v>
       </c>
+      <c r="K506" s="3" t="s">
+        <v>698</v>
+      </c>
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E507" s="3" t="s">
@@ -13190,6 +13193,9 @@
       </c>
       <c r="H508" s="7" t="s">
         <v>228</v>
+      </c>
+      <c r="K508" s="3" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\python\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B69D8E-A767-402C-96BF-08E1761BA9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A1A96-F0D5-4BC8-8D15-1ACE1BB15999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3075" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3077" uniqueCount="615">
   <si>
     <t>Sample Registration</t>
   </si>
@@ -12813,6 +12813,9 @@
       <c r="J506" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="K506" s="2" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E507" s="2" t="s">
@@ -12840,6 +12843,9 @@
       </c>
       <c r="H508" s="6" t="s">
         <v>113</v>
+      </c>
+      <c r="K508" s="2" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\python\mohccn-omop-etl\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A1A96-F0D5-4BC8-8D15-1ACE1BB15999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E356004-6E7F-4FDE-B5CC-B7CD68E49688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformation Model" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3077" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="619">
   <si>
     <t>Sample Registration</t>
   </si>
@@ -1886,6 +1886,18 @@
   </si>
   <si>
     <t>Will probably need to create a comorbidity episode and link procedure_occurrence via episode_event</t>
+  </si>
+  <si>
+    <t>$.donors[].followups[]</t>
+  </si>
+  <si>
+    <t>$.donors[].primary_diagnoses[].followups[]</t>
+  </si>
+  <si>
+    <t>OMOP Primary Dx Episode / Visit Occurrence Event</t>
+  </si>
+  <si>
+    <t>OMOP Treatment Episode / Visit Occurrence Event</t>
   </si>
 </sst>
 </file>
@@ -2315,25 +2327,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9C41B9-3FB6-4282-940B-7420BB7A8AED}">
-  <dimension ref="A1:L528"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L586"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="47.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.5703125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="43.85546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.85546875" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="25.7265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="47.453125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.81640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.54296875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="43.81640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.81640625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>121</v>
       </c>
@@ -2371,7 +2383,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
@@ -2403,7 +2415,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D3" s="2" t="s">
         <v>130</v>
       </c>
@@ -2425,7 +2437,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D4" s="2" t="s">
         <v>136</v>
       </c>
@@ -2451,7 +2463,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D5" s="2" t="s">
         <v>138</v>
       </c>
@@ -2477,7 +2489,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D6" s="2" t="s">
         <v>574</v>
       </c>
@@ -2503,7 +2515,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D7" s="2" t="s">
         <v>140</v>
       </c>
@@ -2529,7 +2541,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D8" s="2" t="s">
         <v>140</v>
       </c>
@@ -2549,7 +2561,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D9" s="2" t="s">
         <v>143</v>
       </c>
@@ -2575,7 +2587,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D10" s="2" t="s">
         <v>145</v>
       </c>
@@ -2602,7 +2614,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D11" s="2" t="s">
         <v>179</v>
       </c>
@@ -2626,7 +2638,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D12" s="2" t="s">
         <v>130</v>
       </c>
@@ -2650,7 +2662,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
         <v>145</v>
       </c>
@@ -2674,7 +2686,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
         <v>284</v>
       </c>
@@ -2698,7 +2710,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
         <v>143</v>
       </c>
@@ -2722,7 +2734,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
         <v>140</v>
       </c>
@@ -2746,7 +2758,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
         <v>574</v>
       </c>
@@ -2770,7 +2782,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D18" s="2" t="s">
         <v>138</v>
       </c>
@@ -2794,7 +2806,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D19" s="2" t="s">
         <v>136</v>
       </c>
@@ -2818,7 +2830,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D20" s="2" t="s">
         <v>140</v>
       </c>
@@ -2839,7 +2851,7 @@
         <v>OMOP Specimen</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D21" s="2" t="s">
         <v>140</v>
       </c>
@@ -2860,7 +2872,7 @@
         <v>OMOP Primary Dx Episode</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D22" s="2" t="s">
         <v>140</v>
       </c>
@@ -2881,7 +2893,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D23" s="2" t="s">
         <v>140</v>
       </c>
@@ -2902,7 +2914,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D24" s="2" t="s">
         <v>140</v>
       </c>
@@ -2928,7 +2940,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D25" s="2" t="s">
         <v>140</v>
       </c>
@@ -2954,7 +2966,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
         <v>140</v>
       </c>
@@ -2980,7 +2992,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D27" s="2" t="s">
         <v>140</v>
       </c>
@@ -3006,7 +3018,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>534</v>
       </c>
@@ -3030,7 +3042,7 @@
       </c>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D29" s="2" t="s">
         <v>543</v>
       </c>
@@ -3050,7 +3062,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D30" s="2" t="s">
         <v>543</v>
       </c>
@@ -3070,7 +3082,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D31" s="2" t="s">
         <v>543</v>
       </c>
@@ -3090,7 +3102,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D32" s="2" t="s">
         <v>543</v>
       </c>
@@ -3110,7 +3122,7 @@
         <v>4255047</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="2" t="s">
         <v>543</v>
       </c>
@@ -3130,7 +3142,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="3" t="s">
         <v>605</v>
@@ -3151,7 +3163,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D35" s="2" t="s">
         <v>543</v>
       </c>
@@ -3168,7 +3180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D36" s="2" t="s">
         <v>543</v>
       </c>
@@ -3185,7 +3197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D37" s="2" t="s">
         <v>543</v>
       </c>
@@ -3202,7 +3214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B38" s="2"/>
       <c r="D38" s="2" t="s">
         <v>594</v>
@@ -3226,7 +3238,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="3" t="s">
         <v>433</v>
@@ -3250,7 +3262,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E40" s="2" t="s">
         <v>156</v>
       </c>
@@ -3270,7 +3282,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C41" s="2" t="s">
         <v>157</v>
       </c>
@@ -3296,7 +3308,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C42" s="2" t="s">
         <v>161</v>
       </c>
@@ -3313,7 +3325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C43" s="2" t="s">
         <v>163</v>
       </c>
@@ -3333,7 +3345,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C44" s="2" t="s">
         <v>166</v>
       </c>
@@ -3353,7 +3365,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C45" s="2" t="s">
         <v>169</v>
       </c>
@@ -3373,7 +3385,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E46" s="2" t="s">
         <v>592</v>
       </c>
@@ -3390,7 +3402,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E47" s="2" t="s">
         <v>593</v>
       </c>
@@ -3407,7 +3419,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>434</v>
       </c>
@@ -3430,7 +3442,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E49" s="2" t="s">
         <v>173</v>
       </c>
@@ -3453,7 +3465,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C50" s="2" t="s">
         <v>175</v>
       </c>
@@ -3473,7 +3485,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C51" s="2" t="s">
         <v>177</v>
       </c>
@@ -3490,7 +3502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>435</v>
       </c>
@@ -3520,7 +3532,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C53" s="2" t="s">
         <v>181</v>
       </c>
@@ -3540,7 +3552,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C54" s="2" t="s">
         <v>184</v>
       </c>
@@ -3557,7 +3569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C55" s="2" t="s">
         <v>186</v>
       </c>
@@ -3574,7 +3586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>481</v>
       </c>
@@ -3588,7 +3600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E57" s="2" t="s">
         <v>188</v>
       </c>
@@ -3599,7 +3611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E58" s="2" t="s">
         <v>188</v>
       </c>
@@ -3610,7 +3622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>535</v>
       </c>
@@ -3636,7 +3648,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="D60" s="2" t="s">
         <v>145</v>
@@ -3657,7 +3669,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C61" s="2" t="s">
         <v>190</v>
       </c>
@@ -3680,7 +3692,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C62" s="2" t="s">
         <v>194</v>
       </c>
@@ -3697,7 +3709,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C63" s="2" t="s">
         <v>196</v>
       </c>
@@ -3718,7 +3730,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E64" s="2" t="s">
         <v>198</v>
       </c>
@@ -3742,7 +3754,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>437</v>
       </c>
@@ -3765,7 +3777,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E66" s="2" t="s">
         <v>201</v>
       </c>
@@ -3788,7 +3800,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E67" s="2" t="s">
         <v>205</v>
       </c>
@@ -3805,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E68" s="2" t="s">
         <v>206</v>
       </c>
@@ -3826,7 +3838,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E69" s="2" t="s">
         <v>207</v>
       </c>
@@ -3843,7 +3855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E70" s="2" t="s">
         <v>208</v>
       </c>
@@ -3860,7 +3872,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E71" s="2" t="s">
         <v>209</v>
       </c>
@@ -3877,7 +3889,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="72" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>485</v>
       </c>
@@ -3904,7 +3916,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E73" s="2" t="s">
         <v>211</v>
       </c>
@@ -3925,7 +3937,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E74" s="2" t="s">
         <v>212</v>
       </c>
@@ -3948,7 +3960,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="75" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>439</v>
       </c>
@@ -3971,7 +3983,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E76" s="2" t="s">
         <v>214</v>
       </c>
@@ -3994,7 +4006,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E77" s="2" t="s">
         <v>142</v>
       </c>
@@ -4011,7 +4023,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E78" s="2" t="s">
         <v>149</v>
       </c>
@@ -4032,7 +4044,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E79" s="2" t="s">
         <v>150</v>
       </c>
@@ -4055,7 +4067,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C80" s="2" t="s">
         <v>217</v>
       </c>
@@ -4072,7 +4084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C81" s="2" t="s">
         <v>218</v>
       </c>
@@ -4089,7 +4101,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>440</v>
       </c>
@@ -4112,7 +4124,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E83" s="2" t="s">
         <v>214</v>
       </c>
@@ -4135,7 +4147,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E84" s="2" t="s">
         <v>142</v>
       </c>
@@ -4152,7 +4164,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E85" s="2" t="s">
         <v>149</v>
       </c>
@@ -4173,7 +4185,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E86" s="2" t="s">
         <v>150</v>
       </c>
@@ -4196,7 +4208,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C87" s="2" t="s">
         <v>221</v>
       </c>
@@ -4216,7 +4228,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C88" s="2" t="s">
         <v>222</v>
       </c>
@@ -4233,7 +4245,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
         <v>441</v>
       </c>
@@ -4256,7 +4268,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E90" s="2" t="s">
         <v>173</v>
       </c>
@@ -4279,7 +4291,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E91" s="2" t="s">
         <v>135</v>
       </c>
@@ -4296,7 +4308,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C92" s="2" t="s">
         <v>226</v>
       </c>
@@ -4316,7 +4328,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C93" s="2" t="s">
         <v>227</v>
       </c>
@@ -4333,7 +4345,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E94" s="2" t="s">
         <v>228</v>
       </c>
@@ -4354,7 +4366,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E95" s="2" t="s">
         <v>229</v>
       </c>
@@ -4377,7 +4389,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="96" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
         <v>431</v>
       </c>
@@ -4400,7 +4412,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E97" s="2" t="s">
         <v>214</v>
       </c>
@@ -4423,7 +4435,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E98" s="2" t="s">
         <v>142</v>
       </c>
@@ -4440,7 +4452,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E99" s="2" t="s">
         <v>149</v>
       </c>
@@ -4461,7 +4473,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E100" s="2" t="s">
         <v>150</v>
       </c>
@@ -4484,7 +4496,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C101" s="2" t="s">
         <v>233</v>
       </c>
@@ -4504,7 +4516,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C102" s="2" t="s">
         <v>234</v>
       </c>
@@ -4521,7 +4533,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="103" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B103" s="3" t="s">
         <v>432</v>
       </c>
@@ -4544,7 +4556,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E104" s="2" t="s">
         <v>214</v>
       </c>
@@ -4567,7 +4579,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E105" s="2" t="s">
         <v>142</v>
       </c>
@@ -4584,7 +4596,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E106" s="2" t="s">
         <v>149</v>
       </c>
@@ -4605,7 +4617,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E107" s="2" t="s">
         <v>150</v>
       </c>
@@ -4628,7 +4640,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C108" s="2" t="s">
         <v>235</v>
       </c>
@@ -4648,7 +4660,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C109" s="2" t="s">
         <v>236</v>
       </c>
@@ -4665,7 +4677,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B110" s="3" t="s">
         <v>438</v>
       </c>
@@ -4688,7 +4700,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E111" s="2" t="s">
         <v>214</v>
       </c>
@@ -4711,7 +4723,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E112" s="2" t="s">
         <v>142</v>
       </c>
@@ -4728,7 +4740,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E113" s="2" t="s">
         <v>149</v>
       </c>
@@ -4749,7 +4761,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E114" s="2" t="s">
         <v>150</v>
       </c>
@@ -4772,7 +4784,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C115" s="2" t="s">
         <v>237</v>
       </c>
@@ -4792,7 +4804,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C116" s="2" t="s">
         <v>238</v>
       </c>
@@ -4809,7 +4821,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="117" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B117" s="3" t="s">
         <v>442</v>
       </c>
@@ -4832,7 +4844,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C118" s="2" t="s">
         <v>230</v>
       </c>
@@ -4852,7 +4864,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C119" s="2" t="s">
         <v>231</v>
       </c>
@@ -4869,7 +4881,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E120" s="2" t="s">
         <v>142</v>
       </c>
@@ -4886,7 +4898,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E121" s="2" t="s">
         <v>149</v>
       </c>
@@ -4904,7 +4916,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E122" s="2" t="s">
         <v>150</v>
       </c>
@@ -4927,7 +4939,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C123" s="2" t="s">
         <v>239</v>
       </c>
@@ -4944,7 +4956,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C124" s="2" t="s">
         <v>240</v>
       </c>
@@ -4961,7 +4973,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="125" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B125" s="3" t="s">
         <v>443</v>
       </c>
@@ -4984,7 +4996,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E126" s="2" t="s">
         <v>214</v>
       </c>
@@ -5007,7 +5019,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E127" s="2" t="s">
         <v>142</v>
       </c>
@@ -5024,7 +5036,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E128" s="2" t="s">
         <v>149</v>
       </c>
@@ -5045,7 +5057,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E129" s="2" t="s">
         <v>150</v>
       </c>
@@ -5068,7 +5080,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C130" s="2" t="s">
         <v>243</v>
       </c>
@@ -5088,7 +5100,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C131" s="2" t="s">
         <v>244</v>
       </c>
@@ -5105,7 +5117,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B132" s="3" t="s">
         <v>444</v>
       </c>
@@ -5128,7 +5140,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E133" s="2" t="s">
         <v>214</v>
       </c>
@@ -5151,7 +5163,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E134" s="2" t="s">
         <v>142</v>
       </c>
@@ -5168,7 +5180,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E135" s="2" t="s">
         <v>149</v>
       </c>
@@ -5189,7 +5201,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E136" s="2" t="s">
         <v>150</v>
       </c>
@@ -5212,7 +5224,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C137" s="2" t="s">
         <v>245</v>
       </c>
@@ -5232,7 +5244,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C138" s="2" t="s">
         <v>246</v>
       </c>
@@ -5249,7 +5261,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="139" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B139" s="3" t="s">
         <v>445</v>
       </c>
@@ -5272,7 +5284,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E140" s="2" t="s">
         <v>214</v>
       </c>
@@ -5295,7 +5307,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E141" s="2" t="s">
         <v>142</v>
       </c>
@@ -5312,7 +5324,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E142" s="2" t="s">
         <v>149</v>
       </c>
@@ -5333,7 +5345,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E143" s="2" t="s">
         <v>150</v>
       </c>
@@ -5356,7 +5368,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C144" s="2" t="s">
         <v>247</v>
       </c>
@@ -5376,7 +5388,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C145" s="2" t="s">
         <v>248</v>
       </c>
@@ -5393,7 +5405,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B146" s="3" t="s">
         <v>446</v>
       </c>
@@ -5416,7 +5428,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C147" s="2" t="s">
         <v>241</v>
       </c>
@@ -5436,7 +5448,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C148" s="2" t="s">
         <v>242</v>
       </c>
@@ -5453,7 +5465,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E149" s="2" t="s">
         <v>142</v>
       </c>
@@ -5470,7 +5482,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E150" s="2" t="s">
         <v>149</v>
       </c>
@@ -5491,7 +5503,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E151" s="2" t="s">
         <v>150</v>
       </c>
@@ -5514,7 +5526,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C152" s="2" t="s">
         <v>249</v>
       </c>
@@ -5531,7 +5543,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C153" s="2" t="s">
         <v>509</v>
       </c>
@@ -5548,7 +5560,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>536</v>
       </c>
@@ -5574,7 +5586,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D155" s="2" t="s">
         <v>543</v>
       </c>
@@ -5594,7 +5606,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D156" s="2" t="s">
         <v>543</v>
       </c>
@@ -5611,7 +5623,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="D157" s="2" t="s">
@@ -5633,7 +5645,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E158" s="2" t="s">
         <v>201</v>
       </c>
@@ -5656,7 +5668,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E159" s="2" t="s">
         <v>205</v>
       </c>
@@ -5673,7 +5685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E160" s="2" t="s">
         <v>206</v>
       </c>
@@ -5690,7 +5702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C161" s="2" t="s">
         <v>252</v>
       </c>
@@ -5710,7 +5722,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C162" s="2" t="s">
         <v>253</v>
       </c>
@@ -5727,7 +5739,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C163" s="2" t="s">
         <v>254</v>
       </c>
@@ -5744,7 +5756,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="164" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B164" s="3" t="s">
         <v>448</v>
       </c>
@@ -5767,7 +5779,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E165" s="2" t="s">
         <v>173</v>
       </c>
@@ -5790,7 +5802,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E166" s="2" t="s">
         <v>135</v>
       </c>
@@ -5807,7 +5819,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E167" s="2" t="s">
         <v>228</v>
       </c>
@@ -5828,7 +5840,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E168" s="2" t="s">
         <v>229</v>
       </c>
@@ -5851,7 +5863,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C169" s="2" t="s">
         <v>266</v>
       </c>
@@ -5871,7 +5883,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C170" s="2" t="s">
         <v>267</v>
       </c>
@@ -5888,7 +5900,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="171" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B171" s="3" t="s">
         <v>449</v>
       </c>
@@ -5911,7 +5923,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E172" s="2" t="s">
         <v>173</v>
       </c>
@@ -5934,7 +5946,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C173" s="2" t="s">
         <v>272</v>
       </c>
@@ -5954,7 +5966,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C174" s="2" t="s">
         <v>273</v>
       </c>
@@ -5971,7 +5983,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E175" s="2" t="s">
         <v>135</v>
       </c>
@@ -5988,7 +6000,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E176" s="2" t="s">
         <v>228</v>
       </c>
@@ -6009,7 +6021,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E177" s="2" t="s">
         <v>229</v>
       </c>
@@ -6032,7 +6044,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C178" s="2" t="s">
         <v>274</v>
       </c>
@@ -6049,7 +6061,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C179" s="2" t="s">
         <v>276</v>
       </c>
@@ -6066,7 +6078,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>608</v>
       </c>
@@ -6092,7 +6104,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E181" s="2" t="s">
         <v>256</v>
       </c>
@@ -6109,7 +6121,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C182" s="2" t="s">
         <v>257</v>
       </c>
@@ -6126,7 +6138,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E183" s="2" t="s">
         <v>259</v>
       </c>
@@ -6146,7 +6158,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C184" s="2" t="s">
         <v>260</v>
       </c>
@@ -6166,7 +6178,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C185" s="2" t="s">
         <v>262</v>
       </c>
@@ -6186,7 +6198,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B186" s="3" t="s">
         <v>610</v>
       </c>
@@ -6213,7 +6225,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E187" s="2" t="s">
         <v>211</v>
       </c>
@@ -6234,7 +6246,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E188" s="2" t="s">
         <v>212</v>
       </c>
@@ -6257,7 +6269,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
         <v>537</v>
       </c>
@@ -6284,7 +6296,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E190" s="2" t="s">
         <v>201</v>
       </c>
@@ -6307,7 +6319,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E191" s="2" t="s">
         <v>205</v>
       </c>
@@ -6324,7 +6336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E192" s="2" t="s">
         <v>206</v>
       </c>
@@ -6342,7 +6354,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E193" s="2" t="s">
         <v>208</v>
       </c>
@@ -6359,7 +6371,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E194" s="2" t="s">
         <v>209</v>
       </c>
@@ -6373,7 +6385,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="195" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B195" s="3" t="s">
         <v>486</v>
       </c>
@@ -6400,7 +6412,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="196" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E196" s="2" t="s">
         <v>211</v>
       </c>
@@ -6421,7 +6433,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="197" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E197" s="2" t="s">
         <v>212</v>
       </c>
@@ -6444,7 +6456,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B198" s="3" t="s">
         <v>451</v>
       </c>
@@ -6468,7 +6480,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C199" s="2" t="s">
         <v>280</v>
       </c>
@@ -6488,7 +6500,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C200" s="2" t="s">
         <v>281</v>
       </c>
@@ -6505,7 +6517,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="201" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E201" s="2" t="s">
         <v>259</v>
       </c>
@@ -6522,7 +6534,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="202" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C202" s="2" t="s">
         <v>282</v>
       </c>
@@ -6539,7 +6551,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B203" s="3" t="s">
         <v>484</v>
       </c>
@@ -6566,7 +6578,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="204" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E204" s="2" t="s">
         <v>211</v>
       </c>
@@ -6587,7 +6599,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="205" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E205" s="2" t="s">
         <v>212</v>
       </c>
@@ -6610,7 +6622,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B206" s="3" t="s">
         <v>452</v>
       </c>
@@ -6634,7 +6646,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="207" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B207" s="2"/>
       <c r="D207" s="2" t="s">
         <v>284</v>
@@ -6655,7 +6667,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="208" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E208" s="2" t="s">
         <v>286</v>
       </c>
@@ -6678,7 +6690,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E209" s="2" t="s">
         <v>289</v>
       </c>
@@ -6698,7 +6710,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="C210" s="5" t="s">
         <v>291</v>
       </c>
@@ -6715,7 +6727,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="211" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C211" s="2" t="s">
         <v>293</v>
       </c>
@@ -6735,7 +6747,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="212" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C212" s="2" t="s">
         <v>295</v>
       </c>
@@ -6755,7 +6767,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C213" s="2" t="s">
         <v>297</v>
       </c>
@@ -6772,7 +6784,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C214" s="2" t="s">
         <v>299</v>
       </c>
@@ -6789,7 +6801,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B215" s="3" t="s">
         <v>483</v>
       </c>
@@ -6816,7 +6828,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E216" s="2" t="s">
         <v>211</v>
       </c>
@@ -6837,7 +6849,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E217" s="2" t="s">
         <v>212</v>
       </c>
@@ -6860,7 +6872,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B218" s="3" t="s">
         <v>453</v>
       </c>
@@ -6883,7 +6895,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E219" s="2" t="s">
         <v>286</v>
       </c>
@@ -6906,7 +6918,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E220" s="2" t="s">
         <v>289</v>
       </c>
@@ -6926,7 +6938,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="C221" s="5" t="s">
         <v>291</v>
       </c>
@@ -6943,7 +6955,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C222" s="2" t="s">
         <v>293</v>
       </c>
@@ -6963,7 +6975,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C223" s="2" t="s">
         <v>295</v>
       </c>
@@ -6983,7 +6995,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C224" s="2" t="s">
         <v>297</v>
       </c>
@@ -7000,7 +7012,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C225" s="2" t="s">
         <v>304</v>
       </c>
@@ -7017,7 +7029,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B226" s="3" t="s">
         <v>487</v>
       </c>
@@ -7044,7 +7056,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E227" s="2" t="s">
         <v>211</v>
       </c>
@@ -7065,7 +7077,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E228" s="2" t="s">
         <v>212</v>
       </c>
@@ -7088,7 +7100,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B229" s="3" t="s">
         <v>482</v>
       </c>
@@ -7099,7 +7111,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>538</v>
       </c>
@@ -7125,7 +7137,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E231" s="2" t="s">
         <v>201</v>
       </c>
@@ -7148,7 +7160,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E232" s="2" t="s">
         <v>205</v>
       </c>
@@ -7165,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E233" s="2" t="s">
         <v>206</v>
       </c>
@@ -7183,7 +7195,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E234" s="2" t="s">
         <v>208</v>
       </c>
@@ -7203,7 +7215,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B235" s="3" t="s">
         <v>488</v>
       </c>
@@ -7230,7 +7242,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E236" s="2" t="s">
         <v>211</v>
       </c>
@@ -7251,7 +7263,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E237" s="2" t="s">
         <v>212</v>
       </c>
@@ -7274,7 +7286,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B238" s="3" t="s">
         <v>455</v>
       </c>
@@ -7297,7 +7309,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C239" s="2" t="s">
         <v>307</v>
       </c>
@@ -7317,7 +7329,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C240" s="2" t="s">
         <v>308</v>
       </c>
@@ -7334,7 +7346,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="241" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E241" s="2" t="s">
         <v>259</v>
       </c>
@@ -7354,7 +7366,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="242" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C242" s="2" t="s">
         <v>309</v>
       </c>
@@ -7372,7 +7384,7 @@
       </c>
       <c r="I242" s="10"/>
     </row>
-    <row r="243" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C243" s="2" t="s">
         <v>310</v>
       </c>
@@ -7390,7 +7402,7 @@
       </c>
       <c r="I243" s="10"/>
     </row>
-    <row r="244" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B244" s="3" t="s">
         <v>489</v>
       </c>
@@ -7417,7 +7429,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="245" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E245" s="2" t="s">
         <v>211</v>
       </c>
@@ -7438,7 +7450,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="246" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E246" s="2" t="s">
         <v>212</v>
       </c>
@@ -7461,7 +7473,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="247" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B247" s="3" t="s">
         <v>456</v>
       </c>
@@ -7484,7 +7496,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="248" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E248" s="2" t="s">
         <v>214</v>
       </c>
@@ -7507,7 +7519,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="249" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E249" s="2" t="s">
         <v>142</v>
       </c>
@@ -7527,7 +7539,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="250" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E250" s="2" t="s">
         <v>149</v>
       </c>
@@ -7548,7 +7560,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="251" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E251" s="2" t="s">
         <v>150</v>
       </c>
@@ -7571,7 +7583,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="252" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C252" s="2" t="s">
         <v>313</v>
       </c>
@@ -7591,7 +7603,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="253" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C253" s="2" t="s">
         <v>315</v>
       </c>
@@ -7617,7 +7629,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="254" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B254" s="3" t="s">
         <v>457</v>
       </c>
@@ -7640,7 +7652,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="255" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E255" s="2" t="s">
         <v>214</v>
       </c>
@@ -7661,7 +7673,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="256" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E256" s="2" t="s">
         <v>142</v>
       </c>
@@ -7681,7 +7693,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="257" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E257" s="2" t="s">
         <v>149</v>
       </c>
@@ -7702,7 +7714,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="258" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E258" s="2" t="s">
         <v>150</v>
       </c>
@@ -7725,7 +7737,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="259" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C259" s="2" t="s">
         <v>313</v>
       </c>
@@ -7745,7 +7757,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="260" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B260" s="3" t="s">
         <v>458</v>
       </c>
@@ -7768,7 +7780,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="261" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E261" s="2" t="s">
         <v>173</v>
       </c>
@@ -7791,7 +7803,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="262" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E262" s="2" t="s">
         <v>135</v>
       </c>
@@ -7811,7 +7823,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="263" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E263" s="2" t="s">
         <v>228</v>
       </c>
@@ -7832,7 +7844,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="264" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E264" s="2" t="s">
         <v>229</v>
       </c>
@@ -7855,7 +7867,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="265" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C265" s="2" t="s">
         <v>323</v>
       </c>
@@ -7875,7 +7887,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="266" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C266" s="2" t="s">
         <v>324</v>
       </c>
@@ -7892,7 +7904,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="267" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B267" s="3" t="s">
         <v>459</v>
       </c>
@@ -7915,7 +7927,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="268" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E268" s="2" t="s">
         <v>256</v>
       </c>
@@ -7938,7 +7950,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="269" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E269" s="2" t="s">
         <v>259</v>
       </c>
@@ -7958,7 +7970,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="270" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E270" s="2" t="s">
         <v>261</v>
       </c>
@@ -7975,7 +7987,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="271" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E271" s="2" t="s">
         <v>263</v>
       </c>
@@ -7989,7 +8001,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="272" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B272" s="3" t="s">
         <v>490</v>
       </c>
@@ -8016,7 +8028,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E273" s="2" t="s">
         <v>211</v>
       </c>
@@ -8037,7 +8049,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E274" s="2" t="s">
         <v>212</v>
       </c>
@@ -8060,7 +8072,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A275" s="5" t="s">
         <v>539</v>
       </c>
@@ -8083,7 +8095,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D276" s="2" t="s">
         <v>136</v>
       </c>
@@ -8103,7 +8115,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E277" s="2" t="s">
         <v>201</v>
       </c>
@@ -8126,7 +8138,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E278" s="2" t="s">
         <v>205</v>
       </c>
@@ -8143,7 +8155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E279" s="2" t="s">
         <v>206</v>
       </c>
@@ -8164,7 +8176,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E280" s="2" t="s">
         <v>208</v>
       </c>
@@ -8184,7 +8196,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B281" s="3" t="s">
         <v>491</v>
       </c>
@@ -8211,7 +8223,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E282" s="2" t="s">
         <v>211</v>
       </c>
@@ -8232,7 +8244,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E283" s="2" t="s">
         <v>212</v>
       </c>
@@ -8255,7 +8267,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B284" s="3" t="s">
         <v>461</v>
       </c>
@@ -8278,7 +8290,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C285" s="2" t="s">
         <v>329</v>
       </c>
@@ -8302,7 +8314,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" ht="39" x14ac:dyDescent="0.3">
       <c r="C286" s="5" t="s">
         <v>330</v>
       </c>
@@ -8319,7 +8331,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E287" s="2" t="s">
         <v>259</v>
       </c>
@@ -8339,7 +8351,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B288" s="3" t="s">
         <v>492</v>
       </c>
@@ -8366,7 +8378,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="289" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E289" s="2" t="s">
         <v>211</v>
       </c>
@@ -8387,7 +8399,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="290" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E290" s="2" t="s">
         <v>212</v>
       </c>
@@ -8410,7 +8422,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="291" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B291" s="3" t="s">
         <v>462</v>
       </c>
@@ -8433,7 +8445,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="292" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E292" s="2" t="s">
         <v>214</v>
       </c>
@@ -8451,7 +8463,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="293" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E293" s="2" t="s">
         <v>142</v>
       </c>
@@ -8471,7 +8483,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="294" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E294" s="2" t="s">
         <v>149</v>
       </c>
@@ -8492,7 +8504,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="295" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E295" s="2" t="s">
         <v>150</v>
       </c>
@@ -8515,7 +8527,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="296" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C296" s="2" t="s">
         <v>334</v>
       </c>
@@ -8535,7 +8547,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="297" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E297" s="2" t="s">
         <v>316</v>
       </c>
@@ -8558,7 +8570,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="298" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B298" s="3" t="s">
         <v>463</v>
       </c>
@@ -8581,7 +8593,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="299" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E299" s="2" t="s">
         <v>214</v>
       </c>
@@ -8599,7 +8611,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="300" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E300" s="2" t="s">
         <v>142</v>
       </c>
@@ -8619,7 +8631,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="301" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E301" s="2" t="s">
         <v>149</v>
       </c>
@@ -8640,7 +8652,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="302" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E302" s="2" t="s">
         <v>150</v>
       </c>
@@ -8663,7 +8675,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="303" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C303" s="2" t="s">
         <v>339</v>
       </c>
@@ -8683,7 +8695,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="304" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E304" s="2" t="s">
         <v>316</v>
       </c>
@@ -8706,7 +8718,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="305" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B305" s="3" t="s">
         <v>464</v>
       </c>
@@ -8729,7 +8741,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="306" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E306" s="2" t="s">
         <v>214</v>
       </c>
@@ -8747,7 +8759,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="307" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E307" s="2" t="s">
         <v>142</v>
       </c>
@@ -8767,7 +8779,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="308" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E308" s="2" t="s">
         <v>149</v>
       </c>
@@ -8788,7 +8800,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="309" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E309" s="2" t="s">
         <v>150</v>
       </c>
@@ -8811,7 +8823,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="310" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C310" s="2" t="s">
         <v>339</v>
       </c>
@@ -8831,7 +8843,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="311" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E311" s="2" t="s">
         <v>316</v>
       </c>
@@ -8854,7 +8866,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="312" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B312" s="3" t="s">
         <v>465</v>
       </c>
@@ -8877,7 +8889,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="313" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E313" s="2" t="s">
         <v>173</v>
       </c>
@@ -8900,7 +8912,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="314" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E314" s="2" t="s">
         <v>135</v>
       </c>
@@ -8920,7 +8932,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="315" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E315" s="2" t="s">
         <v>228</v>
       </c>
@@ -8941,7 +8953,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="316" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E316" s="2" t="s">
         <v>229</v>
       </c>
@@ -8964,7 +8976,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="317" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C317" s="2" t="s">
         <v>342</v>
       </c>
@@ -8987,7 +8999,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="318" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C318" s="2" t="s">
         <v>343</v>
       </c>
@@ -9004,7 +9016,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="319" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B319" s="3" t="s">
         <v>466</v>
       </c>
@@ -9027,7 +9039,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="320" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E320" s="2" t="s">
         <v>173</v>
       </c>
@@ -9050,7 +9062,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="321" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E321" s="2" t="s">
         <v>135</v>
       </c>
@@ -9070,7 +9082,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="322" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E322" s="2" t="s">
         <v>228</v>
       </c>
@@ -9091,7 +9103,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="323" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E323" s="2" t="s">
         <v>229</v>
       </c>
@@ -9114,7 +9126,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="324" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C324" s="2" t="s">
         <v>346</v>
       </c>
@@ -9134,7 +9146,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="325" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C325" s="2" t="s">
         <v>347</v>
       </c>
@@ -9151,7 +9163,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="326" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B326" s="3" t="s">
         <v>467</v>
       </c>
@@ -9174,7 +9186,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="327" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E327" s="2" t="s">
         <v>173</v>
       </c>
@@ -9197,7 +9209,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="328" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E328" s="2" t="s">
         <v>135</v>
       </c>
@@ -9217,7 +9229,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="329" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E329" s="2" t="s">
         <v>228</v>
       </c>
@@ -9238,7 +9250,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="330" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E330" s="2" t="s">
         <v>229</v>
       </c>
@@ -9261,7 +9273,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="331" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C331" s="2" t="s">
         <v>350</v>
       </c>
@@ -9281,7 +9293,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="332" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C332" s="2" t="s">
         <v>351</v>
       </c>
@@ -9298,7 +9310,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="333" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B333" s="3" t="s">
         <v>468</v>
       </c>
@@ -9321,7 +9333,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="334" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E334" s="2" t="s">
         <v>173</v>
       </c>
@@ -9344,7 +9356,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="335" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E335" s="2" t="s">
         <v>135</v>
       </c>
@@ -9364,7 +9376,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="336" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E336" s="2" t="s">
         <v>228</v>
       </c>
@@ -9385,7 +9397,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="337" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E337" s="2" t="s">
         <v>229</v>
       </c>
@@ -9408,7 +9420,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="338" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C338" s="2" t="s">
         <v>354</v>
       </c>
@@ -9428,7 +9440,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="339" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C339" s="2" t="s">
         <v>355</v>
       </c>
@@ -9445,7 +9457,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="340" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B340" s="3" t="s">
         <v>472</v>
       </c>
@@ -9468,7 +9480,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="341" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E341" s="2" t="s">
         <v>173</v>
       </c>
@@ -9491,7 +9503,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="342" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E342" s="2" t="s">
         <v>135</v>
       </c>
@@ -9511,7 +9523,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="343" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E343" s="2" t="s">
         <v>228</v>
       </c>
@@ -9532,7 +9544,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="344" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E344" s="2" t="s">
         <v>229</v>
       </c>
@@ -9555,7 +9567,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="345" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C345" s="2" t="s">
         <v>372</v>
       </c>
@@ -9575,7 +9587,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="346" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C346" s="2" t="s">
         <v>373</v>
       </c>
@@ -9592,7 +9604,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="347" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B347" s="3" t="s">
         <v>473</v>
       </c>
@@ -9615,7 +9627,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="348" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E348" s="2" t="s">
         <v>173</v>
       </c>
@@ -9638,7 +9650,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="349" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E349" s="2" t="s">
         <v>135</v>
       </c>
@@ -9658,7 +9670,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="350" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E350" s="2" t="s">
         <v>228</v>
       </c>
@@ -9679,7 +9691,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="351" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E351" s="2" t="s">
         <v>229</v>
       </c>
@@ -9702,7 +9714,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="352" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C352" s="2" t="s">
         <v>376</v>
       </c>
@@ -9722,7 +9734,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="353" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C353" s="2" t="s">
         <v>377</v>
       </c>
@@ -9739,7 +9751,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="354" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B354" s="3" t="s">
         <v>469</v>
       </c>
@@ -9762,7 +9774,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="355" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E355" s="2" t="s">
         <v>173</v>
       </c>
@@ -9785,7 +9797,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="356" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E356" s="2" t="s">
         <v>135</v>
       </c>
@@ -9805,7 +9817,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="357" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E357" s="2" t="s">
         <v>228</v>
       </c>
@@ -9826,7 +9838,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="358" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E358" s="2" t="s">
         <v>229</v>
       </c>
@@ -9849,7 +9861,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="359" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C359" s="2" t="s">
         <v>358</v>
       </c>
@@ -9869,7 +9881,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="360" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C360" s="2" t="s">
         <v>359</v>
       </c>
@@ -9889,7 +9901,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="361" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E361" s="2" t="s">
         <v>275</v>
       </c>
@@ -9912,7 +9924,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="362" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B362" s="3" t="s">
         <v>470</v>
       </c>
@@ -9935,7 +9947,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="363" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E363" s="2" t="s">
         <v>173</v>
       </c>
@@ -9958,7 +9970,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="364" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E364" s="2" t="s">
         <v>135</v>
       </c>
@@ -9978,7 +9990,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="365" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E365" s="2" t="s">
         <v>228</v>
       </c>
@@ -9999,7 +10011,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="366" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E366" s="2" t="s">
         <v>229</v>
       </c>
@@ -10022,7 +10034,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="367" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C367" s="2" t="s">
         <v>362</v>
       </c>
@@ -10042,7 +10054,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="368" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C368" s="2" t="s">
         <v>363</v>
       </c>
@@ -10062,7 +10074,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E369" s="2" t="s">
         <v>275</v>
       </c>
@@ -10085,7 +10097,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B370" s="3" t="s">
         <v>471</v>
       </c>
@@ -10108,7 +10120,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E371" s="2" t="s">
         <v>173</v>
       </c>
@@ -10131,7 +10143,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E372" s="2" t="s">
         <v>135</v>
       </c>
@@ -10151,7 +10163,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E373" s="2" t="s">
         <v>228</v>
       </c>
@@ -10172,7 +10184,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E374" s="2" t="s">
         <v>229</v>
       </c>
@@ -10195,7 +10207,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C375" s="2" t="s">
         <v>366</v>
       </c>
@@ -10215,7 +10227,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C376" s="2" t="s">
         <v>367</v>
       </c>
@@ -10235,7 +10247,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E377" s="2" t="s">
         <v>275</v>
       </c>
@@ -10258,7 +10270,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A378" s="5" t="s">
         <v>540</v>
       </c>
@@ -10284,7 +10296,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="D379" s="2" t="s">
@@ -10303,7 +10315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="E380" s="2" t="s">
@@ -10328,7 +10340,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C381" s="2" t="s">
         <v>379</v>
       </c>
@@ -10348,7 +10360,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C382" s="2" t="s">
         <v>381</v>
       </c>
@@ -10368,7 +10380,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C383" s="2" t="s">
         <v>383</v>
       </c>
@@ -10385,7 +10397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B384" s="3" t="s">
         <v>475</v>
       </c>
@@ -10408,7 +10420,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="385" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E385" s="2" t="s">
         <v>173</v>
       </c>
@@ -10431,7 +10443,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="386" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E386" s="2" t="s">
         <v>135</v>
       </c>
@@ -10448,7 +10460,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="387" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E387" s="2" t="s">
         <v>228</v>
       </c>
@@ -10469,7 +10481,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="388" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E388" s="2" t="s">
         <v>229</v>
       </c>
@@ -10492,7 +10504,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="389" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C389" s="2" t="s">
         <v>387</v>
       </c>
@@ -10515,7 +10527,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="390" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C390" s="2" t="s">
         <v>388</v>
       </c>
@@ -10532,7 +10544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="391" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B391" s="3" t="s">
         <v>476</v>
       </c>
@@ -10555,7 +10567,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="392" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E392" s="2" t="s">
         <v>173</v>
       </c>
@@ -10578,7 +10590,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E393" s="2" t="s">
         <v>135</v>
       </c>
@@ -10595,7 +10607,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="394" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E394" s="2" t="s">
         <v>228</v>
       </c>
@@ -10616,7 +10628,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="395" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E395" s="2" t="s">
         <v>229</v>
       </c>
@@ -10639,7 +10651,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="396" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C396" s="2" t="s">
         <v>392</v>
       </c>
@@ -10659,7 +10671,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="397" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C397" s="2" t="s">
         <v>392</v>
       </c>
@@ -10676,7 +10688,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="398" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C398" s="2" t="s">
         <v>393</v>
       </c>
@@ -10693,7 +10705,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="399" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C399" s="2" t="s">
         <v>393</v>
       </c>
@@ -10710,7 +10722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="400" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B400" s="3" t="s">
         <v>477</v>
       </c>
@@ -10733,7 +10745,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="401" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E401" s="2" t="s">
         <v>173</v>
       </c>
@@ -10756,7 +10768,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="402" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E402" s="2" t="s">
         <v>135</v>
       </c>
@@ -10773,7 +10785,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="403" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E403" s="2" t="s">
         <v>228</v>
       </c>
@@ -10794,7 +10806,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="404" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E404" s="2" t="s">
         <v>229</v>
       </c>
@@ -10817,7 +10829,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="405" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C405" s="2" t="s">
         <v>396</v>
       </c>
@@ -10837,7 +10849,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="406" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C406" s="2" t="s">
         <v>397</v>
       </c>
@@ -10854,7 +10866,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="407" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B407" s="3" t="s">
         <v>496</v>
       </c>
@@ -10877,7 +10889,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="408" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E408" s="2" t="s">
         <v>173</v>
       </c>
@@ -10900,7 +10912,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="409" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E409" s="2" t="s">
         <v>135</v>
       </c>
@@ -10917,7 +10929,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="410" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E410" s="2" t="s">
         <v>228</v>
       </c>
@@ -10938,7 +10950,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="411" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E411" s="2" t="s">
         <v>229</v>
       </c>
@@ -10961,7 +10973,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="412" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C412" s="2" t="s">
         <v>400</v>
       </c>
@@ -10981,7 +10993,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="413" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C413" s="2" t="s">
         <v>400</v>
       </c>
@@ -10998,7 +11010,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="414" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B414" s="3" t="s">
         <v>495</v>
       </c>
@@ -11021,7 +11033,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="415" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E415" s="2" t="s">
         <v>173</v>
       </c>
@@ -11044,7 +11056,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="416" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E416" s="2" t="s">
         <v>135</v>
       </c>
@@ -11061,7 +11073,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E417" s="2" t="s">
         <v>228</v>
       </c>
@@ -11082,7 +11094,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E418" s="2" t="s">
         <v>229</v>
       </c>
@@ -11105,7 +11117,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C419" s="2" t="s">
         <v>403</v>
       </c>
@@ -11125,7 +11137,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C420" s="2" t="s">
         <v>403</v>
       </c>
@@ -11142,7 +11154,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B421" s="3" t="s">
         <v>493</v>
       </c>
@@ -11169,7 +11181,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E422" s="2" t="s">
         <v>211</v>
       </c>
@@ -11190,7 +11202,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E423" s="2" t="s">
         <v>212</v>
       </c>
@@ -11213,7 +11225,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B424" s="3" t="s">
         <v>494</v>
       </c>
@@ -11240,7 +11252,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E425" s="2" t="s">
         <v>211</v>
       </c>
@@ -11261,7 +11273,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E426" s="2" t="s">
         <v>212</v>
       </c>
@@ -11284,7 +11296,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B427" s="3" t="s">
         <v>479</v>
       </c>
@@ -11295,7 +11307,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="G428" s="2" t="s">
         <v>19</v>
       </c>
@@ -11303,7 +11315,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G429" s="2" t="s">
         <v>19</v>
       </c>
@@ -11311,7 +11323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="G430" s="2" t="s">
         <v>19</v>
       </c>
@@ -11319,9 +11331,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A431" s="5" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>567</v>
@@ -11342,7 +11354,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="D432" s="2" t="s">
@@ -11364,7 +11376,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="433" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E433" s="2" t="s">
         <v>568</v>
       </c>
@@ -11387,7 +11399,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="434" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E434" s="2" t="s">
         <v>572</v>
       </c>
@@ -11404,7 +11416,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="435" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E435" s="2" t="s">
         <v>573</v>
       </c>
@@ -11422,7 +11434,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="436" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B436" s="3" t="s">
         <v>565</v>
       </c>
@@ -11445,7 +11457,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="437" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E437" s="2" t="s">
         <v>173</v>
       </c>
@@ -11468,7 +11480,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="438" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E438" s="2" t="s">
         <v>135</v>
       </c>
@@ -11485,7 +11497,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="439" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E439" s="2" t="s">
         <v>228</v>
       </c>
@@ -11503,7 +11515,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="440" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E440" s="2" t="s">
         <v>229</v>
       </c>
@@ -11526,7 +11538,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="441" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E441" s="2" t="s">
         <v>176</v>
       </c>
@@ -11543,7 +11555,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="442" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E442" s="2" t="s">
         <v>178</v>
       </c>
@@ -11557,7 +11569,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="443" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B443" s="3" t="s">
         <v>582</v>
       </c>
@@ -11580,7 +11592,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="444" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E444" s="2" t="s">
         <v>173</v>
       </c>
@@ -11603,7 +11615,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="445" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E445" s="2" t="s">
         <v>135</v>
       </c>
@@ -11620,7 +11632,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="446" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E446" s="2" t="s">
         <v>228</v>
       </c>
@@ -11641,7 +11653,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="447" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E447" s="2" t="s">
         <v>229</v>
       </c>
@@ -11664,7 +11676,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="448" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E448" s="2" t="s">
         <v>176</v>
       </c>
@@ -11681,7 +11693,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E449" s="2" t="s">
         <v>178</v>
       </c>
@@ -11695,7 +11707,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B450" s="3" t="s">
         <v>478</v>
       </c>
@@ -11718,7 +11730,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E451" s="2" t="s">
         <v>173</v>
       </c>
@@ -11741,7 +11753,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E452" s="2" t="s">
         <v>135</v>
       </c>
@@ -11758,7 +11770,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E453" s="2" t="s">
         <v>228</v>
       </c>
@@ -11779,7 +11791,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E454" s="2" t="s">
         <v>229</v>
       </c>
@@ -11802,7 +11814,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E455" s="2" t="s">
         <v>176</v>
       </c>
@@ -11822,7 +11834,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E456" s="2" t="s">
         <v>178</v>
       </c>
@@ -11836,7 +11848,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B457" s="3" t="s">
         <v>480</v>
       </c>
@@ -11847,138 +11859,135 @@
         <v>96</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A458" s="5" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>497</v>
+        <v>567</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>140</v>
+        <v>543</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>213</v>
+        <v>133</v>
       </c>
       <c r="F458" s="2" t="s">
-        <v>590</v>
+        <v>555</v>
       </c>
       <c r="G458" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H458" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K458" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H458" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A459" s="2"/>
+      <c r="B459" s="2"/>
+      <c r="D459" s="2" t="s">
+        <v>574</v>
+      </c>
       <c r="E459" s="2" t="s">
-        <v>214</v>
+        <v>566</v>
       </c>
       <c r="F459" s="2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="G459" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H459" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I459" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J459" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L459" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H459" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K459" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E460" s="2" t="s">
-        <v>142</v>
+        <v>568</v>
       </c>
       <c r="F460" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G460" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H460" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I460" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="J460" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L460" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E461" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F461" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G460" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H460" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K460" s="2" t="s">
+      <c r="G461" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H461" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K461" s="2" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E461" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F461" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G461" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H461" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="K461" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E462" s="2" t="s">
-        <v>316</v>
+        <v>573</v>
       </c>
       <c r="F462" s="2" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="G462" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H462" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I462" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="J462" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L462" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="463" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H462" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I462" s="8"/>
+      <c r="K462" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="463" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B463" s="3" t="s">
-        <v>498</v>
+        <v>565</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="F463" s="2" t="s">
-        <v>590</v>
+        <v>153</v>
       </c>
       <c r="G463" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H463" s="5" t="s">
-        <v>2</v>
+        <v>90</v>
+      </c>
+      <c r="H463" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K463" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E464" s="2" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>132</v>
@@ -11990,272 +11999,268 @@
         <v>133</v>
       </c>
       <c r="I464" s="3" t="s">
-        <v>410</v>
+        <v>576</v>
       </c>
       <c r="J464" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L464" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="465" spans="2:12" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="465" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E465" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F465" s="2" t="s">
         <v>183</v>
       </c>
       <c r="G465" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H465" s="11" t="s">
-        <v>99</v>
+        <v>90</v>
+      </c>
+      <c r="H465" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="K465" s="2" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="466" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E466" s="2" t="s">
-        <v>314</v>
+        <v>228</v>
       </c>
       <c r="F466" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G466" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H466" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I466" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+    </row>
+    <row r="467" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E467" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F467" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G467" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H467" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I467" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J467" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L467" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="468" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E468" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F468" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G468" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H468" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K468" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="469" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E469" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F469" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G466" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H466" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K466" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="467" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E467" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F467" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G467" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H467" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I467" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="J467" s="2" t="s">
+      <c r="G469" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H469" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="470" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B470" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D470" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E470" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F470" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G470" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H470" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K470" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="471" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E471" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F471" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G471" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H471" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I471" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="J471" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L467" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="468" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B468" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E468" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F468" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G468" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H468" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K468" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="469" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E469" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F469" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G469" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H469" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I469" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="J469" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L469" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="470" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E470" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F470" s="2" t="s">
+      <c r="L471" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="472" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E472" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F472" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G470" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H470" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K470" s="2" t="s">
+      <c r="G472" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H472" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K472" s="2" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="471" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E471" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F471" s="2" t="s">
+    <row r="473" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E473" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F473" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G473" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H473" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I473" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K473" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="474" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E474" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F474" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G474" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H474" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I474" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J474" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L474" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="475" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E475" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F475" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G475" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H475" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K475" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="476" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E476" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F476" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G471" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H471" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K471" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="472" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E472" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F472" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G472" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H472" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I472" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="J472" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L472" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="473" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B473" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="D473" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E473" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F473" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G473" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H473" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K473" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="474" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E474" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F474" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G474" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H474" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I474" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="J474" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L474" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="475" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E475" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F475" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G475" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H475" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K475" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="476" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E476" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F476" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="G476" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H476" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K476" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="477" spans="2:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H476" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="477" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B477" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D477" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="E477" s="2" t="s">
-        <v>314</v>
+        <v>172</v>
       </c>
       <c r="F477" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G477" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H477" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="478" spans="2:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H477" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K477" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="478" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E478" s="2" t="s">
-        <v>316</v>
+        <v>173</v>
       </c>
       <c r="F478" s="2" t="s">
         <v>132</v>
@@ -12267,392 +12272,422 @@
         <v>133</v>
       </c>
       <c r="I478" s="3" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="J478" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L478" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="479" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B479" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="D479" s="2" t="s">
-        <v>140</v>
-      </c>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="479" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E479" s="2" t="s">
-        <v>213</v>
+        <v>135</v>
       </c>
       <c r="F479" s="2" t="s">
-        <v>590</v>
+        <v>183</v>
       </c>
       <c r="G479" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H479" s="5" t="s">
-        <v>2</v>
+        <v>90</v>
+      </c>
+      <c r="H479" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="K479" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="480" spans="2:12" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="480" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E480" s="2" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="F480" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G480" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H480" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I480" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="J480" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L480" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H480" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I480" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K480" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E481" s="2" t="s">
-        <v>142</v>
+        <v>229</v>
       </c>
       <c r="F481" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G481" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H481" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K481" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="H481" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I481" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J481" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L481" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E482" s="2" t="s">
         <v>176</v>
       </c>
       <c r="F482" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G482" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H482" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J482" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K482" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E483" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F483" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G483" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H483" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="484" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B484" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D484" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E484" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F484" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G484" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H484" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I484" s="5" t="str">
+        <f>$B$65</f>
+        <v>OMOP Primary Dx Episode</v>
+      </c>
+      <c r="K484" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E485" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F485" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G485" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H485" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I485" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K485" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E486" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F486" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G486" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H486" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I486" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J486" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L486" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="487" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="A487" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D487" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E487" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F487" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="G487" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H487" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A488" s="2"/>
+      <c r="B488" s="2"/>
+      <c r="D488" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E488" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F488" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G488" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H488" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K488" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E489" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F489" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G489" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H489" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I489" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="J489" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L489" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E490" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F490" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G490" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H490" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K490" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E491" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F491" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G491" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H491" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I491" s="8"/>
+      <c r="K491" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="492" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B492" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D492" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E492" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F492" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G492" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H492" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K492" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E493" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F493" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G493" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H493" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I493" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="J493" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L493" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E494" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F494" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G494" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H494" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K494" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E495" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F495" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G495" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H495" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I495" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+    </row>
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E496" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F496" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G496" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H496" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I496" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J496" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L496" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="497" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E497" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F497" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G482" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H482" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="K482" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="483" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B483" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="D483" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E483" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F483" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G483" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H483" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K483" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E484" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F484" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G484" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H484" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I484" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="J484" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L484" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E485" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F485" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G485" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H485" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K485" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E486" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F486" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G486" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H486" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="K486" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="487" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B487" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="G487" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H487" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G488" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H488" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G489" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H489" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="490" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="A490" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="B490" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D490" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E490" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F490" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G490" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H490" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K490" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E491" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F491" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G491" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H491" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I491" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="J491" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="L491" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E492" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F492" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G492" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H492" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="K492" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E493" s="2" t="s">
+      <c r="G497" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H497" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K497" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="498" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E498" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="F493" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G493" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H493" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="494" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B494" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D494" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E494" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F494" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G494" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H494" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K494" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E495" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F495" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G495" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H495" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I495" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="J495" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L495" s="2" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E496" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F496" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="G496" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H496" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I496" s="3" t="str">
-        <f>$B$490</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
-      <c r="K496" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E497" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F497" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G497" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H497" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I497" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="J497" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L497" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E498" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="F498" s="2" t="s">
         <v>154</v>
       </c>
       <c r="G498" s="2" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="H498" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="K498" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="499" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="499" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B499" s="3" t="s">
-        <v>504</v>
+        <v>582</v>
       </c>
       <c r="D499" s="2" t="s">
         <v>130</v>
@@ -12661,19 +12696,19 @@
         <v>172</v>
       </c>
       <c r="F499" s="2" t="s">
-        <v>590</v>
+        <v>153</v>
       </c>
       <c r="G499" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H499" s="5" t="s">
-        <v>2</v>
+        <v>90</v>
+      </c>
+      <c r="H499" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K499" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E500" s="2" t="s">
         <v>173</v>
       </c>
@@ -12687,377 +12722,1530 @@
         <v>133</v>
       </c>
       <c r="I500" s="3" t="s">
-        <v>426</v>
+        <v>580</v>
       </c>
       <c r="J500" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L500" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="501" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E501" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F501" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G501" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H501" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K501" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="502" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E502" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F501" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="G501" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H501" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I501" s="3" t="str">
-        <f>$B$490</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
-      <c r="K501" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E502" s="2" t="s">
+      <c r="F502" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G502" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H502" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I502" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K502" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="503" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E503" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F502" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G502" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H502" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I502" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="J502" s="2" t="s">
+      <c r="F503" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G503" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H503" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I503" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J503" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L502" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E503" s="2" t="s">
+      <c r="L503" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="504" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E504" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F503" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G503" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H503" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I503" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E504" s="2" t="s">
+      <c r="F504" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G504" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H504" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K504" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="505" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E505" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F504" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="G504" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H504" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="K504" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A505" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="B505" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D505" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E505" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="F505" s="2" t="s">
-        <v>590</v>
+        <v>154</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H505" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H505" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="506" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B506" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D506" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="E506" s="2" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="F506" s="2" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H506" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J506" s="2" t="s">
-        <v>193</v>
+        <v>90</v>
+      </c>
+      <c r="H506" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K506" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="507" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E507" s="2" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H507" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="H507" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I507" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J507" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L507" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="508" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E508" s="2" t="s">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="F508" s="2" t="s">
-        <v>613</v>
+        <v>183</v>
       </c>
       <c r="G508" s="2" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H508" s="6" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="K508" s="2" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E509" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="F509" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G509" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H509" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H509" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I509" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K509" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="510" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E510" s="2" t="s">
-        <v>430</v>
+        <v>229</v>
       </c>
       <c r="F510" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G510" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H510" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I510" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J510" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L510" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="511" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E511" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F511" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G511" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H511" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J511" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K511" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="512" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E512" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F512" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G510" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H510" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="511" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B511" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D511" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E511" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F511" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G511" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H511" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E512" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F512" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="G512" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H512" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I512" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J512" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="513" spans="2:10" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H512" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="513" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B513" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D513" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="E513" s="2" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="F513" s="2" t="s">
         <v>148</v>
       </c>
       <c r="G513" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H513" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I513" s="3" t="str">
+        <f>$B$154</f>
+        <v>OMOP Treatment Episode</v>
+      </c>
+      <c r="K513" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E514" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F514" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G514" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H514" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I514" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K514" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E515" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F515" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G515" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H515" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I515" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J515" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L515" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="516" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="A516" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="B516" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E516" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F516" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G516" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H516" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K516" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E517" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F517" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G517" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H517" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I517" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="J517" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L517" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E518" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F518" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G518" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H518" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K518" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E519" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F519" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G519" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H519" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K519" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E520" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F520" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G520" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H520" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I520" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="J520" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L520" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="521" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B521" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D521" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E521" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F521" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G521" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H521" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K521" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E522" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F522" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G522" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H522" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I522" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="J522" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L522" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E523" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F523" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G523" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H523" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K523" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E524" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G524" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H524" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K524" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E525" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F525" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G525" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H525" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I525" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="J525" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L525" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="526" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B526" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D526" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E526" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F526" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G526" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H526" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K526" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E527" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F527" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G527" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H527" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I527" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J527" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L527" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E528" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F528" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G528" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H528" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K528" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="529" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E529" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F529" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G529" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H529" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K529" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="530" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E530" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F530" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G530" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H530" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I530" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="J530" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L530" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="531" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B531" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D531" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E531" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F531" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G531" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H531" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K531" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="532" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E532" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F532" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G532" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H532" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I532" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J532" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L532" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="533" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E533" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F533" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G533" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H533" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K533" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="534" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E534" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F534" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G534" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H534" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K534" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="535" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E535" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F535" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G535" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H535" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="536" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E536" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F536" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G536" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H536" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I536" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="J536" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L536" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="537" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B537" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D537" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E537" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F537" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G537" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H537" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K537" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="538" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E538" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F538" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G538" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H538" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I538" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="J538" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L538" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="539" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E539" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F539" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G539" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H539" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K539" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="540" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E540" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F540" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G540" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H540" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K540" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="541" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B541" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D541" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E541" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F541" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G541" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H541" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K541" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="542" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E542" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F542" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G542" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H542" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I542" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="J542" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L542" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="543" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E543" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F543" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G543" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H543" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K543" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="544" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E544" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F544" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G544" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H544" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K544" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="545" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B545" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="G545" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H545" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G546" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H546" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G547" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H547" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="548" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="A548" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="B548" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D548" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E548" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F548" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G548" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H548" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K548" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E549" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F549" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G549" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H549" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I549" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J549" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="L549" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E550" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F550" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G550" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H550" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K550" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E551" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F551" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G551" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H551" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="552" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B552" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D552" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E552" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F552" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G552" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H552" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K552" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E553" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F553" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G553" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H553" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I553" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="J553" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L553" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E554" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F554" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="G554" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H554" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I554" s="3" t="str">
+        <f>$B$548</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
+      <c r="K554" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E555" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F555" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G555" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H555" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I555" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J555" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L555" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E556" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F556" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G556" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H556" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K556" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="557" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+      <c r="B557" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D557" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E557" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F557" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G557" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H557" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K557" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E558" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F558" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G558" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H558" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I558" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J558" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L558" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E559" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F559" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="G559" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H559" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I559" s="3" t="str">
+        <f>$B$548</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
+      <c r="K559" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E560" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F560" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G560" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H560" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I560" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J560" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L560" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E561" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F561" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G561" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H561" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I561" s="3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E562" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F562" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G562" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H562" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K562" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A563" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D563" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E563" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F563" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G563" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H563" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E564" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F564" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G564" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H513" s="5" t="s">
+      <c r="H564" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J564" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K564" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E565" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F565" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G565" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H565" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E566" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F566" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="G566" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H566" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K566" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E567" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F567" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G567" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H567" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E568" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F568" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G568" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H568" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="569" spans="1:11" ht="26" x14ac:dyDescent="0.3">
+      <c r="B569" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D569" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E569" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F569" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G569" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H569" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E570" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F570" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G570" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H570" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I570" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J570" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E571" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F571" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G571" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H571" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="I513" s="3" t="str">
-        <f>$B$505</f>
+      <c r="I571" s="3" t="str">
+        <f>$B$563</f>
         <v>OMOP Comorbidity Condition</v>
       </c>
     </row>
-    <row r="514" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E514" s="2" t="s">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E572" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F514" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G514" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H514" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I514" s="3">
+      <c r="F572" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G572" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H572" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I572" s="3">
         <v>1147127</v>
       </c>
-      <c r="J514" s="2" t="s">
+      <c r="J572" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="515" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E515" s="2" t="s">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E573" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F515" s="2" t="s">
+      <c r="F573" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G515" s="2" t="s">
+      <c r="G573" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H515" s="6" t="s">
+      <c r="H573" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="516" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E516" s="2" t="s">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E574" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F516" s="2" t="s">
+      <c r="F574" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G516" s="2" t="s">
+      <c r="G574" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H516" s="6" t="s">
+      <c r="H574" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="517" spans="2:10" ht="27" x14ac:dyDescent="0.25">
-      <c r="B517" s="3" t="s">
+    <row r="575" spans="1:11" ht="26" x14ac:dyDescent="0.3">
+      <c r="B575" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="C517" s="2" t="s">
+      <c r="C575" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="G517" s="12" t="s">
+      <c r="G575" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H517" s="9" t="s">
+      <c r="H575" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="518" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G518" s="12" t="s">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G576" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H518" s="7" t="s">
+      <c r="H576" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="519" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H519" s="6"/>
-    </row>
-    <row r="520" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H520" s="6"/>
-    </row>
-    <row r="523" spans="2:10" ht="27" x14ac:dyDescent="0.25">
-      <c r="B523" s="3" t="s">
+    <row r="577" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H577" s="6"/>
+    </row>
+    <row r="578" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H578" s="6"/>
+    </row>
+    <row r="581" spans="2:8" ht="26" x14ac:dyDescent="0.3">
+      <c r="B581" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="G523" s="12" t="s">
+      <c r="G581" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H523" s="7" t="s">
+      <c r="H581" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="524" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G524" s="12" t="s">
+    <row r="582" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G582" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H524" s="7" t="s">
+      <c r="H582" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="525" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G525" s="12" t="s">
+    <row r="583" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G583" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H525" s="7" t="s">
+      <c r="H583" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="526" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G526" s="12" t="s">
+    <row r="584" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G584" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H526" s="7" t="s">
+      <c r="H584" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="527" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G527" s="12" t="s">
+    <row r="585" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G585" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H527" s="7" t="s">
+      <c r="H585" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="528" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G528" s="12" t="s">
+    <row r="586" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G586" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H528" s="7" t="s">
+      <c r="H586" s="7" t="s">
         <v>8</v>
       </c>
     </row>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\python\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E356004-6E7F-4FDE-B5CC-B7CD68E49688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B160ED-C3BD-4DB2-9746-438DD84A4F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformation Model" sheetId="2" r:id="rId1"/>
@@ -2328,24 +2328,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9C41B9-3FB6-4282-940B-7420BB7A8AED}">
   <dimension ref="A1:L586"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="47.453125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.81640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.54296875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="43.81640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.81640625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="25.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="47.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="43.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.85546875" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>121</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D3" s="2" t="s">
         <v>130</v>
       </c>
@@ -2437,7 +2437,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D4" s="2" t="s">
         <v>136</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>138</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
         <v>574</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D7" s="2" t="s">
         <v>140</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
         <v>140</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D9" s="2" t="s">
         <v>143</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D10" s="2" t="s">
         <v>145</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D11" s="2" t="s">
         <v>179</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D12" s="2" t="s">
         <v>130</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
         <v>145</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D14" s="2" t="s">
         <v>284</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D15" s="2" t="s">
         <v>143</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
         <v>140</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D17" s="2" t="s">
         <v>574</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D18" s="2" t="s">
         <v>138</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
         <v>136</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D20" s="2" t="s">
         <v>140</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>OMOP Specimen</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
         <v>140</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>OMOP Primary Dx Episode</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
         <v>140</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
         <v>140</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
         <v>140</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
         <v>140</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
         <v>140</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
         <v>140</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>534</v>
       </c>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
         <v>543</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
         <v>543</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D31" s="2" t="s">
         <v>543</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D32" s="2" t="s">
         <v>543</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>4255047</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
         <v>543</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3" t="s">
         <v>605</v>
@@ -3163,7 +3163,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D35" s="2" t="s">
         <v>543</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D36" s="2" t="s">
         <v>543</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D37" s="2" t="s">
         <v>543</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="D38" s="2" t="s">
         <v>594</v>
@@ -3238,7 +3238,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3" t="s">
         <v>433</v>
@@ -3262,7 +3262,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2" t="s">
         <v>156</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C41" s="2" t="s">
         <v>157</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C42" s="2" t="s">
         <v>161</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C43" s="2" t="s">
         <v>163</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C44" s="2" t="s">
         <v>166</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C45" s="2" t="s">
         <v>169</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E46" s="2" t="s">
         <v>592</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E47" s="2" t="s">
         <v>593</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>434</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E49" s="2" t="s">
         <v>173</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C50" s="2" t="s">
         <v>175</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C51" s="2" t="s">
         <v>177</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
         <v>435</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C53" s="2" t="s">
         <v>181</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C54" s="2" t="s">
         <v>184</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C55" s="2" t="s">
         <v>186</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
         <v>481</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E57" s="2" t="s">
         <v>188</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E58" s="2" t="s">
         <v>188</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>535</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="D60" s="2" t="s">
         <v>145</v>
@@ -3669,7 +3669,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="s">
         <v>190</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C62" s="2" t="s">
         <v>194</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C63" s="2" t="s">
         <v>196</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E64" s="2" t="s">
         <v>198</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
         <v>437</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E66" s="2" t="s">
         <v>201</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E67" s="2" t="s">
         <v>205</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E68" s="2" t="s">
         <v>206</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E69" s="2" t="s">
         <v>207</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E70" s="2" t="s">
         <v>208</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E71" s="2" t="s">
         <v>209</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="72" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
         <v>485</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E73" s="2" t="s">
         <v>211</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E74" s="2" t="s">
         <v>212</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="75" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
         <v>439</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E76" s="2" t="s">
         <v>214</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E77" s="2" t="s">
         <v>142</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E78" s="2" t="s">
         <v>149</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E79" s="2" t="s">
         <v>150</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C80" s="2" t="s">
         <v>217</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C81" s="2" t="s">
         <v>218</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
         <v>440</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E83" s="2" t="s">
         <v>214</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E84" s="2" t="s">
         <v>142</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E85" s="2" t="s">
         <v>149</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E86" s="2" t="s">
         <v>150</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C87" s="2" t="s">
         <v>221</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C88" s="2" t="s">
         <v>222</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B89" s="3" t="s">
         <v>441</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E90" s="2" t="s">
         <v>173</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E91" s="2" t="s">
         <v>135</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C92" s="2" t="s">
         <v>226</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C93" s="2" t="s">
         <v>227</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E94" s="2" t="s">
         <v>228</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E95" s="2" t="s">
         <v>229</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="96" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
         <v>431</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E97" s="2" t="s">
         <v>214</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E98" s="2" t="s">
         <v>142</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E99" s="2" t="s">
         <v>149</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E100" s="2" t="s">
         <v>150</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C101" s="2" t="s">
         <v>233</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C102" s="2" t="s">
         <v>234</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="103" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B103" s="3" t="s">
         <v>432</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E104" s="2" t="s">
         <v>214</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E105" s="2" t="s">
         <v>142</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E106" s="2" t="s">
         <v>149</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E107" s="2" t="s">
         <v>150</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C108" s="2" t="s">
         <v>235</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C109" s="2" t="s">
         <v>236</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B110" s="3" t="s">
         <v>438</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E111" s="2" t="s">
         <v>214</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E112" s="2" t="s">
         <v>142</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E113" s="2" t="s">
         <v>149</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E114" s="2" t="s">
         <v>150</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C115" s="2" t="s">
         <v>237</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C116" s="2" t="s">
         <v>238</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="117" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B117" s="3" t="s">
         <v>442</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C118" s="2" t="s">
         <v>230</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C119" s="2" t="s">
         <v>231</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E120" s="2" t="s">
         <v>142</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E121" s="2" t="s">
         <v>149</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E122" s="2" t="s">
         <v>150</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C123" s="2" t="s">
         <v>239</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C124" s="2" t="s">
         <v>240</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="125" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B125" s="3" t="s">
         <v>443</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E126" s="2" t="s">
         <v>214</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E127" s="2" t="s">
         <v>142</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E128" s="2" t="s">
         <v>149</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E129" s="2" t="s">
         <v>150</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C130" s="2" t="s">
         <v>243</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C131" s="2" t="s">
         <v>244</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B132" s="3" t="s">
         <v>444</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E133" s="2" t="s">
         <v>214</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E134" s="2" t="s">
         <v>142</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E135" s="2" t="s">
         <v>149</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E136" s="2" t="s">
         <v>150</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C137" s="2" t="s">
         <v>245</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C138" s="2" t="s">
         <v>246</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="139" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B139" s="3" t="s">
         <v>445</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E140" s="2" t="s">
         <v>214</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E141" s="2" t="s">
         <v>142</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E142" s="2" t="s">
         <v>149</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E143" s="2" t="s">
         <v>150</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C144" s="2" t="s">
         <v>247</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C145" s="2" t="s">
         <v>248</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B146" s="3" t="s">
         <v>446</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C147" s="2" t="s">
         <v>241</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C148" s="2" t="s">
         <v>242</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E149" s="2" t="s">
         <v>142</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E150" s="2" t="s">
         <v>149</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E151" s="2" t="s">
         <v>150</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C152" s="2" t="s">
         <v>249</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C153" s="2" t="s">
         <v>509</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>536</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D155" s="2" t="s">
         <v>543</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D156" s="2" t="s">
         <v>543</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="D157" s="2" t="s">
@@ -5645,7 +5645,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E158" s="2" t="s">
         <v>201</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E159" s="2" t="s">
         <v>205</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E160" s="2" t="s">
         <v>206</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C161" s="2" t="s">
         <v>252</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C162" s="2" t="s">
         <v>253</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C163" s="2" t="s">
         <v>254</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="164" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B164" s="3" t="s">
         <v>448</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E165" s="2" t="s">
         <v>173</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E166" s="2" t="s">
         <v>135</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E167" s="2" t="s">
         <v>228</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E168" s="2" t="s">
         <v>229</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C169" s="2" t="s">
         <v>266</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C170" s="2" t="s">
         <v>267</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="171" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B171" s="3" t="s">
         <v>449</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E172" s="2" t="s">
         <v>173</v>
       </c>
@@ -5946,7 +5946,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C173" s="2" t="s">
         <v>272</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C174" s="2" t="s">
         <v>273</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E175" s="2" t="s">
         <v>135</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E176" s="2" t="s">
         <v>228</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E177" s="2" t="s">
         <v>229</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C178" s="2" t="s">
         <v>274</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C179" s="2" t="s">
         <v>276</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
         <v>608</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E181" s="2" t="s">
         <v>256</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C182" s="2" t="s">
         <v>257</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E183" s="2" t="s">
         <v>259</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C184" s="2" t="s">
         <v>260</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C185" s="2" t="s">
         <v>262</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B186" s="3" t="s">
         <v>610</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E187" s="2" t="s">
         <v>211</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E188" s="2" t="s">
         <v>212</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
         <v>537</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E190" s="2" t="s">
         <v>201</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E191" s="2" t="s">
         <v>205</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E192" s="2" t="s">
         <v>206</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E193" s="2" t="s">
         <v>208</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E194" s="2" t="s">
         <v>209</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="195" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B195" s="3" t="s">
         <v>486</v>
       </c>
@@ -6412,7 +6412,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="196" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E196" s="2" t="s">
         <v>211</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="197" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E197" s="2" t="s">
         <v>212</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B198" s="3" t="s">
         <v>451</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C199" s="2" t="s">
         <v>280</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C200" s="2" t="s">
         <v>281</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="201" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E201" s="2" t="s">
         <v>259</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="202" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C202" s="2" t="s">
         <v>282</v>
       </c>
@@ -6551,7 +6551,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B203" s="3" t="s">
         <v>484</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="204" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E204" s="2" t="s">
         <v>211</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="205" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E205" s="2" t="s">
         <v>212</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B206" s="3" t="s">
         <v>452</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="207" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B207" s="2"/>
       <c r="D207" s="2" t="s">
         <v>284</v>
@@ -6667,7 +6667,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="208" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E208" s="2" t="s">
         <v>286</v>
       </c>
@@ -6690,7 +6690,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E209" s="2" t="s">
         <v>289</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="C210" s="5" t="s">
         <v>291</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="211" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C211" s="2" t="s">
         <v>293</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="212" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C212" s="2" t="s">
         <v>295</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C213" s="2" t="s">
         <v>297</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C214" s="2" t="s">
         <v>299</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B215" s="3" t="s">
         <v>483</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E216" s="2" t="s">
         <v>211</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E217" s="2" t="s">
         <v>212</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B218" s="3" t="s">
         <v>453</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E219" s="2" t="s">
         <v>286</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E220" s="2" t="s">
         <v>289</v>
       </c>
@@ -6938,7 +6938,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="C221" s="5" t="s">
         <v>291</v>
       </c>
@@ -6955,7 +6955,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C222" s="2" t="s">
         <v>293</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C223" s="2" t="s">
         <v>295</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C224" s="2" t="s">
         <v>297</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C225" s="2" t="s">
         <v>304</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B226" s="3" t="s">
         <v>487</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E227" s="2" t="s">
         <v>211</v>
       </c>
@@ -7077,7 +7077,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E228" s="2" t="s">
         <v>212</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B229" s="3" t="s">
         <v>482</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
         <v>538</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E231" s="2" t="s">
         <v>201</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E232" s="2" t="s">
         <v>205</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E233" s="2" t="s">
         <v>206</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E234" s="2" t="s">
         <v>208</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B235" s="3" t="s">
         <v>488</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E236" s="2" t="s">
         <v>211</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E237" s="2" t="s">
         <v>212</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B238" s="3" t="s">
         <v>455</v>
       </c>
@@ -7309,7 +7309,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C239" s="2" t="s">
         <v>307</v>
       </c>
@@ -7329,7 +7329,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C240" s="2" t="s">
         <v>308</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="241" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E241" s="2" t="s">
         <v>259</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="242" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C242" s="2" t="s">
         <v>309</v>
       </c>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I242" s="10"/>
     </row>
-    <row r="243" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C243" s="2" t="s">
         <v>310</v>
       </c>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="I243" s="10"/>
     </row>
-    <row r="244" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B244" s="3" t="s">
         <v>489</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="245" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E245" s="2" t="s">
         <v>211</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="246" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E246" s="2" t="s">
         <v>212</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="247" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B247" s="3" t="s">
         <v>456</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="248" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E248" s="2" t="s">
         <v>214</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="249" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E249" s="2" t="s">
         <v>142</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="250" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E250" s="2" t="s">
         <v>149</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="251" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E251" s="2" t="s">
         <v>150</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="252" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C252" s="2" t="s">
         <v>313</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="253" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C253" s="2" t="s">
         <v>315</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="254" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B254" s="3" t="s">
         <v>457</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="255" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E255" s="2" t="s">
         <v>214</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="256" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E256" s="2" t="s">
         <v>142</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="257" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E257" s="2" t="s">
         <v>149</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="258" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E258" s="2" t="s">
         <v>150</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="259" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C259" s="2" t="s">
         <v>313</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="260" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B260" s="3" t="s">
         <v>458</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="261" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E261" s="2" t="s">
         <v>173</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="262" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E262" s="2" t="s">
         <v>135</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="263" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E263" s="2" t="s">
         <v>228</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="264" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E264" s="2" t="s">
         <v>229</v>
       </c>
@@ -7867,7 +7867,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="265" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C265" s="2" t="s">
         <v>323</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="266" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C266" s="2" t="s">
         <v>324</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="267" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B267" s="3" t="s">
         <v>459</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="268" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E268" s="2" t="s">
         <v>256</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="269" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E269" s="2" t="s">
         <v>259</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="270" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E270" s="2" t="s">
         <v>261</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="271" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E271" s="2" t="s">
         <v>263</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="272" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B272" s="3" t="s">
         <v>490</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E273" s="2" t="s">
         <v>211</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E274" s="2" t="s">
         <v>212</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
         <v>539</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D276" s="2" t="s">
         <v>136</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E277" s="2" t="s">
         <v>201</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E278" s="2" t="s">
         <v>205</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E279" s="2" t="s">
         <v>206</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E280" s="2" t="s">
         <v>208</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B281" s="3" t="s">
         <v>491</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E282" s="2" t="s">
         <v>211</v>
       </c>
@@ -8244,7 +8244,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E283" s="2" t="s">
         <v>212</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B284" s="3" t="s">
         <v>461</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C285" s="2" t="s">
         <v>329</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="C286" s="5" t="s">
         <v>330</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E287" s="2" t="s">
         <v>259</v>
       </c>
@@ -8351,7 +8351,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B288" s="3" t="s">
         <v>492</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="289" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E289" s="2" t="s">
         <v>211</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="290" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E290" s="2" t="s">
         <v>212</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="291" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B291" s="3" t="s">
         <v>462</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="292" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E292" s="2" t="s">
         <v>214</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="293" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E293" s="2" t="s">
         <v>142</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="294" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E294" s="2" t="s">
         <v>149</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="295" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E295" s="2" t="s">
         <v>150</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="296" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C296" s="2" t="s">
         <v>334</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="297" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E297" s="2" t="s">
         <v>316</v>
       </c>
@@ -8570,7 +8570,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="298" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B298" s="3" t="s">
         <v>463</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="299" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E299" s="2" t="s">
         <v>214</v>
       </c>
@@ -8611,7 +8611,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="300" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E300" s="2" t="s">
         <v>142</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="301" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E301" s="2" t="s">
         <v>149</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="302" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E302" s="2" t="s">
         <v>150</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="303" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C303" s="2" t="s">
         <v>339</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="304" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E304" s="2" t="s">
         <v>316</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="305" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B305" s="3" t="s">
         <v>464</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="306" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E306" s="2" t="s">
         <v>214</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="307" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E307" s="2" t="s">
         <v>142</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="308" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E308" s="2" t="s">
         <v>149</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="309" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E309" s="2" t="s">
         <v>150</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="310" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C310" s="2" t="s">
         <v>339</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="311" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E311" s="2" t="s">
         <v>316</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="312" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B312" s="3" t="s">
         <v>465</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="313" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E313" s="2" t="s">
         <v>173</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="314" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E314" s="2" t="s">
         <v>135</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="315" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E315" s="2" t="s">
         <v>228</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="316" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E316" s="2" t="s">
         <v>229</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="317" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C317" s="2" t="s">
         <v>342</v>
       </c>
@@ -8984,7 +8984,7 @@
         <v>176</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>75</v>
@@ -8999,7 +8999,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="318" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C318" s="2" t="s">
         <v>343</v>
       </c>
@@ -9016,7 +9016,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="319" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B319" s="3" t="s">
         <v>466</v>
       </c>
@@ -9039,7 +9039,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="320" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E320" s="2" t="s">
         <v>173</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="321" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E321" s="2" t="s">
         <v>135</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="322" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E322" s="2" t="s">
         <v>228</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="323" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E323" s="2" t="s">
         <v>229</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="324" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C324" s="2" t="s">
         <v>346</v>
       </c>
@@ -9146,7 +9146,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="325" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C325" s="2" t="s">
         <v>347</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="326" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B326" s="3" t="s">
         <v>467</v>
       </c>
@@ -9186,7 +9186,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="327" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E327" s="2" t="s">
         <v>173</v>
       </c>
@@ -9209,7 +9209,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="328" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E328" s="2" t="s">
         <v>135</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="329" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E329" s="2" t="s">
         <v>228</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="330" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E330" s="2" t="s">
         <v>229</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="331" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C331" s="2" t="s">
         <v>350</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="332" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C332" s="2" t="s">
         <v>351</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="333" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B333" s="3" t="s">
         <v>468</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="334" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E334" s="2" t="s">
         <v>173</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="335" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E335" s="2" t="s">
         <v>135</v>
       </c>
@@ -9376,7 +9376,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="336" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E336" s="2" t="s">
         <v>228</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="337" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E337" s="2" t="s">
         <v>229</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="338" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C338" s="2" t="s">
         <v>354</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="339" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C339" s="2" t="s">
         <v>355</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="340" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B340" s="3" t="s">
         <v>472</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="341" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E341" s="2" t="s">
         <v>173</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="342" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E342" s="2" t="s">
         <v>135</v>
       </c>
@@ -9523,7 +9523,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="343" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E343" s="2" t="s">
         <v>228</v>
       </c>
@@ -9544,7 +9544,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="344" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E344" s="2" t="s">
         <v>229</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="345" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C345" s="2" t="s">
         <v>372</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="346" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C346" s="2" t="s">
         <v>373</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="347" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B347" s="3" t="s">
         <v>473</v>
       </c>
@@ -9627,7 +9627,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="348" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E348" s="2" t="s">
         <v>173</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="349" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E349" s="2" t="s">
         <v>135</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="350" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E350" s="2" t="s">
         <v>228</v>
       </c>
@@ -9691,7 +9691,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="351" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E351" s="2" t="s">
         <v>229</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="352" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C352" s="2" t="s">
         <v>376</v>
       </c>
@@ -9734,7 +9734,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="353" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C353" s="2" t="s">
         <v>377</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="354" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B354" s="3" t="s">
         <v>469</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="355" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E355" s="2" t="s">
         <v>173</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="356" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E356" s="2" t="s">
         <v>135</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="357" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E357" s="2" t="s">
         <v>228</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="358" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E358" s="2" t="s">
         <v>229</v>
       </c>
@@ -9861,7 +9861,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="359" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C359" s="2" t="s">
         <v>358</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="360" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C360" s="2" t="s">
         <v>359</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="361" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E361" s="2" t="s">
         <v>275</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="362" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B362" s="3" t="s">
         <v>470</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="363" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E363" s="2" t="s">
         <v>173</v>
       </c>
@@ -9970,7 +9970,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="364" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E364" s="2" t="s">
         <v>135</v>
       </c>
@@ -9990,7 +9990,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="365" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E365" s="2" t="s">
         <v>228</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="366" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E366" s="2" t="s">
         <v>229</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="367" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C367" s="2" t="s">
         <v>362</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="368" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C368" s="2" t="s">
         <v>363</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E369" s="2" t="s">
         <v>275</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B370" s="3" t="s">
         <v>471</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E371" s="2" t="s">
         <v>173</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E372" s="2" t="s">
         <v>135</v>
       </c>
@@ -10163,7 +10163,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E373" s="2" t="s">
         <v>228</v>
       </c>
@@ -10184,7 +10184,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E374" s="2" t="s">
         <v>229</v>
       </c>
@@ -10207,7 +10207,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C375" s="2" t="s">
         <v>366</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C376" s="2" t="s">
         <v>367</v>
       </c>
@@ -10247,7 +10247,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E377" s="2" t="s">
         <v>275</v>
       </c>
@@ -10270,7 +10270,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="s">
         <v>540</v>
       </c>
@@ -10296,7 +10296,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="D379" s="2" t="s">
@@ -10315,7 +10315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="E380" s="2" t="s">
@@ -10340,7 +10340,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C381" s="2" t="s">
         <v>379</v>
       </c>
@@ -10360,7 +10360,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C382" s="2" t="s">
         <v>381</v>
       </c>
@@ -10380,7 +10380,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C383" s="2" t="s">
         <v>383</v>
       </c>
@@ -10397,7 +10397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B384" s="3" t="s">
         <v>475</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="385" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E385" s="2" t="s">
         <v>173</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="386" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E386" s="2" t="s">
         <v>135</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="387" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E387" s="2" t="s">
         <v>228</v>
       </c>
@@ -10481,7 +10481,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="388" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E388" s="2" t="s">
         <v>229</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="389" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C389" s="2" t="s">
         <v>387</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="390" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C390" s="2" t="s">
         <v>388</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="391" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B391" s="3" t="s">
         <v>476</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="392" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E392" s="2" t="s">
         <v>173</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E393" s="2" t="s">
         <v>135</v>
       </c>
@@ -10607,7 +10607,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="394" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E394" s="2" t="s">
         <v>228</v>
       </c>
@@ -10628,7 +10628,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="395" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E395" s="2" t="s">
         <v>229</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="396" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C396" s="2" t="s">
         <v>392</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="397" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C397" s="2" t="s">
         <v>392</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="398" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C398" s="2" t="s">
         <v>393</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="399" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C399" s="2" t="s">
         <v>393</v>
       </c>
@@ -10722,7 +10722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="400" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B400" s="3" t="s">
         <v>477</v>
       </c>
@@ -10745,7 +10745,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="401" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E401" s="2" t="s">
         <v>173</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="402" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E402" s="2" t="s">
         <v>135</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="403" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E403" s="2" t="s">
         <v>228</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="404" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E404" s="2" t="s">
         <v>229</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="405" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C405" s="2" t="s">
         <v>396</v>
       </c>
@@ -10849,7 +10849,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="406" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C406" s="2" t="s">
         <v>397</v>
       </c>
@@ -10866,7 +10866,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="407" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B407" s="3" t="s">
         <v>496</v>
       </c>
@@ -10889,7 +10889,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="408" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E408" s="2" t="s">
         <v>173</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="409" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E409" s="2" t="s">
         <v>135</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="410" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E410" s="2" t="s">
         <v>228</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="411" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E411" s="2" t="s">
         <v>229</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="412" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C412" s="2" t="s">
         <v>400</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="413" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C413" s="2" t="s">
         <v>400</v>
       </c>
@@ -11010,7 +11010,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="414" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B414" s="3" t="s">
         <v>495</v>
       </c>
@@ -11033,7 +11033,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="415" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E415" s="2" t="s">
         <v>173</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="416" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E416" s="2" t="s">
         <v>135</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E417" s="2" t="s">
         <v>228</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E418" s="2" t="s">
         <v>229</v>
       </c>
@@ -11117,7 +11117,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C419" s="2" t="s">
         <v>403</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C420" s="2" t="s">
         <v>403</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B421" s="3" t="s">
         <v>493</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E422" s="2" t="s">
         <v>211</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E423" s="2" t="s">
         <v>212</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B424" s="3" t="s">
         <v>494</v>
       </c>
@@ -11252,7 +11252,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E425" s="2" t="s">
         <v>211</v>
       </c>
@@ -11273,7 +11273,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E426" s="2" t="s">
         <v>212</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B427" s="3" t="s">
         <v>479</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="G428" s="2" t="s">
         <v>19</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G429" s="2" t="s">
         <v>19</v>
       </c>
@@ -11323,7 +11323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="G430" s="2" t="s">
         <v>19</v>
       </c>
@@ -11331,7 +11331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="s">
         <v>615</v>
       </c>
@@ -11354,7 +11354,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="D432" s="2" t="s">
@@ -11376,7 +11376,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="433" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E433" s="2" t="s">
         <v>568</v>
       </c>
@@ -11399,7 +11399,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="434" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E434" s="2" t="s">
         <v>572</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="435" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E435" s="2" t="s">
         <v>573</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="436" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B436" s="3" t="s">
         <v>565</v>
       </c>
@@ -11457,7 +11457,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="437" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E437" s="2" t="s">
         <v>173</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="438" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E438" s="2" t="s">
         <v>135</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="439" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E439" s="2" t="s">
         <v>228</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="440" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E440" s="2" t="s">
         <v>229</v>
       </c>
@@ -11538,7 +11538,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="441" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E441" s="2" t="s">
         <v>176</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="442" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E442" s="2" t="s">
         <v>178</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="443" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B443" s="3" t="s">
         <v>582</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="444" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E444" s="2" t="s">
         <v>173</v>
       </c>
@@ -11615,7 +11615,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="445" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E445" s="2" t="s">
         <v>135</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="446" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E446" s="2" t="s">
         <v>228</v>
       </c>
@@ -11653,7 +11653,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="447" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E447" s="2" t="s">
         <v>229</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="448" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E448" s="2" t="s">
         <v>176</v>
       </c>
@@ -11693,7 +11693,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E449" s="2" t="s">
         <v>178</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B450" s="3" t="s">
         <v>478</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E451" s="2" t="s">
         <v>173</v>
       </c>
@@ -11753,7 +11753,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E452" s="2" t="s">
         <v>135</v>
       </c>
@@ -11770,7 +11770,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E453" s="2" t="s">
         <v>228</v>
       </c>
@@ -11791,7 +11791,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E454" s="2" t="s">
         <v>229</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E455" s="2" t="s">
         <v>176</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E456" s="2" t="s">
         <v>178</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B457" s="3" t="s">
         <v>480</v>
       </c>
@@ -11859,7 +11859,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A458" s="5" t="s">
         <v>616</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="D459" s="2" t="s">
@@ -11904,7 +11904,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E460" s="2" t="s">
         <v>568</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E461" s="2" t="s">
         <v>572</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E462" s="2" t="s">
         <v>573</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B463" s="3" t="s">
         <v>565</v>
       </c>
@@ -11985,7 +11985,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E464" s="2" t="s">
         <v>173</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="465" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E465" s="2" t="s">
         <v>135</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="466" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E466" s="2" t="s">
         <v>228</v>
       </c>
@@ -12043,7 +12043,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="467" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E467" s="2" t="s">
         <v>229</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="468" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E468" s="2" t="s">
         <v>176</v>
       </c>
@@ -12083,7 +12083,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="469" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E469" s="2" t="s">
         <v>178</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="470" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B470" s="3" t="s">
         <v>582</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="471" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E471" s="2" t="s">
         <v>173</v>
       </c>
@@ -12143,7 +12143,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="472" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E472" s="2" t="s">
         <v>135</v>
       </c>
@@ -12160,7 +12160,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="473" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E473" s="2" t="s">
         <v>228</v>
       </c>
@@ -12181,7 +12181,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="474" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E474" s="2" t="s">
         <v>229</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="475" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E475" s="2" t="s">
         <v>176</v>
       </c>
@@ -12221,7 +12221,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="476" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="476" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E476" s="2" t="s">
         <v>178</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="477" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B477" s="3" t="s">
         <v>478</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="478" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E478" s="2" t="s">
         <v>173</v>
       </c>
@@ -12281,7 +12281,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="479" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E479" s="2" t="s">
         <v>135</v>
       </c>
@@ -12298,7 +12298,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="480" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E480" s="2" t="s">
         <v>228</v>
       </c>
@@ -12319,7 +12319,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E481" s="2" t="s">
         <v>229</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E482" s="2" t="s">
         <v>176</v>
       </c>
@@ -12362,7 +12362,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E483" s="2" t="s">
         <v>178</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B484" s="3" t="s">
         <v>617</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E485" s="2" t="s">
         <v>211</v>
       </c>
@@ -12424,7 +12424,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E486" s="2" t="s">
         <v>212</v>
       </c>
@@ -12447,7 +12447,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
         <v>603</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="D488" s="2" t="s">
@@ -12492,7 +12492,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E489" s="2" t="s">
         <v>568</v>
       </c>
@@ -12515,7 +12515,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E490" s="2" t="s">
         <v>572</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E491" s="2" t="s">
         <v>573</v>
       </c>
@@ -12550,7 +12550,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B492" s="3" t="s">
         <v>565</v>
       </c>
@@ -12573,7 +12573,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E493" s="2" t="s">
         <v>173</v>
       </c>
@@ -12596,7 +12596,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E494" s="2" t="s">
         <v>135</v>
       </c>
@@ -12613,7 +12613,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E495" s="2" t="s">
         <v>228</v>
       </c>
@@ -12631,7 +12631,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E496" s="2" t="s">
         <v>229</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="497" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E497" s="2" t="s">
         <v>176</v>
       </c>
@@ -12671,7 +12671,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="498" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E498" s="2" t="s">
         <v>178</v>
       </c>
@@ -12685,7 +12685,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="499" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B499" s="3" t="s">
         <v>582</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="500" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E500" s="2" t="s">
         <v>173</v>
       </c>
@@ -12731,7 +12731,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="501" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E501" s="2" t="s">
         <v>135</v>
       </c>
@@ -12748,7 +12748,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="502" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E502" s="2" t="s">
         <v>228</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="503" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E503" s="2" t="s">
         <v>229</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="504" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E504" s="2" t="s">
         <v>176</v>
       </c>
@@ -12809,7 +12809,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="505" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E505" s="2" t="s">
         <v>178</v>
       </c>
@@ -12823,7 +12823,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="506" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B506" s="3" t="s">
         <v>478</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="507" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E507" s="2" t="s">
         <v>173</v>
       </c>
@@ -12869,7 +12869,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="508" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E508" s="2" t="s">
         <v>135</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="509" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E509" s="2" t="s">
         <v>228</v>
       </c>
@@ -12907,7 +12907,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="510" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E510" s="2" t="s">
         <v>229</v>
       </c>
@@ -12930,7 +12930,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="511" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E511" s="2" t="s">
         <v>176</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="512" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E512" s="2" t="s">
         <v>178</v>
       </c>
@@ -12964,7 +12964,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="513" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B513" s="3" t="s">
         <v>618</v>
       </c>
@@ -12991,7 +12991,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E514" s="2" t="s">
         <v>211</v>
       </c>
@@ -13012,7 +13012,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E515" s="2" t="s">
         <v>212</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="516" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A516" s="5" t="s">
         <v>587</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E517" s="2" t="s">
         <v>214</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E518" s="2" t="s">
         <v>142</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E519" s="2" t="s">
         <v>314</v>
       </c>
@@ -13118,7 +13118,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E520" s="2" t="s">
         <v>316</v>
       </c>
@@ -13141,7 +13141,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="521" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B521" s="3" t="s">
         <v>498</v>
       </c>
@@ -13164,7 +13164,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E522" s="2" t="s">
         <v>214</v>
       </c>
@@ -13187,7 +13187,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E523" s="2" t="s">
         <v>142</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E524" s="2" t="s">
         <v>314</v>
       </c>
@@ -13221,7 +13221,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E525" s="2" t="s">
         <v>316</v>
       </c>
@@ -13244,7 +13244,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="526" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B526" s="3" t="s">
         <v>499</v>
       </c>
@@ -13267,7 +13267,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E527" s="2" t="s">
         <v>214</v>
       </c>
@@ -13290,7 +13290,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E528" s="2" t="s">
         <v>142</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="529" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E529" s="2" t="s">
         <v>314</v>
       </c>
@@ -13324,7 +13324,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="530" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E530" s="2" t="s">
         <v>316</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="531" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B531" s="3" t="s">
         <v>500</v>
       </c>
@@ -13370,7 +13370,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="532" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="532" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E532" s="2" t="s">
         <v>214</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="533" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="533" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E533" s="2" t="s">
         <v>142</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="534" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="534" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E534" s="2" t="s">
         <v>176</v>
       </c>
@@ -13427,7 +13427,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="535" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E535" s="2" t="s">
         <v>314</v>
       </c>
@@ -13441,7 +13441,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="536" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E536" s="2" t="s">
         <v>316</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="537" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B537" s="3" t="s">
         <v>501</v>
       </c>
@@ -13487,7 +13487,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="538" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E538" s="2" t="s">
         <v>214</v>
       </c>
@@ -13510,7 +13510,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="539" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E539" s="2" t="s">
         <v>142</v>
       </c>
@@ -13527,7 +13527,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="540" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E540" s="2" t="s">
         <v>176</v>
       </c>
@@ -13544,7 +13544,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="541" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="541" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B541" s="3" t="s">
         <v>502</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="542" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E542" s="2" t="s">
         <v>214</v>
       </c>
@@ -13590,7 +13590,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="543" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E543" s="2" t="s">
         <v>142</v>
       </c>
@@ -13607,7 +13607,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="544" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E544" s="2" t="s">
         <v>176</v>
       </c>
@@ -13624,7 +13624,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B545" s="3" t="s">
         <v>510</v>
       </c>
@@ -13635,7 +13635,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G546" s="2" t="s">
         <v>98</v>
       </c>
@@ -13643,7 +13643,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G547" s="2" t="s">
         <v>98</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="548" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A548" s="5" t="s">
         <v>541</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E549" s="2" t="s">
         <v>173</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E550" s="2" t="s">
         <v>176</v>
       </c>
@@ -13717,7 +13717,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E551" s="2" t="s">
         <v>178</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="552" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B552" s="3" t="s">
         <v>505</v>
       </c>
@@ -13754,7 +13754,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E553" s="2" t="s">
         <v>173</v>
       </c>
@@ -13777,7 +13777,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E554" s="2" t="s">
         <v>228</v>
       </c>
@@ -13798,7 +13798,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E555" s="2" t="s">
         <v>229</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E556" s="2" t="s">
         <v>314</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="557" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B557" s="3" t="s">
         <v>504</v>
       </c>
@@ -13861,7 +13861,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E558" s="2" t="s">
         <v>173</v>
       </c>
@@ -13884,7 +13884,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E559" s="2" t="s">
         <v>228</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E560" s="2" t="s">
         <v>229</v>
       </c>
@@ -13928,7 +13928,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E561" s="2" t="s">
         <v>176</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E562" s="2" t="s">
         <v>178</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A563" s="5" t="s">
         <v>542</v>
       </c>
@@ -13985,7 +13985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E564" s="2" t="s">
         <v>191</v>
       </c>
@@ -14005,7 +14005,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E565" s="2" t="s">
         <v>195</v>
       </c>
@@ -14019,7 +14019,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E566" s="2" t="s">
         <v>197</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E567" s="2" t="s">
         <v>198</v>
       </c>
@@ -14050,7 +14050,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E568" s="2" t="s">
         <v>430</v>
       </c>
@@ -14064,7 +14064,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="569" spans="1:11" ht="26" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:11" ht="27" x14ac:dyDescent="0.25">
       <c r="B569" s="3" t="s">
         <v>507</v>
       </c>
@@ -14084,7 +14084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E570" s="2" t="s">
         <v>214</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E571" s="2" t="s">
         <v>149</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>OMOP Comorbidity Condition</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E572" s="2" t="s">
         <v>150</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E573" s="2" t="s">
         <v>176</v>
       </c>
@@ -14156,7 +14156,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E574" s="2" t="s">
         <v>178</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="575" spans="1:11" ht="26" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:11" ht="27" x14ac:dyDescent="0.25">
       <c r="B575" s="3" t="s">
         <v>515</v>
       </c>
@@ -14184,7 +14184,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G576" s="12" t="s">
         <v>110</v>
       </c>
@@ -14192,13 +14192,13 @@
         <v>116</v>
       </c>
     </row>
-    <row r="577" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H577" s="6"/>
     </row>
-    <row r="578" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H578" s="6"/>
     </row>
-    <row r="581" spans="2:8" ht="26" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:8" ht="27" x14ac:dyDescent="0.25">
       <c r="B581" s="3" t="s">
         <v>508</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="582" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G582" s="12" t="s">
         <v>0</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="583" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G583" s="12" t="s">
         <v>0</v>
       </c>
@@ -14225,7 +14225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="584" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G584" s="12" t="s">
         <v>0</v>
       </c>
@@ -14233,7 +14233,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="585" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G585" s="12" t="s">
         <v>0</v>
       </c>
@@ -14241,7 +14241,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="586" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G586" s="12" t="s">
         <v>0</v>
       </c>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\python\mohccn-omop-etl\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B160ED-C3BD-4DB2-9746-438DD84A4F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CD8083-A6BE-47F8-B305-AE6D1CB9D6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformation Model" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3414" uniqueCount="621">
   <si>
     <t>Sample Registration</t>
   </si>
@@ -1898,6 +1898,12 @@
   </si>
   <si>
     <t>OMOP Treatment Episode / Visit Occurrence Event</t>
+  </si>
+  <si>
+    <t>Concept ID By Node</t>
+  </si>
+  <si>
+    <t>treatment_type</t>
   </si>
 </sst>
 </file>
@@ -2328,24 +2334,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9C41B9-3FB6-4282-940B-7420BB7A8AED}">
   <dimension ref="A1:L586"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="47.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.5703125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="43.85546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.85546875" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="25.7265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="47.453125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.81640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.54296875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="43.81640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.81640625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>121</v>
       </c>
@@ -2383,7 +2389,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
@@ -2415,7 +2421,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D3" s="2" t="s">
         <v>130</v>
       </c>
@@ -2437,7 +2443,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D4" s="2" t="s">
         <v>136</v>
       </c>
@@ -2463,7 +2469,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D5" s="2" t="s">
         <v>138</v>
       </c>
@@ -2489,7 +2495,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D6" s="2" t="s">
         <v>574</v>
       </c>
@@ -2515,7 +2521,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D7" s="2" t="s">
         <v>140</v>
       </c>
@@ -2541,7 +2547,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D8" s="2" t="s">
         <v>140</v>
       </c>
@@ -2561,7 +2567,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D9" s="2" t="s">
         <v>143</v>
       </c>
@@ -2587,7 +2593,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D10" s="2" t="s">
         <v>145</v>
       </c>
@@ -2614,7 +2620,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D11" s="2" t="s">
         <v>179</v>
       </c>
@@ -2638,7 +2644,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D12" s="2" t="s">
         <v>130</v>
       </c>
@@ -2662,7 +2668,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
         <v>145</v>
       </c>
@@ -2686,7 +2692,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
         <v>284</v>
       </c>
@@ -2710,7 +2716,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
         <v>143</v>
       </c>
@@ -2734,7 +2740,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
         <v>140</v>
       </c>
@@ -2758,7 +2764,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
         <v>574</v>
       </c>
@@ -2782,7 +2788,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D18" s="2" t="s">
         <v>138</v>
       </c>
@@ -2806,7 +2812,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D19" s="2" t="s">
         <v>136</v>
       </c>
@@ -2830,7 +2836,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D20" s="2" t="s">
         <v>140</v>
       </c>
@@ -2851,7 +2857,7 @@
         <v>OMOP Specimen</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D21" s="2" t="s">
         <v>140</v>
       </c>
@@ -2872,7 +2878,7 @@
         <v>OMOP Primary Dx Episode</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D22" s="2" t="s">
         <v>140</v>
       </c>
@@ -2893,7 +2899,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D23" s="2" t="s">
         <v>140</v>
       </c>
@@ -2914,7 +2920,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D24" s="2" t="s">
         <v>140</v>
       </c>
@@ -2940,7 +2946,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D25" s="2" t="s">
         <v>140</v>
       </c>
@@ -2966,7 +2972,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
         <v>140</v>
       </c>
@@ -2992,7 +2998,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D27" s="2" t="s">
         <v>140</v>
       </c>
@@ -3018,7 +3024,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>534</v>
       </c>
@@ -3042,7 +3048,7 @@
       </c>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D29" s="2" t="s">
         <v>543</v>
       </c>
@@ -3062,7 +3068,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D30" s="2" t="s">
         <v>543</v>
       </c>
@@ -3082,7 +3088,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D31" s="2" t="s">
         <v>543</v>
       </c>
@@ -3102,7 +3108,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D32" s="2" t="s">
         <v>543</v>
       </c>
@@ -3122,7 +3128,7 @@
         <v>4255047</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="2" t="s">
         <v>543</v>
       </c>
@@ -3142,7 +3148,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="3" t="s">
         <v>605</v>
@@ -3163,7 +3169,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D35" s="2" t="s">
         <v>543</v>
       </c>
@@ -3180,7 +3186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D36" s="2" t="s">
         <v>543</v>
       </c>
@@ -3197,7 +3203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D37" s="2" t="s">
         <v>543</v>
       </c>
@@ -3214,7 +3220,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B38" s="2"/>
       <c r="D38" s="2" t="s">
         <v>594</v>
@@ -3238,7 +3244,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="3" t="s">
         <v>433</v>
@@ -3262,7 +3268,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E40" s="2" t="s">
         <v>156</v>
       </c>
@@ -3282,7 +3288,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C41" s="2" t="s">
         <v>157</v>
       </c>
@@ -3308,7 +3314,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C42" s="2" t="s">
         <v>161</v>
       </c>
@@ -3325,7 +3331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C43" s="2" t="s">
         <v>163</v>
       </c>
@@ -3345,7 +3351,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C44" s="2" t="s">
         <v>166</v>
       </c>
@@ -3365,7 +3371,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C45" s="2" t="s">
         <v>169</v>
       </c>
@@ -3385,7 +3391,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E46" s="2" t="s">
         <v>592</v>
       </c>
@@ -3402,7 +3408,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E47" s="2" t="s">
         <v>593</v>
       </c>
@@ -3419,7 +3425,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>434</v>
       </c>
@@ -3442,7 +3448,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E49" s="2" t="s">
         <v>173</v>
       </c>
@@ -3465,7 +3471,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C50" s="2" t="s">
         <v>175</v>
       </c>
@@ -3485,7 +3491,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C51" s="2" t="s">
         <v>177</v>
       </c>
@@ -3502,7 +3508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>435</v>
       </c>
@@ -3532,7 +3538,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C53" s="2" t="s">
         <v>181</v>
       </c>
@@ -3552,7 +3558,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C54" s="2" t="s">
         <v>184</v>
       </c>
@@ -3569,7 +3575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C55" s="2" t="s">
         <v>186</v>
       </c>
@@ -3586,7 +3592,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>481</v>
       </c>
@@ -3600,7 +3606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E57" s="2" t="s">
         <v>188</v>
       </c>
@@ -3611,7 +3617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E58" s="2" t="s">
         <v>188</v>
       </c>
@@ -3622,7 +3628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>535</v>
       </c>
@@ -3648,7 +3654,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="D60" s="2" t="s">
         <v>145</v>
@@ -3669,7 +3675,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C61" s="2" t="s">
         <v>190</v>
       </c>
@@ -3692,7 +3698,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C62" s="2" t="s">
         <v>194</v>
       </c>
@@ -3709,7 +3715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C63" s="2" t="s">
         <v>196</v>
       </c>
@@ -3730,7 +3736,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E64" s="2" t="s">
         <v>198</v>
       </c>
@@ -3754,7 +3760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>437</v>
       </c>
@@ -3777,7 +3783,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E66" s="2" t="s">
         <v>201</v>
       </c>
@@ -3800,7 +3806,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E67" s="2" t="s">
         <v>205</v>
       </c>
@@ -3817,7 +3823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E68" s="2" t="s">
         <v>206</v>
       </c>
@@ -3838,7 +3844,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E69" s="2" t="s">
         <v>207</v>
       </c>
@@ -3855,7 +3861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E70" s="2" t="s">
         <v>208</v>
       </c>
@@ -3872,7 +3878,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E71" s="2" t="s">
         <v>209</v>
       </c>
@@ -3889,7 +3895,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="72" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>485</v>
       </c>
@@ -3916,7 +3922,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E73" s="2" t="s">
         <v>211</v>
       </c>
@@ -3937,7 +3943,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E74" s="2" t="s">
         <v>212</v>
       </c>
@@ -3960,7 +3966,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="75" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>439</v>
       </c>
@@ -3983,7 +3989,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E76" s="2" t="s">
         <v>214</v>
       </c>
@@ -4006,7 +4012,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E77" s="2" t="s">
         <v>142</v>
       </c>
@@ -4023,7 +4029,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E78" s="2" t="s">
         <v>149</v>
       </c>
@@ -4044,7 +4050,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E79" s="2" t="s">
         <v>150</v>
       </c>
@@ -4067,7 +4073,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C80" s="2" t="s">
         <v>217</v>
       </c>
@@ -4084,7 +4090,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C81" s="2" t="s">
         <v>218</v>
       </c>
@@ -4101,7 +4107,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>440</v>
       </c>
@@ -4124,7 +4130,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E83" s="2" t="s">
         <v>214</v>
       </c>
@@ -4147,7 +4153,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E84" s="2" t="s">
         <v>142</v>
       </c>
@@ -4164,7 +4170,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E85" s="2" t="s">
         <v>149</v>
       </c>
@@ -4185,7 +4191,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E86" s="2" t="s">
         <v>150</v>
       </c>
@@ -4208,7 +4214,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C87" s="2" t="s">
         <v>221</v>
       </c>
@@ -4228,7 +4234,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C88" s="2" t="s">
         <v>222</v>
       </c>
@@ -4245,7 +4251,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
         <v>441</v>
       </c>
@@ -4268,7 +4274,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E90" s="2" t="s">
         <v>173</v>
       </c>
@@ -4291,7 +4297,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E91" s="2" t="s">
         <v>135</v>
       </c>
@@ -4308,7 +4314,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C92" s="2" t="s">
         <v>226</v>
       </c>
@@ -4328,7 +4334,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C93" s="2" t="s">
         <v>227</v>
       </c>
@@ -4345,7 +4351,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E94" s="2" t="s">
         <v>228</v>
       </c>
@@ -4366,7 +4372,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E95" s="2" t="s">
         <v>229</v>
       </c>
@@ -4389,7 +4395,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="96" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
         <v>431</v>
       </c>
@@ -4412,7 +4418,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E97" s="2" t="s">
         <v>214</v>
       </c>
@@ -4435,7 +4441,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E98" s="2" t="s">
         <v>142</v>
       </c>
@@ -4452,7 +4458,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E99" s="2" t="s">
         <v>149</v>
       </c>
@@ -4473,7 +4479,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E100" s="2" t="s">
         <v>150</v>
       </c>
@@ -4496,7 +4502,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C101" s="2" t="s">
         <v>233</v>
       </c>
@@ -4516,7 +4522,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C102" s="2" t="s">
         <v>234</v>
       </c>
@@ -4533,7 +4539,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="103" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B103" s="3" t="s">
         <v>432</v>
       </c>
@@ -4556,7 +4562,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E104" s="2" t="s">
         <v>214</v>
       </c>
@@ -4579,7 +4585,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E105" s="2" t="s">
         <v>142</v>
       </c>
@@ -4596,7 +4602,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E106" s="2" t="s">
         <v>149</v>
       </c>
@@ -4617,7 +4623,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E107" s="2" t="s">
         <v>150</v>
       </c>
@@ -4640,7 +4646,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C108" s="2" t="s">
         <v>235</v>
       </c>
@@ -4660,7 +4666,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C109" s="2" t="s">
         <v>236</v>
       </c>
@@ -4677,7 +4683,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B110" s="3" t="s">
         <v>438</v>
       </c>
@@ -4700,7 +4706,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E111" s="2" t="s">
         <v>214</v>
       </c>
@@ -4723,7 +4729,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E112" s="2" t="s">
         <v>142</v>
       </c>
@@ -4740,7 +4746,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E113" s="2" t="s">
         <v>149</v>
       </c>
@@ -4761,7 +4767,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E114" s="2" t="s">
         <v>150</v>
       </c>
@@ -4784,7 +4790,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C115" s="2" t="s">
         <v>237</v>
       </c>
@@ -4804,7 +4810,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C116" s="2" t="s">
         <v>238</v>
       </c>
@@ -4821,7 +4827,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="117" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B117" s="3" t="s">
         <v>442</v>
       </c>
@@ -4844,7 +4850,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C118" s="2" t="s">
         <v>230</v>
       </c>
@@ -4864,7 +4870,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C119" s="2" t="s">
         <v>231</v>
       </c>
@@ -4881,7 +4887,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E120" s="2" t="s">
         <v>142</v>
       </c>
@@ -4898,7 +4904,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E121" s="2" t="s">
         <v>149</v>
       </c>
@@ -4916,7 +4922,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E122" s="2" t="s">
         <v>150</v>
       </c>
@@ -4939,7 +4945,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C123" s="2" t="s">
         <v>239</v>
       </c>
@@ -4956,7 +4962,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C124" s="2" t="s">
         <v>240</v>
       </c>
@@ -4973,7 +4979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="125" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B125" s="3" t="s">
         <v>443</v>
       </c>
@@ -4996,7 +5002,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E126" s="2" t="s">
         <v>214</v>
       </c>
@@ -5019,7 +5025,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E127" s="2" t="s">
         <v>142</v>
       </c>
@@ -5036,7 +5042,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E128" s="2" t="s">
         <v>149</v>
       </c>
@@ -5057,7 +5063,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E129" s="2" t="s">
         <v>150</v>
       </c>
@@ -5080,7 +5086,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C130" s="2" t="s">
         <v>243</v>
       </c>
@@ -5100,7 +5106,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C131" s="2" t="s">
         <v>244</v>
       </c>
@@ -5117,7 +5123,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B132" s="3" t="s">
         <v>444</v>
       </c>
@@ -5140,7 +5146,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E133" s="2" t="s">
         <v>214</v>
       </c>
@@ -5163,7 +5169,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E134" s="2" t="s">
         <v>142</v>
       </c>
@@ -5180,7 +5186,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E135" s="2" t="s">
         <v>149</v>
       </c>
@@ -5201,7 +5207,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E136" s="2" t="s">
         <v>150</v>
       </c>
@@ -5224,7 +5230,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C137" s="2" t="s">
         <v>245</v>
       </c>
@@ -5244,7 +5250,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C138" s="2" t="s">
         <v>246</v>
       </c>
@@ -5261,7 +5267,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="139" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B139" s="3" t="s">
         <v>445</v>
       </c>
@@ -5284,7 +5290,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E140" s="2" t="s">
         <v>214</v>
       </c>
@@ -5307,7 +5313,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E141" s="2" t="s">
         <v>142</v>
       </c>
@@ -5324,7 +5330,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E142" s="2" t="s">
         <v>149</v>
       </c>
@@ -5345,7 +5351,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E143" s="2" t="s">
         <v>150</v>
       </c>
@@ -5368,7 +5374,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C144" s="2" t="s">
         <v>247</v>
       </c>
@@ -5388,7 +5394,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C145" s="2" t="s">
         <v>248</v>
       </c>
@@ -5405,7 +5411,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B146" s="3" t="s">
         <v>446</v>
       </c>
@@ -5428,7 +5434,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C147" s="2" t="s">
         <v>241</v>
       </c>
@@ -5448,7 +5454,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C148" s="2" t="s">
         <v>242</v>
       </c>
@@ -5465,7 +5471,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E149" s="2" t="s">
         <v>142</v>
       </c>
@@ -5482,7 +5488,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E150" s="2" t="s">
         <v>149</v>
       </c>
@@ -5503,7 +5509,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E151" s="2" t="s">
         <v>150</v>
       </c>
@@ -5526,7 +5532,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C152" s="2" t="s">
         <v>249</v>
       </c>
@@ -5543,7 +5549,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C153" s="2" t="s">
         <v>509</v>
       </c>
@@ -5560,7 +5566,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>536</v>
       </c>
@@ -5586,7 +5592,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D155" s="2" t="s">
         <v>543</v>
       </c>
@@ -5606,7 +5612,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D156" s="2" t="s">
         <v>543</v>
       </c>
@@ -5623,7 +5629,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="D157" s="2" t="s">
@@ -5645,7 +5651,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E158" s="2" t="s">
         <v>201</v>
       </c>
@@ -5668,7 +5674,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E159" s="2" t="s">
         <v>205</v>
       </c>
@@ -5685,7 +5691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E160" s="2" t="s">
         <v>206</v>
       </c>
@@ -5702,7 +5708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C161" s="2" t="s">
         <v>252</v>
       </c>
@@ -5722,7 +5728,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C162" s="2" t="s">
         <v>253</v>
       </c>
@@ -5739,7 +5745,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C163" s="2" t="s">
         <v>254</v>
       </c>
@@ -5756,7 +5762,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="164" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B164" s="3" t="s">
         <v>448</v>
       </c>
@@ -5779,7 +5785,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E165" s="2" t="s">
         <v>173</v>
       </c>
@@ -5802,7 +5808,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E166" s="2" t="s">
         <v>135</v>
       </c>
@@ -5819,7 +5825,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E167" s="2" t="s">
         <v>228</v>
       </c>
@@ -5840,7 +5846,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E168" s="2" t="s">
         <v>229</v>
       </c>
@@ -5863,7 +5869,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C169" s="2" t="s">
         <v>266</v>
       </c>
@@ -5883,7 +5889,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C170" s="2" t="s">
         <v>267</v>
       </c>
@@ -5900,7 +5906,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="171" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B171" s="3" t="s">
         <v>449</v>
       </c>
@@ -5923,7 +5929,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E172" s="2" t="s">
         <v>173</v>
       </c>
@@ -5946,7 +5952,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C173" s="2" t="s">
         <v>272</v>
       </c>
@@ -5966,7 +5972,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C174" s="2" t="s">
         <v>273</v>
       </c>
@@ -5983,7 +5989,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E175" s="2" t="s">
         <v>135</v>
       </c>
@@ -6000,7 +6006,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E176" s="2" t="s">
         <v>228</v>
       </c>
@@ -6021,7 +6027,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E177" s="2" t="s">
         <v>229</v>
       </c>
@@ -6044,7 +6050,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C178" s="2" t="s">
         <v>274</v>
       </c>
@@ -6061,7 +6067,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C179" s="2" t="s">
         <v>276</v>
       </c>
@@ -6078,7 +6084,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>608</v>
       </c>
@@ -6104,24 +6110,21 @@
         <v>562</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E181" s="2" t="s">
         <v>256</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>132</v>
+        <v>619</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H181" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I181" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="H181" s="6" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C182" s="2" t="s">
         <v>257</v>
       </c>
@@ -6138,7 +6141,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E183" s="2" t="s">
         <v>259</v>
       </c>
@@ -6158,7 +6161,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C184" s="2" t="s">
         <v>260</v>
       </c>
@@ -6169,16 +6172,16 @@
         <v>151</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C185" s="2" t="s">
         <v>262</v>
       </c>
@@ -6198,7 +6201,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B186" s="3" t="s">
         <v>610</v>
       </c>
@@ -6225,7 +6228,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E187" s="2" t="s">
         <v>211</v>
       </c>
@@ -6246,7 +6249,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E188" s="2" t="s">
         <v>212</v>
       </c>
@@ -6269,7 +6272,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
         <v>537</v>
       </c>
@@ -6296,7 +6299,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E190" s="2" t="s">
         <v>201</v>
       </c>
@@ -6319,7 +6322,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E191" s="2" t="s">
         <v>205</v>
       </c>
@@ -6336,7 +6339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E192" s="2" t="s">
         <v>206</v>
       </c>
@@ -6354,7 +6357,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E193" s="2" t="s">
         <v>208</v>
       </c>
@@ -6371,7 +6374,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E194" s="2" t="s">
         <v>209</v>
       </c>
@@ -6385,7 +6388,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="195" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B195" s="3" t="s">
         <v>486</v>
       </c>
@@ -6412,7 +6415,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="196" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E196" s="2" t="s">
         <v>211</v>
       </c>
@@ -6433,7 +6436,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="197" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E197" s="2" t="s">
         <v>212</v>
       </c>
@@ -6456,7 +6459,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B198" s="3" t="s">
         <v>451</v>
       </c>
@@ -6480,7 +6483,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C199" s="2" t="s">
         <v>280</v>
       </c>
@@ -6500,7 +6503,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C200" s="2" t="s">
         <v>281</v>
       </c>
@@ -6517,7 +6520,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="201" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E201" s="2" t="s">
         <v>259</v>
       </c>
@@ -6534,7 +6537,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="202" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C202" s="2" t="s">
         <v>282</v>
       </c>
@@ -6551,7 +6554,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B203" s="3" t="s">
         <v>484</v>
       </c>
@@ -6578,7 +6581,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="204" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E204" s="2" t="s">
         <v>211</v>
       </c>
@@ -6599,7 +6602,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="205" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E205" s="2" t="s">
         <v>212</v>
       </c>
@@ -6622,7 +6625,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B206" s="3" t="s">
         <v>452</v>
       </c>
@@ -6646,7 +6649,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="207" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B207" s="2"/>
       <c r="D207" s="2" t="s">
         <v>284</v>
@@ -6667,7 +6670,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="208" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E208" s="2" t="s">
         <v>286</v>
       </c>
@@ -6690,7 +6693,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E209" s="2" t="s">
         <v>289</v>
       </c>
@@ -6710,7 +6713,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="C210" s="5" t="s">
         <v>291</v>
       </c>
@@ -6727,7 +6730,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="211" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C211" s="2" t="s">
         <v>293</v>
       </c>
@@ -6747,7 +6750,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="212" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C212" s="2" t="s">
         <v>295</v>
       </c>
@@ -6767,7 +6770,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C213" s="2" t="s">
         <v>297</v>
       </c>
@@ -6784,7 +6787,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C214" s="2" t="s">
         <v>299</v>
       </c>
@@ -6801,7 +6804,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B215" s="3" t="s">
         <v>483</v>
       </c>
@@ -6828,7 +6831,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E216" s="2" t="s">
         <v>211</v>
       </c>
@@ -6849,7 +6852,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E217" s="2" t="s">
         <v>212</v>
       </c>
@@ -6872,7 +6875,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B218" s="3" t="s">
         <v>453</v>
       </c>
@@ -6895,7 +6898,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E219" s="2" t="s">
         <v>286</v>
       </c>
@@ -6918,7 +6921,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E220" s="2" t="s">
         <v>289</v>
       </c>
@@ -6938,7 +6941,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="C221" s="5" t="s">
         <v>291</v>
       </c>
@@ -6955,7 +6958,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C222" s="2" t="s">
         <v>293</v>
       </c>
@@ -6975,7 +6978,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C223" s="2" t="s">
         <v>295</v>
       </c>
@@ -6995,7 +6998,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C224" s="2" t="s">
         <v>297</v>
       </c>
@@ -7012,7 +7015,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C225" s="2" t="s">
         <v>304</v>
       </c>
@@ -7029,7 +7032,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B226" s="3" t="s">
         <v>487</v>
       </c>
@@ -7056,7 +7059,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E227" s="2" t="s">
         <v>211</v>
       </c>
@@ -7077,7 +7080,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E228" s="2" t="s">
         <v>212</v>
       </c>
@@ -7100,7 +7103,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B229" s="3" t="s">
         <v>482</v>
       </c>
@@ -7111,7 +7114,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>538</v>
       </c>
@@ -7137,7 +7140,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E231" s="2" t="s">
         <v>201</v>
       </c>
@@ -7160,7 +7163,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E232" s="2" t="s">
         <v>205</v>
       </c>
@@ -7177,7 +7180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E233" s="2" t="s">
         <v>206</v>
       </c>
@@ -7195,7 +7198,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E234" s="2" t="s">
         <v>208</v>
       </c>
@@ -7215,7 +7218,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B235" s="3" t="s">
         <v>488</v>
       </c>
@@ -7242,7 +7245,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E236" s="2" t="s">
         <v>211</v>
       </c>
@@ -7263,7 +7266,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E237" s="2" t="s">
         <v>212</v>
       </c>
@@ -7286,7 +7289,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B238" s="3" t="s">
         <v>455</v>
       </c>
@@ -7309,7 +7312,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C239" s="2" t="s">
         <v>307</v>
       </c>
@@ -7329,7 +7332,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C240" s="2" t="s">
         <v>308</v>
       </c>
@@ -7346,7 +7349,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="241" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E241" s="2" t="s">
         <v>259</v>
       </c>
@@ -7366,7 +7369,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="242" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C242" s="2" t="s">
         <v>309</v>
       </c>
@@ -7384,7 +7387,7 @@
       </c>
       <c r="I242" s="10"/>
     </row>
-    <row r="243" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C243" s="2" t="s">
         <v>310</v>
       </c>
@@ -7402,7 +7405,7 @@
       </c>
       <c r="I243" s="10"/>
     </row>
-    <row r="244" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B244" s="3" t="s">
         <v>489</v>
       </c>
@@ -7429,7 +7432,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="245" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E245" s="2" t="s">
         <v>211</v>
       </c>
@@ -7450,7 +7453,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="246" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E246" s="2" t="s">
         <v>212</v>
       </c>
@@ -7473,7 +7476,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="247" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B247" s="3" t="s">
         <v>456</v>
       </c>
@@ -7496,7 +7499,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="248" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E248" s="2" t="s">
         <v>214</v>
       </c>
@@ -7519,7 +7522,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="249" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E249" s="2" t="s">
         <v>142</v>
       </c>
@@ -7539,7 +7542,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="250" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E250" s="2" t="s">
         <v>149</v>
       </c>
@@ -7560,7 +7563,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="251" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E251" s="2" t="s">
         <v>150</v>
       </c>
@@ -7583,7 +7586,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="252" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C252" s="2" t="s">
         <v>313</v>
       </c>
@@ -7603,7 +7606,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="253" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C253" s="2" t="s">
         <v>315</v>
       </c>
@@ -7629,7 +7632,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="254" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B254" s="3" t="s">
         <v>457</v>
       </c>
@@ -7652,7 +7655,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="255" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E255" s="2" t="s">
         <v>214</v>
       </c>
@@ -7673,7 +7676,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="256" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E256" s="2" t="s">
         <v>142</v>
       </c>
@@ -7693,7 +7696,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="257" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E257" s="2" t="s">
         <v>149</v>
       </c>
@@ -7714,7 +7717,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="258" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E258" s="2" t="s">
         <v>150</v>
       </c>
@@ -7737,7 +7740,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="259" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C259" s="2" t="s">
         <v>313</v>
       </c>
@@ -7757,7 +7760,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="260" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B260" s="3" t="s">
         <v>458</v>
       </c>
@@ -7780,7 +7783,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="261" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E261" s="2" t="s">
         <v>173</v>
       </c>
@@ -7803,7 +7806,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="262" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E262" s="2" t="s">
         <v>135</v>
       </c>
@@ -7823,7 +7826,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="263" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E263" s="2" t="s">
         <v>228</v>
       </c>
@@ -7844,7 +7847,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="264" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E264" s="2" t="s">
         <v>229</v>
       </c>
@@ -7867,7 +7870,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="265" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C265" s="2" t="s">
         <v>323</v>
       </c>
@@ -7887,7 +7890,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="266" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C266" s="2" t="s">
         <v>324</v>
       </c>
@@ -7904,7 +7907,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="267" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B267" s="3" t="s">
         <v>459</v>
       </c>
@@ -7927,7 +7930,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="268" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E268" s="2" t="s">
         <v>256</v>
       </c>
@@ -7950,7 +7953,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="269" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E269" s="2" t="s">
         <v>259</v>
       </c>
@@ -7970,7 +7973,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="270" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E270" s="2" t="s">
         <v>261</v>
       </c>
@@ -7987,7 +7990,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="271" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E271" s="2" t="s">
         <v>263</v>
       </c>
@@ -8001,7 +8004,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="272" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B272" s="3" t="s">
         <v>490</v>
       </c>
@@ -8028,7 +8031,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E273" s="2" t="s">
         <v>211</v>
       </c>
@@ -8049,7 +8052,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E274" s="2" t="s">
         <v>212</v>
       </c>
@@ -8072,7 +8075,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A275" s="5" t="s">
         <v>539</v>
       </c>
@@ -8095,7 +8098,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D276" s="2" t="s">
         <v>136</v>
       </c>
@@ -8115,7 +8118,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E277" s="2" t="s">
         <v>201</v>
       </c>
@@ -8138,7 +8141,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E278" s="2" t="s">
         <v>205</v>
       </c>
@@ -8155,7 +8158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E279" s="2" t="s">
         <v>206</v>
       </c>
@@ -8176,7 +8179,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E280" s="2" t="s">
         <v>208</v>
       </c>
@@ -8196,7 +8199,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B281" s="3" t="s">
         <v>491</v>
       </c>
@@ -8223,7 +8226,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E282" s="2" t="s">
         <v>211</v>
       </c>
@@ -8244,7 +8247,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E283" s="2" t="s">
         <v>212</v>
       </c>
@@ -8267,7 +8270,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B284" s="3" t="s">
         <v>461</v>
       </c>
@@ -8290,7 +8293,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C285" s="2" t="s">
         <v>329</v>
       </c>
@@ -8314,7 +8317,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" ht="39" x14ac:dyDescent="0.3">
       <c r="C286" s="5" t="s">
         <v>330</v>
       </c>
@@ -8331,7 +8334,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E287" s="2" t="s">
         <v>259</v>
       </c>
@@ -8351,7 +8354,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B288" s="3" t="s">
         <v>492</v>
       </c>
@@ -8378,7 +8381,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="289" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E289" s="2" t="s">
         <v>211</v>
       </c>
@@ -8399,7 +8402,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="290" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E290" s="2" t="s">
         <v>212</v>
       </c>
@@ -8422,7 +8425,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="291" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B291" s="3" t="s">
         <v>462</v>
       </c>
@@ -8445,7 +8448,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="292" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E292" s="2" t="s">
         <v>214</v>
       </c>
@@ -8463,7 +8466,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="293" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E293" s="2" t="s">
         <v>142</v>
       </c>
@@ -8483,7 +8486,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="294" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E294" s="2" t="s">
         <v>149</v>
       </c>
@@ -8504,7 +8507,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="295" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E295" s="2" t="s">
         <v>150</v>
       </c>
@@ -8527,7 +8530,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="296" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C296" s="2" t="s">
         <v>334</v>
       </c>
@@ -8547,7 +8550,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="297" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E297" s="2" t="s">
         <v>316</v>
       </c>
@@ -8570,7 +8573,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="298" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B298" s="3" t="s">
         <v>463</v>
       </c>
@@ -8593,7 +8596,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="299" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E299" s="2" t="s">
         <v>214</v>
       </c>
@@ -8611,7 +8614,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="300" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E300" s="2" t="s">
         <v>142</v>
       </c>
@@ -8631,7 +8634,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="301" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E301" s="2" t="s">
         <v>149</v>
       </c>
@@ -8652,7 +8655,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="302" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E302" s="2" t="s">
         <v>150</v>
       </c>
@@ -8675,7 +8678,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="303" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C303" s="2" t="s">
         <v>339</v>
       </c>
@@ -8695,7 +8698,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="304" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E304" s="2" t="s">
         <v>316</v>
       </c>
@@ -8718,7 +8721,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="305" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B305" s="3" t="s">
         <v>464</v>
       </c>
@@ -8741,7 +8744,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="306" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E306" s="2" t="s">
         <v>214</v>
       </c>
@@ -8759,7 +8762,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="307" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E307" s="2" t="s">
         <v>142</v>
       </c>
@@ -8779,7 +8782,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="308" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E308" s="2" t="s">
         <v>149</v>
       </c>
@@ -8800,7 +8803,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="309" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E309" s="2" t="s">
         <v>150</v>
       </c>
@@ -8823,7 +8826,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="310" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C310" s="2" t="s">
         <v>339</v>
       </c>
@@ -8843,7 +8846,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="311" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E311" s="2" t="s">
         <v>316</v>
       </c>
@@ -8866,7 +8869,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="312" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B312" s="3" t="s">
         <v>465</v>
       </c>
@@ -8889,7 +8892,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="313" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E313" s="2" t="s">
         <v>173</v>
       </c>
@@ -8912,7 +8915,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="314" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E314" s="2" t="s">
         <v>135</v>
       </c>
@@ -8932,7 +8935,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="315" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E315" s="2" t="s">
         <v>228</v>
       </c>
@@ -8953,7 +8956,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="316" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E316" s="2" t="s">
         <v>229</v>
       </c>
@@ -8976,7 +8979,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="317" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C317" s="2" t="s">
         <v>342</v>
       </c>
@@ -8999,7 +9002,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="318" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C318" s="2" t="s">
         <v>343</v>
       </c>
@@ -9016,7 +9019,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="319" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B319" s="3" t="s">
         <v>466</v>
       </c>
@@ -9039,7 +9042,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="320" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E320" s="2" t="s">
         <v>173</v>
       </c>
@@ -9062,7 +9065,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="321" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E321" s="2" t="s">
         <v>135</v>
       </c>
@@ -9082,7 +9085,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="322" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E322" s="2" t="s">
         <v>228</v>
       </c>
@@ -9103,7 +9106,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="323" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E323" s="2" t="s">
         <v>229</v>
       </c>
@@ -9126,7 +9129,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="324" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C324" s="2" t="s">
         <v>346</v>
       </c>
@@ -9146,7 +9149,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="325" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C325" s="2" t="s">
         <v>347</v>
       </c>
@@ -9163,7 +9166,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="326" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B326" s="3" t="s">
         <v>467</v>
       </c>
@@ -9186,7 +9189,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="327" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E327" s="2" t="s">
         <v>173</v>
       </c>
@@ -9209,7 +9212,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="328" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E328" s="2" t="s">
         <v>135</v>
       </c>
@@ -9229,7 +9232,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="329" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E329" s="2" t="s">
         <v>228</v>
       </c>
@@ -9250,7 +9253,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="330" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E330" s="2" t="s">
         <v>229</v>
       </c>
@@ -9273,7 +9276,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="331" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C331" s="2" t="s">
         <v>350</v>
       </c>
@@ -9293,7 +9296,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="332" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C332" s="2" t="s">
         <v>351</v>
       </c>
@@ -9310,7 +9313,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="333" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B333" s="3" t="s">
         <v>468</v>
       </c>
@@ -9333,7 +9336,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="334" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E334" s="2" t="s">
         <v>173</v>
       </c>
@@ -9356,7 +9359,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="335" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E335" s="2" t="s">
         <v>135</v>
       </c>
@@ -9376,7 +9379,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="336" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E336" s="2" t="s">
         <v>228</v>
       </c>
@@ -9397,7 +9400,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="337" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E337" s="2" t="s">
         <v>229</v>
       </c>
@@ -9420,7 +9423,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="338" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C338" s="2" t="s">
         <v>354</v>
       </c>
@@ -9440,7 +9443,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="339" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C339" s="2" t="s">
         <v>355</v>
       </c>
@@ -9457,7 +9460,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="340" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B340" s="3" t="s">
         <v>472</v>
       </c>
@@ -9480,7 +9483,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="341" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E341" s="2" t="s">
         <v>173</v>
       </c>
@@ -9503,7 +9506,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="342" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E342" s="2" t="s">
         <v>135</v>
       </c>
@@ -9523,7 +9526,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="343" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E343" s="2" t="s">
         <v>228</v>
       </c>
@@ -9544,7 +9547,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="344" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E344" s="2" t="s">
         <v>229</v>
       </c>
@@ -9567,7 +9570,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="345" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C345" s="2" t="s">
         <v>372</v>
       </c>
@@ -9587,7 +9590,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="346" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C346" s="2" t="s">
         <v>373</v>
       </c>
@@ -9604,7 +9607,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="347" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B347" s="3" t="s">
         <v>473</v>
       </c>
@@ -9627,7 +9630,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="348" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E348" s="2" t="s">
         <v>173</v>
       </c>
@@ -9650,7 +9653,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="349" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E349" s="2" t="s">
         <v>135</v>
       </c>
@@ -9670,7 +9673,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="350" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E350" s="2" t="s">
         <v>228</v>
       </c>
@@ -9691,7 +9694,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="351" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E351" s="2" t="s">
         <v>229</v>
       </c>
@@ -9714,7 +9717,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="352" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C352" s="2" t="s">
         <v>376</v>
       </c>
@@ -9734,7 +9737,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="353" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C353" s="2" t="s">
         <v>377</v>
       </c>
@@ -9751,7 +9754,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="354" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B354" s="3" t="s">
         <v>469</v>
       </c>
@@ -9774,7 +9777,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="355" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E355" s="2" t="s">
         <v>173</v>
       </c>
@@ -9797,7 +9800,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="356" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E356" s="2" t="s">
         <v>135</v>
       </c>
@@ -9817,7 +9820,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="357" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E357" s="2" t="s">
         <v>228</v>
       </c>
@@ -9838,7 +9841,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="358" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E358" s="2" t="s">
         <v>229</v>
       </c>
@@ -9861,7 +9864,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="359" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C359" s="2" t="s">
         <v>358</v>
       </c>
@@ -9881,7 +9884,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="360" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C360" s="2" t="s">
         <v>359</v>
       </c>
@@ -9901,7 +9904,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="361" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E361" s="2" t="s">
         <v>275</v>
       </c>
@@ -9924,7 +9927,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="362" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B362" s="3" t="s">
         <v>470</v>
       </c>
@@ -9947,7 +9950,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="363" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E363" s="2" t="s">
         <v>173</v>
       </c>
@@ -9970,7 +9973,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="364" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E364" s="2" t="s">
         <v>135</v>
       </c>
@@ -9990,7 +9993,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="365" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E365" s="2" t="s">
         <v>228</v>
       </c>
@@ -10011,7 +10014,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="366" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E366" s="2" t="s">
         <v>229</v>
       </c>
@@ -10034,7 +10037,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="367" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C367" s="2" t="s">
         <v>362</v>
       </c>
@@ -10054,7 +10057,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="368" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C368" s="2" t="s">
         <v>363</v>
       </c>
@@ -10074,7 +10077,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E369" s="2" t="s">
         <v>275</v>
       </c>
@@ -10097,7 +10100,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" ht="39" x14ac:dyDescent="0.3">
       <c r="B370" s="3" t="s">
         <v>471</v>
       </c>
@@ -10120,7 +10123,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E371" s="2" t="s">
         <v>173</v>
       </c>
@@ -10143,7 +10146,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E372" s="2" t="s">
         <v>135</v>
       </c>
@@ -10163,7 +10166,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E373" s="2" t="s">
         <v>228</v>
       </c>
@@ -10184,7 +10187,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E374" s="2" t="s">
         <v>229</v>
       </c>
@@ -10207,7 +10210,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C375" s="2" t="s">
         <v>366</v>
       </c>
@@ -10227,7 +10230,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C376" s="2" t="s">
         <v>367</v>
       </c>
@@ -10247,7 +10250,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E377" s="2" t="s">
         <v>275</v>
       </c>
@@ -10270,7 +10273,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A378" s="5" t="s">
         <v>540</v>
       </c>
@@ -10296,7 +10299,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="D379" s="2" t="s">
@@ -10315,7 +10318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="E380" s="2" t="s">
@@ -10340,7 +10343,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C381" s="2" t="s">
         <v>379</v>
       </c>
@@ -10360,7 +10363,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C382" s="2" t="s">
         <v>381</v>
       </c>
@@ -10380,7 +10383,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C383" s="2" t="s">
         <v>383</v>
       </c>
@@ -10397,7 +10400,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B384" s="3" t="s">
         <v>475</v>
       </c>
@@ -10420,7 +10423,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="385" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E385" s="2" t="s">
         <v>173</v>
       </c>
@@ -10443,7 +10446,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="386" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E386" s="2" t="s">
         <v>135</v>
       </c>
@@ -10460,7 +10463,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="387" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E387" s="2" t="s">
         <v>228</v>
       </c>
@@ -10481,7 +10484,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="388" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E388" s="2" t="s">
         <v>229</v>
       </c>
@@ -10504,7 +10507,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="389" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C389" s="2" t="s">
         <v>387</v>
       </c>
@@ -10527,7 +10530,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="390" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C390" s="2" t="s">
         <v>388</v>
       </c>
@@ -10544,7 +10547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="391" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B391" s="3" t="s">
         <v>476</v>
       </c>
@@ -10567,7 +10570,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="392" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E392" s="2" t="s">
         <v>173</v>
       </c>
@@ -10590,7 +10593,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E393" s="2" t="s">
         <v>135</v>
       </c>
@@ -10607,7 +10610,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="394" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E394" s="2" t="s">
         <v>228</v>
       </c>
@@ -10628,7 +10631,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="395" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E395" s="2" t="s">
         <v>229</v>
       </c>
@@ -10651,7 +10654,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="396" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C396" s="2" t="s">
         <v>392</v>
       </c>
@@ -10671,7 +10674,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="397" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C397" s="2" t="s">
         <v>392</v>
       </c>
@@ -10688,7 +10691,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="398" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C398" s="2" t="s">
         <v>393</v>
       </c>
@@ -10705,7 +10708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="399" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C399" s="2" t="s">
         <v>393</v>
       </c>
@@ -10722,7 +10725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="400" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B400" s="3" t="s">
         <v>477</v>
       </c>
@@ -10745,7 +10748,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="401" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E401" s="2" t="s">
         <v>173</v>
       </c>
@@ -10768,7 +10771,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="402" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E402" s="2" t="s">
         <v>135</v>
       </c>
@@ -10785,7 +10788,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="403" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E403" s="2" t="s">
         <v>228</v>
       </c>
@@ -10806,7 +10809,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="404" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E404" s="2" t="s">
         <v>229</v>
       </c>
@@ -10829,7 +10832,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="405" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C405" s="2" t="s">
         <v>396</v>
       </c>
@@ -10849,7 +10852,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="406" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C406" s="2" t="s">
         <v>397</v>
       </c>
@@ -10866,7 +10869,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="407" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B407" s="3" t="s">
         <v>496</v>
       </c>
@@ -10889,7 +10892,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="408" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E408" s="2" t="s">
         <v>173</v>
       </c>
@@ -10912,7 +10915,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="409" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E409" s="2" t="s">
         <v>135</v>
       </c>
@@ -10929,7 +10932,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="410" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E410" s="2" t="s">
         <v>228</v>
       </c>
@@ -10950,7 +10953,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="411" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E411" s="2" t="s">
         <v>229</v>
       </c>
@@ -10973,7 +10976,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="412" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C412" s="2" t="s">
         <v>400</v>
       </c>
@@ -10993,7 +10996,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="413" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C413" s="2" t="s">
         <v>400</v>
       </c>
@@ -11010,7 +11013,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="414" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B414" s="3" t="s">
         <v>495</v>
       </c>
@@ -11033,7 +11036,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="415" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E415" s="2" t="s">
         <v>173</v>
       </c>
@@ -11056,7 +11059,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="416" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E416" s="2" t="s">
         <v>135</v>
       </c>
@@ -11073,7 +11076,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E417" s="2" t="s">
         <v>228</v>
       </c>
@@ -11094,7 +11097,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E418" s="2" t="s">
         <v>229</v>
       </c>
@@ -11117,7 +11120,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C419" s="2" t="s">
         <v>403</v>
       </c>
@@ -11137,7 +11140,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C420" s="2" t="s">
         <v>403</v>
       </c>
@@ -11154,7 +11157,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B421" s="3" t="s">
         <v>493</v>
       </c>
@@ -11181,7 +11184,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E422" s="2" t="s">
         <v>211</v>
       </c>
@@ -11202,7 +11205,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E423" s="2" t="s">
         <v>212</v>
       </c>
@@ -11225,7 +11228,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B424" s="3" t="s">
         <v>494</v>
       </c>
@@ -11252,7 +11255,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E425" s="2" t="s">
         <v>211</v>
       </c>
@@ -11273,7 +11276,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E426" s="2" t="s">
         <v>212</v>
       </c>
@@ -11296,7 +11299,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B427" s="3" t="s">
         <v>479</v>
       </c>
@@ -11307,7 +11310,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="G428" s="2" t="s">
         <v>19</v>
       </c>
@@ -11315,7 +11318,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G429" s="2" t="s">
         <v>19</v>
       </c>
@@ -11323,7 +11326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="G430" s="2" t="s">
         <v>19</v>
       </c>
@@ -11331,7 +11334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A431" s="5" t="s">
         <v>615</v>
       </c>
@@ -11354,7 +11357,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="D432" s="2" t="s">
@@ -11376,7 +11379,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="433" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E433" s="2" t="s">
         <v>568</v>
       </c>
@@ -11399,7 +11402,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="434" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E434" s="2" t="s">
         <v>572</v>
       </c>
@@ -11416,7 +11419,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="435" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E435" s="2" t="s">
         <v>573</v>
       </c>
@@ -11434,7 +11437,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="436" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B436" s="3" t="s">
         <v>565</v>
       </c>
@@ -11457,7 +11460,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="437" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E437" s="2" t="s">
         <v>173</v>
       </c>
@@ -11480,7 +11483,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="438" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E438" s="2" t="s">
         <v>135</v>
       </c>
@@ -11497,7 +11500,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="439" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E439" s="2" t="s">
         <v>228</v>
       </c>
@@ -11515,7 +11518,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="440" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E440" s="2" t="s">
         <v>229</v>
       </c>
@@ -11538,7 +11541,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="441" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E441" s="2" t="s">
         <v>176</v>
       </c>
@@ -11555,7 +11558,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="442" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E442" s="2" t="s">
         <v>178</v>
       </c>
@@ -11569,7 +11572,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="443" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B443" s="3" t="s">
         <v>582</v>
       </c>
@@ -11592,7 +11595,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="444" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E444" s="2" t="s">
         <v>173</v>
       </c>
@@ -11615,7 +11618,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="445" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E445" s="2" t="s">
         <v>135</v>
       </c>
@@ -11632,7 +11635,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="446" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E446" s="2" t="s">
         <v>228</v>
       </c>
@@ -11653,7 +11656,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="447" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E447" s="2" t="s">
         <v>229</v>
       </c>
@@ -11676,7 +11679,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="448" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E448" s="2" t="s">
         <v>176</v>
       </c>
@@ -11693,7 +11696,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E449" s="2" t="s">
         <v>178</v>
       </c>
@@ -11707,7 +11710,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B450" s="3" t="s">
         <v>478</v>
       </c>
@@ -11730,7 +11733,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E451" s="2" t="s">
         <v>173</v>
       </c>
@@ -11753,7 +11756,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E452" s="2" t="s">
         <v>135</v>
       </c>
@@ -11770,7 +11773,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E453" s="2" t="s">
         <v>228</v>
       </c>
@@ -11791,7 +11794,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E454" s="2" t="s">
         <v>229</v>
       </c>
@@ -11814,7 +11817,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E455" s="2" t="s">
         <v>176</v>
       </c>
@@ -11834,7 +11837,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E456" s="2" t="s">
         <v>178</v>
       </c>
@@ -11848,7 +11851,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B457" s="3" t="s">
         <v>480</v>
       </c>
@@ -11859,7 +11862,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A458" s="5" t="s">
         <v>616</v>
       </c>
@@ -11882,7 +11885,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="D459" s="2" t="s">
@@ -11904,7 +11907,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E460" s="2" t="s">
         <v>568</v>
       </c>
@@ -11927,7 +11930,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E461" s="2" t="s">
         <v>572</v>
       </c>
@@ -11944,7 +11947,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E462" s="2" t="s">
         <v>573</v>
       </c>
@@ -11962,7 +11965,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B463" s="3" t="s">
         <v>565</v>
       </c>
@@ -11985,7 +11988,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E464" s="2" t="s">
         <v>173</v>
       </c>
@@ -12008,7 +12011,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="465" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E465" s="2" t="s">
         <v>135</v>
       </c>
@@ -12025,7 +12028,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="466" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E466" s="2" t="s">
         <v>228</v>
       </c>
@@ -12043,7 +12046,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="467" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E467" s="2" t="s">
         <v>229</v>
       </c>
@@ -12066,7 +12069,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="468" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E468" s="2" t="s">
         <v>176</v>
       </c>
@@ -12083,7 +12086,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="469" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E469" s="2" t="s">
         <v>178</v>
       </c>
@@ -12097,7 +12100,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="470" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B470" s="3" t="s">
         <v>582</v>
       </c>
@@ -12120,7 +12123,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="471" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E471" s="2" t="s">
         <v>173</v>
       </c>
@@ -12143,7 +12146,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="472" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E472" s="2" t="s">
         <v>135</v>
       </c>
@@ -12160,7 +12163,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="473" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E473" s="2" t="s">
         <v>228</v>
       </c>
@@ -12181,7 +12184,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="474" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E474" s="2" t="s">
         <v>229</v>
       </c>
@@ -12204,7 +12207,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="475" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E475" s="2" t="s">
         <v>176</v>
       </c>
@@ -12221,7 +12224,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="476" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E476" s="2" t="s">
         <v>178</v>
       </c>
@@ -12235,7 +12238,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="477" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B477" s="3" t="s">
         <v>478</v>
       </c>
@@ -12258,7 +12261,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="478" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E478" s="2" t="s">
         <v>173</v>
       </c>
@@ -12281,7 +12284,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="479" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E479" s="2" t="s">
         <v>135</v>
       </c>
@@ -12298,7 +12301,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="480" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E480" s="2" t="s">
         <v>228</v>
       </c>
@@ -12319,7 +12322,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E481" s="2" t="s">
         <v>229</v>
       </c>
@@ -12342,7 +12345,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E482" s="2" t="s">
         <v>176</v>
       </c>
@@ -12362,7 +12365,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E483" s="2" t="s">
         <v>178</v>
       </c>
@@ -12376,7 +12379,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B484" s="3" t="s">
         <v>617</v>
       </c>
@@ -12403,7 +12406,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E485" s="2" t="s">
         <v>211</v>
       </c>
@@ -12424,7 +12427,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E486" s="2" t="s">
         <v>212</v>
       </c>
@@ -12447,7 +12450,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A487" s="5" t="s">
         <v>603</v>
       </c>
@@ -12470,7 +12473,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="D488" s="2" t="s">
@@ -12492,7 +12495,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E489" s="2" t="s">
         <v>568</v>
       </c>
@@ -12515,7 +12518,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E490" s="2" t="s">
         <v>572</v>
       </c>
@@ -12532,7 +12535,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E491" s="2" t="s">
         <v>573</v>
       </c>
@@ -12550,7 +12553,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B492" s="3" t="s">
         <v>565</v>
       </c>
@@ -12573,7 +12576,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E493" s="2" t="s">
         <v>173</v>
       </c>
@@ -12596,7 +12599,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E494" s="2" t="s">
         <v>135</v>
       </c>
@@ -12613,7 +12616,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E495" s="2" t="s">
         <v>228</v>
       </c>
@@ -12631,7 +12634,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E496" s="2" t="s">
         <v>229</v>
       </c>
@@ -12654,7 +12657,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="497" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E497" s="2" t="s">
         <v>176</v>
       </c>
@@ -12671,7 +12674,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="498" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E498" s="2" t="s">
         <v>178</v>
       </c>
@@ -12685,7 +12688,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="499" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B499" s="3" t="s">
         <v>582</v>
       </c>
@@ -12708,7 +12711,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="500" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E500" s="2" t="s">
         <v>173</v>
       </c>
@@ -12731,7 +12734,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="501" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E501" s="2" t="s">
         <v>135</v>
       </c>
@@ -12748,7 +12751,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="502" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E502" s="2" t="s">
         <v>228</v>
       </c>
@@ -12769,7 +12772,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="503" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E503" s="2" t="s">
         <v>229</v>
       </c>
@@ -12792,7 +12795,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="504" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E504" s="2" t="s">
         <v>176</v>
       </c>
@@ -12809,7 +12812,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="505" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E505" s="2" t="s">
         <v>178</v>
       </c>
@@ -12823,7 +12826,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="506" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B506" s="3" t="s">
         <v>478</v>
       </c>
@@ -12846,7 +12849,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="507" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E507" s="2" t="s">
         <v>173</v>
       </c>
@@ -12869,7 +12872,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="508" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E508" s="2" t="s">
         <v>135</v>
       </c>
@@ -12886,7 +12889,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="509" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E509" s="2" t="s">
         <v>228</v>
       </c>
@@ -12907,7 +12910,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="510" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E510" s="2" t="s">
         <v>229</v>
       </c>
@@ -12930,7 +12933,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="511" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E511" s="2" t="s">
         <v>176</v>
       </c>
@@ -12950,7 +12953,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="512" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E512" s="2" t="s">
         <v>178</v>
       </c>
@@ -12964,7 +12967,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="513" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B513" s="3" t="s">
         <v>618</v>
       </c>
@@ -12991,7 +12994,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E514" s="2" t="s">
         <v>211</v>
       </c>
@@ -13012,7 +13015,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E515" s="2" t="s">
         <v>212</v>
       </c>
@@ -13035,7 +13038,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="516" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A516" s="5" t="s">
         <v>587</v>
       </c>
@@ -13061,7 +13064,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E517" s="2" t="s">
         <v>214</v>
       </c>
@@ -13084,7 +13087,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E518" s="2" t="s">
         <v>142</v>
       </c>
@@ -13101,7 +13104,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E519" s="2" t="s">
         <v>314</v>
       </c>
@@ -13118,7 +13121,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E520" s="2" t="s">
         <v>316</v>
       </c>
@@ -13141,7 +13144,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="521" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B521" s="3" t="s">
         <v>498</v>
       </c>
@@ -13164,7 +13167,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E522" s="2" t="s">
         <v>214</v>
       </c>
@@ -13187,7 +13190,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E523" s="2" t="s">
         <v>142</v>
       </c>
@@ -13204,7 +13207,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E524" s="2" t="s">
         <v>314</v>
       </c>
@@ -13221,7 +13224,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E525" s="2" t="s">
         <v>316</v>
       </c>
@@ -13244,7 +13247,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="526" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B526" s="3" t="s">
         <v>499</v>
       </c>
@@ -13267,7 +13270,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E527" s="2" t="s">
         <v>214</v>
       </c>
@@ -13290,7 +13293,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E528" s="2" t="s">
         <v>142</v>
       </c>
@@ -13307,7 +13310,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="529" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E529" s="2" t="s">
         <v>314</v>
       </c>
@@ -13324,7 +13327,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="530" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E530" s="2" t="s">
         <v>316</v>
       </c>
@@ -13347,7 +13350,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="531" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B531" s="3" t="s">
         <v>500</v>
       </c>
@@ -13370,7 +13373,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="532" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E532" s="2" t="s">
         <v>214</v>
       </c>
@@ -13393,7 +13396,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="533" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E533" s="2" t="s">
         <v>142</v>
       </c>
@@ -13410,7 +13413,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="534" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E534" s="2" t="s">
         <v>176</v>
       </c>
@@ -13427,7 +13430,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="535" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E535" s="2" t="s">
         <v>314</v>
       </c>
@@ -13441,7 +13444,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="536" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E536" s="2" t="s">
         <v>316</v>
       </c>
@@ -13464,7 +13467,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="537" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B537" s="3" t="s">
         <v>501</v>
       </c>
@@ -13487,7 +13490,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="538" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E538" s="2" t="s">
         <v>214</v>
       </c>
@@ -13510,7 +13513,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="539" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E539" s="2" t="s">
         <v>142</v>
       </c>
@@ -13527,7 +13530,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="540" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E540" s="2" t="s">
         <v>176</v>
       </c>
@@ -13544,7 +13547,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="541" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B541" s="3" t="s">
         <v>502</v>
       </c>
@@ -13567,7 +13570,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="542" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E542" s="2" t="s">
         <v>214</v>
       </c>
@@ -13590,7 +13593,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="543" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E543" s="2" t="s">
         <v>142</v>
       </c>
@@ -13607,7 +13610,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="544" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E544" s="2" t="s">
         <v>176</v>
       </c>
@@ -13624,7 +13627,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B545" s="3" t="s">
         <v>510</v>
       </c>
@@ -13635,7 +13638,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G546" s="2" t="s">
         <v>98</v>
       </c>
@@ -13643,7 +13646,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G547" s="2" t="s">
         <v>98</v>
       </c>
@@ -13651,7 +13654,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="548" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="A548" s="5" t="s">
         <v>541</v>
       </c>
@@ -13677,7 +13680,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E549" s="2" t="s">
         <v>173</v>
       </c>
@@ -13700,7 +13703,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E550" s="2" t="s">
         <v>176</v>
       </c>
@@ -13717,7 +13720,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E551" s="2" t="s">
         <v>178</v>
       </c>
@@ -13731,7 +13734,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="552" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B552" s="3" t="s">
         <v>505</v>
       </c>
@@ -13754,7 +13757,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E553" s="2" t="s">
         <v>173</v>
       </c>
@@ -13777,7 +13780,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E554" s="2" t="s">
         <v>228</v>
       </c>
@@ -13798,7 +13801,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E555" s="2" t="s">
         <v>229</v>
       </c>
@@ -13821,7 +13824,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E556" s="2" t="s">
         <v>314</v>
       </c>
@@ -13838,7 +13841,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="557" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" ht="26" x14ac:dyDescent="0.3">
       <c r="B557" s="3" t="s">
         <v>504</v>
       </c>
@@ -13861,7 +13864,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E558" s="2" t="s">
         <v>173</v>
       </c>
@@ -13884,7 +13887,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E559" s="2" t="s">
         <v>228</v>
       </c>
@@ -13905,7 +13908,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E560" s="2" t="s">
         <v>229</v>
       </c>
@@ -13928,7 +13931,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E561" s="2" t="s">
         <v>176</v>
       </c>
@@ -13945,7 +13948,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E562" s="2" t="s">
         <v>178</v>
       </c>
@@ -13962,7 +13965,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A563" s="5" t="s">
         <v>542</v>
       </c>
@@ -13985,7 +13988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E564" s="2" t="s">
         <v>191</v>
       </c>
@@ -14005,7 +14008,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E565" s="2" t="s">
         <v>195</v>
       </c>
@@ -14019,7 +14022,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E566" s="2" t="s">
         <v>197</v>
       </c>
@@ -14036,7 +14039,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E567" s="2" t="s">
         <v>198</v>
       </c>
@@ -14050,7 +14053,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E568" s="2" t="s">
         <v>430</v>
       </c>
@@ -14064,7 +14067,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="569" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:11" ht="26" x14ac:dyDescent="0.3">
       <c r="B569" s="3" t="s">
         <v>507</v>
       </c>
@@ -14084,7 +14087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E570" s="2" t="s">
         <v>214</v>
       </c>
@@ -14104,7 +14107,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E571" s="2" t="s">
         <v>149</v>
       </c>
@@ -14122,7 +14125,7 @@
         <v>OMOP Comorbidity Condition</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E572" s="2" t="s">
         <v>150</v>
       </c>
@@ -14142,7 +14145,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E573" s="2" t="s">
         <v>176</v>
       </c>
@@ -14156,7 +14159,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E574" s="2" t="s">
         <v>178</v>
       </c>
@@ -14170,7 +14173,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="575" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:11" ht="26" x14ac:dyDescent="0.3">
       <c r="B575" s="3" t="s">
         <v>515</v>
       </c>
@@ -14184,7 +14187,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G576" s="12" t="s">
         <v>110</v>
       </c>
@@ -14192,13 +14195,13 @@
         <v>116</v>
       </c>
     </row>
-    <row r="577" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H577" s="6"/>
     </row>
-    <row r="578" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H578" s="6"/>
     </row>
-    <row r="581" spans="2:8" ht="27" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:8" ht="26" x14ac:dyDescent="0.3">
       <c r="B581" s="3" t="s">
         <v>508</v>
       </c>
@@ -14209,7 +14212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="582" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G582" s="12" t="s">
         <v>0</v>
       </c>
@@ -14217,7 +14220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="583" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G583" s="12" t="s">
         <v>0</v>
       </c>
@@ -14225,7 +14228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="584" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G584" s="12" t="s">
         <v>0</v>
       </c>
@@ -14233,7 +14236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="585" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G585" s="12" t="s">
         <v>0</v>
       </c>
@@ -14241,7 +14244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="586" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G586" s="12" t="s">
         <v>0</v>
       </c>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CD8083-A6BE-47F8-B305-AE6D1CB9D6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD64129-D1F8-4DAE-921D-C11AC951EB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformation Model" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3414" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3384" uniqueCount="621">
   <si>
     <t>Sample Registration</t>
   </si>
@@ -2333,25 +2333,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9C41B9-3FB6-4282-940B-7420BB7A8AED}">
-  <dimension ref="A1:L586"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L580"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="47.453125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.81640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.54296875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="43.81640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.81640625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="25.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="47.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="43.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.85546875" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>121</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D3" s="2" t="s">
         <v>130</v>
       </c>
@@ -2443,7 +2443,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D4" s="2" t="s">
         <v>136</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>138</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
         <v>574</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D7" s="2" t="s">
         <v>140</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
         <v>140</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D9" s="2" t="s">
         <v>143</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D10" s="2" t="s">
         <v>145</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D11" s="2" t="s">
         <v>179</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D12" s="2" t="s">
         <v>130</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
         <v>145</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D14" s="2" t="s">
         <v>284</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D15" s="2" t="s">
         <v>143</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
         <v>140</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D17" s="2" t="s">
         <v>574</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D18" s="2" t="s">
         <v>138</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
         <v>136</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D20" s="2" t="s">
         <v>140</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>OMOP Specimen</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
         <v>140</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>OMOP Primary Dx Episode</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
         <v>140</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
         <v>140</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
         <v>140</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
         <v>140</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
         <v>140</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
         <v>140</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>534</v>
       </c>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
         <v>543</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
         <v>543</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D31" s="2" t="s">
         <v>543</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D32" s="2" t="s">
         <v>543</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>4255047</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
         <v>543</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3" t="s">
         <v>605</v>
@@ -3169,7 +3169,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D35" s="2" t="s">
         <v>543</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D36" s="2" t="s">
         <v>543</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D37" s="2" t="s">
         <v>543</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="D38" s="2" t="s">
         <v>594</v>
@@ -3244,7 +3244,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3" t="s">
         <v>433</v>
@@ -3268,7 +3268,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2" t="s">
         <v>156</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C41" s="2" t="s">
         <v>157</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C42" s="2" t="s">
         <v>161</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C43" s="2" t="s">
         <v>163</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C44" s="2" t="s">
         <v>166</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C45" s="2" t="s">
         <v>169</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E46" s="2" t="s">
         <v>592</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E47" s="2" t="s">
         <v>593</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>434</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E49" s="2" t="s">
         <v>173</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C50" s="2" t="s">
         <v>175</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C51" s="2" t="s">
         <v>177</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
         <v>435</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C53" s="2" t="s">
         <v>181</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C54" s="2" t="s">
         <v>184</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C55" s="2" t="s">
         <v>186</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
         <v>481</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E57" s="2" t="s">
         <v>188</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E58" s="2" t="s">
         <v>188</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>535</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="D60" s="2" t="s">
         <v>145</v>
@@ -3675,7 +3675,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="s">
         <v>190</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C62" s="2" t="s">
         <v>194</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C63" s="2" t="s">
         <v>196</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E64" s="2" t="s">
         <v>198</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
         <v>437</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E66" s="2" t="s">
         <v>201</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E67" s="2" t="s">
         <v>205</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E68" s="2" t="s">
         <v>206</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E69" s="2" t="s">
         <v>207</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E70" s="2" t="s">
         <v>208</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E71" s="2" t="s">
         <v>209</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="72" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
         <v>485</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E73" s="2" t="s">
         <v>211</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E74" s="2" t="s">
         <v>212</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="75" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
         <v>439</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E76" s="2" t="s">
         <v>214</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E77" s="2" t="s">
         <v>142</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E78" s="2" t="s">
         <v>149</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E79" s="2" t="s">
         <v>150</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C80" s="2" t="s">
         <v>217</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C81" s="2" t="s">
         <v>218</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
         <v>440</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E83" s="2" t="s">
         <v>214</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E84" s="2" t="s">
         <v>142</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E85" s="2" t="s">
         <v>149</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E86" s="2" t="s">
         <v>150</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C87" s="2" t="s">
         <v>221</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C88" s="2" t="s">
         <v>222</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B89" s="3" t="s">
         <v>441</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E90" s="2" t="s">
         <v>173</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E91" s="2" t="s">
         <v>135</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C92" s="2" t="s">
         <v>226</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C93" s="2" t="s">
         <v>227</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E94" s="2" t="s">
         <v>228</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E95" s="2" t="s">
         <v>229</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="96" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
         <v>431</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E97" s="2" t="s">
         <v>214</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E98" s="2" t="s">
         <v>142</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E99" s="2" t="s">
         <v>149</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E100" s="2" t="s">
         <v>150</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C101" s="2" t="s">
         <v>233</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C102" s="2" t="s">
         <v>234</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="103" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B103" s="3" t="s">
         <v>432</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E104" s="2" t="s">
         <v>214</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E105" s="2" t="s">
         <v>142</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E106" s="2" t="s">
         <v>149</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E107" s="2" t="s">
         <v>150</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C108" s="2" t="s">
         <v>235</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C109" s="2" t="s">
         <v>236</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B110" s="3" t="s">
         <v>438</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E111" s="2" t="s">
         <v>214</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E112" s="2" t="s">
         <v>142</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E113" s="2" t="s">
         <v>149</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E114" s="2" t="s">
         <v>150</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C115" s="2" t="s">
         <v>237</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C116" s="2" t="s">
         <v>238</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="117" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B117" s="3" t="s">
         <v>442</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C118" s="2" t="s">
         <v>230</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C119" s="2" t="s">
         <v>231</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E120" s="2" t="s">
         <v>142</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E121" s="2" t="s">
         <v>149</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E122" s="2" t="s">
         <v>150</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C123" s="2" t="s">
         <v>239</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C124" s="2" t="s">
         <v>240</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="125" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B125" s="3" t="s">
         <v>443</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E126" s="2" t="s">
         <v>214</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E127" s="2" t="s">
         <v>142</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E128" s="2" t="s">
         <v>149</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E129" s="2" t="s">
         <v>150</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C130" s="2" t="s">
         <v>243</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C131" s="2" t="s">
         <v>244</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B132" s="3" t="s">
         <v>444</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E133" s="2" t="s">
         <v>214</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E134" s="2" t="s">
         <v>142</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E135" s="2" t="s">
         <v>149</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E136" s="2" t="s">
         <v>150</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C137" s="2" t="s">
         <v>245</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C138" s="2" t="s">
         <v>246</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="139" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B139" s="3" t="s">
         <v>445</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E140" s="2" t="s">
         <v>214</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E141" s="2" t="s">
         <v>142</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E142" s="2" t="s">
         <v>149</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E143" s="2" t="s">
         <v>150</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C144" s="2" t="s">
         <v>247</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C145" s="2" t="s">
         <v>248</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B146" s="3" t="s">
         <v>446</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C147" s="2" t="s">
         <v>241</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C148" s="2" t="s">
         <v>242</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E149" s="2" t="s">
         <v>142</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E150" s="2" t="s">
         <v>149</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E151" s="2" t="s">
         <v>150</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C152" s="2" t="s">
         <v>249</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C153" s="2" t="s">
         <v>509</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>536</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D155" s="2" t="s">
         <v>543</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D156" s="2" t="s">
         <v>543</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="D157" s="2" t="s">
@@ -5651,7 +5651,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E158" s="2" t="s">
         <v>201</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E159" s="2" t="s">
         <v>205</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E160" s="2" t="s">
         <v>206</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C161" s="2" t="s">
         <v>252</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C162" s="2" t="s">
         <v>253</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C163" s="2" t="s">
         <v>254</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="164" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B164" s="3" t="s">
         <v>448</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E165" s="2" t="s">
         <v>173</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E166" s="2" t="s">
         <v>135</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E167" s="2" t="s">
         <v>228</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E168" s="2" t="s">
         <v>229</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C169" s="2" t="s">
         <v>266</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C170" s="2" t="s">
         <v>267</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="171" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B171" s="3" t="s">
         <v>449</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E172" s="2" t="s">
         <v>173</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C173" s="2" t="s">
         <v>272</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C174" s="2" t="s">
         <v>273</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E175" s="2" t="s">
         <v>135</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E176" s="2" t="s">
         <v>228</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E177" s="2" t="s">
         <v>229</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C178" s="2" t="s">
         <v>274</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C179" s="2" t="s">
         <v>276</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
         <v>608</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E181" s="2" t="s">
         <v>256</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C182" s="2" t="s">
         <v>257</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E183" s="2" t="s">
         <v>259</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C184" s="2" t="s">
         <v>260</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C185" s="2" t="s">
         <v>262</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B186" s="3" t="s">
         <v>610</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E187" s="2" t="s">
         <v>211</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E188" s="2" t="s">
         <v>212</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
         <v>537</v>
       </c>
@@ -6299,7 +6299,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E190" s="2" t="s">
         <v>201</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E191" s="2" t="s">
         <v>205</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E192" s="2" t="s">
         <v>206</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E193" s="2" t="s">
         <v>208</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E194" s="2" t="s">
         <v>209</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="195" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B195" s="3" t="s">
         <v>486</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="196" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E196" s="2" t="s">
         <v>211</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="197" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E197" s="2" t="s">
         <v>212</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B198" s="3" t="s">
         <v>451</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C199" s="2" t="s">
         <v>280</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C200" s="2" t="s">
         <v>281</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="201" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E201" s="2" t="s">
         <v>259</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="202" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C202" s="2" t="s">
         <v>282</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B203" s="3" t="s">
         <v>484</v>
       </c>
@@ -6581,7 +6581,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="204" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E204" s="2" t="s">
         <v>211</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="205" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E205" s="2" t="s">
         <v>212</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B206" s="3" t="s">
         <v>452</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="207" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B207" s="2"/>
       <c r="D207" s="2" t="s">
         <v>284</v>
@@ -6670,7 +6670,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="208" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E208" s="2" t="s">
         <v>286</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E209" s="2" t="s">
         <v>289</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="C210" s="5" t="s">
         <v>291</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="211" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C211" s="2" t="s">
         <v>293</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="212" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C212" s="2" t="s">
         <v>295</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C213" s="2" t="s">
         <v>297</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C214" s="2" t="s">
         <v>299</v>
       </c>
@@ -6804,7 +6804,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B215" s="3" t="s">
         <v>483</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E216" s="2" t="s">
         <v>211</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E217" s="2" t="s">
         <v>212</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B218" s="3" t="s">
         <v>453</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E219" s="2" t="s">
         <v>286</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E220" s="2" t="s">
         <v>289</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="C221" s="5" t="s">
         <v>291</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C222" s="2" t="s">
         <v>293</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C223" s="2" t="s">
         <v>295</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C224" s="2" t="s">
         <v>297</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C225" s="2" t="s">
         <v>304</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B226" s="3" t="s">
         <v>487</v>
       </c>
@@ -7059,7 +7059,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E227" s="2" t="s">
         <v>211</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E228" s="2" t="s">
         <v>212</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B229" s="3" t="s">
         <v>482</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
         <v>538</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E231" s="2" t="s">
         <v>201</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E232" s="2" t="s">
         <v>205</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E233" s="2" t="s">
         <v>206</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E234" s="2" t="s">
         <v>208</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B235" s="3" t="s">
         <v>488</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E236" s="2" t="s">
         <v>211</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E237" s="2" t="s">
         <v>212</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B238" s="3" t="s">
         <v>455</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C239" s="2" t="s">
         <v>307</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C240" s="2" t="s">
         <v>308</v>
       </c>
@@ -7349,7 +7349,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="241" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E241" s="2" t="s">
         <v>259</v>
       </c>
@@ -7369,7 +7369,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="242" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C242" s="2" t="s">
         <v>309</v>
       </c>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="I242" s="10"/>
     </row>
-    <row r="243" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C243" s="2" t="s">
         <v>310</v>
       </c>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="I243" s="10"/>
     </row>
-    <row r="244" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B244" s="3" t="s">
         <v>489</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="245" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E245" s="2" t="s">
         <v>211</v>
       </c>
@@ -7453,7 +7453,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="246" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E246" s="2" t="s">
         <v>212</v>
       </c>
@@ -7476,7 +7476,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="247" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B247" s="3" t="s">
         <v>456</v>
       </c>
@@ -7499,7 +7499,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="248" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E248" s="2" t="s">
         <v>214</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="249" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E249" s="2" t="s">
         <v>142</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="250" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E250" s="2" t="s">
         <v>149</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="251" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E251" s="2" t="s">
         <v>150</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="252" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C252" s="2" t="s">
         <v>313</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="253" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C253" s="2" t="s">
         <v>315</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="254" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B254" s="3" t="s">
         <v>457</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="255" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E255" s="2" t="s">
         <v>214</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="256" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E256" s="2" t="s">
         <v>142</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="257" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E257" s="2" t="s">
         <v>149</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="258" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E258" s="2" t="s">
         <v>150</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="259" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C259" s="2" t="s">
         <v>313</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="260" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B260" s="3" t="s">
         <v>458</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="261" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E261" s="2" t="s">
         <v>173</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="262" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E262" s="2" t="s">
         <v>135</v>
       </c>
@@ -7826,7 +7826,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="263" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E263" s="2" t="s">
         <v>228</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="264" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E264" s="2" t="s">
         <v>229</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="265" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C265" s="2" t="s">
         <v>323</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="266" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C266" s="2" t="s">
         <v>324</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="267" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B267" s="3" t="s">
         <v>459</v>
       </c>
@@ -7930,7 +7930,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="268" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E268" s="2" t="s">
         <v>256</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="269" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E269" s="2" t="s">
         <v>259</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="270" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E270" s="2" t="s">
         <v>261</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="271" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E271" s="2" t="s">
         <v>263</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="272" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B272" s="3" t="s">
         <v>490</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E273" s="2" t="s">
         <v>211</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E274" s="2" t="s">
         <v>212</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
         <v>539</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D276" s="2" t="s">
         <v>136</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E277" s="2" t="s">
         <v>201</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E278" s="2" t="s">
         <v>205</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E279" s="2" t="s">
         <v>206</v>
       </c>
@@ -8179,7 +8179,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E280" s="2" t="s">
         <v>208</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B281" s="3" t="s">
         <v>491</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E282" s="2" t="s">
         <v>211</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E283" s="2" t="s">
         <v>212</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B284" s="3" t="s">
         <v>461</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C285" s="2" t="s">
         <v>329</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="C286" s="5" t="s">
         <v>330</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E287" s="2" t="s">
         <v>259</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B288" s="3" t="s">
         <v>492</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="289" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E289" s="2" t="s">
         <v>211</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="290" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E290" s="2" t="s">
         <v>212</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="291" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B291" s="3" t="s">
         <v>462</v>
       </c>
@@ -8448,7 +8448,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="292" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E292" s="2" t="s">
         <v>214</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="293" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E293" s="2" t="s">
         <v>142</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="294" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E294" s="2" t="s">
         <v>149</v>
       </c>
@@ -8507,7 +8507,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="295" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E295" s="2" t="s">
         <v>150</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="296" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C296" s="2" t="s">
         <v>334</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="297" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E297" s="2" t="s">
         <v>316</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="298" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B298" s="3" t="s">
         <v>463</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="299" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E299" s="2" t="s">
         <v>214</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="300" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E300" s="2" t="s">
         <v>142</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="301" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E301" s="2" t="s">
         <v>149</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="302" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E302" s="2" t="s">
         <v>150</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="303" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C303" s="2" t="s">
         <v>339</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="304" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E304" s="2" t="s">
         <v>316</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="305" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B305" s="3" t="s">
         <v>464</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="306" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E306" s="2" t="s">
         <v>214</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="307" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E307" s="2" t="s">
         <v>142</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="308" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E308" s="2" t="s">
         <v>149</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="309" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E309" s="2" t="s">
         <v>150</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="310" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C310" s="2" t="s">
         <v>339</v>
       </c>
@@ -8846,7 +8846,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="311" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E311" s="2" t="s">
         <v>316</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="312" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B312" s="3" t="s">
         <v>465</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="313" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E313" s="2" t="s">
         <v>173</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="314" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E314" s="2" t="s">
         <v>135</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="315" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E315" s="2" t="s">
         <v>228</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="316" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E316" s="2" t="s">
         <v>229</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="317" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C317" s="2" t="s">
         <v>342</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="318" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C318" s="2" t="s">
         <v>343</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="319" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B319" s="3" t="s">
         <v>466</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="320" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E320" s="2" t="s">
         <v>173</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="321" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E321" s="2" t="s">
         <v>135</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="322" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E322" s="2" t="s">
         <v>228</v>
       </c>
@@ -9106,7 +9106,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="323" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E323" s="2" t="s">
         <v>229</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="324" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C324" s="2" t="s">
         <v>346</v>
       </c>
@@ -9149,7 +9149,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="325" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C325" s="2" t="s">
         <v>347</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="326" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B326" s="3" t="s">
         <v>467</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="327" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E327" s="2" t="s">
         <v>173</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="328" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E328" s="2" t="s">
         <v>135</v>
       </c>
@@ -9232,7 +9232,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="329" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E329" s="2" t="s">
         <v>228</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="330" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E330" s="2" t="s">
         <v>229</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="331" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C331" s="2" t="s">
         <v>350</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="332" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C332" s="2" t="s">
         <v>351</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="333" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B333" s="3" t="s">
         <v>468</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="334" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E334" s="2" t="s">
         <v>173</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="335" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E335" s="2" t="s">
         <v>135</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="336" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E336" s="2" t="s">
         <v>228</v>
       </c>
@@ -9400,7 +9400,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="337" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E337" s="2" t="s">
         <v>229</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="338" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C338" s="2" t="s">
         <v>354</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="339" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C339" s="2" t="s">
         <v>355</v>
       </c>
@@ -9460,7 +9460,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="340" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B340" s="3" t="s">
         <v>472</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="341" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E341" s="2" t="s">
         <v>173</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="342" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E342" s="2" t="s">
         <v>135</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="343" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E343" s="2" t="s">
         <v>228</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="344" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E344" s="2" t="s">
         <v>229</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="345" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C345" s="2" t="s">
         <v>372</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="346" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C346" s="2" t="s">
         <v>373</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="347" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B347" s="3" t="s">
         <v>473</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="348" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E348" s="2" t="s">
         <v>173</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="349" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E349" s="2" t="s">
         <v>135</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="350" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E350" s="2" t="s">
         <v>228</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="351" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E351" s="2" t="s">
         <v>229</v>
       </c>
@@ -9717,7 +9717,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="352" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C352" s="2" t="s">
         <v>376</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="353" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C353" s="2" t="s">
         <v>377</v>
       </c>
@@ -9754,7 +9754,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="354" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B354" s="3" t="s">
         <v>469</v>
       </c>
@@ -9777,7 +9777,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="355" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E355" s="2" t="s">
         <v>173</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="356" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E356" s="2" t="s">
         <v>135</v>
       </c>
@@ -9820,7 +9820,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="357" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E357" s="2" t="s">
         <v>228</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="358" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E358" s="2" t="s">
         <v>229</v>
       </c>
@@ -9864,7 +9864,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="359" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C359" s="2" t="s">
         <v>358</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="360" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C360" s="2" t="s">
         <v>359</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="361" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E361" s="2" t="s">
         <v>275</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="362" spans="2:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B362" s="3" t="s">
         <v>470</v>
       </c>
@@ -9950,7 +9950,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="363" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E363" s="2" t="s">
         <v>173</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="364" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E364" s="2" t="s">
         <v>135</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="365" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E365" s="2" t="s">
         <v>228</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="366" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E366" s="2" t="s">
         <v>229</v>
       </c>
@@ -10037,7 +10037,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="367" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C367" s="2" t="s">
         <v>362</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="368" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C368" s="2" t="s">
         <v>363</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E369" s="2" t="s">
         <v>275</v>
       </c>
@@ -10100,7 +10100,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="39" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="B370" s="3" t="s">
         <v>471</v>
       </c>
@@ -10123,7 +10123,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E371" s="2" t="s">
         <v>173</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E372" s="2" t="s">
         <v>135</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E373" s="2" t="s">
         <v>228</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E374" s="2" t="s">
         <v>229</v>
       </c>
@@ -10210,7 +10210,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C375" s="2" t="s">
         <v>366</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C376" s="2" t="s">
         <v>367</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E377" s="2" t="s">
         <v>275</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="s">
         <v>540</v>
       </c>
@@ -10299,7 +10299,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="D379" s="2" t="s">
@@ -10318,7 +10318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="E380" s="2" t="s">
@@ -10343,7 +10343,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C381" s="2" t="s">
         <v>379</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C382" s="2" t="s">
         <v>381</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C383" s="2" t="s">
         <v>383</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B384" s="3" t="s">
         <v>475</v>
       </c>
@@ -10423,7 +10423,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="385" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E385" s="2" t="s">
         <v>173</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="386" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E386" s="2" t="s">
         <v>135</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="387" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E387" s="2" t="s">
         <v>228</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="388" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E388" s="2" t="s">
         <v>229</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="389" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C389" s="2" t="s">
         <v>387</v>
       </c>
@@ -10530,7 +10530,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="390" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C390" s="2" t="s">
         <v>388</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="391" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B391" s="3" t="s">
         <v>476</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="392" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E392" s="2" t="s">
         <v>173</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E393" s="2" t="s">
         <v>135</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="394" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E394" s="2" t="s">
         <v>228</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="395" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E395" s="2" t="s">
         <v>229</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="396" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C396" s="2" t="s">
         <v>392</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="397" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C397" s="2" t="s">
         <v>392</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="398" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C398" s="2" t="s">
         <v>393</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="399" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C399" s="2" t="s">
         <v>393</v>
       </c>
@@ -10725,7 +10725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="400" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B400" s="3" t="s">
         <v>477</v>
       </c>
@@ -10748,7 +10748,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="401" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E401" s="2" t="s">
         <v>173</v>
       </c>
@@ -10771,7 +10771,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="402" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E402" s="2" t="s">
         <v>135</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="403" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E403" s="2" t="s">
         <v>228</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="404" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E404" s="2" t="s">
         <v>229</v>
       </c>
@@ -10832,7 +10832,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="405" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C405" s="2" t="s">
         <v>396</v>
       </c>
@@ -10852,7 +10852,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="406" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C406" s="2" t="s">
         <v>397</v>
       </c>
@@ -10869,7 +10869,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="407" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B407" s="3" t="s">
         <v>496</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="408" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E408" s="2" t="s">
         <v>173</v>
       </c>
@@ -10915,7 +10915,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="409" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E409" s="2" t="s">
         <v>135</v>
       </c>
@@ -10932,7 +10932,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="410" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E410" s="2" t="s">
         <v>228</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="411" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E411" s="2" t="s">
         <v>229</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="412" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C412" s="2" t="s">
         <v>400</v>
       </c>
@@ -10996,7 +10996,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="413" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C413" s="2" t="s">
         <v>400</v>
       </c>
@@ -11013,7 +11013,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="414" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B414" s="3" t="s">
         <v>495</v>
       </c>
@@ -11036,7 +11036,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="415" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E415" s="2" t="s">
         <v>173</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="416" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E416" s="2" t="s">
         <v>135</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E417" s="2" t="s">
         <v>228</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E418" s="2" t="s">
         <v>229</v>
       </c>
@@ -11120,7 +11120,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C419" s="2" t="s">
         <v>403</v>
       </c>
@@ -11140,7 +11140,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C420" s="2" t="s">
         <v>403</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B421" s="3" t="s">
         <v>493</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E422" s="2" t="s">
         <v>211</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E423" s="2" t="s">
         <v>212</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B424" s="3" t="s">
         <v>494</v>
       </c>
@@ -11255,7 +11255,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E425" s="2" t="s">
         <v>211</v>
       </c>
@@ -11276,7 +11276,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E426" s="2" t="s">
         <v>212</v>
       </c>
@@ -11299,7 +11299,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B427" s="3" t="s">
         <v>479</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="G428" s="2" t="s">
         <v>19</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G429" s="2" t="s">
         <v>19</v>
       </c>
@@ -11326,7 +11326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="G430" s="2" t="s">
         <v>19</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="s">
         <v>615</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="D432" s="2" t="s">
@@ -11379,7 +11379,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="433" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E433" s="2" t="s">
         <v>568</v>
       </c>
@@ -11402,7 +11402,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="434" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E434" s="2" t="s">
         <v>572</v>
       </c>
@@ -11419,7 +11419,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="435" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E435" s="2" t="s">
         <v>573</v>
       </c>
@@ -11437,7 +11437,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="436" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B436" s="3" t="s">
         <v>565</v>
       </c>
@@ -11460,7 +11460,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="437" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E437" s="2" t="s">
         <v>173</v>
       </c>
@@ -11483,7 +11483,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="438" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E438" s="2" t="s">
         <v>135</v>
       </c>
@@ -11493,14 +11493,14 @@
       <c r="G438" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H438" s="8" t="s">
-        <v>92</v>
+      <c r="H438" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="K438" s="2" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="439" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E439" s="2" t="s">
         <v>228</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="440" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E440" s="2" t="s">
         <v>229</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="441" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E441" s="2" t="s">
         <v>176</v>
       </c>
@@ -11558,7 +11558,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="442" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E442" s="2" t="s">
         <v>178</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="443" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B443" s="3" t="s">
         <v>582</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="444" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E444" s="2" t="s">
         <v>173</v>
       </c>
@@ -11618,73 +11618,73 @@
         <v>581</v>
       </c>
     </row>
-    <row r="445" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E445" s="2" t="s">
-        <v>135</v>
+        <v>228</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H445" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K445" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="446" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E446" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F446" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G446" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H446" s="3" t="s">
+      <c r="H445" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I446" s="3" t="str">
+      <c r="I445" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-      <c r="K446" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="447" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K445" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="446" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E446" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F446" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G446" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H446" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I446" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J446" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L446" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="447" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E447" s="2" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G447" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H447" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I447" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="J447" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L447" s="2" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="448" spans="2:12" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="H447" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K447" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="448" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E448" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F448" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>90</v>
@@ -11692,936 +11692,946 @@
       <c r="H448" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="K448" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="449" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B449" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="E449" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F449" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H449" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="450" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B450" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="D450" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="H449" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K449" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E450" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F450" s="2" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G450" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H450" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I450" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J450" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L450" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E451" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F451" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G451" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H450" s="3" t="s">
+      <c r="H451" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K450" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E451" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F451" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G451" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H451" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I451" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J451" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L451" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I451" s="3" t="str">
+        <f>$B$431</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K451" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E452" s="2" t="s">
-        <v>135</v>
+        <v>229</v>
       </c>
       <c r="F452" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G452" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H452" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K452" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="H452" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I452" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J452" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L452" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E453" s="2" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H453" s="3" t="s">
+      <c r="H453" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J453" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K453" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E454" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F454" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G454" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H454" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="455" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B455" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="G455" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H455" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="456" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A456" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D456" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E456" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F456" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="G456" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H456" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I453" s="3" t="str">
+    </row>
+    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A457" s="2"/>
+      <c r="B457" s="2"/>
+      <c r="D457" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E457" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F457" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G457" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H457" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K457" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E458" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F458" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G458" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H458" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I458" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="J458" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L458" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E459" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F459" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G459" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H459" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K459" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E460" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F460" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G460" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H460" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I460" s="8"/>
+      <c r="K460" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="461" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B461" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D461" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E461" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F461" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G461" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H461" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K461" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E462" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F462" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G462" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H462" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I462" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="J462" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L462" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E463" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F463" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G463" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H463" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K463" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E464" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F464" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G464" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H464" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I464" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-      <c r="K453" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E454" s="2" t="s">
+    </row>
+    <row r="465" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E465" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F454" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G454" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H454" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I454" s="3" t="s">
+      <c r="F465" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G465" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H465" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I465" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J454" s="2" t="s">
+      <c r="J465" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L454" s="2" t="s">
+      <c r="L465" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E455" s="2" t="s">
+    <row r="466" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E466" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F455" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G455" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H455" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="J455" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K455" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E456" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F456" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G456" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H456" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="457" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B457" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="G457" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H457" s="13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="458" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="A458" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B458" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D458" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E458" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F458" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G458" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H458" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A459" s="2"/>
-      <c r="B459" s="2"/>
-      <c r="D459" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E459" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F459" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G459" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H459" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K459" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E460" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F460" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G460" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H460" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I460" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="J460" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="L460" s="2" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E461" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F461" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G461" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H461" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K461" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E462" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F462" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G462" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H462" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="I462" s="8"/>
-      <c r="K462" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="463" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B463" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="D463" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E463" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F463" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G463" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H463" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K463" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E464" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F464" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G464" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H464" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I464" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="J464" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L464" s="2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="465" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E465" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F465" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G465" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H465" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K465" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="466" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E466" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F466" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H466" s="3" t="s">
+      <c r="H466" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K466" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="467" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E467" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F467" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G467" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H467" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="468" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B468" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D468" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E468" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F468" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G468" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H468" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I466" s="3" t="str">
+      <c r="K468" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="469" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E469" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F469" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G469" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H469" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I469" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="J469" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L469" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="470" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E470" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F470" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G470" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H470" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I470" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-    </row>
-    <row r="467" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E467" s="2" t="s">
+      <c r="K470" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="471" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E471" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F467" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G467" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H467" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I467" s="3" t="s">
+      <c r="F471" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G471" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H471" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I471" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J467" s="2" t="s">
+      <c r="J471" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L467" s="2" t="s">
+      <c r="L471" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="468" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E468" s="2" t="s">
+    <row r="472" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E472" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F468" s="2" t="s">
+      <c r="F472" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G468" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H468" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K468" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="469" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E469" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F469" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G469" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H469" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="470" spans="2:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B470" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="D470" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E470" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F470" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G470" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H470" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K470" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="471" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E471" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F471" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G471" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H471" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I471" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="J471" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L471" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="472" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E472" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F472" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="G472" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H472" s="6" t="s">
-        <v>95</v>
+      <c r="H472" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="K472" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="473" spans="2:12" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="473" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E473" s="2" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="F473" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G473" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H473" s="3" t="s">
+      <c r="H473" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="474" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B474" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D474" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E474" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F474" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G474" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H474" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I473" s="3" t="str">
+      <c r="K474" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="475" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E475" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F475" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G475" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H475" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I475" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J475" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L475" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="476" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E476" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F476" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G476" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H476" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I476" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-      <c r="K473" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="474" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E474" s="2" t="s">
+      <c r="K476" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="477" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E477" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F474" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G474" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H474" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I474" s="3" t="s">
+      <c r="F477" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G477" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H477" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I477" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J474" s="2" t="s">
+      <c r="J477" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L474" s="2" t="s">
+      <c r="L477" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="475" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E475" s="2" t="s">
+    <row r="478" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E478" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F475" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G475" s="2" t="s">
+      <c r="F478" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G478" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H475" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K475" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="476" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E476" s="2" t="s">
+      <c r="H478" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J478" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K478" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="479" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E479" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F476" s="2" t="s">
+      <c r="F479" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="G476" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H476" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="477" spans="2:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B477" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="D477" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E477" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F477" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G477" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H477" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K477" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="478" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E478" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F478" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G478" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H478" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I478" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J478" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L478" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="479" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E479" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F479" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="G479" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H479" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K479" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="480" spans="2:12" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="480" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B480" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D480" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="E480" s="2" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="F480" s="2" t="s">
         <v>148</v>
       </c>
       <c r="G480" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H480" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I480" s="5" t="str">
+        <f>$B$65</f>
+        <v>OMOP Primary Dx Episode</v>
+      </c>
+      <c r="K480" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E481" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F481" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G481" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H480" s="3" t="s">
+      <c r="H481" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I480" s="3" t="str">
+      <c r="I481" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-      <c r="K480" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E481" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F481" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G481" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H481" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I481" s="3" t="s">
+      <c r="K481" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E482" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F482" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G482" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H482" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I482" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J481" s="2" t="s">
+      <c r="J482" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L481" s="2" t="s">
+      <c r="L482" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E482" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F482" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G482" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H482" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="J482" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K482" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A483" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="B483" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D483" s="2" t="s">
+        <v>543</v>
+      </c>
       <c r="E483" s="2" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="F483" s="2" t="s">
-        <v>154</v>
+        <v>555</v>
       </c>
       <c r="G483" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H483" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="484" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B484" s="3" t="s">
-        <v>617</v>
-      </c>
+      <c r="H483" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A484" s="2"/>
+      <c r="B484" s="2"/>
       <c r="D484" s="2" t="s">
-        <v>210</v>
+        <v>574</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>200</v>
+        <v>566</v>
       </c>
       <c r="F484" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G484" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H484" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K484" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E485" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F485" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G485" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H485" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I485" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="J485" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L485" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E486" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F486" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G486" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H486" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K486" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E487" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F487" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G487" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H487" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I487" s="8"/>
+      <c r="K487" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="488" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B488" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D488" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E488" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F488" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G488" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H488" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K488" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E489" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F489" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G489" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H489" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I489" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="J489" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L489" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E490" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F490" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G490" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H490" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K490" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E491" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F491" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G484" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H484" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I484" s="5" t="str">
-        <f>$B$65</f>
-        <v>OMOP Primary Dx Episode</v>
-      </c>
-      <c r="K484" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E485" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F485" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G485" s="2" t="s">
+      <c r="G491" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H485" s="3" t="s">
+      <c r="H491" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I485" s="3" t="str">
+      <c r="I491" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-      <c r="K485" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E486" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F486" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G486" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H486" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I486" s="3" t="s">
+    </row>
+    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E492" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F492" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G492" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H492" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I492" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J486" s="2" t="s">
+      <c r="J492" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L486" s="2" t="s">
+      <c r="L492" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="A487" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="B487" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D487" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E487" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F487" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G487" s="2" t="s">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E493" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F493" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G493" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H487" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A488" s="2"/>
-      <c r="B488" s="2"/>
-      <c r="D488" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E488" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F488" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G488" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H488" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K488" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E489" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F489" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G489" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H489" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I489" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="J489" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="L489" s="2" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E490" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F490" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G490" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H490" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K490" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E491" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F491" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G491" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H491" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="I491" s="8"/>
-      <c r="K491" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="492" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B492" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="D492" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E492" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F492" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G492" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H492" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K492" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E493" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F493" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G493" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H493" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I493" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="J493" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L493" s="2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H493" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K493" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E494" s="2" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="F494" s="2" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="G494" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H494" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K494" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H494" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="495" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B495" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D495" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="E495" s="2" t="s">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="F495" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G495" s="2" t="s">
         <v>90</v>
@@ -12629,688 +12639,696 @@
       <c r="H495" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I495" s="3" t="str">
+      <c r="K495" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E496" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F496" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G496" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H496" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I496" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="J496" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L496" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E497" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F497" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G497" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H497" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I497" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-    </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E496" s="2" t="s">
+      <c r="K497" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E498" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F496" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G496" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H496" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I496" s="3" t="s">
+      <c r="F498" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G498" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H498" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I498" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J496" s="2" t="s">
+      <c r="J498" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L496" s="2" t="s">
+      <c r="L498" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="497" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E497" s="2" t="s">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E499" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F497" s="2" t="s">
+      <c r="F499" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G497" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H497" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K497" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="498" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E498" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F498" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G498" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H498" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="499" spans="2:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B499" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E499" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F499" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="G499" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H499" s="3" t="s">
-        <v>91</v>
+      <c r="H499" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="K499" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="500" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E500" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F500" s="2" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="G500" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H500" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I500" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="J500" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L500" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="501" spans="2:12" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="H500" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="501" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B501" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D501" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="E501" s="2" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="F501" s="2" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="G501" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H501" s="6" t="s">
-        <v>95</v>
+      <c r="H501" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K501" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="502" spans="2:12" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E502" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F502" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G502" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H502" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I502" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J502" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L502" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E503" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F502" s="2" t="s">
+      <c r="F503" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G502" s="2" t="s">
+      <c r="G503" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H502" s="3" t="s">
+      <c r="H503" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I502" s="3" t="str">
+      <c r="I503" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-      <c r="K502" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="503" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E503" s="2" t="s">
+      <c r="K503" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E504" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F503" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G503" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H503" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I503" s="3" t="s">
+      <c r="F504" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G504" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H504" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I504" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J503" s="2" t="s">
+      <c r="J504" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L503" s="2" t="s">
+      <c r="L504" s="2" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="504" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E504" s="2" t="s">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E505" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F504" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G504" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H504" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K504" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="505" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E505" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="F505" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G505" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H505" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="506" spans="2:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B506" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="D506" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="H505" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J505" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K505" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E506" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F506" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G506" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H506" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K506" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="507" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H506" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="507" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B507" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D507" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="E507" s="2" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H507" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I507" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J507" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L507" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="508" spans="2:12" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="H507" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I507" s="3" t="str">
+        <f>$B$154</f>
+        <v>OMOP Treatment Episode</v>
+      </c>
+      <c r="K507" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E508" s="2" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="F508" s="2" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="G508" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H508" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K508" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="509" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E509" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F509" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G509" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H509" s="3" t="s">
+      <c r="H508" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I509" s="3" t="str">
+      <c r="I508" s="3" t="str">
         <f>$B$431</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-      <c r="K509" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="510" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K508" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E509" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F509" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G509" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H509" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I509" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J509" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L509" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="510" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A510" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="B510" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D510" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="E510" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="F510" s="2" t="s">
-        <v>132</v>
+        <v>590</v>
       </c>
       <c r="G510" s="2" t="s">
-        <v>133</v>
+        <v>9</v>
       </c>
       <c r="H510" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I510" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="J510" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L510" s="2" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="511" spans="2:12" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K510" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E511" s="2" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="F511" s="2" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="G511" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H511" s="6" t="s">
-        <v>97</v>
+        <v>133</v>
+      </c>
+      <c r="H511" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I511" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="J511" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K511" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="512" spans="2:12" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="L511" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E512" s="2" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="F512" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G512" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H512" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K512" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="513" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E513" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F513" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G512" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H512" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="513" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B513" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="D513" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E513" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F513" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="G513" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H513" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I513" s="3" t="str">
-        <f>$B$154</f>
-        <v>OMOP Treatment Episode</v>
+        <v>98</v>
+      </c>
+      <c r="H513" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="K513" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E514" s="2" t="s">
-        <v>211</v>
+        <v>316</v>
       </c>
       <c r="F514" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H514" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I514" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K514" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="H514" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I514" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="J514" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L514" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="515" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B515" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D515" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="E515" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F515" s="2" t="s">
-        <v>132</v>
+        <v>590</v>
       </c>
       <c r="G515" s="2" t="s">
-        <v>133</v>
+        <v>9</v>
       </c>
       <c r="H515" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I515" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="J515" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L515" s="2" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="516" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="A516" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="B516" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>140</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K515" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="516" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E516" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F516" s="2" t="s">
-        <v>590</v>
+        <v>132</v>
       </c>
       <c r="G516" s="2" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="H516" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K516" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="I516" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="J516" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L516" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="517" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E517" s="2" t="s">
-        <v>214</v>
+        <v>142</v>
       </c>
       <c r="F517" s="2" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="G517" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H517" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I517" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J517" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L517" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="H517" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K517" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="518" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E518" s="2" t="s">
-        <v>142</v>
+        <v>314</v>
       </c>
       <c r="F518" s="2" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="G518" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H518" s="11" t="s">
+      <c r="H518" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K518" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="519" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E519" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F519" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G519" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H519" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I519" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="J519" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L519" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="520" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B520" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E520" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F520" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G520" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H520" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K520" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="521" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E521" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F521" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G521" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H521" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I521" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J521" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L521" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="522" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E522" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F522" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G522" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H522" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="K518" s="2" t="s">
+      <c r="K522" s="2" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E519" s="2" t="s">
+    <row r="523" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E523" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F519" s="2" t="s">
+      <c r="F523" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="G519" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H519" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="K519" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E520" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F520" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G520" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H520" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I520" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="J520" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L520" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="521" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B521" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E521" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F521" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G521" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H521" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K521" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E522" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F522" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G522" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H522" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I522" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="J522" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L522" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E523" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F523" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="G523" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H523" s="11" t="s">
+      <c r="H523" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K523" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="524" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E524" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G524" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H524" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I524" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="J524" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L524" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="525" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B525" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D525" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E525" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F525" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G525" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H525" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K525" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="526" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E526" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F526" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G526" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H526" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I526" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J526" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L526" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="527" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E527" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F527" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G527" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H527" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="K523" s="2" t="s">
+      <c r="K527" s="2" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E524" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F524" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G524" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H524" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K524" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E525" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F525" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G525" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H525" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I525" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="J525" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L525" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="526" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B526" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E526" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F526" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G526" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H526" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K526" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E527" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F527" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G527" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H527" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I527" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="J527" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L527" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E528" s="2" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="F528" s="2" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="G528" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H528" s="11" t="s">
-        <v>99</v>
+      <c r="H528" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="K528" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="529" spans="2:12" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E529" s="2" t="s">
         <v>314</v>
       </c>
@@ -13321,13 +13339,10 @@
         <v>98</v>
       </c>
       <c r="H529" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K529" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="530" spans="2:12" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E530" s="2" t="s">
         <v>316</v>
       </c>
@@ -13341,18 +13356,18 @@
         <v>133</v>
       </c>
       <c r="I530" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="J530" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L530" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="531" spans="2:12" ht="26" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="531" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B531" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D531" s="2" t="s">
         <v>140</v>
@@ -13373,7 +13388,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="532" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E532" s="2" t="s">
         <v>214</v>
       </c>
@@ -13387,16 +13402,16 @@
         <v>133</v>
       </c>
       <c r="I532" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="J532" s="2" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="L532" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="533" spans="2:12" x14ac:dyDescent="0.3">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E533" s="2" t="s">
         <v>142</v>
       </c>
@@ -13413,7 +13428,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="534" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E534" s="2" t="s">
         <v>176</v>
       </c>
@@ -13424,193 +13439,169 @@
         <v>98</v>
       </c>
       <c r="H534" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K534" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="535" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B535" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D535" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="E535" s="2" t="s">
-        <v>314</v>
+        <v>213</v>
       </c>
       <c r="F535" s="2" t="s">
-        <v>154</v>
+        <v>590</v>
       </c>
       <c r="G535" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H535" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K535" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E536" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F536" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G536" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H536" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I536" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="J536" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L536" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E537" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F537" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G537" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H535" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="536" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E536" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F536" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G536" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H536" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I536" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="J536" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L536" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="537" spans="2:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B537" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="D537" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E537" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F537" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G537" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H537" s="5" t="s">
-        <v>2</v>
+      <c r="H537" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="K537" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="538" spans="2:12" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E538" s="2" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="F538" s="2" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G538" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H538" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I538" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="J538" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L538" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="539" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E539" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F539" s="2" t="s">
-        <v>183</v>
+        <v>98</v>
+      </c>
+      <c r="H538" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K538" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="539" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B539" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="G539" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H539" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K539" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="540" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E540" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F540" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="H539" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G540" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H540" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="K540" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="541" spans="2:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B541" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="D541" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E541" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F541" s="2" t="s">
+      <c r="H540" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G541" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H541" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="542" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A542" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="B542" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D542" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E542" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F542" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G541" s="2" t="s">
+      <c r="G542" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H541" s="5" t="s">
+      <c r="H542" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K541" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="542" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E542" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F542" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G542" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H542" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I542" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="J542" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L542" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="543" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K542" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E543" s="2" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="F543" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G543" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H543" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K543" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="544" spans="2:12" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="H543" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I543" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J543" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="L543" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E544" s="2" t="s">
         <v>176</v>
       </c>
@@ -13618,57 +13609,81 @@
         <v>151</v>
       </c>
       <c r="G544" s="2" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="H544" s="6" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K544" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B545" s="3" t="s">
-        <v>510</v>
+    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E545" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F545" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="G545" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H545" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="H545" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="546" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B546" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E546" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F546" s="2" t="s">
+        <v>590</v>
+      </c>
       <c r="G546" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H546" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="H546" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K546" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E547" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F547" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="G547" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H547" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="548" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="A548" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="B548" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D548" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="H547" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I547" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="J547" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L547" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E548" s="2" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="F548" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G548" s="2" t="s">
         <v>9</v>
@@ -13676,13 +13691,17 @@
       <c r="H548" s="5" t="s">
         <v>2</v>
       </c>
+      <c r="I548" s="3" t="str">
+        <f>$B$542</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
       <c r="K548" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E549" s="2" t="s">
-        <v>173</v>
+        <v>229</v>
       </c>
       <c r="F549" s="2" t="s">
         <v>132</v>
@@ -13694,162 +13713,168 @@
         <v>133</v>
       </c>
       <c r="I549" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="J549" s="2" t="s">
-        <v>224</v>
+        <v>152</v>
       </c>
       <c r="L549" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E550" s="2" t="s">
-        <v>176</v>
+        <v>314</v>
       </c>
       <c r="F550" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G550" s="2" t="s">
         <v>117</v>
       </c>
       <c r="H550" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K550" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B551" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D551" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="E551" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F551" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G551" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H551" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K551" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E552" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F552" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G552" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H552" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I552" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J552" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L552" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E553" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F553" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="G553" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H553" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I553" s="3" t="str">
+        <f>$B$542</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
+      <c r="K553" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E554" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F554" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G554" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H554" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I554" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J554" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L554" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E555" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F555" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G555" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H555" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I555" s="3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E556" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F551" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G551" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H551" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="552" spans="1:12" ht="26" x14ac:dyDescent="0.3">
-      <c r="B552" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D552" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E552" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F552" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G552" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H552" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K552" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E553" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F553" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G553" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H553" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I553" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="J553" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L553" s="2" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E554" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F554" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="G554" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H554" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I554" s="3" t="str">
-        <f>$B$548</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
-      <c r="K554" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E555" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F555" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G555" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H555" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I555" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="J555" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L555" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E556" s="2" t="s">
-        <v>314</v>
-      </c>
       <c r="F556" s="2" t="s">
-        <v>154</v>
+        <v>550</v>
       </c>
       <c r="G556" s="2" t="s">
         <v>117</v>
       </c>
       <c r="H556" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K556" s="2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="557" spans="1:12" ht="26" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A557" s="5" t="s">
+        <v>542</v>
+      </c>
       <c r="B557" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="F557" s="2" t="s">
         <v>590</v>
@@ -13860,123 +13885,95 @@
       <c r="H557" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K557" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E558" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F558" s="2" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="G558" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H558" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I558" s="3" t="s">
-        <v>426</v>
+        <v>110</v>
+      </c>
+      <c r="H558" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="J558" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L558" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+      <c r="K558" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E559" s="2" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="F559" s="2" t="s">
-        <v>591</v>
+        <v>154</v>
       </c>
       <c r="G559" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H559" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I559" s="3" t="str">
-        <f>$B$548</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
-      <c r="K559" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="H559" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E560" s="2" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="F560" s="2" t="s">
-        <v>132</v>
+        <v>613</v>
       </c>
       <c r="G560" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H560" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I560" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="J560" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L560" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="H560" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K560" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="561" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E561" s="2" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F561" s="2" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G561" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H561" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I561" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="H561" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="562" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E562" s="2" t="s">
-        <v>178</v>
+        <v>430</v>
       </c>
       <c r="F562" s="2" t="s">
-        <v>550</v>
+        <v>154</v>
       </c>
       <c r="G562" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H562" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="K562" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A563" s="5" t="s">
-        <v>542</v>
-      </c>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="563" spans="2:10" ht="27" x14ac:dyDescent="0.25">
       <c r="B563" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="F563" s="2" t="s">
         <v>590</v>
@@ -13988,60 +13985,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E564" s="2" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="F564" s="2" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="G564" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H564" s="6" t="s">
-        <v>114</v>
+        <v>133</v>
+      </c>
+      <c r="H564" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I564" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="J564" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="K564" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="565" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E565" s="2" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="F565" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G565" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H565" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H565" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="I565" s="3" t="str">
+        <f>$B$557</f>
+        <v>OMOP Comorbidity Condition</v>
+      </c>
+    </row>
+    <row r="566" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E566" s="2" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="F566" s="2" t="s">
-        <v>613</v>
+        <v>132</v>
       </c>
       <c r="G566" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H566" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="K566" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="H566" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I566" s="3">
+        <v>1147127</v>
+      </c>
+      <c r="J566" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="567" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E567" s="2" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F567" s="2" t="s">
         <v>151</v>
@@ -14050,12 +14054,12 @@
         <v>110</v>
       </c>
       <c r="H567" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="568" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E568" s="2" t="s">
-        <v>430</v>
+        <v>178</v>
       </c>
       <c r="F568" s="2" t="s">
         <v>154</v>
@@ -14064,191 +14068,85 @@
         <v>110</v>
       </c>
       <c r="H568" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="569" spans="1:11" ht="26" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="569" spans="2:10" ht="27" x14ac:dyDescent="0.25">
       <c r="B569" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D569" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E569" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F569" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G569" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H569" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E570" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F570" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G570" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H570" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I570" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J570" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E571" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F571" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G571" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C569" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="G569" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H571" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="I571" s="3" t="str">
-        <f>$B$563</f>
-        <v>OMOP Comorbidity Condition</v>
-      </c>
-    </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E572" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F572" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G572" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H572" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I572" s="3">
-        <v>1147127</v>
-      </c>
-      <c r="J572" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E573" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F573" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G573" s="2" t="s">
+      <c r="H569" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="570" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G570" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H573" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E574" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F574" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G574" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H574" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="575" spans="1:11" ht="26" x14ac:dyDescent="0.3">
+      <c r="H570" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="571" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H571" s="6"/>
+    </row>
+    <row r="572" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H572" s="6"/>
+    </row>
+    <row r="575" spans="2:10" ht="27" x14ac:dyDescent="0.25">
       <c r="B575" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="C575" s="2" t="s">
-        <v>614</v>
+        <v>508</v>
       </c>
       <c r="G575" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H575" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H575" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="576" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G576" s="12" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H576" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="577" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="H577" s="6"/>
-    </row>
-    <row r="578" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="H578" s="6"/>
-    </row>
-    <row r="581" spans="2:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="B581" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="G581" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="577" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G577" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H581" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="582" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G582" s="12" t="s">
+      <c r="H577" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="578" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G578" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H582" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="583" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G583" s="12" t="s">
+      <c r="H578" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="579" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G579" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H583" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="584" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G584" s="12" t="s">
+      <c r="H579" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="580" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G580" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H584" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="585" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G585" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H585" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="586" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G586" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H586" s="7" t="s">
+      <c r="H580" s="7" t="s">
         <v>8</v>
       </c>
     </row>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD64129-D1F8-4DAE-921D-C11AC951EB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E729826-CDB9-41C9-9474-8DF622B9B916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformation Model" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3384" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3380" uniqueCount="624">
   <si>
     <t>Sample Registration</t>
   </si>
@@ -1690,9 +1690,6 @@
     <t>2000-01-01</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Concatenate Values</t>
   </si>
   <si>
@@ -1904,6 +1901,18 @@
   </si>
   <si>
     <t>treatment_type</t>
+  </si>
+  <si>
+    <t>$.donors[].exposures[].tobacco_type[]</t>
+  </si>
+  <si>
+    <t>$.donors[].primary_diagnoses[].treatments[].surgeries[].margin_types_involved[]</t>
+  </si>
+  <si>
+    <t>$.donors[].primary_diagnoses[].treatments[].surgeries[].margin_types_not_involved[]</t>
+  </si>
+  <si>
+    <t>$.donors[].primary_diagnoses[].treatments[].surgeries[].margin_types_not_assessed[]</t>
   </si>
 </sst>
 </file>
@@ -2383,7 +2392,7 @@
         <v>127</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>128</v>
@@ -2438,7 +2447,7 @@
         <v>133</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -2497,10 +2506,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>132</v>
@@ -2564,7 +2573,7 @@
         <v>133</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2641,7 +2650,7 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2665,7 +2674,7 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2689,7 +2698,7 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2713,7 +2722,7 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2737,7 +2746,7 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2761,12 +2770,12 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D17" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>147</v>
@@ -2785,7 +2794,7 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -2809,7 +2818,7 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -2833,7 +2842,7 @@
         <v>OMOP Patient Person</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -2844,7 +2853,7 @@
         <v>149</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -2865,7 +2874,7 @@
         <v>149</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -2886,7 +2895,7 @@
         <v>149</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>50</v>
@@ -2907,7 +2916,7 @@
         <v>149</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>90</v>
@@ -2928,7 +2937,7 @@
         <v>150</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -2954,7 +2963,7 @@
         <v>150</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -2980,7 +2989,7 @@
         <v>150</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>50</v>
@@ -3006,7 +3015,7 @@
         <v>150</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>90</v>
@@ -3015,13 +3024,13 @@
         <v>91</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -3038,7 +3047,7 @@
         <v>133</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>133</v>
@@ -3093,7 +3102,7 @@
         <v>543</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>132</v>
@@ -3105,7 +3114,7 @@
         <v>133</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -3113,7 +3122,7 @@
         <v>543</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>132</v>
@@ -3133,25 +3142,25 @@
         <v>543</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I33" s="14" t="s">
         <v>560</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>543</v>
@@ -3160,7 +3169,7 @@
         <v>133</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>9</v>
@@ -3177,7 +3186,7 @@
         <v>133</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>9</v>
@@ -3194,7 +3203,7 @@
         <v>133</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>9</v>
@@ -3211,7 +3220,7 @@
         <v>133</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>9</v>
@@ -3223,10 +3232,10 @@
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="D38" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>154</v>
@@ -3238,10 +3247,10 @@
         <v>133</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -3265,7 +3274,7 @@
         <v>2</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -3282,10 +3291,10 @@
         <v>133</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -3308,7 +3317,7 @@
         <v>159</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>160</v>
@@ -3348,7 +3357,7 @@
         <v>12</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -3368,7 +3377,7 @@
         <v>12</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -3388,12 +3397,12 @@
         <v>12</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E46" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>154</v>
@@ -3405,12 +3414,12 @@
         <v>133</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E47" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>154</v>
@@ -3422,7 +3431,7 @@
         <v>133</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="27" x14ac:dyDescent="0.25">
@@ -3445,7 +3454,7 @@
         <v>2</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -3488,7 +3497,7 @@
         <v>10</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -3555,7 +3564,7 @@
         <v>13</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3642,7 +3651,7 @@
         <v>133</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>34</v>
@@ -3651,7 +3660,7 @@
         <v>20</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3672,7 +3681,7 @@
         <v>20</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3695,7 +3704,7 @@
         <v>193</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3733,7 +3742,7 @@
       </c>
       <c r="I63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3780,7 +3789,7 @@
         <v>20</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.25">
@@ -3841,7 +3850,7 @@
         <v>193</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.25">
@@ -3919,7 +3928,7 @@
         <v>OMOP Primary Dx Episode</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.25">
@@ -3940,7 +3949,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="74" spans="2:12" x14ac:dyDescent="0.25">
@@ -3986,7 +3995,7 @@
         <v>20</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.25">
@@ -4047,7 +4056,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="79" spans="2:12" x14ac:dyDescent="0.25">
@@ -4127,7 +4136,7 @@
         <v>20</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="83" spans="2:12" x14ac:dyDescent="0.25">
@@ -4188,7 +4197,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="86" spans="2:12" x14ac:dyDescent="0.25">
@@ -4231,7 +4240,7 @@
         <v>39</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="88" spans="2:12" x14ac:dyDescent="0.25">
@@ -4271,7 +4280,7 @@
         <v>20</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="90" spans="2:12" x14ac:dyDescent="0.25">
@@ -4331,7 +4340,7 @@
         <v>37</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.25">
@@ -4369,7 +4378,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="95" spans="2:12" x14ac:dyDescent="0.25">
@@ -4415,7 +4424,7 @@
         <v>20</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.25">
@@ -4476,7 +4485,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.25">
@@ -4519,7 +4528,7 @@
         <v>44</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.25">
@@ -4559,7 +4568,7 @@
         <v>20</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="104" spans="2:12" x14ac:dyDescent="0.25">
@@ -4620,7 +4629,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="107" spans="2:12" x14ac:dyDescent="0.25">
@@ -4663,7 +4672,7 @@
         <v>45</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="109" spans="2:12" x14ac:dyDescent="0.25">
@@ -4703,7 +4712,7 @@
         <v>20</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="111" spans="2:12" x14ac:dyDescent="0.25">
@@ -4764,7 +4773,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="114" spans="2:12" x14ac:dyDescent="0.25">
@@ -4807,7 +4816,7 @@
         <v>46</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="116" spans="2:12" x14ac:dyDescent="0.25">
@@ -4847,7 +4856,7 @@
         <v>20</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="118" spans="2:12" x14ac:dyDescent="0.25">
@@ -4867,7 +4876,7 @@
         <v>40</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="119" spans="2:12" x14ac:dyDescent="0.25">
@@ -4999,7 +5008,7 @@
         <v>20</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="126" spans="2:12" x14ac:dyDescent="0.25">
@@ -5060,7 +5069,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="129" spans="2:12" x14ac:dyDescent="0.25">
@@ -5103,7 +5112,7 @@
         <v>47</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="131" spans="2:12" x14ac:dyDescent="0.25">
@@ -5143,7 +5152,7 @@
         <v>20</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="133" spans="2:12" x14ac:dyDescent="0.25">
@@ -5204,7 +5213,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="136" spans="2:12" x14ac:dyDescent="0.25">
@@ -5247,7 +5256,7 @@
         <v>48</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="138" spans="2:12" x14ac:dyDescent="0.25">
@@ -5287,7 +5296,7 @@
         <v>20</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="140" spans="2:12" x14ac:dyDescent="0.25">
@@ -5348,7 +5357,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="143" spans="2:12" x14ac:dyDescent="0.25">
@@ -5391,7 +5400,7 @@
         <v>49</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -5431,7 +5440,7 @@
         <v>20</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -5451,7 +5460,7 @@
         <v>42</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -5506,7 +5515,7 @@
         <v>OMOP Primary Dx Condition</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -5580,7 +5589,7 @@
         <v>133</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>50</v>
@@ -5589,7 +5598,7 @@
         <v>21</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -5600,7 +5609,7 @@
         <v>133</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>50</v>
@@ -5609,7 +5618,7 @@
         <v>52</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -5620,7 +5629,7 @@
         <v>133</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>50</v>
@@ -5648,7 +5657,7 @@
         <v>21</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -5725,7 +5734,7 @@
         <v>52</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="162" spans="2:12" x14ac:dyDescent="0.25">
@@ -5782,7 +5791,7 @@
         <v>21</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="165" spans="2:12" x14ac:dyDescent="0.25">
@@ -5799,13 +5808,13 @@
         <v>133</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="166" spans="2:12" x14ac:dyDescent="0.25">
@@ -5822,7 +5831,7 @@
         <v>52</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="167" spans="2:12" x14ac:dyDescent="0.25">
@@ -5843,7 +5852,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="168" spans="2:12" x14ac:dyDescent="0.25">
@@ -5886,7 +5895,7 @@
         <v>54</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="170" spans="2:12" x14ac:dyDescent="0.25">
@@ -5926,7 +5935,7 @@
         <v>21</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="172" spans="2:12" x14ac:dyDescent="0.25">
@@ -5969,7 +5978,7 @@
         <v>530</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="174" spans="2:12" x14ac:dyDescent="0.25">
@@ -6003,7 +6012,7 @@
         <v>52</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="176" spans="2:12" x14ac:dyDescent="0.25">
@@ -6024,7 +6033,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -6086,10 +6095,10 @@
     </row>
     <row r="180" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B180" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>609</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>143</v>
@@ -6098,7 +6107,7 @@
         <v>255</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>50</v>
@@ -6107,7 +6116,7 @@
         <v>21</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -6115,13 +6124,13 @@
         <v>256</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>50</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -6132,7 +6141,7 @@
         <v>258</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>133</v>
@@ -6155,10 +6164,10 @@
         <v>133</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -6178,7 +6187,7 @@
         <v>56</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -6198,12 +6207,12 @@
         <v>133</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="186" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B186" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>210</v>
@@ -6225,7 +6234,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -6233,7 +6242,7 @@
         <v>211</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>50</v>
@@ -6246,7 +6255,7 @@
         <v>OMOP Treatment Episode Procedure Occurrence</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -6286,7 +6295,7 @@
         <v>200</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>50</v>
@@ -6296,7 +6305,7 @@
       </c>
       <c r="I189" s="2"/>
       <c r="K189" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -6354,7 +6363,7 @@
       </c>
       <c r="I192" s="5"/>
       <c r="K192" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="193" spans="2:12" x14ac:dyDescent="0.25">
@@ -6371,7 +6380,7 @@
         <v>59</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="194" spans="2:12" x14ac:dyDescent="0.25">
@@ -6412,7 +6421,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="196" spans="2:12" x14ac:dyDescent="0.25">
@@ -6420,7 +6429,7 @@
         <v>211</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>50</v>
@@ -6433,7 +6442,7 @@
         <v>OMOP Systemic Therapy Episode</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="197" spans="2:12" x14ac:dyDescent="0.25">
@@ -6470,7 +6479,7 @@
         <v>255</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>50</v>
@@ -6480,7 +6489,7 @@
       </c>
       <c r="I198" s="2"/>
       <c r="K198" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="199" spans="2:12" x14ac:dyDescent="0.25">
@@ -6500,7 +6509,7 @@
         <v>58</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="200" spans="2:12" x14ac:dyDescent="0.25">
@@ -6534,7 +6543,7 @@
         <v>59</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="202" spans="2:12" x14ac:dyDescent="0.25">
@@ -6565,7 +6574,7 @@
         <v>200</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>50</v>
@@ -6578,7 +6587,7 @@
         <v>OMOP Systemic Therapy Episode</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="204" spans="2:12" x14ac:dyDescent="0.25">
@@ -6586,7 +6595,7 @@
         <v>211</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>50</v>
@@ -6599,7 +6608,7 @@
         <v>OMOP Systemic Therapy Procedure</v>
       </c>
       <c r="K204" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="205" spans="2:12" x14ac:dyDescent="0.25">
@@ -6633,7 +6642,7 @@
         <v>543</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>154</v>
@@ -6646,7 +6655,7 @@
       </c>
       <c r="I206" s="10"/>
       <c r="K206" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="207" spans="2:12" x14ac:dyDescent="0.25">
@@ -6658,7 +6667,7 @@
         <v>285</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>50</v>
@@ -6667,7 +6676,7 @@
         <v>21</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="208" spans="2:12" x14ac:dyDescent="0.25">
@@ -6707,10 +6716,10 @@
         <v>62</v>
       </c>
       <c r="J209" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="210" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
@@ -6721,7 +6730,7 @@
         <v>292</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>57</v>
@@ -6747,7 +6756,7 @@
         <v>59</v>
       </c>
       <c r="K211" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="212" spans="2:12" x14ac:dyDescent="0.25">
@@ -6767,7 +6776,7 @@
         <v>60</v>
       </c>
       <c r="K212" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="213" spans="2:12" x14ac:dyDescent="0.25">
@@ -6815,7 +6824,7 @@
         <v>200</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>50</v>
@@ -6828,7 +6837,7 @@
         <v>OMOP Systemic Therapy Episode</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="216" spans="2:12" x14ac:dyDescent="0.25">
@@ -6836,7 +6845,7 @@
         <v>211</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>50</v>
@@ -6849,7 +6858,7 @@
         <v>OMOP Systemic Therapy Dose Given Drug Exposure</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.25">
@@ -6886,7 +6895,7 @@
         <v>285</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>50</v>
@@ -6895,7 +6904,7 @@
         <v>21</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="219" spans="2:12" x14ac:dyDescent="0.25">
@@ -6935,10 +6944,10 @@
         <v>62</v>
       </c>
       <c r="J220" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="221" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
@@ -6949,7 +6958,7 @@
         <v>292</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>57</v>
@@ -6975,7 +6984,7 @@
         <v>59</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="223" spans="2:12" x14ac:dyDescent="0.25">
@@ -6995,7 +7004,7 @@
         <v>60</v>
       </c>
       <c r="K223" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="224" spans="2:12" x14ac:dyDescent="0.25">
@@ -7043,7 +7052,7 @@
         <v>200</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>50</v>
@@ -7056,7 +7065,7 @@
         <v>OMOP Systemic Therapy Episode</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
@@ -7064,7 +7073,7 @@
         <v>211</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>50</v>
@@ -7077,7 +7086,7 @@
         <v>OMOP Systemic Therapy Dose Prescribed Drug Exposure</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
@@ -7128,7 +7137,7 @@
         <v>200</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>50</v>
@@ -7137,7 +7146,7 @@
         <v>21</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
@@ -7195,7 +7204,7 @@
       </c>
       <c r="I233" s="5"/>
       <c r="K233" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
@@ -7212,10 +7221,10 @@
         <v>133</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="235" spans="1:12" ht="27" x14ac:dyDescent="0.25">
@@ -7242,7 +7251,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
@@ -7250,7 +7259,7 @@
         <v>211</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>50</v>
@@ -7263,7 +7272,7 @@
         <v>OMOP Radiation Episode</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
@@ -7300,7 +7309,7 @@
         <v>255</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>50</v>
@@ -7309,7 +7318,7 @@
         <v>21</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
@@ -7329,7 +7338,7 @@
         <v>69</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
@@ -7363,10 +7372,10 @@
         <v>133</v>
       </c>
       <c r="I241" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K241" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="242" spans="2:12" x14ac:dyDescent="0.25">
@@ -7416,7 +7425,7 @@
         <v>200</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>50</v>
@@ -7429,7 +7438,7 @@
         <v>OMOP Radiation Episode</v>
       </c>
       <c r="K244" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="245" spans="2:12" x14ac:dyDescent="0.25">
@@ -7437,7 +7446,7 @@
         <v>211</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>50</v>
@@ -7450,7 +7459,7 @@
         <v>OMOP Radiation Procedure</v>
       </c>
       <c r="K245" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="246" spans="2:12" x14ac:dyDescent="0.25">
@@ -7487,7 +7496,7 @@
         <v>213</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>50</v>
@@ -7496,7 +7505,7 @@
         <v>21</v>
       </c>
       <c r="K247" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="248" spans="2:12" x14ac:dyDescent="0.25">
@@ -7536,10 +7545,10 @@
         <v>133</v>
       </c>
       <c r="I249" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K249" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="250" spans="2:12" x14ac:dyDescent="0.25">
@@ -7547,7 +7556,7 @@
         <v>149</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>50</v>
@@ -7560,7 +7569,7 @@
         <v>OMOP Radiation Episode</v>
       </c>
       <c r="K250" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="251" spans="2:12" x14ac:dyDescent="0.25">
@@ -7603,7 +7612,7 @@
         <v>72</v>
       </c>
       <c r="K252" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="253" spans="2:12" x14ac:dyDescent="0.25">
@@ -7643,7 +7652,7 @@
         <v>213</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>50</v>
@@ -7652,7 +7661,7 @@
         <v>21</v>
       </c>
       <c r="K254" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="255" spans="2:12" x14ac:dyDescent="0.25">
@@ -7690,10 +7699,10 @@
         <v>133</v>
       </c>
       <c r="I256" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K256" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="257" spans="2:12" x14ac:dyDescent="0.25">
@@ -7701,7 +7710,7 @@
         <v>149</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>50</v>
@@ -7714,7 +7723,7 @@
         <v>OMOP Radiation Episode</v>
       </c>
       <c r="K257" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="258" spans="2:12" x14ac:dyDescent="0.25">
@@ -7757,7 +7766,7 @@
         <v>71</v>
       </c>
       <c r="K259" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="260" spans="2:12" ht="27" x14ac:dyDescent="0.25">
@@ -7771,7 +7780,7 @@
         <v>172</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>50</v>
@@ -7780,7 +7789,7 @@
         <v>21</v>
       </c>
       <c r="K260" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="261" spans="2:12" x14ac:dyDescent="0.25">
@@ -7820,10 +7829,10 @@
         <v>133</v>
       </c>
       <c r="I262" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K262" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="263" spans="2:12" x14ac:dyDescent="0.25">
@@ -7831,7 +7840,7 @@
         <v>228</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>50</v>
@@ -7844,7 +7853,7 @@
         <v>OMOP Radiation Episode</v>
       </c>
       <c r="K263" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="264" spans="2:12" x14ac:dyDescent="0.25">
@@ -7887,7 +7896,7 @@
         <v>73</v>
       </c>
       <c r="K265" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="266" spans="2:12" x14ac:dyDescent="0.25">
@@ -7918,7 +7927,7 @@
         <v>255</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>50</v>
@@ -7927,7 +7936,7 @@
         <v>21</v>
       </c>
       <c r="K267" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="268" spans="2:12" x14ac:dyDescent="0.25">
@@ -7967,10 +7976,10 @@
         <v>133</v>
       </c>
       <c r="I269" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K269" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="270" spans="2:12" x14ac:dyDescent="0.25">
@@ -7987,7 +7996,7 @@
         <v>74</v>
       </c>
       <c r="K270" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="271" spans="2:12" x14ac:dyDescent="0.25">
@@ -8015,7 +8024,7 @@
         <v>200</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>50</v>
@@ -8028,7 +8037,7 @@
         <v>OMOP Radiation Episode</v>
       </c>
       <c r="K272" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
@@ -8036,7 +8045,7 @@
         <v>211</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>50</v>
@@ -8049,7 +8058,7 @@
         <v>OMOP Radiation Boost Procedure</v>
       </c>
       <c r="K273" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
@@ -8089,7 +8098,7 @@
         <v>133</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>75</v>
@@ -8106,7 +8115,7 @@
         <v>200</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>50</v>
@@ -8115,7 +8124,7 @@
         <v>21</v>
       </c>
       <c r="K276" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
@@ -8173,10 +8182,10 @@
       </c>
       <c r="I279" s="5"/>
       <c r="J279" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K279" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
@@ -8193,10 +8202,10 @@
         <v>133</v>
       </c>
       <c r="I280" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K280" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="281" spans="1:12" ht="27" x14ac:dyDescent="0.25">
@@ -8223,7 +8232,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
       <c r="K281" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
@@ -8231,7 +8240,7 @@
         <v>211</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>50</v>
@@ -8244,7 +8253,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K282" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
@@ -8281,7 +8290,7 @@
         <v>255</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>50</v>
@@ -8290,7 +8299,7 @@
         <v>21</v>
       </c>
       <c r="K284" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
@@ -8311,10 +8320,10 @@
       </c>
       <c r="I285" s="5"/>
       <c r="J285" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K285" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="286" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
@@ -8325,7 +8334,7 @@
         <v>258</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>75</v>
@@ -8348,10 +8357,10 @@
         <v>133</v>
       </c>
       <c r="I287" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K287" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="288" spans="1:12" ht="27" x14ac:dyDescent="0.25">
@@ -8365,7 +8374,7 @@
         <v>200</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>50</v>
@@ -8378,7 +8387,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K288" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="289" spans="2:12" x14ac:dyDescent="0.25">
@@ -8386,7 +8395,7 @@
         <v>211</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>50</v>
@@ -8399,7 +8408,7 @@
         <v>OMOP Surgery Procedure</v>
       </c>
       <c r="K289" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="290" spans="2:12" x14ac:dyDescent="0.25">
@@ -8436,7 +8445,7 @@
         <v>213</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>50</v>
@@ -8445,7 +8454,7 @@
         <v>21</v>
       </c>
       <c r="K291" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="292" spans="2:12" x14ac:dyDescent="0.25">
@@ -8480,10 +8489,10 @@
         <v>133</v>
       </c>
       <c r="I293" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K293" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="294" spans="2:12" x14ac:dyDescent="0.25">
@@ -8491,7 +8500,7 @@
         <v>149</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>50</v>
@@ -8504,7 +8513,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K294" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="295" spans="2:12" x14ac:dyDescent="0.25">
@@ -8547,7 +8556,7 @@
         <v>80</v>
       </c>
       <c r="K296" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="297" spans="2:12" x14ac:dyDescent="0.25">
@@ -8584,7 +8593,7 @@
         <v>213</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>50</v>
@@ -8593,7 +8602,7 @@
         <v>21</v>
       </c>
       <c r="K298" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="299" spans="2:12" x14ac:dyDescent="0.25">
@@ -8628,10 +8637,10 @@
         <v>133</v>
       </c>
       <c r="I300" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K300" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="301" spans="2:12" x14ac:dyDescent="0.25">
@@ -8639,7 +8648,7 @@
         <v>149</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>50</v>
@@ -8652,7 +8661,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K301" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="302" spans="2:12" x14ac:dyDescent="0.25">
@@ -8695,7 +8704,7 @@
         <v>81</v>
       </c>
       <c r="K303" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="304" spans="2:12" x14ac:dyDescent="0.25">
@@ -8732,7 +8741,7 @@
         <v>213</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>50</v>
@@ -8741,7 +8750,7 @@
         <v>21</v>
       </c>
       <c r="K305" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="306" spans="2:12" x14ac:dyDescent="0.25">
@@ -8776,10 +8785,10 @@
         <v>133</v>
       </c>
       <c r="I307" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K307" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="308" spans="2:12" x14ac:dyDescent="0.25">
@@ -8787,7 +8796,7 @@
         <v>149</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>50</v>
@@ -8800,7 +8809,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K308" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="309" spans="2:12" x14ac:dyDescent="0.25">
@@ -8843,7 +8852,7 @@
         <v>82</v>
       </c>
       <c r="K310" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="311" spans="2:12" x14ac:dyDescent="0.25">
@@ -8880,7 +8889,7 @@
         <v>172</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>50</v>
@@ -8889,7 +8898,7 @@
         <v>21</v>
       </c>
       <c r="K312" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="313" spans="2:12" x14ac:dyDescent="0.25">
@@ -8929,10 +8938,10 @@
         <v>133</v>
       </c>
       <c r="I314" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K314" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="315" spans="2:12" x14ac:dyDescent="0.25">
@@ -8940,7 +8949,7 @@
         <v>228</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>50</v>
@@ -8953,7 +8962,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K315" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="316" spans="2:12" x14ac:dyDescent="0.25">
@@ -8999,7 +9008,7 @@
         <v>531</v>
       </c>
       <c r="K317" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="318" spans="2:12" x14ac:dyDescent="0.25">
@@ -9030,7 +9039,7 @@
         <v>172</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>50</v>
@@ -9039,7 +9048,7 @@
         <v>21</v>
       </c>
       <c r="K319" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="320" spans="2:12" x14ac:dyDescent="0.25">
@@ -9079,10 +9088,10 @@
         <v>133</v>
       </c>
       <c r="I321" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K321" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="322" spans="2:12" x14ac:dyDescent="0.25">
@@ -9090,7 +9099,7 @@
         <v>228</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>50</v>
@@ -9103,7 +9112,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K322" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="323" spans="2:12" x14ac:dyDescent="0.25">
@@ -9146,7 +9155,7 @@
         <v>83</v>
       </c>
       <c r="K324" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="325" spans="2:12" x14ac:dyDescent="0.25">
@@ -9177,7 +9186,7 @@
         <v>172</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>50</v>
@@ -9186,7 +9195,7 @@
         <v>21</v>
       </c>
       <c r="K326" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="327" spans="2:12" x14ac:dyDescent="0.25">
@@ -9226,10 +9235,10 @@
         <v>133</v>
       </c>
       <c r="I328" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K328" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="329" spans="2:12" x14ac:dyDescent="0.25">
@@ -9237,7 +9246,7 @@
         <v>228</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>50</v>
@@ -9250,7 +9259,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K329" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="330" spans="2:12" x14ac:dyDescent="0.25">
@@ -9293,7 +9302,7 @@
         <v>79</v>
       </c>
       <c r="K331" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="332" spans="2:12" x14ac:dyDescent="0.25">
@@ -9324,7 +9333,7 @@
         <v>172</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>50</v>
@@ -9333,7 +9342,7 @@
         <v>21</v>
       </c>
       <c r="K333" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="334" spans="2:12" x14ac:dyDescent="0.25">
@@ -9373,10 +9382,10 @@
         <v>133</v>
       </c>
       <c r="I335" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K335" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="336" spans="2:12" x14ac:dyDescent="0.25">
@@ -9384,7 +9393,7 @@
         <v>228</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>50</v>
@@ -9397,7 +9406,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K336" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="337" spans="2:12" x14ac:dyDescent="0.25">
@@ -9440,7 +9449,7 @@
         <v>84</v>
       </c>
       <c r="K338" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="339" spans="2:12" x14ac:dyDescent="0.25">
@@ -9471,7 +9480,7 @@
         <v>172</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>50</v>
@@ -9480,7 +9489,7 @@
         <v>21</v>
       </c>
       <c r="K340" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="341" spans="2:12" x14ac:dyDescent="0.25">
@@ -9520,10 +9529,10 @@
         <v>133</v>
       </c>
       <c r="I342" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K342" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="343" spans="2:12" x14ac:dyDescent="0.25">
@@ -9531,7 +9540,7 @@
         <v>228</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>50</v>
@@ -9544,7 +9553,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K343" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="344" spans="2:12" x14ac:dyDescent="0.25">
@@ -9587,7 +9596,7 @@
         <v>88</v>
       </c>
       <c r="K345" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="346" spans="2:12" x14ac:dyDescent="0.25">
@@ -9618,7 +9627,7 @@
         <v>172</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>50</v>
@@ -9627,7 +9636,7 @@
         <v>21</v>
       </c>
       <c r="K347" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="348" spans="2:12" x14ac:dyDescent="0.25">
@@ -9667,10 +9676,10 @@
         <v>133</v>
       </c>
       <c r="I349" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K349" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="350" spans="2:12" x14ac:dyDescent="0.25">
@@ -9678,7 +9687,7 @@
         <v>228</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>50</v>
@@ -9691,7 +9700,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K350" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="351" spans="2:12" x14ac:dyDescent="0.25">
@@ -9734,10 +9743,10 @@
         <v>89</v>
       </c>
       <c r="K352" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="353" spans="2:12" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C353" s="2" t="s">
         <v>377</v>
       </c>
@@ -9754,7 +9763,10 @@
         <v>89</v>
       </c>
     </row>
-    <row r="354" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A354" s="5" t="s">
+        <v>621</v>
+      </c>
       <c r="B354" s="3" t="s">
         <v>469</v>
       </c>
@@ -9765,7 +9777,7 @@
         <v>172</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>50</v>
@@ -9774,10 +9786,10 @@
         <v>21</v>
       </c>
       <c r="K354" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="355" spans="2:12" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E355" s="2" t="s">
         <v>173</v>
       </c>
@@ -9800,7 +9812,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="356" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E356" s="2" t="s">
         <v>135</v>
       </c>
@@ -9814,18 +9826,18 @@
         <v>133</v>
       </c>
       <c r="I356" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K356" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="357" spans="2:12" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E357" s="2" t="s">
         <v>228</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>50</v>
@@ -9838,10 +9850,10 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K357" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="358" spans="2:12" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E358" s="2" t="s">
         <v>229</v>
       </c>
@@ -9864,7 +9876,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="359" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C359" s="2" t="s">
         <v>358</v>
       </c>
@@ -9872,19 +9884,16 @@
         <v>176</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>132</v>
+        <v>618</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="H359" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I359" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="360" spans="2:12" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C360" s="2" t="s">
         <v>359</v>
       </c>
@@ -9892,19 +9901,16 @@
         <v>178</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>550</v>
+        <v>611</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="H360" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K360" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="361" spans="2:12" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E361" s="2" t="s">
         <v>275</v>
       </c>
@@ -9927,7 +9933,10 @@
         <v>361</v>
       </c>
     </row>
-    <row r="362" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A362" s="5" t="s">
+        <v>622</v>
+      </c>
       <c r="B362" s="3" t="s">
         <v>470</v>
       </c>
@@ -9938,7 +9947,7 @@
         <v>172</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>50</v>
@@ -9947,10 +9956,10 @@
         <v>21</v>
       </c>
       <c r="K362" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="363" spans="2:12" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E363" s="2" t="s">
         <v>173</v>
       </c>
@@ -9973,7 +9982,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="364" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E364" s="2" t="s">
         <v>135</v>
       </c>
@@ -9987,18 +9996,18 @@
         <v>133</v>
       </c>
       <c r="I364" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K364" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="365" spans="2:12" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E365" s="2" t="s">
         <v>228</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>50</v>
@@ -10011,10 +10020,10 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K365" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="366" spans="2:12" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E366" s="2" t="s">
         <v>229</v>
       </c>
@@ -10037,7 +10046,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="367" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C367" s="2" t="s">
         <v>362</v>
       </c>
@@ -10045,19 +10054,16 @@
         <v>176</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>132</v>
+        <v>618</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="H367" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I367" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="368" spans="2:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C368" s="2" t="s">
         <v>363</v>
       </c>
@@ -10065,16 +10071,13 @@
         <v>178</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>550</v>
+        <v>611</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="H368" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="K368" s="2" t="s">
-        <v>562</v>
+        <v>133</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.25">
@@ -10101,6 +10104,9 @@
       </c>
     </row>
     <row r="370" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A370" s="5" t="s">
+        <v>623</v>
+      </c>
       <c r="B370" s="3" t="s">
         <v>471</v>
       </c>
@@ -10111,7 +10117,7 @@
         <v>172</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>50</v>
@@ -10120,7 +10126,7 @@
         <v>21</v>
       </c>
       <c r="K370" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.25">
@@ -10160,10 +10166,10 @@
         <v>133</v>
       </c>
       <c r="I372" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K372" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
@@ -10171,7 +10177,7 @@
         <v>228</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>50</v>
@@ -10184,7 +10190,7 @@
         <v>OMOP Surgery Episode</v>
       </c>
       <c r="K373" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
@@ -10218,16 +10224,13 @@
         <v>176</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>132</v>
+        <v>618</v>
       </c>
       <c r="G375" s="2" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="H375" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I375" s="3" t="s">
-        <v>549</v>
+        <v>87</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.25">
@@ -10238,16 +10241,13 @@
         <v>178</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>550</v>
+        <v>611</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="H376" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K376" s="2" t="s">
-        <v>562</v>
+        <v>133</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.25">
@@ -10284,7 +10284,7 @@
         <v>543</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>154</v>
@@ -10296,7 +10296,7 @@
         <v>3</v>
       </c>
       <c r="K378" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.25">
@@ -10322,25 +10322,25 @@
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="E380" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F380" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G380" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H380" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I380" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="F380" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G380" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H380" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I380" s="3" t="s">
-        <v>597</v>
       </c>
       <c r="J380" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L380" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.25">
@@ -10360,7 +10360,7 @@
         <v>22</v>
       </c>
       <c r="K381" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.25">
@@ -10420,7 +10420,7 @@
         <v>3</v>
       </c>
       <c r="K384" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="385" spans="2:12" x14ac:dyDescent="0.25">
@@ -10460,7 +10460,7 @@
         <v>22</v>
       </c>
       <c r="K386" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="387" spans="2:12" x14ac:dyDescent="0.25">
@@ -10481,7 +10481,7 @@
         <v>OMOP Specimen</v>
       </c>
       <c r="K387" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="388" spans="2:12" x14ac:dyDescent="0.25">
@@ -10527,7 +10527,7 @@
         <v>531</v>
       </c>
       <c r="K389" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="390" spans="2:12" x14ac:dyDescent="0.25">
@@ -10567,7 +10567,7 @@
         <v>3</v>
       </c>
       <c r="K391" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="392" spans="2:12" x14ac:dyDescent="0.25">
@@ -10584,7 +10584,7 @@
         <v>133</v>
       </c>
       <c r="I392" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J392" s="2" t="s">
         <v>174</v>
@@ -10607,7 +10607,7 @@
         <v>22</v>
       </c>
       <c r="K393" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="394" spans="2:12" x14ac:dyDescent="0.25">
@@ -10628,7 +10628,7 @@
         <v>OMOP Specimen</v>
       </c>
       <c r="K394" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="395" spans="2:12" x14ac:dyDescent="0.25">
@@ -10671,7 +10671,7 @@
         <v>29</v>
       </c>
       <c r="K396" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="397" spans="2:12" x14ac:dyDescent="0.25">
@@ -10745,7 +10745,7 @@
         <v>3</v>
       </c>
       <c r="K400" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="401" spans="2:12" x14ac:dyDescent="0.25">
@@ -10785,7 +10785,7 @@
         <v>22</v>
       </c>
       <c r="K402" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="403" spans="2:12" x14ac:dyDescent="0.25">
@@ -10806,7 +10806,7 @@
         <v>OMOP Specimen</v>
       </c>
       <c r="K403" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="404" spans="2:12" x14ac:dyDescent="0.25">
@@ -10849,7 +10849,7 @@
         <v>24</v>
       </c>
       <c r="K405" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="406" spans="2:12" x14ac:dyDescent="0.25">
@@ -10889,7 +10889,7 @@
         <v>3</v>
       </c>
       <c r="K407" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="408" spans="2:12" x14ac:dyDescent="0.25">
@@ -10929,7 +10929,7 @@
         <v>22</v>
       </c>
       <c r="K409" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="410" spans="2:12" x14ac:dyDescent="0.25">
@@ -10950,7 +10950,7 @@
         <v>OMOP Specimen</v>
       </c>
       <c r="K410" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="411" spans="2:12" x14ac:dyDescent="0.25">
@@ -10993,7 +10993,7 @@
         <v>33</v>
       </c>
       <c r="K412" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="413" spans="2:12" x14ac:dyDescent="0.25">
@@ -11033,7 +11033,7 @@
         <v>3</v>
       </c>
       <c r="K414" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="415" spans="2:12" x14ac:dyDescent="0.25">
@@ -11073,7 +11073,7 @@
         <v>22</v>
       </c>
       <c r="K416" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.25">
@@ -11094,7 +11094,7 @@
         <v>OMOP Specimen</v>
       </c>
       <c r="K417" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.25">
@@ -11137,7 +11137,7 @@
         <v>32</v>
       </c>
       <c r="K419" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.25">
@@ -11181,7 +11181,7 @@
         <v>OMOP Primary Dx Episode</v>
       </c>
       <c r="K421" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.25">
@@ -11202,7 +11202,7 @@
         <v>OMOP Specimen</v>
       </c>
       <c r="K422" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.25">
@@ -11252,7 +11252,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
       <c r="K424" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
         <v>OMOP Specimen</v>
       </c>
       <c r="K425" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.25">
@@ -11336,10 +11336,10 @@
     </row>
     <row r="431" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D431" s="2" t="s">
         <v>543</v>
@@ -11348,7 +11348,7 @@
         <v>133</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>90</v>
@@ -11361,10 +11361,10 @@
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="D432" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F432" s="2" t="s">
         <v>153</v>
@@ -11376,35 +11376,35 @@
         <v>91</v>
       </c>
       <c r="K432" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="433" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E433" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F433" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G433" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H433" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I433" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="F433" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G433" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H433" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I433" s="3" t="s">
+      <c r="J433" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="J433" s="2" t="s">
+      <c r="L433" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="L433" s="2" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="434" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E434" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F434" s="2" t="s">
         <v>183</v>
@@ -11416,12 +11416,12 @@
         <v>92</v>
       </c>
       <c r="K434" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="435" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E435" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F435" s="2" t="s">
         <v>183</v>
@@ -11434,12 +11434,12 @@
       </c>
       <c r="I435" s="8"/>
       <c r="K435" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="436" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B436" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>130</v>
@@ -11457,7 +11457,7 @@
         <v>91</v>
       </c>
       <c r="K436" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="437" spans="2:12" x14ac:dyDescent="0.25">
@@ -11474,13 +11474,13 @@
         <v>133</v>
       </c>
       <c r="I437" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J437" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L437" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="438" spans="2:12" x14ac:dyDescent="0.25">
@@ -11497,7 +11497,7 @@
         <v>95</v>
       </c>
       <c r="K438" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="439" spans="2:12" x14ac:dyDescent="0.25">
@@ -11532,13 +11532,13 @@
         <v>133</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J440" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L440" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="441" spans="2:12" x14ac:dyDescent="0.25">
@@ -11555,7 +11555,7 @@
         <v>93</v>
       </c>
       <c r="K441" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="442" spans="2:12" x14ac:dyDescent="0.25">
@@ -11574,7 +11574,7 @@
     </row>
     <row r="443" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B443" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>130</v>
@@ -11592,7 +11592,7 @@
         <v>91</v>
       </c>
       <c r="K443" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="444" spans="2:12" x14ac:dyDescent="0.25">
@@ -11609,13 +11609,13 @@
         <v>133</v>
       </c>
       <c r="I444" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J444" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L444" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="445" spans="2:12" x14ac:dyDescent="0.25">
@@ -11636,7 +11636,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K445" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="446" spans="2:12" x14ac:dyDescent="0.25">
@@ -11653,13 +11653,13 @@
         <v>133</v>
       </c>
       <c r="I446" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J446" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L446" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="447" spans="2:12" x14ac:dyDescent="0.25">
@@ -11676,7 +11676,7 @@
         <v>94</v>
       </c>
       <c r="K447" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="448" spans="2:12" x14ac:dyDescent="0.25">
@@ -11713,7 +11713,7 @@
         <v>91</v>
       </c>
       <c r="K449" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.25">
@@ -11757,7 +11757,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K451" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.25">
@@ -11774,13 +11774,13 @@
         <v>133</v>
       </c>
       <c r="I452" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J452" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L452" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.25">
@@ -11800,7 +11800,7 @@
         <v>531</v>
       </c>
       <c r="K453" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.25">
@@ -11830,10 +11830,10 @@
     </row>
     <row r="456" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A456" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D456" s="2" t="s">
         <v>543</v>
@@ -11842,7 +11842,7 @@
         <v>133</v>
       </c>
       <c r="F456" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>90</v>
@@ -11855,10 +11855,10 @@
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="D457" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F457" s="2" t="s">
         <v>153</v>
@@ -11870,35 +11870,35 @@
         <v>91</v>
       </c>
       <c r="K457" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E458" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F458" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G458" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H458" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I458" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="F458" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G458" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H458" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I458" s="3" t="s">
+      <c r="J458" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="J458" s="2" t="s">
+      <c r="L458" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="L458" s="2" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E459" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F459" s="2" t="s">
         <v>183</v>
@@ -11910,12 +11910,12 @@
         <v>92</v>
       </c>
       <c r="K459" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E460" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F460" s="2" t="s">
         <v>183</v>
@@ -11928,12 +11928,12 @@
       </c>
       <c r="I460" s="8"/>
       <c r="K460" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="461" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B461" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D461" s="2" t="s">
         <v>130</v>
@@ -11951,7 +11951,7 @@
         <v>91</v>
       </c>
       <c r="K461" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.25">
@@ -11968,13 +11968,13 @@
         <v>133</v>
       </c>
       <c r="I462" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J462" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L462" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.25">
@@ -11991,7 +11991,7 @@
         <v>95</v>
       </c>
       <c r="K463" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.25">
@@ -12026,13 +12026,13 @@
         <v>133</v>
       </c>
       <c r="I465" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J465" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L465" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="466" spans="2:12" x14ac:dyDescent="0.25">
@@ -12049,7 +12049,7 @@
         <v>93</v>
       </c>
       <c r="K466" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="467" spans="2:12" x14ac:dyDescent="0.25">
@@ -12068,7 +12068,7 @@
     </row>
     <row r="468" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B468" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D468" s="2" t="s">
         <v>130</v>
@@ -12086,7 +12086,7 @@
         <v>91</v>
       </c>
       <c r="K468" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="469" spans="2:12" x14ac:dyDescent="0.25">
@@ -12103,13 +12103,13 @@
         <v>133</v>
       </c>
       <c r="I469" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J469" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L469" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="470" spans="2:12" x14ac:dyDescent="0.25">
@@ -12130,7 +12130,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K470" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="471" spans="2:12" x14ac:dyDescent="0.25">
@@ -12147,13 +12147,13 @@
         <v>133</v>
       </c>
       <c r="I471" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J471" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L471" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="472" spans="2:12" x14ac:dyDescent="0.25">
@@ -12170,7 +12170,7 @@
         <v>94</v>
       </c>
       <c r="K472" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="473" spans="2:12" x14ac:dyDescent="0.25">
@@ -12207,7 +12207,7 @@
         <v>91</v>
       </c>
       <c r="K474" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="475" spans="2:12" x14ac:dyDescent="0.25">
@@ -12251,7 +12251,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K476" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="477" spans="2:12" x14ac:dyDescent="0.25">
@@ -12268,13 +12268,13 @@
         <v>133</v>
       </c>
       <c r="I477" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J477" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L477" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="478" spans="2:12" x14ac:dyDescent="0.25">
@@ -12294,7 +12294,7 @@
         <v>531</v>
       </c>
       <c r="K478" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="479" spans="2:12" x14ac:dyDescent="0.25">
@@ -12313,7 +12313,7 @@
     </row>
     <row r="480" spans="2:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B480" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D480" s="2" t="s">
         <v>210</v>
@@ -12335,7 +12335,7 @@
         <v>OMOP Primary Dx Episode</v>
       </c>
       <c r="K480" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.25">
@@ -12356,7 +12356,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K481" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.25">
@@ -12373,21 +12373,21 @@
         <v>133</v>
       </c>
       <c r="I482" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J482" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L482" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="483" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A483" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D483" s="2" t="s">
         <v>543</v>
@@ -12396,7 +12396,7 @@
         <v>133</v>
       </c>
       <c r="F483" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G483" s="2" t="s">
         <v>90</v>
@@ -12409,10 +12409,10 @@
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="D484" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F484" s="2" t="s">
         <v>153</v>
@@ -12424,35 +12424,35 @@
         <v>91</v>
       </c>
       <c r="K484" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E485" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F485" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G485" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H485" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I485" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="F485" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G485" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H485" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I485" s="3" t="s">
+      <c r="J485" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="J485" s="2" t="s">
+      <c r="L485" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="L485" s="2" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E486" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F486" s="2" t="s">
         <v>183</v>
@@ -12464,12 +12464,12 @@
         <v>92</v>
       </c>
       <c r="K486" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E487" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F487" s="2" t="s">
         <v>183</v>
@@ -12482,12 +12482,12 @@
       </c>
       <c r="I487" s="8"/>
       <c r="K487" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="488" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B488" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>130</v>
@@ -12505,7 +12505,7 @@
         <v>91</v>
       </c>
       <c r="K488" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.25">
@@ -12522,13 +12522,13 @@
         <v>133</v>
       </c>
       <c r="I489" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J489" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L489" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.25">
@@ -12545,7 +12545,7 @@
         <v>95</v>
       </c>
       <c r="K490" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.25">
@@ -12580,13 +12580,13 @@
         <v>133</v>
       </c>
       <c r="I492" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J492" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L492" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.25">
@@ -12603,7 +12603,7 @@
         <v>93</v>
       </c>
       <c r="K493" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.25">
@@ -12622,7 +12622,7 @@
     </row>
     <row r="495" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B495" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D495" s="2" t="s">
         <v>130</v>
@@ -12640,7 +12640,7 @@
         <v>91</v>
       </c>
       <c r="K495" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.25">
@@ -12657,13 +12657,13 @@
         <v>133</v>
       </c>
       <c r="I496" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J496" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L496" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.25">
@@ -12684,7 +12684,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K497" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.25">
@@ -12701,13 +12701,13 @@
         <v>133</v>
       </c>
       <c r="I498" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J498" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L498" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.25">
@@ -12724,7 +12724,7 @@
         <v>94</v>
       </c>
       <c r="K499" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.25">
@@ -12761,7 +12761,7 @@
         <v>91</v>
       </c>
       <c r="K501" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.25">
@@ -12805,7 +12805,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K503" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.25">
@@ -12822,13 +12822,13 @@
         <v>133</v>
       </c>
       <c r="I504" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J504" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L504" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.25">
@@ -12848,7 +12848,7 @@
         <v>531</v>
       </c>
       <c r="K505" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.25">
@@ -12867,7 +12867,7 @@
     </row>
     <row r="507" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="B507" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D507" s="2" t="s">
         <v>210</v>
@@ -12889,7 +12889,7 @@
         <v>OMOP Treatment Episode</v>
       </c>
       <c r="K507" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.25">
@@ -12910,7 +12910,7 @@
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K508" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">
@@ -12927,18 +12927,18 @@
         <v>133</v>
       </c>
       <c r="I509" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J509" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L509" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="510" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="A510" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>497</v>
@@ -12950,7 +12950,7 @@
         <v>213</v>
       </c>
       <c r="F510" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G510" s="2" t="s">
         <v>9</v>
@@ -12959,7 +12959,7 @@
         <v>2</v>
       </c>
       <c r="K510" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.25">
@@ -12999,7 +12999,7 @@
         <v>99</v>
       </c>
       <c r="K512" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="513" spans="2:12" x14ac:dyDescent="0.25">
@@ -13016,7 +13016,7 @@
         <v>100</v>
       </c>
       <c r="K513" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="514" spans="2:12" x14ac:dyDescent="0.25">
@@ -13053,7 +13053,7 @@
         <v>213</v>
       </c>
       <c r="F515" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G515" s="2" t="s">
         <v>9</v>
@@ -13062,7 +13062,7 @@
         <v>2</v>
       </c>
       <c r="K515" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="516" spans="2:12" x14ac:dyDescent="0.25">
@@ -13102,7 +13102,7 @@
         <v>99</v>
       </c>
       <c r="K517" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="518" spans="2:12" x14ac:dyDescent="0.25">
@@ -13119,7 +13119,7 @@
         <v>101</v>
       </c>
       <c r="K518" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="519" spans="2:12" x14ac:dyDescent="0.25">
@@ -13156,7 +13156,7 @@
         <v>213</v>
       </c>
       <c r="F520" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G520" s="2" t="s">
         <v>9</v>
@@ -13165,7 +13165,7 @@
         <v>2</v>
       </c>
       <c r="K520" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="521" spans="2:12" x14ac:dyDescent="0.25">
@@ -13205,7 +13205,7 @@
         <v>99</v>
       </c>
       <c r="K522" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="523" spans="2:12" x14ac:dyDescent="0.25">
@@ -13222,7 +13222,7 @@
         <v>102</v>
       </c>
       <c r="K523" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="524" spans="2:12" x14ac:dyDescent="0.25">
@@ -13259,7 +13259,7 @@
         <v>213</v>
       </c>
       <c r="F525" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G525" s="2" t="s">
         <v>9</v>
@@ -13268,7 +13268,7 @@
         <v>2</v>
       </c>
       <c r="K525" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.25">
@@ -13308,7 +13308,7 @@
         <v>99</v>
       </c>
       <c r="K527" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="528" spans="2:12" x14ac:dyDescent="0.25">
@@ -13325,7 +13325,7 @@
         <v>103</v>
       </c>
       <c r="K528" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.25">
@@ -13376,7 +13376,7 @@
         <v>213</v>
       </c>
       <c r="F531" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G531" s="2" t="s">
         <v>9</v>
@@ -13385,7 +13385,7 @@
         <v>2</v>
       </c>
       <c r="K531" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.25">
@@ -13425,7 +13425,7 @@
         <v>99</v>
       </c>
       <c r="K533" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.25">
@@ -13442,7 +13442,7 @@
         <v>105</v>
       </c>
       <c r="K534" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="535" spans="1:12" ht="27" x14ac:dyDescent="0.25">
@@ -13456,7 +13456,7 @@
         <v>213</v>
       </c>
       <c r="F535" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G535" s="2" t="s">
         <v>9</v>
@@ -13465,7 +13465,7 @@
         <v>2</v>
       </c>
       <c r="K535" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.25">
@@ -13505,7 +13505,7 @@
         <v>99</v>
       </c>
       <c r="K537" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.25">
@@ -13522,7 +13522,7 @@
         <v>106</v>
       </c>
       <c r="K538" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="539" spans="1:12" ht="27" x14ac:dyDescent="0.25">
@@ -13566,7 +13566,7 @@
         <v>172</v>
       </c>
       <c r="F542" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G542" s="2" t="s">
         <v>9</v>
@@ -13575,7 +13575,7 @@
         <v>2</v>
       </c>
       <c r="K542" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.25">
@@ -13615,7 +13615,7 @@
         <v>118</v>
       </c>
       <c r="K544" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.25">
@@ -13643,7 +13643,7 @@
         <v>172</v>
       </c>
       <c r="F546" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G546" s="2" t="s">
         <v>9</v>
@@ -13652,7 +13652,7 @@
         <v>2</v>
       </c>
       <c r="K546" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="547" spans="1:12" x14ac:dyDescent="0.25">
@@ -13669,13 +13669,13 @@
         <v>133</v>
       </c>
       <c r="I547" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J547" s="2" t="s">
         <v>174</v>
       </c>
       <c r="L547" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="548" spans="1:12" x14ac:dyDescent="0.25">
@@ -13683,7 +13683,7 @@
         <v>228</v>
       </c>
       <c r="F548" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G548" s="2" t="s">
         <v>9</v>
@@ -13696,7 +13696,7 @@
         <v>OMOP Tobacco Smoking Status Observation</v>
       </c>
       <c r="K548" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.25">
@@ -13736,10 +13736,13 @@
         <v>120</v>
       </c>
       <c r="K550" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="551" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A551" s="5" t="s">
+        <v>620</v>
+      </c>
       <c r="B551" s="3" t="s">
         <v>504</v>
       </c>
@@ -13750,7 +13753,7 @@
         <v>172</v>
       </c>
       <c r="F551" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G551" s="2" t="s">
         <v>9</v>
@@ -13759,7 +13762,7 @@
         <v>2</v>
       </c>
       <c r="K551" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.25">
@@ -13790,7 +13793,7 @@
         <v>228</v>
       </c>
       <c r="F553" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G553" s="2" t="s">
         <v>9</v>
@@ -13803,7 +13806,7 @@
         <v>OMOP Tobacco Smoking Status Observation</v>
       </c>
       <c r="K553" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="554" spans="1:12" x14ac:dyDescent="0.25">
@@ -13834,16 +13837,13 @@
         <v>176</v>
       </c>
       <c r="F555" s="2" t="s">
-        <v>132</v>
+        <v>618</v>
       </c>
       <c r="G555" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H555" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I555" s="3" t="s">
-        <v>549</v>
+        <v>117</v>
+      </c>
+      <c r="H555" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.25">
@@ -13851,16 +13851,13 @@
         <v>178</v>
       </c>
       <c r="F556" s="2" t="s">
-        <v>550</v>
+        <v>611</v>
       </c>
       <c r="G556" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H556" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="K556" s="2" t="s">
-        <v>562</v>
+        <v>133</v>
+      </c>
+      <c r="H556" s="5" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.25">
@@ -13877,7 +13874,7 @@
         <v>189</v>
       </c>
       <c r="F557" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G557" s="2" t="s">
         <v>9</v>
@@ -13903,7 +13900,7 @@
         <v>193</v>
       </c>
       <c r="K558" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.25">
@@ -13925,7 +13922,7 @@
         <v>197</v>
       </c>
       <c r="F560" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G560" s="2" t="s">
         <v>110</v>
@@ -13934,7 +13931,7 @@
         <v>113</v>
       </c>
       <c r="K560" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="561" spans="2:10" x14ac:dyDescent="0.25">
@@ -13976,7 +13973,7 @@
         <v>213</v>
       </c>
       <c r="F563" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G563" s="2" t="s">
         <v>9</v>
@@ -14076,7 +14073,7 @@
         <v>515</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G569" s="12" t="s">
         <v>110</v>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E729826-CDB9-41C9-9474-8DF622B9B916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF74A9B5-6A43-441E-BE9D-DC0C52FBFF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5959937F-EF1A-4EF7-9756-DEAA4796FC13}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3380" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="626">
   <si>
     <t>Sample Registration</t>
   </si>
@@ -1913,6 +1913,12 @@
   </si>
   <si>
     <t>$.donors[].primary_diagnoses[].treatments[].surgeries[].margin_types_not_assessed[]</t>
+  </si>
+  <si>
+    <t>{current_surgery_episode_id}</t>
+  </si>
+  <si>
+    <t>{current_tobacco_status_observation_id}</t>
   </si>
 </sst>
 </file>
@@ -2342,7 +2348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9C41B9-3FB6-4282-940B-7420BB7A8AED}">
-  <dimension ref="A1:L580"/>
+  <dimension ref="A1:L582"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" style="5" customWidth="1"/>
@@ -2862,7 +2868,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="3" t="str">
-        <f>$B$378</f>
+        <f>$B$379</f>
         <v>OMOP Specimen</v>
       </c>
     </row>
@@ -2925,7 +2931,7 @@
         <v>91</v>
       </c>
       <c r="I23" s="3" t="str">
-        <f>$B$431</f>
+        <f>$B$432</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
@@ -8208,18 +8214,15 @@
         <v>582</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B281" s="3" t="s">
-        <v>491</v>
-      </c>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D281" s="2" t="s">
-        <v>210</v>
+        <v>543</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>200</v>
+        <v>624</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>148</v>
+        <v>590</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>50</v>
@@ -8227,709 +8230,710 @@
       <c r="H281" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I281" s="5" t="str">
+      <c r="I281" s="3" t="str">
+        <f>$B$275</f>
+        <v>OMOP Surgery Episode</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B282" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H282" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I282" s="5" t="str">
         <f>$B$154</f>
         <v>OMOP Treatment Episode</v>
       </c>
-      <c r="K281" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E282" s="2" t="s">
+      <c r="K282" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E283" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F282" s="2" t="s">
+      <c r="F283" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G282" s="2" t="s">
+      <c r="G283" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H282" s="3" t="s">
+      <c r="H283" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I282" s="3" t="str">
+      <c r="I283" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K282" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E283" s="2" t="s">
+      <c r="K283" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E284" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F283" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G283" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H283" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I283" s="3" t="s">
+      <c r="F284" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G284" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H284" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I284" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J283" s="2" t="s">
+      <c r="J284" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L283" s="2" t="s">
+      <c r="L284" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B284" s="3" t="s">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B285" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="D284" s="2" t="s">
+      <c r="D285" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E284" s="2" t="s">
+      <c r="E285" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F284" s="2" t="s">
+      <c r="F285" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G284" s="2" t="s">
+      <c r="G285" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H284" s="3" t="s">
+      <c r="H285" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K284" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C285" s="2" t="s">
+      <c r="K285" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C286" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="E285" s="2" t="s">
+      <c r="E286" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F285" s="2" t="s">
+      <c r="F286" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="G285" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H285" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I285" s="5"/>
-      <c r="J285" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="K285" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="286" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="C286" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H286" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I286" s="5"/>
+      <c r="J286" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="K286" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="C287" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F287" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H287" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E287" s="2" t="s">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E288" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F287" s="2" t="s">
+      <c r="F288" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G287" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H287" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I287" s="3" t="s">
+      <c r="G288" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I288" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="K287" s="2" t="s">
+      <c r="K288" s="2" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B288" s="3" t="s">
+    <row r="289" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B289" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D288" s="2" t="s">
+      <c r="D289" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E288" s="2" t="s">
+      <c r="E289" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F288" s="2" t="s">
+      <c r="F289" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G288" s="2" t="s">
+      <c r="G289" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H288" s="3" t="s">
+      <c r="H289" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I288" s="3" t="str">
+      <c r="I289" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K288" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="289" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E289" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G289" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H289" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I289" s="3" t="str">
-        <f>$B$284</f>
-        <v>OMOP Surgery Procedure</v>
-      </c>
       <c r="K289" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="290" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E290" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F290" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G290" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H290" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I290" s="3" t="str">
+        <f>$B$285</f>
+        <v>OMOP Surgery Procedure</v>
+      </c>
+      <c r="K290" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="291" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E291" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F290" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G290" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H290" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I290" s="3" t="s">
+      <c r="F291" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G291" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H291" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I291" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="J290" s="2" t="s">
+      <c r="J291" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L290" s="2" t="s">
+      <c r="L291" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="291" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B291" s="3" t="s">
+    <row r="292" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B292" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="D291" s="2" t="s">
+      <c r="D292" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E291" s="2" t="s">
+      <c r="E292" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F291" s="2" t="s">
+      <c r="F292" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G291" s="2" t="s">
+      <c r="G292" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H291" s="3" t="s">
+      <c r="H292" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K291" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="292" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E292" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H292" s="6"/>
-      <c r="I292" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="J292" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L292" s="2" t="s">
-        <v>333</v>
+      <c r="K292" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="293" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E293" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H293" s="5" t="s">
-        <v>133</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="H293" s="6"/>
       <c r="I293" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K293" s="2" t="s">
-        <v>582</v>
+        <v>332</v>
+      </c>
+      <c r="J293" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L293" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="294" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E294" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F294" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G294" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H294" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I294" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K294" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="295" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E295" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F294" s="2" t="s">
+      <c r="F295" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G294" s="2" t="s">
+      <c r="G295" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H294" s="3" t="s">
+      <c r="H295" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I294" s="3" t="str">
+      <c r="I295" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K294" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="295" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E295" s="2" t="s">
+      <c r="K295" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="296" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E296" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F295" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G295" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H295" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I295" s="3" t="s">
+      <c r="F296" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H296" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I296" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J295" s="2" t="s">
+      <c r="J296" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L295" s="2" t="s">
+      <c r="L296" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="296" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C296" s="2" t="s">
+    <row r="297" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C297" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E296" s="2" t="s">
+      <c r="E297" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F296" s="2" t="s">
+      <c r="F297" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G296" s="2" t="s">
+      <c r="G297" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H296" s="6" t="s">
+      <c r="H297" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K296" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="297" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E297" s="2" t="s">
+      <c r="K297" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="298" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E298" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F297" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G297" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H297" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I297" s="3" t="s">
+      <c r="F298" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G298" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H298" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I298" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="J297" s="2" t="s">
+      <c r="J298" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L297" s="2" t="s">
+      <c r="L298" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="298" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B298" s="3" t="s">
+    <row r="299" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B299" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D298" s="2" t="s">
+      <c r="D299" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E298" s="2" t="s">
+      <c r="E299" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F298" s="2" t="s">
+      <c r="F299" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G298" s="2" t="s">
+      <c r="G299" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H298" s="3" t="s">
+      <c r="H299" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K298" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="299" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E299" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H299" s="6"/>
-      <c r="I299" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="J299" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L299" s="2" t="s">
-        <v>338</v>
+      <c r="K299" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="300" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E300" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G300" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H300" s="5" t="s">
-        <v>133</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="H300" s="6"/>
       <c r="I300" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K300" s="2" t="s">
-        <v>582</v>
+        <v>337</v>
+      </c>
+      <c r="J300" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L300" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="301" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E301" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F301" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G301" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H301" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I301" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K301" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="302" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E302" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F301" s="2" t="s">
+      <c r="F302" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G301" s="2" t="s">
+      <c r="G302" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H301" s="3" t="s">
+      <c r="H302" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I301" s="3" t="str">
+      <c r="I302" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K301" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="302" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E302" s="2" t="s">
+      <c r="K302" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="303" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E303" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F302" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G302" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H302" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I302" s="3" t="s">
+      <c r="F303" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G303" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H303" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I303" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J302" s="2" t="s">
+      <c r="J303" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L302" s="2" t="s">
+      <c r="L303" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="303" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C303" s="2" t="s">
+    <row r="304" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C304" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E303" s="2" t="s">
+      <c r="E304" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F303" s="2" t="s">
+      <c r="F304" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G303" s="2" t="s">
+      <c r="G304" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H303" s="6" t="s">
+      <c r="H304" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K303" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="304" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E304" s="2" t="s">
+      <c r="K304" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="305" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E305" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F304" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G304" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H304" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I304" s="3" t="s">
+      <c r="F305" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G305" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H305" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I305" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="J304" s="2" t="s">
+      <c r="J305" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L304" s="2" t="s">
+      <c r="L305" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="305" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="B305" s="3" t="s">
+    <row r="306" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="B306" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="D305" s="2" t="s">
+      <c r="D306" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E305" s="2" t="s">
+      <c r="E306" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F305" s="2" t="s">
+      <c r="F306" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G305" s="2" t="s">
+      <c r="G306" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H305" s="3" t="s">
+      <c r="H306" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K305" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="306" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E306" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H306" s="6"/>
-      <c r="I306" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="J306" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L306" s="2" t="s">
-        <v>341</v>
+      <c r="K306" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="307" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E307" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G307" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H307" s="5" t="s">
-        <v>133</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="H307" s="6"/>
       <c r="I307" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K307" s="2" t="s">
-        <v>582</v>
+        <v>340</v>
+      </c>
+      <c r="J307" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L307" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="308" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E308" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F308" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G308" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H308" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I308" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K308" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="309" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E309" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F308" s="2" t="s">
+      <c r="F309" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G308" s="2" t="s">
+      <c r="G309" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H308" s="3" t="s">
+      <c r="H309" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I308" s="3" t="str">
+      <c r="I309" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K308" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="309" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E309" s="2" t="s">
+      <c r="K309" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="310" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E310" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F309" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G309" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H309" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I309" s="3" t="s">
+      <c r="F310" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G310" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H310" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I310" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J309" s="2" t="s">
+      <c r="J310" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L309" s="2" t="s">
+      <c r="L310" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="310" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C310" s="2" t="s">
+    <row r="311" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C311" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E310" s="2" t="s">
+      <c r="E311" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F310" s="2" t="s">
+      <c r="F311" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G310" s="2" t="s">
+      <c r="G311" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H310" s="6" t="s">
+      <c r="H311" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K310" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="311" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E311" s="2" t="s">
+      <c r="K311" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="312" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E312" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F311" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G311" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H311" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I311" s="3" t="s">
+      <c r="F312" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G312" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H312" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I312" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="J311" s="2" t="s">
+      <c r="J312" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L311" s="2" t="s">
+      <c r="L312" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="312" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B312" s="3" t="s">
+    <row r="313" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B313" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="D312" s="2" t="s">
+      <c r="D313" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E312" s="2" t="s">
+      <c r="E313" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F312" s="2" t="s">
+      <c r="F313" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G312" s="2" t="s">
+      <c r="G313" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H312" s="3" t="s">
+      <c r="H313" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K312" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="313" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E313" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G313" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H313" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I313" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J313" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L313" s="2" t="s">
-        <v>322</v>
+      <c r="K313" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="314" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E314" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>133</v>
@@ -8938,88 +8942,88 @@
         <v>133</v>
       </c>
       <c r="I314" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K314" s="2" t="s">
-        <v>582</v>
+        <v>321</v>
+      </c>
+      <c r="J314" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L314" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="315" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E315" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F315" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G315" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H315" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K315" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="316" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E316" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F315" s="2" t="s">
+      <c r="F316" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G315" s="2" t="s">
+      <c r="G316" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H315" s="3" t="s">
+      <c r="H316" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I315" s="3" t="str">
+      <c r="I316" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K315" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="316" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E316" s="2" t="s">
+      <c r="K316" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="317" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E317" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F316" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G316" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H316" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I316" s="3" t="s">
+      <c r="F317" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G317" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H317" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I317" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J316" s="2" t="s">
+      <c r="J317" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L316" s="2" t="s">
+      <c r="L317" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="317" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C317" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G317" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H317" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J317" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K317" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="318" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C318" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>75</v>
@@ -9027,59 +9031,59 @@
       <c r="H318" s="6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="319" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B319" s="3" t="s">
+      <c r="J318" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K318" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="319" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C319" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F319" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G319" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H319" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="320" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B320" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="D319" s="2" t="s">
+      <c r="D320" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E319" s="2" t="s">
+      <c r="E320" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F319" s="2" t="s">
+      <c r="F320" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G319" s="2" t="s">
+      <c r="G320" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H319" s="3" t="s">
+      <c r="H320" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K319" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="320" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E320" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G320" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H320" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I320" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J320" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L320" s="2" t="s">
-        <v>345</v>
+      <c r="K320" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="321" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E321" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>133</v>
@@ -9088,85 +9092,88 @@
         <v>133</v>
       </c>
       <c r="I321" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K321" s="2" t="s">
-        <v>582</v>
+        <v>344</v>
+      </c>
+      <c r="J321" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L321" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="322" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E322" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F322" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G322" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H322" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I322" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K322" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="323" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E323" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F322" s="2" t="s">
+      <c r="F323" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G322" s="2" t="s">
+      <c r="G323" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H322" s="3" t="s">
+      <c r="H323" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I322" s="3" t="str">
+      <c r="I323" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K322" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="323" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E323" s="2" t="s">
+      <c r="K323" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="324" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E324" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F323" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G323" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H323" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I323" s="3" t="s">
+      <c r="F324" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G324" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H324" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I324" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J323" s="2" t="s">
+      <c r="J324" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L323" s="2" t="s">
+      <c r="L324" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="324" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C324" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G324" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H324" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K324" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="325" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C325" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>75</v>
@@ -9174,59 +9181,56 @@
       <c r="H325" s="6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="326" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B326" s="3" t="s">
+      <c r="K325" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="326" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C326" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F326" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G326" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H326" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="327" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B327" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="D326" s="2" t="s">
+      <c r="D327" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E326" s="2" t="s">
+      <c r="E327" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F326" s="2" t="s">
+      <c r="F327" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G326" s="2" t="s">
+      <c r="G327" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H326" s="3" t="s">
+      <c r="H327" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K326" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="327" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E327" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F327" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G327" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H327" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I327" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="J327" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L327" s="2" t="s">
-        <v>349</v>
+      <c r="K327" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="328" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E328" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>133</v>
@@ -9235,85 +9239,88 @@
         <v>133</v>
       </c>
       <c r="I328" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K328" s="2" t="s">
-        <v>582</v>
+        <v>348</v>
+      </c>
+      <c r="J328" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L328" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="329" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E329" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F329" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G329" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H329" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I329" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K329" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="330" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E330" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F329" s="2" t="s">
+      <c r="F330" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G329" s="2" t="s">
+      <c r="G330" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H329" s="3" t="s">
+      <c r="H330" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I329" s="3" t="str">
+      <c r="I330" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K329" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="330" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E330" s="2" t="s">
+      <c r="K330" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="331" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E331" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F330" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G330" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H330" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I330" s="3" t="s">
+      <c r="F331" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G331" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H331" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I331" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J330" s="2" t="s">
+      <c r="J331" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L330" s="2" t="s">
+      <c r="L331" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="331" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C331" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E331" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F331" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G331" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H331" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K331" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="332" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C332" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>75</v>
@@ -9321,59 +9328,56 @@
       <c r="H332" s="6" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="333" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="B333" s="3" t="s">
+      <c r="K332" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="333" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C333" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F333" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G333" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H333" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="334" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="B334" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D333" s="2" t="s">
+      <c r="D334" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E333" s="2" t="s">
+      <c r="E334" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F333" s="2" t="s">
+      <c r="F334" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G333" s="2" t="s">
+      <c r="G334" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H333" s="3" t="s">
+      <c r="H334" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K333" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="334" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E334" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F334" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G334" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H334" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I334" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="J334" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L334" s="2" t="s">
-        <v>353</v>
+      <c r="K334" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="335" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E335" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>133</v>
@@ -9382,85 +9386,88 @@
         <v>133</v>
       </c>
       <c r="I335" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K335" s="2" t="s">
-        <v>582</v>
+        <v>352</v>
+      </c>
+      <c r="J335" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L335" s="2" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="336" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E336" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F336" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G336" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H336" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I336" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K336" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="337" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E337" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F336" s="2" t="s">
+      <c r="F337" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G336" s="2" t="s">
+      <c r="G337" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H336" s="3" t="s">
+      <c r="H337" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I336" s="3" t="str">
+      <c r="I337" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K336" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="337" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E337" s="2" t="s">
+      <c r="K337" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="338" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E338" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F337" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G337" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H337" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I337" s="3" t="s">
+      <c r="F338" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G338" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H338" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I338" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J337" s="2" t="s">
+      <c r="J338" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L337" s="2" t="s">
+      <c r="L338" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="338" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C338" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E338" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F338" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G338" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H338" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K338" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="339" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C339" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>75</v>
@@ -9468,59 +9475,56 @@
       <c r="H339" s="6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="340" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="B340" s="3" t="s">
+      <c r="K339" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="340" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C340" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F340" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G340" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H340" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="341" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="B341" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="D340" s="2" t="s">
+      <c r="D341" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E340" s="2" t="s">
+      <c r="E341" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F340" s="2" t="s">
+      <c r="F341" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G340" s="2" t="s">
+      <c r="G341" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H340" s="3" t="s">
+      <c r="H341" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K340" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="341" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E341" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F341" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G341" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H341" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I341" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="J341" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L341" s="2" t="s">
-        <v>371</v>
+      <c r="K341" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="342" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E342" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>133</v>
@@ -9529,85 +9533,88 @@
         <v>133</v>
       </c>
       <c r="I342" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K342" s="2" t="s">
-        <v>582</v>
+        <v>370</v>
+      </c>
+      <c r="J342" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L342" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="343" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E343" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F343" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G343" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H343" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I343" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K343" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="344" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E344" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F343" s="2" t="s">
+      <c r="F344" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G343" s="2" t="s">
+      <c r="G344" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H343" s="3" t="s">
+      <c r="H344" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I343" s="3" t="str">
+      <c r="I344" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K343" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="344" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E344" s="2" t="s">
+      <c r="K344" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="345" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E345" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F344" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G344" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H344" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I344" s="3" t="s">
+      <c r="F345" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G345" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H345" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I345" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J344" s="2" t="s">
+      <c r="J345" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L344" s="2" t="s">
+      <c r="L345" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="345" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C345" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E345" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F345" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G345" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H345" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="K345" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="346" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C346" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>75</v>
@@ -9615,59 +9622,56 @@
       <c r="H346" s="6" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="347" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="B347" s="3" t="s">
+      <c r="K346" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="347" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C347" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F347" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G347" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H347" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="348" spans="2:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="B348" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="D347" s="2" t="s">
+      <c r="D348" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E347" s="2" t="s">
+      <c r="E348" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F347" s="2" t="s">
+      <c r="F348" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G347" s="2" t="s">
+      <c r="G348" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H347" s="3" t="s">
+      <c r="H348" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K347" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="348" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E348" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F348" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G348" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H348" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I348" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="J348" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L348" s="2" t="s">
-        <v>375</v>
+      <c r="K348" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="349" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E349" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>133</v>
@@ -9676,85 +9680,88 @@
         <v>133</v>
       </c>
       <c r="I349" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K349" s="2" t="s">
-        <v>582</v>
+        <v>374</v>
+      </c>
+      <c r="J349" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L349" s="2" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="350" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E350" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F350" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G350" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H350" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I350" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K350" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="351" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E351" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F350" s="2" t="s">
+      <c r="F351" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G350" s="2" t="s">
+      <c r="G351" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H350" s="3" t="s">
+      <c r="H351" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I350" s="3" t="str">
+      <c r="I351" s="3" t="str">
         <f>$B$275</f>
         <v>OMOP Surgery Episode</v>
       </c>
-      <c r="K350" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="351" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E351" s="2" t="s">
+      <c r="K351" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="352" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E352" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F351" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G351" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H351" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I351" s="3" t="s">
+      <c r="F352" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G352" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H352" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I352" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J351" s="2" t="s">
+      <c r="J352" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L351" s="2" t="s">
+      <c r="L352" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="352" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C352" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E352" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F352" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G352" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H352" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K352" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C353" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>75</v>
@@ -9762,62 +9769,59 @@
       <c r="H353" s="6" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="354" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A354" s="5" t="s">
+      <c r="K353" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C354" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F354" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G354" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H354" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A355" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="B354" s="3" t="s">
+      <c r="B355" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D354" s="2" t="s">
+      <c r="D355" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E354" s="2" t="s">
+      <c r="E355" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F354" s="2" t="s">
+      <c r="F355" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G354" s="2" t="s">
+      <c r="G355" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H354" s="3" t="s">
+      <c r="H355" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K354" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E355" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F355" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G355" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H355" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I355" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="J355" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L355" s="2" t="s">
-        <v>357</v>
+      <c r="K355" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E356" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>133</v>
@@ -9826,168 +9830,164 @@
         <v>133</v>
       </c>
       <c r="I356" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K356" s="2" t="s">
-        <v>582</v>
+        <v>356</v>
+      </c>
+      <c r="J356" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L356" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E357" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>590</v>
+        <v>183</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H357" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I357" s="3" t="str">
-        <f>$B$275</f>
-        <v>OMOP Surgery Episode</v>
+        <v>133</v>
+      </c>
+      <c r="H357" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I357" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="K357" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E358" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F358" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G358" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H358" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I358" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E359" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F358" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G358" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H358" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I358" s="3" t="s">
+      <c r="F359" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G359" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H359" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I359" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J358" s="2" t="s">
+      <c r="J359" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L358" s="2" t="s">
+      <c r="L359" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C359" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="E359" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F359" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="G359" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H359" s="6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C360" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F360" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G360" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H360" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C361" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E360" s="2" t="s">
+      <c r="E361" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F360" s="2" t="s">
+      <c r="F361" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="G360" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H360" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E361" s="2" t="s">
+      <c r="G361" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H361" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E362" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F361" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G361" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H361" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I361" s="3" t="s">
+      <c r="F362" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G362" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H362" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I362" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="J361" s="2" t="s">
+      <c r="J362" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L361" s="2" t="s">
+      <c r="L362" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A362" s="5" t="s">
+    <row r="363" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A363" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="B362" s="3" t="s">
+      <c r="B363" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="D362" s="2" t="s">
+      <c r="D363" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E362" s="2" t="s">
+      <c r="E363" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F362" s="2" t="s">
+      <c r="F363" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G362" s="2" t="s">
+      <c r="G363" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H362" s="3" t="s">
+      <c r="H363" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K362" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E363" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F363" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G363" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H363" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I363" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="J363" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L363" s="2" t="s">
-        <v>357</v>
+      <c r="K363" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E364" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>133</v>
@@ -9996,168 +9996,164 @@
         <v>133</v>
       </c>
       <c r="I364" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K364" s="2" t="s">
-        <v>582</v>
+        <v>356</v>
+      </c>
+      <c r="J364" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L364" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E365" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>590</v>
+        <v>183</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H365" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I365" s="3" t="str">
-        <f>$B$275</f>
-        <v>OMOP Surgery Episode</v>
+        <v>133</v>
+      </c>
+      <c r="H365" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I365" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="K365" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E366" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F366" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G366" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H366" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I366" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E367" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F366" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G366" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H366" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I366" s="3" t="s">
+      <c r="F367" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G367" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H367" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I367" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J366" s="2" t="s">
+      <c r="J367" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L366" s="2" t="s">
+      <c r="L367" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C367" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E367" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F367" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="G367" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H367" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C368" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F368" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G368" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H368" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C369" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="E368" s="2" t="s">
+      <c r="E369" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F368" s="2" t="s">
+      <c r="F369" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="G368" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H368" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E369" s="2" t="s">
+      <c r="G369" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H369" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E370" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F369" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G369" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H369" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I369" s="3" t="s">
+      <c r="F370" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G370" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H370" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I370" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="J369" s="2" t="s">
+      <c r="J370" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L369" s="2" t="s">
+      <c r="L370" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A370" s="5" t="s">
+    <row r="371" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A371" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="B370" s="3" t="s">
+      <c r="B371" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D370" s="2" t="s">
+      <c r="D371" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E370" s="2" t="s">
+      <c r="E371" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F370" s="2" t="s">
+      <c r="F371" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G370" s="2" t="s">
+      <c r="G371" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H370" s="3" t="s">
+      <c r="H371" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K370" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E371" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F371" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G371" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H371" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I371" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="J371" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L371" s="2" t="s">
-        <v>357</v>
+      <c r="K371" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E372" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>133</v>
@@ -10166,232 +10162,231 @@
         <v>133</v>
       </c>
       <c r="I372" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K372" s="2" t="s">
-        <v>582</v>
+        <v>356</v>
+      </c>
+      <c r="J372" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L372" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E373" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>590</v>
+        <v>183</v>
       </c>
       <c r="G373" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H373" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I373" s="3" t="str">
-        <f>$B$275</f>
-        <v>OMOP Surgery Episode</v>
+        <v>133</v>
+      </c>
+      <c r="H373" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I373" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="K373" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E374" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F374" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G374" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H374" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I374" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E375" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F374" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G374" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H374" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I374" s="3" t="s">
+      <c r="F375" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G375" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H375" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I375" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J374" s="2" t="s">
+      <c r="J375" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L374" s="2" t="s">
+      <c r="L375" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C375" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E375" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F375" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="G375" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H375" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C376" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F376" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G376" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H376" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C377" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E376" s="2" t="s">
+      <c r="E377" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F376" s="2" t="s">
+      <c r="F377" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="G376" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H376" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E377" s="2" t="s">
+      <c r="G377" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H377" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E378" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F377" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G377" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H377" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I377" s="3" t="s">
+      <c r="F378" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G378" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H378" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I378" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="J377" s="2" t="s">
+      <c r="J378" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L377" s="2" t="s">
+      <c r="L378" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="A378" s="5" t="s">
+    <row r="379" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A379" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="B378" s="3" t="s">
+      <c r="B379" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D378" s="2" t="s">
+      <c r="D379" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="E378" s="2" t="s">
+      <c r="E379" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="F378" s="2" t="s">
+      <c r="F379" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="G378" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H378" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K378" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A379" s="2"/>
-      <c r="B379" s="2"/>
-      <c r="D379" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E379" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="F379" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H379" s="5" t="s">
         <v>3</v>
+      </c>
+      <c r="K379" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
+      <c r="D380" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="E380" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F380" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G380" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H380" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A381" s="2"/>
+      <c r="B381" s="2"/>
+      <c r="E381" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F380" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G380" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H380" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I380" s="3" t="s">
+      <c r="F381" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G381" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H381" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I381" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="J380" s="2" t="s">
+      <c r="J381" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L380" s="2" t="s">
+      <c r="L381" s="2" t="s">
         <v>597</v>
-      </c>
-    </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C381" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E381" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F381" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G381" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H381" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K381" s="2" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C382" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H382" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J382" s="2" t="s">
-        <v>531</v>
+        <v>22</v>
+      </c>
+      <c r="K382" s="2" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C383" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>19</v>
@@ -10399,146 +10394,143 @@
       <c r="H383" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="384" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B384" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>130</v>
+      <c r="J383" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C384" s="2" t="s">
+        <v>383</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>172</v>
+        <v>384</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H384" s="5" t="s">
+      <c r="H384" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="385" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B385" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E385" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F385" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G385" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H385" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K384" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="385" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E385" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F385" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G385" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H385" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I385" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="J385" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L385" s="2" t="s">
-        <v>386</v>
+      <c r="K385" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="386" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E386" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H386" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K386" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H386" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I386" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J386" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L386" s="2" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="387" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E387" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H387" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I387" s="3" t="str">
-        <f>$B$378</f>
-        <v>OMOP Specimen</v>
+      <c r="H387" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K387" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="388" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E388" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F388" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G388" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H388" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I388" s="3" t="str">
+        <f>$B$379</f>
+        <v>OMOP Specimen</v>
+      </c>
+      <c r="K388" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="389" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E389" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F388" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G388" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H388" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I388" s="3" t="s">
+      <c r="F389" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G389" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H389" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I389" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J388" s="2" t="s">
+      <c r="J389" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L388" s="2" t="s">
+      <c r="L389" s="2" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="389" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C389" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E389" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F389" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G389" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H389" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J389" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K389" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="390" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C390" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>19</v>
@@ -10546,132 +10538,135 @@
       <c r="H390" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="391" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B391" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="D391" s="2" t="s">
-        <v>130</v>
+      <c r="J390" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K390" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="391" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C391" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H391" s="5" t="s">
+      <c r="H391" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="392" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B392" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E392" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F392" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G392" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H392" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K391" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="392" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E392" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F392" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G392" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H392" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I392" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="J392" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L392" s="2" t="s">
-        <v>391</v>
+      <c r="K392" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="393" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E393" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H393" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K393" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H393" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I393" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="J393" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L393" s="2" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="394" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E394" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H394" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I394" s="3" t="str">
-        <f>$B$378</f>
-        <v>OMOP Specimen</v>
+      <c r="H394" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K394" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="395" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E395" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F395" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G395" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H395" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I395" s="3" t="str">
+        <f>$B$379</f>
+        <v>OMOP Specimen</v>
+      </c>
+      <c r="K395" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="396" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E396" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F395" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G395" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H395" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I395" s="3" t="s">
+      <c r="F396" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G396" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H396" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I396" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J395" s="2" t="s">
+      <c r="J396" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L395" s="2" t="s">
+      <c r="L396" s="2" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="396" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C396" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E396" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F396" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G396" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H396" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K396" s="2" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="397" spans="2:12" x14ac:dyDescent="0.25">
@@ -10679,10 +10674,10 @@
         <v>392</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>19</v>
@@ -10690,22 +10685,25 @@
       <c r="H397" s="6" t="s">
         <v>29</v>
       </c>
+      <c r="K397" s="2" t="s">
+        <v>583</v>
+      </c>
     </row>
     <row r="398" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C398" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>275</v>
+        <v>178</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H398" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="399" spans="2:12" x14ac:dyDescent="0.25">
@@ -10713,10 +10711,10 @@
         <v>393</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>19</v>
@@ -10725,142 +10723,139 @@
         <v>28</v>
       </c>
     </row>
-    <row r="400" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B400" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>130</v>
+    <row r="400" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C400" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>172</v>
+        <v>277</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H400" s="5" t="s">
+      <c r="H400" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="401" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B401" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E401" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F401" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G401" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H401" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K400" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="401" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E401" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F401" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G401" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H401" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I401" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="J401" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L401" s="2" t="s">
-        <v>395</v>
+      <c r="K401" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="402" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E402" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H402" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K402" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H402" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I402" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="J402" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L402" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="403" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E403" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H403" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I403" s="3" t="str">
-        <f>$B$378</f>
-        <v>OMOP Specimen</v>
+      <c r="H403" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K403" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="404" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E404" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F404" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G404" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H404" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I404" s="3" t="str">
+        <f>$B$379</f>
+        <v>OMOP Specimen</v>
+      </c>
+      <c r="K404" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="405" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E405" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F404" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G404" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H404" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I404" s="3" t="s">
+      <c r="F405" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G405" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H405" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I405" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J404" s="2" t="s">
+      <c r="J405" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L404" s="2" t="s">
+      <c r="L405" s="2" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="405" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C405" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E405" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F405" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G405" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H405" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K405" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="406" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C406" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>19</v>
@@ -10868,132 +10863,132 @@
       <c r="H406" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="407" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B407" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>130</v>
+      <c r="K406" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="407" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C407" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H407" s="5" t="s">
+      <c r="H407" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="408" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B408" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E408" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F408" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G408" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H408" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K407" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="408" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E408" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F408" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G408" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H408" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I408" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="J408" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L408" s="2" t="s">
-        <v>399</v>
+      <c r="K408" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="409" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E409" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G409" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H409" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K409" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H409" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I409" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="J409" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L409" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="410" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E410" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H410" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I410" s="3" t="str">
-        <f>$B$378</f>
-        <v>OMOP Specimen</v>
+      <c r="H410" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K410" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="411" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E411" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F411" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G411" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H411" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I411" s="3" t="str">
+        <f>$B$379</f>
+        <v>OMOP Specimen</v>
+      </c>
+      <c r="K411" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="412" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E412" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F411" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G411" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H411" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I411" s="3" t="s">
+      <c r="F412" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G412" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H412" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I412" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J411" s="2" t="s">
+      <c r="J412" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L411" s="2" t="s">
+      <c r="L412" s="2" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="412" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C412" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="E412" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F412" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G412" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H412" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K412" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="413" spans="2:12" x14ac:dyDescent="0.25">
@@ -11001,10 +10996,10 @@
         <v>400</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>19</v>
@@ -11012,132 +11007,132 @@
       <c r="H413" s="6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="414" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B414" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="D414" s="2" t="s">
-        <v>130</v>
+      <c r="K413" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="414" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C414" s="2" t="s">
+        <v>400</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H414" s="5" t="s">
+      <c r="H414" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="415" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B415" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E415" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F415" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G415" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H415" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K414" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="415" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E415" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F415" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G415" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H415" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I415" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="J415" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L415" s="2" t="s">
-        <v>402</v>
+      <c r="K415" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="416" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E416" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G416" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H416" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K416" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H416" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I416" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="J416" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L416" s="2" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E417" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H417" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I417" s="3" t="str">
-        <f>$B$378</f>
-        <v>OMOP Specimen</v>
+      <c r="H417" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K417" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E418" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F418" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G418" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H418" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I418" s="3" t="str">
+        <f>$B$379</f>
+        <v>OMOP Specimen</v>
+      </c>
+      <c r="K418" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E419" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F418" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G418" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H418" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I418" s="3" t="s">
+      <c r="F419" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G419" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H419" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I419" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J418" s="2" t="s">
+      <c r="J419" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L418" s="2" t="s">
+      <c r="L419" s="2" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C419" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E419" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F419" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G419" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H419" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K419" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.25">
@@ -11145,10 +11140,10 @@
         <v>403</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>19</v>
@@ -11156,218 +11151,219 @@
       <c r="H420" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="421" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B421" s="3" t="s">
+      <c r="K420" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C421" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E421" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F421" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G421" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H421" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B422" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="D421" s="2" t="s">
+      <c r="D422" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E421" s="2" t="s">
+      <c r="E422" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F421" s="2" t="s">
+      <c r="F422" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G421" s="2" t="s">
+      <c r="G422" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H421" s="8" t="s">
+      <c r="H422" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I421" s="5" t="str">
+      <c r="I422" s="5" t="str">
         <f>$B$65</f>
         <v>OMOP Primary Dx Episode</v>
       </c>
-      <c r="K421" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E422" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F422" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G422" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H422" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I422" s="3" t="str">
-        <f>$B$378</f>
-        <v>OMOP Specimen</v>
-      </c>
       <c r="K422" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E423" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F423" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G423" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H423" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I423" s="3" t="str">
+        <f>$B$379</f>
+        <v>OMOP Specimen</v>
+      </c>
+      <c r="K423" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E424" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F423" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G423" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H423" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I423" s="3" t="s">
+      <c r="F424" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G424" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H424" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I424" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J423" s="2" t="s">
+      <c r="J424" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L423" s="2" t="s">
+      <c r="L424" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B424" s="3" t="s">
+    <row r="425" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B425" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="D424" s="2" t="s">
+      <c r="D425" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E424" s="2" t="s">
+      <c r="E425" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F424" s="2" t="s">
+      <c r="F425" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G424" s="2" t="s">
+      <c r="G425" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H424" s="8" t="s">
+      <c r="H425" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I424" s="3" t="str">
+      <c r="I425" s="3" t="str">
         <f>$B$154</f>
         <v>OMOP Treatment Episode</v>
       </c>
-      <c r="K424" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E425" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F425" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G425" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H425" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I425" s="3" t="str">
-        <f>$B$378</f>
-        <v>OMOP Specimen</v>
-      </c>
       <c r="K425" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E426" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F426" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G426" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H426" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I426" s="3" t="str">
+        <f>$B$379</f>
+        <v>OMOP Specimen</v>
+      </c>
+      <c r="K426" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E427" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F426" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G426" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H426" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I426" s="3" t="s">
+      <c r="F427" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G427" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H427" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I427" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J426" s="2" t="s">
+      <c r="J427" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L426" s="2" t="s">
+      <c r="L427" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B427" s="3" t="s">
+    <row r="428" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B428" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="G427" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H427" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="428" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="G428" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H428" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" ht="27" x14ac:dyDescent="0.25">
       <c r="G429" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H429" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="430" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G430" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H430" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="G431" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H431" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="A431" s="5" t="s">
+    <row r="432" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A432" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="B431" s="3" t="s">
+      <c r="B432" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="D431" s="2" t="s">
+      <c r="D432" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="E431" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F431" s="2" t="s">
+      <c r="E432" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F432" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="G431" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H431" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A432" s="2"/>
-      <c r="B432" s="2"/>
-      <c r="D432" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E432" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F432" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>90</v>
@@ -11375,53 +11371,55 @@
       <c r="H432" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K432" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="433" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A433" s="2"/>
+      <c r="B433" s="2"/>
+      <c r="D433" s="2" t="s">
+        <v>573</v>
+      </c>
       <c r="E433" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F433" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G433" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H433" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K433" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E434" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="F433" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G433" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H433" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I433" s="3" t="s">
+      <c r="F434" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G434" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H434" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I434" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="J433" s="2" t="s">
+      <c r="J434" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="L433" s="2" t="s">
+      <c r="L434" s="2" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="434" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E434" s="2" t="s">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E435" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="F434" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G434" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H434" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K434" s="2" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="435" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E435" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="F435" s="2" t="s">
         <v>183</v>
@@ -11432,138 +11430,138 @@
       <c r="H435" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I435" s="8"/>
       <c r="K435" s="2" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="436" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B436" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="D436" s="2" t="s">
-        <v>130</v>
-      </c>
+    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E436" s="2" t="s">
-        <v>172</v>
+        <v>572</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H436" s="3" t="s">
+      <c r="H436" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I436" s="8"/>
+      <c r="K436" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="437" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B437" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E437" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F437" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G437" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H437" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K436" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="437" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E437" s="2" t="s">
+      <c r="K437" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E438" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F437" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G437" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H437" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I437" s="3" t="s">
+      <c r="F438" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G438" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H438" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I438" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J437" s="2" t="s">
+      <c r="J438" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L437" s="2" t="s">
+      <c r="L438" s="2" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="438" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E438" s="2" t="s">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E439" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F438" s="2" t="s">
+      <c r="F439" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G438" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H438" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K438" s="2" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="439" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E439" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F439" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H439" s="3" t="s">
+      <c r="H439" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K439" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E440" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F440" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G440" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H440" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I439" s="3" t="str">
-        <f>$B$431</f>
+      <c r="I440" s="3" t="str">
+        <f>$B$432</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
-    <row r="440" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E440" s="2" t="s">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E441" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F440" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G440" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H440" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I440" s="3" t="s">
+      <c r="F441" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G441" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H441" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I441" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="J440" s="2" t="s">
+      <c r="J441" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L440" s="2" t="s">
+      <c r="L441" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="441" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E441" s="2" t="s">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E442" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F441" s="2" t="s">
+      <c r="F442" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G441" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H441" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K441" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="442" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E442" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F442" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>90</v>
@@ -11571,120 +11569,120 @@
       <c r="H442" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="443" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B443" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="D443" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="K442" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E443" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H443" s="3" t="s">
+      <c r="H443" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="444" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B444" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E444" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F444" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G444" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H444" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K443" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="444" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E444" s="2" t="s">
+      <c r="K444" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E445" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F444" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G444" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H444" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I444" s="3" t="s">
+      <c r="F445" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G445" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H445" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I445" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="J444" s="2" t="s">
+      <c r="J445" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L444" s="2" t="s">
+      <c r="L445" s="2" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="445" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E445" s="2" t="s">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E446" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F445" s="2" t="s">
+      <c r="F446" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G445" s="2" t="s">
+      <c r="G446" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H445" s="3" t="s">
+      <c r="H446" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I445" s="3" t="str">
-        <f>$B$431</f>
+      <c r="I446" s="3" t="str">
+        <f>$B$432</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
-      <c r="K445" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="446" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E446" s="2" t="s">
+      <c r="K446" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E447" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F446" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G446" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H446" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I446" s="3" t="s">
+      <c r="F447" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G447" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H447" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I447" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="J446" s="2" t="s">
+      <c r="J447" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L446" s="2" t="s">
+      <c r="L447" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="447" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E447" s="2" t="s">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E448" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F447" s="2" t="s">
+      <c r="F448" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G447" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H447" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K447" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="448" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E448" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F448" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>90</v>
@@ -11692,123 +11690,120 @@
       <c r="H448" s="11" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="449" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B449" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="D449" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="K448" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E449" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F449" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H449" s="3" t="s">
+      <c r="H449" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="450" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B450" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E450" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F450" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G450" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H450" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K449" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E450" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F450" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G450" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H450" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I450" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J450" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L450" s="2" t="s">
-        <v>405</v>
+      <c r="K450" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E451" s="2" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="F451" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G451" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H451" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I451" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K451" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H451" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I451" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J451" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L451" s="2" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E452" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F452" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G452" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H452" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I452" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J452" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L452" s="2" t="s">
-        <v>578</v>
+        <v>90</v>
+      </c>
+      <c r="H452" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I452" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K452" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E453" s="2" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="G453" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H453" s="6" t="s">
-        <v>97</v>
+        <v>133</v>
+      </c>
+      <c r="H453" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I453" s="3" t="s">
+        <v>577</v>
       </c>
       <c r="J453" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K453" s="2" t="s">
-        <v>561</v>
+        <v>152</v>
+      </c>
+      <c r="L453" s="2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E454" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>90</v>
@@ -11816,52 +11811,53 @@
       <c r="H454" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="455" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B455" s="3" t="s">
-        <v>480</v>
+      <c r="J454" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K454" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E455" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F455" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H455" s="13" t="s">
-        <v>96</v>
+      <c r="H455" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="456" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="A456" s="5" t="s">
-        <v>615</v>
-      </c>
       <c r="B456" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="D456" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E456" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F456" s="2" t="s">
-        <v>554</v>
+        <v>480</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H456" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A457" s="2"/>
-      <c r="B457" s="2"/>
+      <c r="H456" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="457" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A457" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>566</v>
+      </c>
       <c r="D457" s="2" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>565</v>
+        <v>133</v>
       </c>
       <c r="F457" s="2" t="s">
-        <v>153</v>
+        <v>554</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>90</v>
@@ -11869,53 +11865,55 @@
       <c r="H457" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K457" s="2" t="s">
-        <v>561</v>
-      </c>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A458" s="2"/>
+      <c r="B458" s="2"/>
+      <c r="D458" s="2" t="s">
+        <v>573</v>
+      </c>
       <c r="E458" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F458" s="2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="G458" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H458" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I458" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="J458" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="L458" s="2" t="s">
-        <v>570</v>
+        <v>90</v>
+      </c>
+      <c r="H458" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K458" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E459" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F459" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G459" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H459" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K459" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H459" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I459" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="J459" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="L459" s="2" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E460" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F460" s="2" t="s">
         <v>183</v>
@@ -11926,138 +11924,138 @@
       <c r="H460" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I460" s="8"/>
       <c r="K460" s="2" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B461" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="D461" s="2" t="s">
-        <v>130</v>
-      </c>
+    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E461" s="2" t="s">
-        <v>172</v>
+        <v>572</v>
       </c>
       <c r="F461" s="2" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H461" s="3" t="s">
+      <c r="H461" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I461" s="8"/>
+      <c r="K461" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="462" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B462" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D462" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E462" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F462" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G462" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H462" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K461" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E462" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F462" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G462" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H462" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I462" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="J462" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L462" s="2" t="s">
-        <v>576</v>
+      <c r="K462" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E463" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F463" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G463" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H463" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K463" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H463" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I463" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="J463" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L463" s="2" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E464" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F464" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H464" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I464" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
+      <c r="H464" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K464" s="2" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="465" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E465" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F465" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G465" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H465" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I465" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J465" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L465" s="2" t="s">
-        <v>578</v>
+        <v>90</v>
+      </c>
+      <c r="H465" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I465" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
     <row r="466" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E466" s="2" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="F466" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="G466" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H466" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K466" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H466" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I466" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="J466" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L466" s="2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="467" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E467" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F467" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>90</v>
@@ -12065,120 +12063,120 @@
       <c r="H467" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="468" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B468" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="K467" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="468" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E468" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F468" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H468" s="3" t="s">
+      <c r="H468" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="469" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B469" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D469" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E469" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F469" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G469" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H469" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K468" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="469" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E469" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F469" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G469" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H469" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I469" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="J469" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L469" s="2" t="s">
-        <v>580</v>
+      <c r="K469" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="470" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E470" s="2" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="F470" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G470" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H470" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I470" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K470" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H470" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I470" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="J470" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L470" s="2" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="471" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E471" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F471" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G471" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H471" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I471" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J471" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L471" s="2" t="s">
-        <v>578</v>
+        <v>90</v>
+      </c>
+      <c r="H471" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I471" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K471" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="472" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E472" s="2" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="F472" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="G472" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H472" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K472" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H472" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I472" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="J472" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L472" s="2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="473" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E473" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F473" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G473" s="2" t="s">
         <v>90</v>
@@ -12186,123 +12184,120 @@
       <c r="H473" s="11" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="474" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B474" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="D474" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="K473" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="474" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E474" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F474" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G474" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H474" s="3" t="s">
+      <c r="H474" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="475" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B475" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D475" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E475" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F475" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G475" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H475" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K474" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="475" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E475" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F475" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G475" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H475" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I475" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J475" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L475" s="2" t="s">
-        <v>405</v>
+      <c r="K475" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="476" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E476" s="2" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="F476" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G476" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H476" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I476" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K476" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H476" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I476" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J476" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L476" s="2" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="477" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E477" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F477" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G477" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H477" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I477" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J477" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L477" s="2" t="s">
-        <v>578</v>
+        <v>90</v>
+      </c>
+      <c r="H477" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I477" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K477" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="478" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E478" s="2" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="F478" s="2" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="G478" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H478" s="6" t="s">
-        <v>97</v>
+        <v>133</v>
+      </c>
+      <c r="H478" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I478" s="3" t="s">
+        <v>577</v>
       </c>
       <c r="J478" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K478" s="2" t="s">
-        <v>561</v>
+        <v>152</v>
+      </c>
+      <c r="L478" s="2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="479" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E479" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F479" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G479" s="2" t="s">
         <v>90</v>
@@ -12310,112 +12305,113 @@
       <c r="H479" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="480" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B480" s="3" t="s">
+      <c r="J479" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K479" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="480" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E480" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F480" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G480" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H480" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="481" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B481" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="D480" s="2" t="s">
+      <c r="D481" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E480" s="2" t="s">
+      <c r="E481" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F480" s="2" t="s">
+      <c r="F481" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G480" s="2" t="s">
+      <c r="G481" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H480" s="8" t="s">
+      <c r="H481" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I480" s="5" t="str">
+      <c r="I481" s="5" t="str">
         <f>$B$65</f>
         <v>OMOP Primary Dx Episode</v>
       </c>
-      <c r="K480" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E481" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F481" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G481" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H481" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I481" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
       <c r="K481" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E482" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F482" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G482" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H482" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I482" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K482" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E483" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F482" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G482" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H482" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I482" s="3" t="s">
+      <c r="F483" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G483" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H483" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I483" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="J482" s="2" t="s">
+      <c r="J483" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L482" s="2" t="s">
+      <c r="L483" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="A483" s="5" t="s">
+    <row r="484" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A484" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="B483" s="3" t="s">
+      <c r="B484" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="D483" s="2" t="s">
+      <c r="D484" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="E483" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F483" s="2" t="s">
+      <c r="E484" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F484" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="G483" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H483" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A484" s="2"/>
-      <c r="B484" s="2"/>
-      <c r="D484" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E484" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F484" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="G484" s="2" t="s">
         <v>90</v>
@@ -12423,53 +12419,55 @@
       <c r="H484" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K484" s="2" t="s">
-        <v>561</v>
-      </c>
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A485" s="2"/>
+      <c r="B485" s="2"/>
+      <c r="D485" s="2" t="s">
+        <v>573</v>
+      </c>
       <c r="E485" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F485" s="2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="G485" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H485" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I485" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="J485" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="L485" s="2" t="s">
-        <v>570</v>
+        <v>90</v>
+      </c>
+      <c r="H485" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K485" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E486" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F486" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G486" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H486" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K486" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H486" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I486" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="J486" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="L486" s="2" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E487" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F487" s="2" t="s">
         <v>183</v>
@@ -12480,138 +12478,138 @@
       <c r="H487" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I487" s="8"/>
       <c r="K487" s="2" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B488" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="D488" s="2" t="s">
-        <v>130</v>
-      </c>
+    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E488" s="2" t="s">
-        <v>172</v>
+        <v>572</v>
       </c>
       <c r="F488" s="2" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G488" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H488" s="3" t="s">
+      <c r="H488" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I488" s="8"/>
+      <c r="K488" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="489" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B489" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D489" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E489" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F489" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G489" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H489" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K488" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E489" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F489" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G489" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H489" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I489" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="J489" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L489" s="2" t="s">
-        <v>576</v>
+      <c r="K489" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E490" s="2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F490" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G490" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H490" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K490" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H490" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I490" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="J490" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L490" s="2" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E491" s="2" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="F491" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="G491" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H491" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I491" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
+      <c r="H491" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K491" s="2" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E492" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F492" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G492" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H492" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I492" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J492" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L492" s="2" t="s">
-        <v>578</v>
+        <v>90</v>
+      </c>
+      <c r="H492" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I492" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E493" s="2" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="F493" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="G493" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H493" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K493" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H493" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I493" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="J493" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L493" s="2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E494" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F494" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G494" s="2" t="s">
         <v>90</v>
@@ -12619,120 +12617,120 @@
       <c r="H494" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="495" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B495" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="D495" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="K494" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E495" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F495" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G495" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H495" s="3" t="s">
+      <c r="H495" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="496" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B496" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D496" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E496" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F496" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G496" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H496" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K495" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E496" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F496" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G496" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H496" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I496" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="J496" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L496" s="2" t="s">
-        <v>580</v>
+      <c r="K496" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E497" s="2" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="F497" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G497" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H497" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I497" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K497" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H497" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I497" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="J497" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L497" s="2" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E498" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F498" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G498" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H498" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I498" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J498" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L498" s="2" t="s">
-        <v>578</v>
+        <v>90</v>
+      </c>
+      <c r="H498" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I498" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K498" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E499" s="2" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="F499" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="G499" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H499" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K499" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H499" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I499" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="J499" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L499" s="2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E500" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F500" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G500" s="2" t="s">
         <v>90</v>
@@ -12740,123 +12738,120 @@
       <c r="H500" s="11" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="501" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B501" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="D501" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="K500" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E501" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F501" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G501" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H501" s="3" t="s">
+      <c r="H501" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="502" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B502" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D502" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E502" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F502" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G502" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H502" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K501" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E502" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F502" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G502" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H502" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I502" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J502" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L502" s="2" t="s">
-        <v>405</v>
+      <c r="K502" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E503" s="2" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="F503" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H503" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I503" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K503" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H503" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I503" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J503" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L503" s="2" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E504" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H504" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I504" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J504" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L504" s="2" t="s">
-        <v>578</v>
+        <v>90</v>
+      </c>
+      <c r="H504" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I504" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K504" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E505" s="2" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="F505" s="2" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H505" s="6" t="s">
-        <v>97</v>
+        <v>133</v>
+      </c>
+      <c r="H505" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I505" s="3" t="s">
+        <v>577</v>
       </c>
       <c r="J505" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K505" s="2" t="s">
-        <v>561</v>
+        <v>152</v>
+      </c>
+      <c r="L505" s="2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E506" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F506" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G506" s="2" t="s">
         <v>90</v>
@@ -12864,684 +12859,696 @@
       <c r="H506" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="507" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B507" s="3" t="s">
+      <c r="J506" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="K506" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E507" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F507" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G507" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H507" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="508" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B508" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="D507" s="2" t="s">
+      <c r="D508" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E507" s="2" t="s">
+      <c r="E508" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F507" s="2" t="s">
+      <c r="F508" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G507" s="2" t="s">
+      <c r="G508" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H507" s="8" t="s">
+      <c r="H508" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I507" s="3" t="str">
+      <c r="I508" s="3" t="str">
         <f>$B$154</f>
         <v>OMOP Treatment Episode</v>
       </c>
-      <c r="K507" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E508" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F508" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G508" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H508" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I508" s="3" t="str">
-        <f>$B$431</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
       <c r="K508" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E509" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F509" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G509" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H509" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I509" s="3" t="str">
+        <f>$B$432</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K509" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E510" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F509" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G509" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H509" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I509" s="3" t="s">
+      <c r="F510" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G510" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H510" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I510" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="J509" s="2" t="s">
+      <c r="J510" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L509" s="2" t="s">
+      <c r="L510" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="A510" s="5" t="s">
+    <row r="511" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A511" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="B510" s="3" t="s">
+      <c r="B511" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="D510" s="2" t="s">
+      <c r="D511" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E510" s="2" t="s">
+      <c r="E511" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F510" s="2" t="s">
+      <c r="F511" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G510" s="2" t="s">
+      <c r="G511" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H510" s="5" t="s">
+      <c r="H511" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K510" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E511" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F511" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G511" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H511" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I511" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J511" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L511" s="2" t="s">
-        <v>407</v>
+      <c r="K511" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E512" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F512" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G512" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H512" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K512" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H512" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I512" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="J512" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L512" s="2" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="513" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E513" s="2" t="s">
-        <v>314</v>
+        <v>142</v>
       </c>
       <c r="F513" s="2" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="G513" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H513" s="6" t="s">
-        <v>100</v>
+      <c r="H513" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="K513" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="514" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E514" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F514" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G514" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H514" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K514" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="515" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E515" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F514" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G514" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H514" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I514" s="3" t="s">
+      <c r="F515" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G515" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H515" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I515" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="J514" s="2" t="s">
+      <c r="J515" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L514" s="2" t="s">
+      <c r="L515" s="2" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="515" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B515" s="3" t="s">
+    <row r="516" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B516" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="D515" s="2" t="s">
+      <c r="D516" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E515" s="2" t="s">
+      <c r="E516" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F515" s="2" t="s">
+      <c r="F516" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G515" s="2" t="s">
+      <c r="G516" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H515" s="5" t="s">
+      <c r="H516" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K515" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="516" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E516" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F516" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G516" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H516" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I516" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="J516" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L516" s="2" t="s">
-        <v>411</v>
+      <c r="K516" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="517" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E517" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F517" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G517" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H517" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K517" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H517" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I517" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="J517" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L517" s="2" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="518" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E518" s="2" t="s">
-        <v>314</v>
+        <v>142</v>
       </c>
       <c r="F518" s="2" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="G518" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H518" s="6" t="s">
-        <v>101</v>
+      <c r="H518" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="K518" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="519" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E519" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F519" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G519" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H519" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K519" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="520" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E520" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F519" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G519" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H519" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I519" s="3" t="s">
+      <c r="F520" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G520" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H520" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I520" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="J519" s="2" t="s">
+      <c r="J520" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L519" s="2" t="s">
+      <c r="L520" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="520" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B520" s="3" t="s">
+    <row r="521" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B521" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D520" s="2" t="s">
+      <c r="D521" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E520" s="2" t="s">
+      <c r="E521" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F520" s="2" t="s">
+      <c r="F521" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G520" s="2" t="s">
+      <c r="G521" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H520" s="5" t="s">
+      <c r="H521" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K520" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="521" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E521" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F521" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G521" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H521" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I521" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="J521" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L521" s="2" t="s">
-        <v>415</v>
+      <c r="K521" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="522" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E522" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F522" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G522" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H522" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K522" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H522" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I522" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J522" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L522" s="2" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="523" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E523" s="2" t="s">
-        <v>314</v>
+        <v>142</v>
       </c>
       <c r="F523" s="2" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="G523" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H523" s="6" t="s">
-        <v>102</v>
+      <c r="H523" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="K523" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="524" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E524" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G524" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H524" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K524" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="525" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E525" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F524" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G524" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H524" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I524" s="3" t="s">
+      <c r="F525" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G525" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H525" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I525" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="J524" s="2" t="s">
+      <c r="J525" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L524" s="2" t="s">
+      <c r="L525" s="2" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="525" spans="2:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B525" s="3" t="s">
+    <row r="526" spans="2:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B526" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="D525" s="2" t="s">
+      <c r="D526" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E525" s="2" t="s">
+      <c r="E526" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F525" s="2" t="s">
+      <c r="F526" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G525" s="2" t="s">
+      <c r="G526" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H525" s="5" t="s">
+      <c r="H526" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K525" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="526" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E526" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F526" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G526" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H526" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I526" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="J526" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L526" s="2" t="s">
-        <v>417</v>
+      <c r="K526" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="527" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E527" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F527" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G527" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H527" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K527" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H527" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I527" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J527" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L527" s="2" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="528" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E528" s="2" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="F528" s="2" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="G528" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H528" s="6" t="s">
-        <v>103</v>
+      <c r="H528" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="K528" s="2" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E529" s="2" t="s">
-        <v>314</v>
+        <v>176</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G529" s="2" t="s">
         <v>98</v>
       </c>
       <c r="H529" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="K529" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E530" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F530" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G530" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H530" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E531" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F530" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G530" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H530" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I530" s="3" t="s">
+      <c r="F531" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G531" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H531" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I531" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="J530" s="2" t="s">
+      <c r="J531" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L530" s="2" t="s">
+      <c r="L531" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="531" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B531" s="3" t="s">
+    <row r="532" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B532" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="D531" s="2" t="s">
+      <c r="D532" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E531" s="2" t="s">
+      <c r="E532" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F531" s="2" t="s">
+      <c r="F532" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G531" s="2" t="s">
+      <c r="G532" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H531" s="5" t="s">
+      <c r="H532" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K531" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E532" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F532" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G532" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H532" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I532" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="J532" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L532" s="2" t="s">
-        <v>421</v>
+      <c r="K532" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E533" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F533" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G533" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H533" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K533" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H533" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I533" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="J533" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L533" s="2" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E534" s="2" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="F534" s="2" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="G534" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H534" s="6" t="s">
+      <c r="H534" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K534" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E535" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F535" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G535" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H535" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="K534" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="535" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B535" s="3" t="s">
+      <c r="K535" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="536" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B536" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="D535" s="2" t="s">
+      <c r="D536" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E535" s="2" t="s">
+      <c r="E536" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F535" s="2" t="s">
+      <c r="F536" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G535" s="2" t="s">
+      <c r="G536" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H535" s="5" t="s">
+      <c r="H536" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K535" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E536" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F536" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G536" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H536" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I536" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="J536" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L536" s="2" t="s">
-        <v>423</v>
+      <c r="K536" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E537" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="F537" s="2" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="G537" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H537" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K537" s="2" t="s">
-        <v>582</v>
+        <v>133</v>
+      </c>
+      <c r="H537" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I537" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="J537" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L537" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E538" s="2" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="F538" s="2" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="G538" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H538" s="6" t="s">
-        <v>106</v>
+      <c r="H538" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="K538" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="539" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B539" s="3" t="s">
-        <v>510</v>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E539" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F539" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="G539" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H539" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H539" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K539" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="540" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B540" s="3" t="s">
+        <v>510</v>
+      </c>
       <c r="G540" s="2" t="s">
         <v>98</v>
       </c>
       <c r="H540" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.25">
@@ -13549,81 +13556,72 @@
         <v>98</v>
       </c>
       <c r="H541" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G542" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H542" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="542" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="A542" s="5" t="s">
+    <row r="543" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A543" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="B542" s="3" t="s">
+      <c r="B543" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="D542" s="2" t="s">
+      <c r="D543" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E542" s="2" t="s">
+      <c r="E543" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F542" s="2" t="s">
+      <c r="F543" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G542" s="2" t="s">
+      <c r="G543" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H542" s="5" t="s">
+      <c r="H543" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K542" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E543" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F543" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G543" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H543" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I543" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="J543" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="L543" s="2" t="s">
-        <v>425</v>
+      <c r="K543" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E544" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F544" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="G544" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H544" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="K544" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="H544" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I544" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J544" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="L544" s="2" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E545" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G545" s="2" t="s">
         <v>117</v>
@@ -13632,58 +13630,53 @@
         <v>118</v>
       </c>
     </row>
-    <row r="546" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="B546" s="3" t="s">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E546" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F546" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G546" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H546" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D547" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E547" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F547" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G547" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H547" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I547" s="3" t="str">
+        <f>$B$543</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
+    </row>
+    <row r="548" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="B548" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D546" s="2" t="s">
+      <c r="D548" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E546" s="2" t="s">
+      <c r="E548" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F546" s="2" t="s">
+      <c r="F548" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="G546" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H546" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K546" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E547" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F547" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G547" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H547" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I547" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="J547" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L547" s="2" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E548" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F548" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="G548" s="2" t="s">
         <v>9</v>
@@ -13691,17 +13684,13 @@
       <c r="H548" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I548" s="3" t="str">
-        <f>$B$542</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
       <c r="K548" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E549" s="2" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="F549" s="2" t="s">
         <v>132</v>
@@ -13713,87 +13702,91 @@
         <v>133</v>
       </c>
       <c r="I549" s="3" t="s">
-        <v>428</v>
+        <v>587</v>
       </c>
       <c r="J549" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="L549" s="2" t="s">
-        <v>429</v>
+        <v>588</v>
       </c>
     </row>
     <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E550" s="2" t="s">
-        <v>314</v>
+        <v>228</v>
       </c>
       <c r="F550" s="2" t="s">
-        <v>154</v>
+        <v>590</v>
       </c>
       <c r="G550" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H550" s="6" t="s">
-        <v>120</v>
+        <v>9</v>
+      </c>
+      <c r="H550" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I550" s="3" t="str">
+        <f>$B$543</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
       </c>
       <c r="K550" s="2" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="551" spans="1:12" ht="27" x14ac:dyDescent="0.25">
-      <c r="A551" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="B551" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="D551" s="2" t="s">
-        <v>130</v>
-      </c>
+    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E551" s="2" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="F551" s="2" t="s">
-        <v>589</v>
+        <v>132</v>
       </c>
       <c r="G551" s="2" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="H551" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K551" s="2" t="s">
-        <v>561</v>
+        <v>133</v>
+      </c>
+      <c r="I551" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J551" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L551" s="2" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E552" s="2" t="s">
-        <v>173</v>
+        <v>314</v>
       </c>
       <c r="F552" s="2" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="G552" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H552" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I552" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="J552" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="L552" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="H552" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K552" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="553" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A553" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="B553" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D553" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="E553" s="2" t="s">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="F553" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G553" s="2" t="s">
         <v>9</v>
@@ -13801,17 +13794,13 @@
       <c r="H553" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I553" s="3" t="str">
-        <f>$B$542</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
       <c r="K553" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E554" s="2" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="F554" s="2" t="s">
         <v>132</v>
@@ -13823,35 +13812,38 @@
         <v>133</v>
       </c>
       <c r="I554" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J554" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="L554" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E555" s="2" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="F555" s="2" t="s">
-        <v>618</v>
+        <v>154</v>
       </c>
       <c r="G555" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H555" s="6" t="s">
-        <v>119</v>
+        <v>133</v>
+      </c>
+      <c r="H555" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I555" s="2" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E556" s="2" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="F556" s="2" t="s">
-        <v>611</v>
+        <v>132</v>
       </c>
       <c r="G556" s="2" t="s">
         <v>133</v>
@@ -13859,291 +13851,328 @@
       <c r="H556" s="5" t="s">
         <v>133</v>
       </c>
+      <c r="I556" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J556" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L556" s="2" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A557" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="B557" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="E557" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="F557" s="2" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="G557" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H557" s="5" t="s">
-        <v>2</v>
+        <v>117</v>
+      </c>
+      <c r="H557" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E558" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="F558" s="2" t="s">
-        <v>192</v>
+        <v>611</v>
       </c>
       <c r="G558" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H558" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J558" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="K558" s="2" t="s">
-        <v>583</v>
+        <v>133</v>
+      </c>
+      <c r="H558" s="5" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A559" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D559" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="E559" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F559" s="2" t="s">
-        <v>154</v>
+        <v>589</v>
       </c>
       <c r="G559" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H559" s="6" t="s">
-        <v>114</v>
+        <v>9</v>
+      </c>
+      <c r="H559" s="5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E560" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F560" s="2" t="s">
-        <v>612</v>
+        <v>192</v>
       </c>
       <c r="G560" s="2" t="s">
         <v>110</v>
       </c>
       <c r="H560" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="J560" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="K560" s="2" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="561" spans="2:10" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="561" spans="2:11" x14ac:dyDescent="0.25">
       <c r="E561" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F561" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G561" s="2" t="s">
         <v>110</v>
       </c>
       <c r="H561" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="562" spans="2:10" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="562" spans="2:11" x14ac:dyDescent="0.25">
       <c r="E562" s="2" t="s">
-        <v>430</v>
+        <v>197</v>
       </c>
       <c r="F562" s="2" t="s">
-        <v>154</v>
+        <v>612</v>
       </c>
       <c r="G562" s="2" t="s">
         <v>110</v>
       </c>
       <c r="H562" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K562" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="563" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E563" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F563" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G563" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H563" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="563" spans="2:10" ht="27" x14ac:dyDescent="0.25">
-      <c r="B563" s="3" t="s">
+    <row r="564" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E564" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F564" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G564" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H564" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="565" spans="2:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="B565" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="D563" s="2" t="s">
+      <c r="D565" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E563" s="2" t="s">
+      <c r="E565" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F563" s="2" t="s">
+      <c r="F565" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G563" s="2" t="s">
+      <c r="G565" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H563" s="5" t="s">
+      <c r="H565" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E564" s="2" t="s">
+    <row r="566" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E566" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F564" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G564" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H564" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I564" s="3" t="s">
+      <c r="F566" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G566" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H566" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I566" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="J564" s="2" t="s">
+      <c r="J566" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="565" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E565" s="2" t="s">
+    <row r="567" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E567" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F565" s="2" t="s">
+      <c r="F567" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="G565" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H565" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="I565" s="3" t="str">
-        <f>$B$557</f>
-        <v>OMOP Comorbidity Condition</v>
-      </c>
-    </row>
-    <row r="566" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E566" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F566" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G566" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H566" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I566" s="3">
-        <v>1147127</v>
-      </c>
-      <c r="J566" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="567" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E567" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F567" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="G567" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H567" s="6" t="s">
+      <c r="H567" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="I567" s="3" t="str">
+        <f>$B$559</f>
+        <v>OMOP Comorbidity Condition</v>
+      </c>
+    </row>
+    <row r="568" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E568" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F568" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G568" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H568" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I568" s="3">
+        <v>1147127</v>
+      </c>
+      <c r="J568" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="569" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E569" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F569" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G569" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H569" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="568" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E568" s="2" t="s">
+    <row r="570" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E570" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F568" s="2" t="s">
+      <c r="F570" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G568" s="2" t="s">
+      <c r="G570" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H568" s="6" t="s">
+      <c r="H570" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="569" spans="2:10" ht="27" x14ac:dyDescent="0.25">
-      <c r="B569" s="3" t="s">
+    <row r="571" spans="2:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="B571" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="C569" s="2" t="s">
+      <c r="C571" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G569" s="12" t="s">
+      <c r="G571" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H569" s="9" t="s">
+      <c r="H571" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="570" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G570" s="12" t="s">
+    <row r="572" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G572" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H570" s="7" t="s">
+      <c r="H572" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="571" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H571" s="6"/>
-    </row>
-    <row r="572" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H572" s="6"/>
-    </row>
-    <row r="575" spans="2:10" ht="27" x14ac:dyDescent="0.25">
-      <c r="B575" s="3" t="s">
+    <row r="573" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H573" s="6"/>
+    </row>
+    <row r="574" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H574" s="6"/>
+    </row>
+    <row r="577" spans="2:8" ht="27" x14ac:dyDescent="0.25">
+      <c r="B577" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="G575" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H575" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="576" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G576" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H576" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="577" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G577" s="12" t="s">
         <v>0</v>
       </c>
       <c r="H577" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="578" spans="7:8" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="578" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G578" s="12" t="s">
         <v>0</v>
       </c>
       <c r="H578" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="579" spans="7:8" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="579" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G579" s="12" t="s">
         <v>0</v>
       </c>
       <c r="H579" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="580" spans="7:8" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="580" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G580" s="12" t="s">
         <v>0</v>
       </c>
       <c r="H580" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="581" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G581" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H581" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="582" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G582" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H582" s="7" t="s">
         <v>8</v>
       </c>
     </row>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3539" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3518" uniqueCount="644">
   <si>
     <t xml:space="preserve">Source JSON Level</t>
   </si>
@@ -1380,7 +1380,49 @@
     <t xml:space="preserve">$.donors[].primary_diagnoses[].treatments[].surgeries[].margin_types_involved[]</t>
   </si>
   <si>
-    <t xml:space="preserve">OMOP Surgery Episode Margin Positive Involvement Observation</t>
+    <t xml:space="preserve">OMOP Surgery Episode Margin Positive Involvement Measurement</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">measurement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">measurement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_concept_id</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">4184217</t>
@@ -1389,6 +1431,48 @@
     <t xml:space="preserve">Surgical margin involved by tumor</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">measurement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_date</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">measurement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_event_id</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Surgery - Margin Types Involved (Code)</t>
   </si>
   <si>
@@ -1398,16 +1482,13 @@
     <t xml:space="preserve">Surgery - Margin Types Involved (Text From Source)</t>
   </si>
   <si>
-    <t xml:space="preserve">9191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive</t>
-  </si>
-  <si>
     <t xml:space="preserve">$.donors[].primary_diagnoses[].treatments[].surgeries[].margin_types_not_involved[]</t>
   </si>
   <si>
-    <t xml:space="preserve">OMOP Surgery Episode Margin Negative Involvement Observation</t>
+    <t xml:space="preserve">OMOP Surgery Episode Margin Not Involvement Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4206020</t>
   </si>
   <si>
     <t xml:space="preserve">Surgery - Margin Types Not Involved (Code)</t>
@@ -1419,16 +1500,13 @@
     <t xml:space="preserve">Surgery - Margin Types Not Involved (Text From Source)</t>
   </si>
   <si>
-    <t xml:space="preserve">9189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative</t>
-  </si>
-  <si>
     <t xml:space="preserve">$.donors[].primary_diagnoses[].treatments[].surgeries[].margin_types_not_assessed[]</t>
   </si>
   <si>
-    <t xml:space="preserve">OMOP Surgery Episode Margin Unassessible Involvement Observation</t>
+    <t xml:space="preserve">OMOP Surgery Episode Margin Not Assessed Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4217572</t>
   </si>
   <si>
     <t xml:space="preserve">Surgery - Margin Types Not Assessable (Code)</t>
@@ -1438,12 +1516,6 @@
   </si>
   <si>
     <t xml:space="preserve">Surgery - Margin Types Not Assessable (Text From Source)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4183475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margins cannot be assessed</t>
   </si>
   <si>
     <t xml:space="preserve">$.donors[].primary_diagnoses[].specimens[]</t>
@@ -1968,7 +2040,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="dd/mmm/yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2012,6 +2084,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2062,76 +2140,80 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2904,7 +2986,7 @@
         <v>46</v>
       </c>
       <c r="I20" s="2" t="str">
-        <f aca="false">$B$384</f>
+        <f aca="false">$B$381</f>
         <v>OMOP Specimen</v>
       </c>
     </row>
@@ -2967,7 +3049,7 @@
         <v>52</v>
       </c>
       <c r="I23" s="2" t="str">
-        <f aca="false">$B$438</f>
+        <f aca="false">$B$435</f>
         <v>OMOP Follow Up Visit Occurrence</v>
       </c>
     </row>
@@ -9930,7 +10012,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="36.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
         <v>450</v>
       </c>
@@ -9938,10 +10020,10 @@
         <v>451</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E360" s="1" t="s">
-        <v>110</v>
+        <v>29</v>
+      </c>
+      <c r="E360" s="13" t="s">
+        <v>452</v>
       </c>
       <c r="F360" s="1" t="s">
         <v>277</v>
@@ -9957,8 +10039,8 @@
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E361" s="1" t="s">
-        <v>111</v>
+      <c r="E361" s="13" t="s">
+        <v>453</v>
       </c>
       <c r="F361" s="1" t="s">
         <v>16</v>
@@ -9970,18 +10052,18 @@
         <v>17</v>
       </c>
       <c r="I361" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J361" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E362" s="1" t="s">
-        <v>20</v>
+      <c r="E362" s="13" t="s">
+        <v>456</v>
       </c>
       <c r="F362" s="1" t="s">
         <v>123</v>
@@ -10000,8 +10082,8 @@
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E363" s="1" t="s">
-        <v>189</v>
+      <c r="E363" s="13" t="s">
+        <v>457</v>
       </c>
       <c r="F363" s="1" t="s">
         <v>21</v>
@@ -10018,7 +10100,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E364" s="1" t="s">
-        <v>190</v>
+        <v>53</v>
       </c>
       <c r="F364" s="1" t="s">
         <v>16</v>
@@ -10041,7 +10123,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C365" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>115</v>
@@ -10053,12 +10135,12 @@
         <v>386</v>
       </c>
       <c r="H365" s="8" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C366" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>118</v>
@@ -10073,175 +10155,178 @@
         <v>17</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E367" s="1" t="s">
-        <v>216</v>
+    <row r="367" customFormat="false" ht="36.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E367" s="13" t="s">
+        <v>452</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H367" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I367" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H367" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K367" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E368" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="F368" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G368" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H368" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I368" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="J368" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L368" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E369" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="F369" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G369" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H369" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I369" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="K369" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E370" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="J367" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L367" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="368" customFormat="false" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="B368" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="D368" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E368" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F368" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G368" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H368" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K368" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E369" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F369" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G369" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H369" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I369" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="J369" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L369" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E370" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F370" s="1" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H370" s="3" t="s">
+      <c r="H370" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I370" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="K370" s="1" t="s">
-        <v>125</v>
+        <v>392</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E371" s="1" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H371" s="4" t="s">
+      <c r="H371" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I371" s="4" t="s">
-        <v>392</v>
+        <v>58</v>
+      </c>
+      <c r="J371" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L371" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C372" s="1" t="s">
+        <v>464</v>
+      </c>
       <c r="E372" s="1" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>16</v>
+        <v>279</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H372" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I372" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J372" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L372" s="1" t="s">
-        <v>59</v>
+        <v>386</v>
+      </c>
+      <c r="H372" s="8" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C373" s="1" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>386</v>
+        <v>17</v>
       </c>
       <c r="H373" s="8" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C374" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E374" s="1" t="s">
-        <v>118</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="36.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E374" s="13" t="s">
+        <v>452</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H374" s="8" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="H374" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K374" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E375" s="1" t="s">
-        <v>216</v>
+      <c r="E375" s="13" t="s">
+        <v>453</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>16</v>
@@ -10249,74 +10334,62 @@
       <c r="G375" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H375" s="8" t="s">
+      <c r="H375" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I375" s="4" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="J375" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L375" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="376" customFormat="false" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="B376" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="D376" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E376" s="1" t="s">
-        <v>110</v>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E376" s="13" t="s">
+        <v>456</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>277</v>
+        <v>123</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H376" s="4" t="s">
-        <v>50</v>
+        <v>17</v>
+      </c>
+      <c r="H376" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I376" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="K376" s="1" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E377" s="1" t="s">
-        <v>111</v>
+      <c r="E377" s="13" t="s">
+        <v>457</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H377" s="3" t="s">
+      <c r="H377" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I377" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="J377" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L377" s="1" t="s">
-        <v>453</v>
+        <v>392</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E378" s="1" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>17</v>
@@ -10325,89 +10398,96 @@
         <v>17</v>
       </c>
       <c r="I378" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="K378" s="1" t="s">
-        <v>125</v>
+        <v>58</v>
+      </c>
+      <c r="J378" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L378" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C379" s="1" t="s">
+        <v>470</v>
+      </c>
       <c r="E379" s="1" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="F379" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G379" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="H379" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C380" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E380" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F380" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G380" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H380" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E381" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F381" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G379" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H379" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I379" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E380" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F380" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G380" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H380" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I380" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J380" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L380" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C381" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="E381" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F381" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="G381" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="H381" s="8" t="s">
-        <v>469</v>
+        <v>45</v>
+      </c>
+      <c r="H381" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K381" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C382" s="1" t="s">
-        <v>470</v>
+      <c r="B382" s="1"/>
+      <c r="D382" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>118</v>
+        <v>476</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H382" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+      <c r="H382" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="383" s="1" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E383" s="1" t="s">
-        <v>216</v>
+        <v>477</v>
       </c>
       <c r="F383" s="1" t="s">
         <v>16</v>
@@ -10415,169 +10495,159 @@
       <c r="G383" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H383" s="8" t="s">
+      <c r="H383" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I383" s="4" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="J383" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L383" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="384" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="B384" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="D384" s="1" t="s">
-        <v>64</v>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C384" s="1" t="s">
+        <v>480</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H384" s="3" t="s">
-        <v>46</v>
+      <c r="H384" s="8" t="s">
+        <v>482</v>
       </c>
       <c r="K384" s="1" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B385" s="1"/>
-      <c r="D385" s="1" t="s">
-        <v>25</v>
+      <c r="C385" s="1" t="s">
+        <v>483</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H385" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="386" s="1" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H385" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="J385" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C386" s="1" t="s">
+        <v>486</v>
+      </c>
       <c r="E386" s="1" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H386" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I386" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="J386" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L386" s="1" t="s">
-        <v>479</v>
+        <v>45</v>
+      </c>
+      <c r="H386" s="8" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C387" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E387" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H387" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="K387" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C388" s="1" t="s">
-        <v>483</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="388" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B388" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>484</v>
+        <v>110</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H388" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="J388" s="1" t="s">
-        <v>418</v>
+      <c r="H388" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K388" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C389" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="E389" s="1" t="s">
-        <v>487</v>
+        <v>111</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H389" s="8" t="s">
-        <v>485</v>
+        <v>17</v>
+      </c>
+      <c r="H389" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I389" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="J389" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L389" s="1" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E390" s="1" t="s">
-        <v>488</v>
+        <v>20</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H390" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="391" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B391" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="D391" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="K390" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E391" s="1" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>45</v>
@@ -10585,13 +10655,17 @@
       <c r="H391" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="I391" s="2" t="str">
+        <f aca="false">$B$381</f>
+        <v>OMOP Specimen</v>
+      </c>
       <c r="K391" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E392" s="1" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="F392" s="1" t="s">
         <v>16</v>
@@ -10603,128 +10677,124 @@
         <v>17</v>
       </c>
       <c r="I392" s="4" t="s">
-        <v>490</v>
+        <v>55</v>
       </c>
       <c r="J392" s="1" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="L392" s="1" t="s">
-        <v>491</v>
+        <v>57</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C393" s="1" t="s">
+        <v>492</v>
+      </c>
       <c r="E393" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H393" s="8" t="s">
-        <v>482</v>
+        <v>493</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>418</v>
       </c>
       <c r="K393" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C394" s="1" t="s">
+        <v>494</v>
+      </c>
       <c r="E394" s="1" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H394" s="3" t="s">
+      <c r="H394" s="8" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B395" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E395" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F395" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G395" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H395" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I394" s="2" t="str">
-        <f aca="false">$B$384</f>
-        <v>OMOP Specimen</v>
-      </c>
-      <c r="K394" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E395" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F395" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G395" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H395" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I395" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J395" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L395" s="1" t="s">
-        <v>57</v>
+      <c r="K395" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C396" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="E396" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H396" s="8" t="s">
-        <v>493</v>
+        <v>17</v>
+      </c>
+      <c r="H396" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I396" s="4" t="s">
+        <v>496</v>
       </c>
       <c r="J396" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="K396" s="1" t="s">
-        <v>41</v>
+        <v>112</v>
+      </c>
+      <c r="L396" s="1" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C397" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="E397" s="1" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H397" s="8" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="398" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B398" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D398" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="K397" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E398" s="1" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>45</v>
@@ -10732,13 +10802,17 @@
       <c r="H398" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="I398" s="2" t="str">
+        <f aca="false">$B$381</f>
+        <v>OMOP Specimen</v>
+      </c>
       <c r="K398" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E399" s="1" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="F399" s="1" t="s">
         <v>16</v>
@@ -10750,159 +10824,155 @@
         <v>17</v>
       </c>
       <c r="I399" s="4" t="s">
-        <v>496</v>
+        <v>55</v>
       </c>
       <c r="J399" s="1" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="L399" s="1" t="s">
-        <v>497</v>
+        <v>57</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C400" s="1" t="s">
+        <v>498</v>
+      </c>
       <c r="E400" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H400" s="8" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="K400" s="1" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C401" s="1" t="s">
+        <v>498</v>
+      </c>
       <c r="E401" s="1" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H401" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I401" s="2" t="str">
-        <f aca="false">$B$384</f>
-        <v>OMOP Specimen</v>
-      </c>
-      <c r="K401" s="1" t="s">
-        <v>41</v>
+      <c r="H401" s="8" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C402" s="1" t="s">
+        <v>500</v>
+      </c>
       <c r="E402" s="1" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G402" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H402" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I402" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J402" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L402" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
+      </c>
+      <c r="H402" s="8" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C403" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>115</v>
+        <v>219</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H403" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="K403" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C404" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="404" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B404" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H404" s="8" t="s">
-        <v>499</v>
+      <c r="H404" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K404" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C405" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="E405" s="1" t="s">
-        <v>216</v>
+        <v>111</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H405" s="8" t="s">
-        <v>501</v>
+        <v>17</v>
+      </c>
+      <c r="H405" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I405" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="J405" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L405" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C406" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="E406" s="1" t="s">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H406" s="8" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="407" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B407" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="D407" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="K406" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E407" s="1" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>45</v>
@@ -10910,13 +10980,17 @@
       <c r="H407" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="I407" s="2" t="str">
+        <f aca="false">$B$381</f>
+        <v>OMOP Specimen</v>
+      </c>
       <c r="K407" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E408" s="1" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="F408" s="1" t="s">
         <v>16</v>
@@ -10928,125 +11002,121 @@
         <v>17</v>
       </c>
       <c r="I408" s="4" t="s">
-        <v>503</v>
+        <v>55</v>
       </c>
       <c r="J408" s="1" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="L408" s="1" t="s">
-        <v>504</v>
+        <v>57</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C409" s="1" t="s">
+        <v>505</v>
+      </c>
       <c r="E409" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H409" s="8" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="K409" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C410" s="1" t="s">
+        <v>507</v>
+      </c>
       <c r="E410" s="1" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H410" s="3" t="s">
+      <c r="H410" s="8" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B411" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E411" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F411" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G411" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H411" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I410" s="2" t="str">
-        <f aca="false">$B$384</f>
-        <v>OMOP Specimen</v>
-      </c>
-      <c r="K410" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E411" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F411" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G411" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H411" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I411" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J411" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L411" s="1" t="s">
-        <v>57</v>
+      <c r="K411" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C412" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="E412" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G412" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H412" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="K412" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="H412" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I412" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="J412" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L412" s="1" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C413" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="E413" s="1" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H413" s="8" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="414" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B414" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="D414" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="K413" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E414" s="1" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>45</v>
@@ -11054,13 +11124,17 @@
       <c r="H414" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="I414" s="2" t="str">
+        <f aca="false">$B$381</f>
+        <v>OMOP Specimen</v>
+      </c>
       <c r="K414" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E415" s="1" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="F415" s="1" t="s">
         <v>16</v>
@@ -11072,125 +11146,121 @@
         <v>17</v>
       </c>
       <c r="I415" s="4" t="s">
-        <v>509</v>
+        <v>55</v>
       </c>
       <c r="J415" s="1" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="L415" s="1" t="s">
-        <v>510</v>
+        <v>57</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C416" s="1" t="s">
+        <v>511</v>
+      </c>
       <c r="E416" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H416" s="8" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="K416" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C417" s="1" t="s">
+        <v>511</v>
+      </c>
       <c r="E417" s="1" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H417" s="3" t="s">
+      <c r="H417" s="8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B418" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E418" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F418" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G418" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H418" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I417" s="2" t="str">
-        <f aca="false">$B$384</f>
-        <v>OMOP Specimen</v>
-      </c>
-      <c r="K417" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E418" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F418" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G418" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H418" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I418" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J418" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L418" s="1" t="s">
-        <v>57</v>
+      <c r="K418" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C419" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="E419" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H419" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="K419" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="H419" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I419" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="J419" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L419" s="1" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C420" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="E420" s="1" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H420" s="8" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="421" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B421" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="D421" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="K420" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E421" s="1" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>45</v>
@@ -11198,13 +11268,17 @@
       <c r="H421" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="I421" s="2" t="str">
+        <f aca="false">$B$381</f>
+        <v>OMOP Specimen</v>
+      </c>
       <c r="K421" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E422" s="1" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="F422" s="1" t="s">
         <v>16</v>
@@ -11216,116 +11290,126 @@
         <v>17</v>
       </c>
       <c r="I422" s="4" t="s">
-        <v>514</v>
+        <v>55</v>
       </c>
       <c r="J422" s="1" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="L422" s="1" t="s">
-        <v>515</v>
+        <v>57</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C423" s="1" t="s">
+        <v>516</v>
+      </c>
       <c r="E423" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H423" s="8" t="s">
-        <v>482</v>
+        <v>517</v>
       </c>
       <c r="K423" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C424" s="1" t="s">
+        <v>516</v>
+      </c>
       <c r="E424" s="1" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H424" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I424" s="2" t="str">
-        <f aca="false">$B$384</f>
-        <v>OMOP Specimen</v>
-      </c>
-      <c r="K424" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H424" s="8" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="425" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B425" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="E425" s="1" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H425" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I425" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J425" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L425" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
+      </c>
+      <c r="H425" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I425" s="1" t="str">
+        <f aca="false">$B$65</f>
+        <v>OMOP Primary Dx Episode</v>
+      </c>
+      <c r="K425" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C426" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="E426" s="1" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H426" s="8" t="s">
-        <v>517</v>
+      <c r="H426" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I426" s="2" t="str">
+        <f aca="false">$B$381</f>
+        <v>OMOP Specimen</v>
       </c>
       <c r="K426" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C427" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="E427" s="1" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H427" s="8" t="s">
-        <v>517</v>
+        <v>17</v>
+      </c>
+      <c r="H427" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I427" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J427" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L427" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B428" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D428" s="1" t="s">
         <v>163</v>
@@ -11337,14 +11421,14 @@
         <v>38</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H428" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I428" s="1" t="str">
-        <f aca="false">$B$65</f>
-        <v>OMOP Primary Dx Episode</v>
+        <v>50</v>
+      </c>
+      <c r="I428" s="2" t="str">
+        <f aca="false">$B$156</f>
+        <v>OMOP Treatment Episode</v>
       </c>
       <c r="K428" s="1" t="s">
         <v>41</v>
@@ -11364,7 +11448,7 @@
         <v>46</v>
       </c>
       <c r="I429" s="2" t="str">
-        <f aca="false">$B$384</f>
+        <f aca="false">$B$381</f>
         <v>OMOP Specimen</v>
       </c>
       <c r="K429" s="1" t="s">
@@ -11396,1660 +11480,1659 @@
     </row>
     <row r="431" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B431" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="D431" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G431" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H431" s="9" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G432" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H432" s="9" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="13.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G433" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H433" s="9" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="434" customFormat="false" ht="13.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G434" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H434" s="9" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A435" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E435" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F435" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G435" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H435" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B436" s="1"/>
+      <c r="D436" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E436" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F436" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G436" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H436" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K436" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E437" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F437" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G437" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H437" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I437" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="J437" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="L437" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E438" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F438" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G438" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H438" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="K438" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E439" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F439" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G439" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H439" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="I439" s="10"/>
+      <c r="K439" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B440" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E440" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F440" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G440" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H440" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K440" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E441" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F441" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G441" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H441" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I441" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="J441" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L441" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E442" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F442" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G442" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H442" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="K442" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E443" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F443" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G443" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H443" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I443" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+    </row>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E444" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F444" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G444" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H444" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I444" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J444" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L444" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E445" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F445" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G445" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H445" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="K445" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E446" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F446" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G446" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H446" s="8" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B447" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="D447" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E447" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F447" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G447" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H447" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K447" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E448" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F448" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G448" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H448" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I448" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="J448" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L448" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E449" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F449" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G449" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H449" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I449" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K449" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E450" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F450" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G450" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H450" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I450" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J450" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L450" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E451" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F451" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G451" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H451" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="K451" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E452" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F452" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G452" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H452" s="14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="453" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B453" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D453" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E453" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F453" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G453" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H453" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K453" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E454" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F454" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G454" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H454" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I454" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="J454" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L454" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E455" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F455" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G455" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H455" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I455" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K455" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E456" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F456" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G456" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H456" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I456" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J456" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L456" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E457" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F457" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G457" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H457" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="J457" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="K457" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E458" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F458" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G458" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H458" s="8" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="459" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B459" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="G459" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H459" s="15" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B460" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="D460" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E460" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F460" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G460" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H460" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B461" s="1"/>
+      <c r="D461" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E461" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F461" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G461" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H461" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K461" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E462" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F462" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G462" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H462" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I462" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="J462" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="L462" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E463" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F463" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G463" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H463" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="K463" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E464" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F464" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G464" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H464" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="I464" s="10"/>
+      <c r="K464" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="465" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B465" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D465" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E465" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F465" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G465" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H465" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K465" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E466" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F466" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G466" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H466" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I466" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="J466" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L466" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E467" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F467" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G467" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H467" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="K467" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E468" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F468" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G468" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H468" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I468" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+    </row>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E469" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F469" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G469" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H469" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I469" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J469" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L469" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E470" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F470" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G470" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H470" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="K470" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E471" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F471" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G471" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H471" s="8" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="472" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B472" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E472" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F472" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G472" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H472" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K472" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E473" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F473" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G473" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H473" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I473" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="J473" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L473" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E474" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F474" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G474" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H474" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I474" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K474" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E475" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F475" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G475" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H475" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I475" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J475" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L475" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E476" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F476" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G476" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H476" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="K476" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E477" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F477" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G477" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H477" s="14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="478" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B478" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D478" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E478" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F478" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G478" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H478" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K478" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E479" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F479" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G479" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H479" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I479" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="J479" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L479" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E480" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F480" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G480" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H480" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I480" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K480" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E481" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F481" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G481" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H481" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I481" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J481" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L481" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="482" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E482" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F482" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G482" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H482" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="J482" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="K482" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="483" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E483" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F483" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G483" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H483" s="8" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="484" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B484" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="D484" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E431" s="1" t="s">
+      <c r="E484" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F431" s="1" t="s">
+      <c r="F484" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G431" s="1" t="s">
+      <c r="G484" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H484" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I484" s="1" t="str">
+        <f aca="false">$B$65</f>
+        <v>OMOP Primary Dx Episode</v>
+      </c>
+      <c r="K484" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E485" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F485" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G485" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H485" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I485" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K485" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E486" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F486" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G486" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H486" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I486" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J486" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L486" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A487" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B487" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="D487" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E487" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F487" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G487" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H487" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B488" s="1"/>
+      <c r="D488" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F488" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G488" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H488" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K488" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E489" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F489" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G489" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H489" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I489" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="J489" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="L489" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E490" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F490" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G490" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H490" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="K490" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E491" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F491" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G491" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H491" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="I491" s="10"/>
+      <c r="K491" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B492" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D492" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E492" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F492" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G492" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H492" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K492" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E493" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F493" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G493" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H493" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I493" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="J493" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L493" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E494" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F494" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G494" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H494" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="K494" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E495" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F495" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G495" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H495" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I495" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+    </row>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E496" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F496" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G496" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H496" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I496" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J496" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L496" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E497" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F497" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G497" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H497" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="K497" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E498" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F498" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G498" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H498" s="8" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B499" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="D499" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E499" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F499" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G499" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H499" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K499" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E500" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F500" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G500" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H500" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I500" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="J500" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L500" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E501" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F501" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G501" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H501" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I501" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K501" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E502" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F502" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G502" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H502" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I502" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J502" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L502" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E503" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F503" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G503" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H503" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="K503" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E504" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F504" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G504" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H504" s="14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="505" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B505" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E505" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F505" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G505" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H505" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K505" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E506" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F506" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G506" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H506" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I506" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="J506" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L506" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E507" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F507" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G507" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H507" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I507" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
+      </c>
+      <c r="K507" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E508" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F508" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G508" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H508" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I508" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J508" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L508" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="509" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E509" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F509" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G509" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H509" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="J509" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="K509" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="510" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E510" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F510" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G510" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H510" s="8" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="511" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B511" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="D511" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E511" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F511" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G511" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H431" s="10" t="s">
+      <c r="H511" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="I431" s="2" t="str">
+      <c r="I511" s="2" t="str">
         <f aca="false">$B$156</f>
         <v>OMOP Treatment Episode</v>
       </c>
-      <c r="K431" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E432" s="1" t="s">
+      <c r="K511" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E512" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F432" s="1" t="s">
+      <c r="F512" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="G432" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H432" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I432" s="2" t="str">
-        <f aca="false">$B$384</f>
-        <v>OMOP Specimen</v>
-      </c>
-      <c r="K432" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E433" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F433" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G433" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H433" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I433" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J433" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L433" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="434" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B434" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="G434" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H434" s="9" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="435" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G435" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H435" s="9" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="436" customFormat="false" ht="13.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G436" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H436" s="9" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="437" customFormat="false" ht="13.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G437" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H437" s="9" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="438" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A438" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="B438" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="D438" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E438" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F438" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G438" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H438" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B439" s="1"/>
-      <c r="D439" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E439" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="F439" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G439" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H439" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K439" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E440" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="F440" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G440" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H440" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I440" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="J440" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="L440" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E441" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F441" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G441" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H441" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="K441" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E442" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F442" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G442" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H442" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="I442" s="10"/>
-      <c r="K442" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="443" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B443" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="D443" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E443" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F443" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G443" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H443" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K443" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E444" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F444" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G444" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H444" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I444" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="J444" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L444" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E445" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F445" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G445" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H445" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="K445" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E446" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F446" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G446" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H446" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I446" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-    </row>
-    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E447" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F447" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G447" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H447" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I447" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J447" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L447" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E448" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F448" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G448" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H448" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="K448" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E449" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F449" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G449" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H449" s="8" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="450" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B450" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="D450" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E450" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F450" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G450" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H450" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K450" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E451" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F451" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G451" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H451" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I451" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="J451" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L451" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E452" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F452" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G452" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H452" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I452" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K452" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E453" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F453" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G453" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H453" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I453" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J453" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L453" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E454" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F454" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G454" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H454" s="13" t="s">
-        <v>543</v>
-      </c>
-      <c r="K454" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E455" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F455" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G455" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H455" s="13" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="456" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B456" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="D456" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E456" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F456" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G456" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H456" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K456" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E457" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F457" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G457" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H457" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I457" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="J457" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L457" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E458" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F458" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G458" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H458" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I458" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K458" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E459" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F459" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G459" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H459" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I459" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J459" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L459" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="460" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E460" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F460" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G460" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H460" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="J460" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="K460" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="461" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E461" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F461" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G461" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H461" s="8" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="462" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B462" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="G462" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H462" s="14" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="463" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A463" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="B463" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="D463" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E463" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F463" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G463" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H463" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B464" s="1"/>
-      <c r="D464" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E464" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="F464" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G464" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H464" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K464" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E465" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="F465" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G465" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H465" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I465" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="J465" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="L465" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E466" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F466" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G466" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H466" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="K466" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E467" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F467" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G467" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H467" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="I467" s="10"/>
-      <c r="K467" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="468" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B468" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="D468" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E468" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F468" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G468" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H468" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K468" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E469" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F469" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G469" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H469" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I469" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="J469" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L469" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E470" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F470" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G470" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H470" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="K470" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E471" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F471" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G471" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H471" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I471" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-    </row>
-    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E472" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F472" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G472" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H472" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I472" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J472" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L472" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E473" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F473" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G473" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H473" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="K473" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E474" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F474" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G474" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H474" s="8" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="475" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B475" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="D475" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E475" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F475" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G475" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H475" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K475" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E476" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F476" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G476" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H476" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I476" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="J476" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L476" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E477" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F477" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G477" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H477" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I477" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K477" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E478" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F478" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G478" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H478" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I478" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J478" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L478" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E479" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F479" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G479" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H479" s="13" t="s">
-        <v>543</v>
-      </c>
-      <c r="K479" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E480" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F480" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G480" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H480" s="13" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="481" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B481" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="D481" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E481" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F481" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G481" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H481" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K481" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E482" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F482" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G482" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H482" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I482" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="J482" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L482" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E483" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F483" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G483" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H483" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I483" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K483" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E484" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F484" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G484" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H484" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I484" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J484" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L484" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="485" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E485" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F485" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G485" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H485" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="J485" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="K485" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="486" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E486" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F486" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G486" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H486" s="8" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="487" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B487" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="D487" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E487" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F487" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G487" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H487" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I487" s="1" t="str">
-        <f aca="false">$B$65</f>
-        <v>OMOP Primary Dx Episode</v>
-      </c>
-      <c r="K487" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E488" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F488" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G488" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H488" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I488" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K488" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E489" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F489" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G489" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H489" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I489" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J489" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L489" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="490" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="B490" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="D490" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E490" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F490" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G490" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H490" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B491" s="1"/>
-      <c r="D491" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E491" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="F491" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G491" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H491" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K491" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E492" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="F492" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G492" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H492" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I492" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="J492" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="L492" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E493" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F493" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G493" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H493" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="K493" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E494" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F494" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G494" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H494" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="I494" s="10"/>
-      <c r="K494" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="495" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B495" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="D495" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E495" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F495" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G495" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H495" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K495" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E496" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F496" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G496" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H496" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I496" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="J496" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L496" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E497" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F497" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G497" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H497" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="K497" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E498" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F498" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G498" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H498" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I498" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-    </row>
-    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E499" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F499" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G499" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H499" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I499" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J499" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L499" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E500" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F500" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G500" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H500" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="K500" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E501" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F501" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G501" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H501" s="8" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="502" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B502" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="D502" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E502" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F502" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G502" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H502" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K502" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E503" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F503" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G503" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H503" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I503" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="J503" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L503" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E504" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F504" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G504" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H504" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I504" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K504" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E505" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F505" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G505" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H505" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I505" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J505" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L505" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E506" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F506" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G506" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H506" s="13" t="s">
-        <v>543</v>
-      </c>
-      <c r="K506" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E507" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F507" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G507" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H507" s="13" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="508" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B508" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="D508" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E508" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F508" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G508" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H508" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K508" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E509" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F509" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G509" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H509" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I509" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="J509" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L509" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E510" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F510" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G510" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H510" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I510" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K510" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E511" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F511" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G511" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H511" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I511" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J511" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L511" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="512" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E512" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F512" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="G512" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H512" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="J512" s="1" t="s">
-        <v>418</v>
+      <c r="H512" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I512" s="2" t="str">
+        <f aca="false">$B$435</f>
+        <v>OMOP Follow Up Visit Occurrence</v>
       </c>
       <c r="K512" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="513" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E513" s="1" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H513" s="8" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="514" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="H513" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I513" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J513" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L513" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="514" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A514" s="3" t="s">
+        <v>554</v>
+      </c>
       <c r="B514" s="4" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F514" s="1" t="s">
-        <v>38</v>
+        <v>277</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H514" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I514" s="2" t="str">
-        <f aca="false">$B$156</f>
-        <v>OMOP Treatment Episode</v>
+        <v>39</v>
+      </c>
+      <c r="H514" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="K514" s="1" t="s">
         <v>41</v>
@@ -13057,69 +13140,56 @@
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E515" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F515" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H515" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I515" s="2" t="str">
-        <f aca="false">$B$438</f>
-        <v>OMOP Follow Up Visit Occurrence</v>
-      </c>
-      <c r="K515" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="H515" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I515" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="J515" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L515" s="1" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E516" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H516" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I516" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J516" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L516" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="517" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A517" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="B517" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="H516" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K516" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E517" s="1" t="s">
-        <v>168</v>
+        <v>363</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H517" s="3" t="s">
-        <v>40</v>
+        <v>558</v>
+      </c>
+      <c r="H517" s="8" t="s">
+        <v>560</v>
       </c>
       <c r="K517" s="1" t="s">
         <v>41</v>
@@ -13127,7 +13197,7 @@
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E518" s="1" t="s">
-        <v>169</v>
+        <v>366</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>16</v>
@@ -13139,90 +13209,90 @@
         <v>17</v>
       </c>
       <c r="I518" s="4" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="J518" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L518" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B519" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E519" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>123</v>
+        <v>277</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H519" s="13" t="s">
-        <v>559</v>
+        <v>39</v>
+      </c>
+      <c r="H519" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="K519" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E520" s="1" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H520" s="8" t="s">
-        <v>560</v>
-      </c>
-      <c r="K520" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="H520" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I520" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="J520" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L520" s="1" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E521" s="1" t="s">
-        <v>366</v>
+        <v>31</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H521" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I521" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="J521" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L521" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="522" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B522" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="D522" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="H521" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K521" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E522" s="1" t="s">
-        <v>168</v>
+        <v>363</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H522" s="3" t="s">
-        <v>40</v>
+        <v>558</v>
+      </c>
+      <c r="H522" s="8" t="s">
+        <v>566</v>
       </c>
       <c r="K522" s="1" t="s">
         <v>41</v>
@@ -13230,7 +13300,7 @@
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E523" s="1" t="s">
-        <v>169</v>
+        <v>366</v>
       </c>
       <c r="F523" s="1" t="s">
         <v>16</v>
@@ -13242,90 +13312,90 @@
         <v>17</v>
       </c>
       <c r="I523" s="4" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J523" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L523" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="524" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B524" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E524" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="F524" s="1" t="s">
-        <v>123</v>
+        <v>277</v>
       </c>
       <c r="G524" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H524" s="13" t="s">
-        <v>559</v>
+        <v>39</v>
+      </c>
+      <c r="H524" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="K524" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E525" s="1" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="F525" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G525" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H525" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="K525" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="H525" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I525" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="J525" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L525" s="1" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E526" s="1" t="s">
-        <v>366</v>
+        <v>31</v>
       </c>
       <c r="F526" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H526" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I526" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="J526" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L526" s="1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="527" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B527" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="D527" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="H526" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K526" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E527" s="1" t="s">
-        <v>168</v>
+        <v>363</v>
       </c>
       <c r="F527" s="1" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H527" s="3" t="s">
-        <v>40</v>
+        <v>558</v>
+      </c>
+      <c r="H527" s="8" t="s">
+        <v>572</v>
       </c>
       <c r="K527" s="1" t="s">
         <v>41</v>
@@ -13333,7 +13403,7 @@
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E528" s="1" t="s">
-        <v>169</v>
+        <v>366</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>16</v>
@@ -13345,90 +13415,90 @@
         <v>17</v>
       </c>
       <c r="I528" s="4" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="J528" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L528" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="529" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B529" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E529" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="F529" s="1" t="s">
-        <v>123</v>
+        <v>277</v>
       </c>
       <c r="G529" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H529" s="13" t="s">
-        <v>559</v>
+        <v>39</v>
+      </c>
+      <c r="H529" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="K529" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E530" s="1" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="F530" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G530" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H530" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="K530" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="H530" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I530" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="J530" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L530" s="1" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E531" s="1" t="s">
-        <v>366</v>
+        <v>31</v>
       </c>
       <c r="F531" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G531" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H531" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I531" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="J531" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L531" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="532" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B532" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="D532" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="H531" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K531" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E532" s="1" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="F532" s="1" t="s">
-        <v>277</v>
+        <v>89</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H532" s="3" t="s">
-        <v>40</v>
+        <v>558</v>
+      </c>
+      <c r="H532" s="8" t="s">
+        <v>576</v>
       </c>
       <c r="K532" s="1" t="s">
         <v>41</v>
@@ -13436,173 +13506,176 @@
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E533" s="1" t="s">
-        <v>169</v>
+        <v>363</v>
       </c>
       <c r="F533" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H533" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I533" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="J533" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L533" s="1" t="s">
-        <v>575</v>
+        <v>558</v>
+      </c>
+      <c r="H533" s="8" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E534" s="1" t="s">
-        <v>31</v>
+        <v>366</v>
       </c>
       <c r="F534" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H534" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="K534" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="H534" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I534" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="J534" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L534" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="535" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B535" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="D535" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E535" s="1" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="F535" s="1" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="G535" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H535" s="8" t="s">
-        <v>576</v>
+        <v>39</v>
+      </c>
+      <c r="H535" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="K535" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E536" s="1" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="F536" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G536" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H536" s="8" t="s">
-        <v>577</v>
+        <v>17</v>
+      </c>
+      <c r="H536" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I536" s="16" t="n">
+        <v>4030384</v>
+      </c>
+      <c r="J536" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L536" s="17" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E537" s="1" t="s">
-        <v>366</v>
+        <v>31</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G537" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H537" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I537" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="J537" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L537" s="1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="538" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B538" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="D538" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="H537" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K537" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E538" s="1" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="F538" s="1" t="s">
-        <v>277</v>
+        <v>89</v>
       </c>
       <c r="G538" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H538" s="3" t="s">
-        <v>40</v>
+        <v>558</v>
+      </c>
+      <c r="H538" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="K538" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="539" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E539" s="1" t="s">
-        <v>169</v>
+        <v>363</v>
       </c>
       <c r="F539" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G539" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H539" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I539" s="15" t="n">
-        <v>4030384</v>
-      </c>
-      <c r="J539" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L539" s="16" t="s">
-        <v>581</v>
+        <v>558</v>
+      </c>
+      <c r="H539" s="8" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E540" s="1" t="s">
-        <v>31</v>
+        <v>366</v>
       </c>
       <c r="F540" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G540" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H540" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="K540" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="H540" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I540" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="J540" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L540" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="541" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B541" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E541" s="1" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="F541" s="1" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="G541" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H541" s="8" t="s">
-        <v>582</v>
+        <v>39</v>
+      </c>
+      <c r="H541" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="K541" s="1" t="s">
         <v>41</v>
@@ -13610,219 +13683,216 @@
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E542" s="1" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="F542" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G542" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H542" s="8" t="s">
-        <v>583</v>
+        <v>17</v>
+      </c>
+      <c r="H542" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I542" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="J542" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L542" s="1" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E543" s="1" t="s">
-        <v>366</v>
+        <v>31</v>
       </c>
       <c r="F543" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G543" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H543" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I543" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="J543" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L543" s="1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="544" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B544" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="D544" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H543" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K543" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E544" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F544" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G544" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H544" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="K544" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="545" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B545" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D545" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E544" s="1" t="s">
+      <c r="E545" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F544" s="1" t="s">
+      <c r="F545" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G544" s="1" t="s">
+      <c r="G545" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H544" s="3" t="s">
+      <c r="H545" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K544" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E545" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F545" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G545" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H545" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I545" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="J545" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L545" s="1" t="s">
-        <v>586</v>
+      <c r="K545" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E546" s="1" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="F546" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G546" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H546" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="K546" s="1" t="s">
-        <v>125</v>
+        <v>17</v>
+      </c>
+      <c r="H546" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I546" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="J546" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L546" s="1" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E547" s="1" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="F547" s="1" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="G547" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H547" s="8" t="s">
-        <v>587</v>
+      <c r="H547" s="14" t="s">
+        <v>559</v>
       </c>
       <c r="K547" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="548" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B548" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="D548" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E548" s="1" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="F548" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G548" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H548" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="K548" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="549" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B549" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E549" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F549" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G548" s="1" t="s">
+      <c r="G549" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H548" s="3" t="s">
+      <c r="H549" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K548" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E549" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F549" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G549" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H549" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I549" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="J549" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L549" s="1" t="s">
-        <v>590</v>
+      <c r="K549" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E550" s="1" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="F550" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G550" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H550" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="K550" s="1" t="s">
-        <v>125</v>
+        <v>17</v>
+      </c>
+      <c r="H550" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I550" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="J550" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L550" s="1" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E551" s="1" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="F551" s="1" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="G551" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H551" s="8" t="s">
-        <v>591</v>
+      <c r="H551" s="14" t="s">
+        <v>559</v>
       </c>
       <c r="K551" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="552" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B552" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="D552" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E552" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F552" s="1" t="s">
-        <v>277</v>
+        <v>89</v>
       </c>
       <c r="G552" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H552" s="3" t="s">
-        <v>40</v>
+        <v>558</v>
+      </c>
+      <c r="H552" s="8" t="s">
+        <v>595</v>
       </c>
       <c r="K552" s="1" t="s">
         <v>41</v>
@@ -13830,7 +13900,7 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E553" s="1" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="F553" s="1" t="s">
         <v>16</v>
@@ -13838,359 +13908,366 @@
       <c r="G553" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H553" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I553" s="4" t="s">
-        <v>593</v>
+      <c r="H553" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I553" s="2" t="s">
+        <v>596</v>
       </c>
       <c r="J553" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L553" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="554" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B554" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="D554" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E554" s="1" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>123</v>
+        <v>277</v>
       </c>
       <c r="G554" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H554" s="13" t="s">
-        <v>559</v>
+        <v>39</v>
+      </c>
+      <c r="H554" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="K554" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E555" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F555" s="1" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G555" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H555" s="8" t="s">
-        <v>595</v>
-      </c>
-      <c r="K555" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="H555" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I555" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="J555" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L555" s="1" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E556" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F556" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G556" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H556" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K556" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E557" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F557" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G557" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H557" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="K557" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E558" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F556" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G556" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H556" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I556" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="J556" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L556" s="1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="557" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B557" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="D557" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E557" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F557" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G557" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H557" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K557" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E558" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="F558" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H558" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I558" s="4" t="s">
-        <v>593</v>
+      <c r="H558" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I558" s="16" t="n">
+        <v>4120014</v>
       </c>
       <c r="J558" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L558" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="559" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A559" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B559" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="D559" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E559" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F559" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G559" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H559" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K559" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E560" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F560" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G560" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H560" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I560" s="17" t="n">
+        <v>4194639</v>
+      </c>
+      <c r="J560" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L560" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E561" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F559" s="1" t="s">
+      <c r="F561" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G559" s="1" t="s">
+      <c r="G561" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H559" s="13" t="s">
+      <c r="H561" s="14" t="s">
         <v>559</v>
       </c>
-      <c r="K559" s="1" t="s">
+      <c r="K561" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E560" s="1" t="s">
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E562" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F560" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G560" s="1" t="s">
+      <c r="F562" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G562" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H560" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="K560" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E561" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F561" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G561" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H561" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I561" s="15" t="n">
-        <v>4120014</v>
-      </c>
-      <c r="J561" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L561" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="562" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A562" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B562" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="D562" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E562" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F562" s="1" t="s">
+      <c r="H562" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="K562" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E563" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F563" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G563" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H563" s="8" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="564" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A564" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="D564" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E564" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F564" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G562" s="1" t="s">
+      <c r="G564" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H562" s="3" t="s">
+      <c r="H564" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K562" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="563" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E563" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F563" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G563" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H563" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I563" s="16" t="n">
-        <v>4194639</v>
-      </c>
-      <c r="J563" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L563" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E564" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F564" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G564" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H564" s="13" t="s">
-        <v>559</v>
-      </c>
       <c r="K564" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E565" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>279</v>
+        <v>16</v>
       </c>
       <c r="G565" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H565" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="K565" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="H565" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I565" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="J565" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L565" s="1" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E566" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F566" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G566" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="H566" s="8" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E567" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F566" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G566" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H566" s="8" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="567" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A567" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="B567" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="D567" s="1" t="s">
+      <c r="F567" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G567" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="H567" s="8" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D568" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E568" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="F568" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G568" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H568" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I568" s="2" t="str">
+        <f aca="false">$B$564</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
+    </row>
+    <row r="569" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B569" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="D569" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E567" s="1" t="s">
+      <c r="E569" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F567" s="1" t="s">
+      <c r="F569" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G567" s="1" t="s">
+      <c r="G569" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H567" s="3" t="s">
+      <c r="H569" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K567" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E568" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F568" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G568" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H568" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I568" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="J568" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L568" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E569" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F569" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G569" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H569" s="8" t="s">
-        <v>610</v>
+      <c r="K569" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E570" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F570" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G570" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H570" s="8" t="s">
-        <v>610</v>
+        <v>17</v>
+      </c>
+      <c r="H570" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I570" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="J570" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L570" s="1" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D571" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="E571" s="1" t="s">
-        <v>611</v>
+        <v>189</v>
       </c>
       <c r="F571" s="1" t="s">
         <v>292</v>
@@ -14202,62 +14279,68 @@
         <v>40</v>
       </c>
       <c r="I571" s="2" t="str">
-        <f aca="false">$B$567</f>
+        <f aca="false">$B$564</f>
         <v>OMOP Tobacco Smoking Status Observation</v>
       </c>
-    </row>
-    <row r="572" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B572" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="D572" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="K571" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E572" s="1" t="s">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="F572" s="1" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="G572" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H572" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K572" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I572" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="J572" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L572" s="1" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E573" s="1" t="s">
-        <v>111</v>
+        <v>363</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G573" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H573" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I573" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="J573" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L573" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>609</v>
+      </c>
+      <c r="H573" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="K573" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="574" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A574" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="D574" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E574" s="1" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="F574" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="G574" s="1" t="s">
         <v>39</v>
@@ -14265,17 +14348,13 @@
       <c r="H574" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I574" s="2" t="str">
-        <f aca="false">$B$567</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
       <c r="K574" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E575" s="1" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>16</v>
@@ -14287,195 +14366,174 @@
         <v>17</v>
       </c>
       <c r="I575" s="4" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="J575" s="1" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="L575" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E576" s="1" t="s">
-        <v>363</v>
+        <v>189</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G576" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H576" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="K576" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="577" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A577" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="B577" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="D577" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="H576" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I576" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E577" s="1" t="s">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="F577" s="1" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="G577" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H577" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K577" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I577" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="J577" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L577" s="1" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E578" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F578" s="1" t="s">
-        <v>16</v>
+        <v>279</v>
       </c>
       <c r="G578" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H578" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I578" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="J578" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L578" s="1" t="s">
-        <v>621</v>
+        <v>609</v>
+      </c>
+      <c r="H578" s="8" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E579" s="1" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="G579" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H579" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I579" s="1" t="s">
-        <v>611</v>
+      <c r="H579" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A580" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B580" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D580" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E580" s="1" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="F580" s="1" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G580" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H580" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I580" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="J580" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L580" s="1" t="s">
-        <v>616</v>
+        <v>40</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E581" s="1" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F581" s="1" t="s">
-        <v>279</v>
+        <v>141</v>
       </c>
       <c r="G581" s="1" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="H581" s="8" t="s">
-        <v>622</v>
+        <v>626</v>
+      </c>
+      <c r="J581" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K581" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E582" s="1" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="G582" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H582" s="3" t="s">
-        <v>17</v>
+        <v>625</v>
+      </c>
+      <c r="H582" s="8" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A583" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="B583" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="D583" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E583" s="1" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F583" s="1" t="s">
-        <v>277</v>
+        <v>627</v>
       </c>
       <c r="G583" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H583" s="3" t="s">
-        <v>40</v>
+        <v>625</v>
+      </c>
+      <c r="H583" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="K583" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E584" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="G584" s="1" t="s">
         <v>625</v>
       </c>
       <c r="H584" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="J584" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K584" s="1" t="s">
-        <v>92</v>
+        <v>629</v>
       </c>
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E585" s="1" t="s">
-        <v>145</v>
+        <v>630</v>
       </c>
       <c r="F585" s="1" t="s">
         <v>21</v>
@@ -14484,239 +14542,197 @@
         <v>625</v>
       </c>
       <c r="H585" s="8" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="586" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B586" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E586" s="1" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="F586" s="1" t="s">
-        <v>627</v>
+        <v>277</v>
       </c>
       <c r="G586" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="H586" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="K586" s="1" t="s">
-        <v>125</v>
+        <v>39</v>
+      </c>
+      <c r="H586" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E587" s="1" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G587" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="H587" s="8" t="s">
-        <v>629</v>
+        <v>17</v>
+      </c>
+      <c r="H587" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I587" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="J587" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E588" s="1" t="s">
-        <v>630</v>
+        <v>43</v>
       </c>
       <c r="F588" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G588" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="H588" s="8" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="589" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B589" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D589" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="H588" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="I588" s="2" t="str">
+        <f aca="false">$B$580</f>
+        <v>OMOP Comorbidity Condition</v>
+      </c>
+    </row>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E589" s="1" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="F589" s="1" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="G589" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H589" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
+      </c>
+      <c r="I589" s="2" t="n">
+        <v>1147127</v>
+      </c>
+      <c r="J589" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E590" s="1" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="F590" s="1" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G590" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H590" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I590" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="J590" s="1" t="s">
-        <v>177</v>
+        <v>625</v>
+      </c>
+      <c r="H590" s="8" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E591" s="1" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="F591" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G591" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="H591" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="I591" s="2" t="str">
-        <f aca="false">$B$583</f>
-        <v>OMOP Comorbidity Condition</v>
-      </c>
-    </row>
-    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E592" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F592" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G592" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H592" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I592" s="2" t="n">
-        <v>1147127</v>
-      </c>
-      <c r="J592" s="1" t="s">
-        <v>56</v>
+      <c r="H591" s="8" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="592" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B592" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="C592" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="G592" s="18" t="s">
+        <v>625</v>
+      </c>
+      <c r="H592" s="12" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E593" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F593" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G593" s="1" t="s">
+      <c r="G593" s="18" t="s">
         <v>625</v>
       </c>
-      <c r="H593" s="8" t="s">
-        <v>632</v>
+      <c r="H593" s="9" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E594" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F594" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G594" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="H594" s="8" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="595" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B595" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="G595" s="17" t="s">
-        <v>625</v>
-      </c>
-      <c r="H595" s="12" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G596" s="17" t="s">
-        <v>625</v>
-      </c>
-      <c r="H596" s="9" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H597" s="8"/>
-    </row>
-    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H598" s="8"/>
-    </row>
-    <row r="601" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B601" s="4" t="s">
+      <c r="H594" s="8"/>
+    </row>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H595" s="8"/>
+    </row>
+    <row r="598" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B598" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="G601" s="17" t="s">
+      <c r="G598" s="18" t="s">
         <v>638</v>
       </c>
+      <c r="H598" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G599" s="18" t="s">
+        <v>638</v>
+      </c>
+      <c r="H599" s="9" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G600" s="18" t="s">
+        <v>638</v>
+      </c>
+      <c r="H600" s="9" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G601" s="18" t="s">
+        <v>638</v>
+      </c>
       <c r="H601" s="9" t="s">
-        <v>46</v>
+        <v>641</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G602" s="17" t="s">
+      <c r="G602" s="18" t="s">
         <v>638</v>
       </c>
       <c r="H602" s="9" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G603" s="17" t="s">
+      <c r="G603" s="18" t="s">
         <v>638</v>
       </c>
       <c r="H603" s="9" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G604" s="17" t="s">
-        <v>638</v>
-      </c>
-      <c r="H604" s="9" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G605" s="17" t="s">
-        <v>638</v>
-      </c>
-      <c r="H605" s="9" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G606" s="17" t="s">
-        <v>638</v>
-      </c>
-      <c r="H606" s="9" t="s">
         <v>643</v>
       </c>
     </row>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3518" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="646">
   <si>
     <t xml:space="preserve">Source JSON Level</t>
   </si>
@@ -1911,7 +1911,13 @@
     <t xml:space="preserve">Human papillomavirus typing</t>
   </si>
   <si>
+    <t xml:space="preserve">Biomarker – HPV strain (Code)</t>
+  </si>
+  <si>
     <t xml:space="preserve">hpv_strain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomarker – HPV strain (Text From Source)</t>
   </si>
   <si>
     <t xml:space="preserve">$.donors[].exposures[]</t>
@@ -13900,159 +13906,138 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E553" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F553" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G553" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H553" s="8" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E554" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F553" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G553" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H553" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I553" s="2" t="s">
+      <c r="F554" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G554" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H554" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I554" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="J553" s="1" t="s">
+      <c r="J554" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L553" s="1" t="s">
+      <c r="L554" s="1" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="554" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B554" s="4" t="s">
+    <row r="555" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B555" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="D554" s="1" t="s">
+      <c r="D555" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E554" s="1" t="s">
+      <c r="E555" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F554" s="1" t="s">
+      <c r="F555" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G554" s="1" t="s">
+      <c r="G555" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H554" s="3" t="s">
+      <c r="H555" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K554" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E555" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F555" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G555" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H555" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I555" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="J555" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L555" s="1" t="s">
-        <v>594</v>
+      <c r="K555" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E556" s="1" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="F556" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G556" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H556" s="14" t="s">
-        <v>559</v>
-      </c>
-      <c r="K556" s="1" t="s">
-        <v>125</v>
+        <v>17</v>
+      </c>
+      <c r="H556" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I556" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="J556" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L556" s="1" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E557" s="1" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="F557" s="1" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="G557" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H557" s="8" t="s">
+      <c r="H557" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K557" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E558" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F558" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G558" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H558" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="K557" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E558" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F558" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G558" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H558" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I558" s="16" t="n">
-        <v>4120014</v>
-      </c>
-      <c r="J558" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L558" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="559" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B559" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="D559" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="K558" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E559" s="1" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="F559" s="1" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H559" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K559" s="1" t="s">
-        <v>41</v>
+        <v>558</v>
+      </c>
+      <c r="H559" s="8" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E560" s="1" t="s">
-        <v>169</v>
+        <v>216</v>
       </c>
       <c r="F560" s="1" t="s">
         <v>16</v>
@@ -14060,217 +14045,232 @@
       <c r="G560" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H560" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I560" s="17" t="n">
-        <v>4194639</v>
+      <c r="H560" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I560" s="16" t="n">
+        <v>4120014</v>
       </c>
       <c r="J560" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L560" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="561" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A561" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B561" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="D561" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E561" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F561" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G561" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H561" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K561" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="562" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E562" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F562" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G562" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H562" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I562" s="17" t="n">
+        <v>4194639</v>
+      </c>
+      <c r="J562" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L562" s="1" t="s">
         <v>603</v>
-      </c>
-    </row>
-    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E561" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F561" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G561" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H561" s="14" t="s">
-        <v>559</v>
-      </c>
-      <c r="K561" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E562" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F562" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G562" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H562" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="K562" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E563" s="1" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="F563" s="1" t="s">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="G563" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H563" s="8" t="s">
+      <c r="H563" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="K563" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C564" s="1" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="564" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A564" s="3" t="s">
+      <c r="E564" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F564" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G564" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H564" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="B564" s="4" t="s">
+      <c r="K564" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C565" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="D564" s="1" t="s">
+      <c r="E565" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F565" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G565" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H565" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="566" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A566" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="D566" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E564" s="1" t="s">
+      <c r="E566" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F564" s="1" t="s">
+      <c r="F566" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G564" s="1" t="s">
+      <c r="G566" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H564" s="3" t="s">
+      <c r="H566" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K564" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E565" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F565" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G565" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H565" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I565" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="J565" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L565" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E566" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F566" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G566" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H566" s="8" t="s">
-        <v>610</v>
+      <c r="K566" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E567" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F567" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G567" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H567" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I567" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="J567" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L567" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E568" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F568" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G568" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H568" s="8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E569" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F567" s="1" t="s">
+      <c r="F569" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G567" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H567" s="8" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D568" s="1" t="s">
+      <c r="G569" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H569" s="8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D570" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E568" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="F568" s="1" t="s">
+      <c r="E570" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="F570" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="G568" s="1" t="s">
+      <c r="G570" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H568" s="3" t="s">
+      <c r="H570" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I568" s="2" t="str">
-        <f aca="false">$B$564</f>
+      <c r="I570" s="2" t="str">
+        <f aca="false">$B$566</f>
         <v>OMOP Tobacco Smoking Status Observation</v>
       </c>
     </row>
-    <row r="569" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B569" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="D569" s="1" t="s">
+    <row r="571" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B571" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="D571" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E569" s="1" t="s">
+      <c r="E571" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F569" s="1" t="s">
+      <c r="F571" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="G569" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H569" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K569" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E570" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F570" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G570" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H570" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I570" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="J570" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L570" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E571" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F571" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="G571" s="1" t="s">
         <v>39</v>
@@ -14278,17 +14278,13 @@
       <c r="H571" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I571" s="2" t="str">
-        <f aca="false">$B$564</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
       <c r="K571" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E572" s="1" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="F572" s="1" t="s">
         <v>16</v>
@@ -14303,7 +14299,7 @@
         <v>615</v>
       </c>
       <c r="J572" s="1" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="L572" s="1" t="s">
         <v>616</v>
@@ -14311,90 +14307,94 @@
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E573" s="1" t="s">
-        <v>363</v>
+        <v>189</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="G573" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H573" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H573" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I573" s="2" t="str">
+        <f aca="false">$B$566</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
+      <c r="K573" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E574" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F574" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G574" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H574" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I574" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="K573" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="574" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A574" s="3" t="s">
+      <c r="J574" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L574" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="B574" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="D574" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E574" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F574" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G574" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H574" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K574" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E575" s="1" t="s">
-        <v>111</v>
+        <v>363</v>
       </c>
       <c r="F575" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G575" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H575" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I575" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="H575" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="K575" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="576" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A576" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="J575" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L575" s="1" t="s">
+      <c r="B576" s="4" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D576" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E576" s="1" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="F576" s="1" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="G576" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H576" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I576" s="1" t="s">
-        <v>611</v>
+        <v>39</v>
+      </c>
+      <c r="H576" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K576" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E577" s="1" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>16</v>
@@ -14406,35 +14406,38 @@
         <v>17</v>
       </c>
       <c r="I577" s="4" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="J577" s="1" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="L577" s="1" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E578" s="1" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="F578" s="1" t="s">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="G578" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H578" s="8" t="s">
-        <v>622</v>
+        <v>17</v>
+      </c>
+      <c r="H578" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I578" s="1" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E579" s="1" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c r="G579" s="1" t="s">
         <v>17</v>
@@ -14442,170 +14445,169 @@
       <c r="H579" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="I579" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="J579" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L579" s="1" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A580" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="B580" s="4" t="s">
+      <c r="E580" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F580" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G580" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="H580" s="8" t="s">
         <v>624</v>
-      </c>
-      <c r="D580" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E580" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F580" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G580" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H580" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E581" s="1" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F581" s="1" t="s">
-        <v>141</v>
+        <v>283</v>
       </c>
       <c r="G581" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H581" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A582" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="H581" s="8" t="s">
+      <c r="B582" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="J581" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K581" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D582" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E582" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="G582" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="H582" s="8" t="s">
-        <v>626</v>
+        <v>39</v>
+      </c>
+      <c r="H582" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E583" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F583" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G583" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="G583" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="H583" s="8" t="s">
         <v>628</v>
       </c>
+      <c r="J583" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="K583" s="1" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E584" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="G584" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H584" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E585" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F585" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G585" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H585" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="F585" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G585" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="H585" s="8" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="586" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B586" s="4" t="s">
+      <c r="K585" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E586" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F586" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G586" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H586" s="8" t="s">
         <v>631</v>
-      </c>
-      <c r="D586" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E586" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F586" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G586" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H586" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E587" s="1" t="s">
-        <v>169</v>
+        <v>632</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G587" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H587" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I587" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="J587" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>627</v>
+      </c>
+      <c r="H587" s="8" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="588" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B588" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E588" s="1" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="F588" s="1" t="s">
-        <v>38</v>
+        <v>277</v>
       </c>
       <c r="G588" s="1" t="s">
-        <v>625</v>
+        <v>39</v>
       </c>
       <c r="H588" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="I588" s="2" t="str">
-        <f aca="false">$B$580</f>
-        <v>OMOP Comorbidity Condition</v>
+        <v>40</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E589" s="1" t="s">
-        <v>53</v>
+        <v>169</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>16</v>
@@ -14616,99 +14618,121 @@
       <c r="H589" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I589" s="2" t="n">
-        <v>1147127</v>
+      <c r="I589" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="J589" s="1" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E590" s="1" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="F590" s="1" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="G590" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H590" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="H590" s="8" t="s">
-        <v>632</v>
+      <c r="I590" s="2" t="str">
+        <f aca="false">$B$582</f>
+        <v>OMOP Comorbidity Condition</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E591" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F591" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G591" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H591" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I591" s="2" t="n">
+        <v>1147127</v>
+      </c>
+      <c r="J591" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E592" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F592" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G592" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H592" s="8" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E593" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F591" s="1" t="s">
+      <c r="F593" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G591" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="H591" s="8" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="592" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B592" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="C592" s="1" t="s">
+      <c r="G593" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H593" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="G592" s="18" t="s">
-        <v>625</v>
-      </c>
-      <c r="H592" s="12" t="s">
+    </row>
+    <row r="594" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B594" s="4" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G593" s="18" t="s">
-        <v>625</v>
-      </c>
-      <c r="H593" s="9" t="s">
+      <c r="C594" s="1" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H594" s="8"/>
+      <c r="G594" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="H594" s="12" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H595" s="8"/>
-    </row>
-    <row r="598" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B598" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="G598" s="18" t="s">
+      <c r="G595" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="H595" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="H598" s="9" t="s">
+    </row>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H596" s="8"/>
+    </row>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H597" s="8"/>
+    </row>
+    <row r="600" customFormat="false" ht="25.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B600" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G600" s="18" t="s">
+        <v>640</v>
+      </c>
+      <c r="H600" s="9" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G599" s="18" t="s">
-        <v>638</v>
-      </c>
-      <c r="H599" s="9" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G600" s="18" t="s">
-        <v>638</v>
-      </c>
-      <c r="H600" s="9" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G601" s="18" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H601" s="9" t="s">
         <v>641</v>
@@ -14716,7 +14740,7 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G602" s="18" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H602" s="9" t="s">
         <v>642</v>
@@ -14724,14 +14748,28 @@
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G603" s="18" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H603" s="9" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G604" s="18" t="s">
+        <v>640</v>
+      </c>
+      <c r="H604" s="9" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G605" s="18" t="s">
+        <v>640</v>
+      </c>
+      <c r="H605" s="9" t="s">
+        <v>645</v>
+      </c>
+    </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\serverfiles\projects\dhdp\mohccn-omop-etl\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30804DCB-837B-4224-862C-41F712EDF26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B7A6B5-82AD-407C-BB41-794FF427B239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5774,10 +5774,10 @@
         <v>38</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H166" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="I166" s="2" t="str">
         <f>$B$156</f>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3534" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3535" uniqueCount="649">
   <si>
     <t xml:space="preserve">Source JSON Level</t>
   </si>
@@ -1491,6 +1491,9 @@
     <t xml:space="preserve">4206020</t>
   </si>
   <si>
+    <t xml:space="preserve">Surgical margin uninvolved by tumor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Surgery - Margin Types Not Involved (Code)</t>
   </si>
   <si>
@@ -1507,6 +1510,9 @@
   </si>
   <si>
     <t xml:space="preserve">4217572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surgical margin involvement by tumor cannot be assessed</t>
   </si>
   <si>
     <t xml:space="preserve">Surgery - Margin Types Not Assessable (Code)</t>
@@ -2502,7 +2508,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="24.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="47.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="43.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="33.54"/>
@@ -5960,7 +5966,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="5" t="s">
         <v>258</v>
       </c>
@@ -5974,10 +5980,10 @@
         <v>38</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I166" s="3" t="str">
         <f aca="false">$B$156</f>
@@ -10233,7 +10239,7 @@
         <v>112</v>
       </c>
       <c r="L368" s="1" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10298,7 +10304,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C372" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>115</v>
@@ -10310,12 +10316,12 @@
         <v>386</v>
       </c>
       <c r="H372" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C373" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>118</v>
@@ -10332,10 +10338,10 @@
     </row>
     <row r="374" customFormat="false" ht="36.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>29</v>
@@ -10370,13 +10376,13 @@
         <v>17</v>
       </c>
       <c r="I375" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J375" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L375" s="1" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10441,7 +10447,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C379" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>115</v>
@@ -10453,12 +10459,12 @@
         <v>386</v>
       </c>
       <c r="H379" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C380" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>118</v>
@@ -10475,16 +10481,16 @@
     </row>
     <row r="381" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>21</v>
@@ -10505,7 +10511,7 @@
         <v>25</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>84</v>
@@ -10519,7 +10525,7 @@
     </row>
     <row r="383" s="1" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E383" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F383" s="1" t="s">
         <v>16</v>
@@ -10531,21 +10537,21 @@
         <v>17</v>
       </c>
       <c r="I383" s="6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J383" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L383" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C384" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>123</v>
@@ -10554,7 +10560,7 @@
         <v>45</v>
       </c>
       <c r="H384" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K384" s="1" t="s">
         <v>125</v>
@@ -10562,10 +10568,10 @@
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C385" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>141</v>
@@ -10574,7 +10580,7 @@
         <v>45</v>
       </c>
       <c r="H385" s="11" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J385" s="1" t="s">
         <v>418</v>
@@ -10582,10 +10588,10 @@
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C386" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F386" s="1" t="s">
         <v>21</v>
@@ -10594,12 +10600,12 @@
         <v>45</v>
       </c>
       <c r="H386" s="11" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E387" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>21</v>
@@ -10613,7 +10619,7 @@
     </row>
     <row r="388" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B388" s="5" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>14</v>
@@ -10648,13 +10654,13 @@
         <v>17</v>
       </c>
       <c r="I389" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J389" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L389" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10668,7 +10674,7 @@
         <v>45</v>
       </c>
       <c r="H390" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K390" s="1" t="s">
         <v>125</v>
@@ -10720,7 +10726,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C393" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>115</v>
@@ -10732,7 +10738,7 @@
         <v>45</v>
       </c>
       <c r="H393" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J393" s="1" t="s">
         <v>418</v>
@@ -10743,7 +10749,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C394" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>118</v>
@@ -10755,12 +10761,12 @@
         <v>45</v>
       </c>
       <c r="H394" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B395" s="5" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>14</v>
@@ -10795,13 +10801,13 @@
         <v>17</v>
       </c>
       <c r="I396" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J396" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L396" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10815,7 +10821,7 @@
         <v>45</v>
       </c>
       <c r="H397" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K397" s="1" t="s">
         <v>125</v>
@@ -10867,7 +10873,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C400" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>115</v>
@@ -10879,7 +10885,7 @@
         <v>45</v>
       </c>
       <c r="H400" s="11" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K400" s="1" t="s">
         <v>92</v>
@@ -10887,7 +10893,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C401" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>118</v>
@@ -10899,12 +10905,12 @@
         <v>45</v>
       </c>
       <c r="H401" s="11" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C402" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>216</v>
@@ -10916,12 +10922,12 @@
         <v>45</v>
       </c>
       <c r="H402" s="11" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C403" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>219</v>
@@ -10933,12 +10939,12 @@
         <v>45</v>
       </c>
       <c r="H403" s="11" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B404" s="5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>14</v>
@@ -10973,13 +10979,13 @@
         <v>17</v>
       </c>
       <c r="I405" s="6" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J405" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L405" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10993,7 +10999,7 @@
         <v>45</v>
       </c>
       <c r="H406" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K406" s="1" t="s">
         <v>125</v>
@@ -11045,7 +11051,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C409" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>115</v>
@@ -11057,7 +11063,7 @@
         <v>45</v>
       </c>
       <c r="H409" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K409" s="1" t="s">
         <v>41</v>
@@ -11065,7 +11071,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C410" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>118</v>
@@ -11077,12 +11083,12 @@
         <v>45</v>
       </c>
       <c r="H410" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B411" s="5" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D411" s="1" t="s">
         <v>14</v>
@@ -11117,13 +11123,13 @@
         <v>17</v>
       </c>
       <c r="I412" s="6" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J412" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L412" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11137,7 +11143,7 @@
         <v>45</v>
       </c>
       <c r="H413" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K413" s="1" t="s">
         <v>125</v>
@@ -11189,7 +11195,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C416" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>115</v>
@@ -11201,7 +11207,7 @@
         <v>45</v>
       </c>
       <c r="H416" s="11" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K416" s="1" t="s">
         <v>41</v>
@@ -11209,7 +11215,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C417" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>118</v>
@@ -11221,12 +11227,12 @@
         <v>45</v>
       </c>
       <c r="H417" s="11" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B418" s="5" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D418" s="1" t="s">
         <v>14</v>
@@ -11261,13 +11267,13 @@
         <v>17</v>
       </c>
       <c r="I419" s="6" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J419" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L419" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11281,7 +11287,7 @@
         <v>45</v>
       </c>
       <c r="H420" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K420" s="1" t="s">
         <v>125</v>
@@ -11333,7 +11339,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C423" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>115</v>
@@ -11345,7 +11351,7 @@
         <v>45</v>
       </c>
       <c r="H423" s="11" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K423" s="1" t="s">
         <v>41</v>
@@ -11353,7 +11359,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C424" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>118</v>
@@ -11365,12 +11371,12 @@
         <v>45</v>
       </c>
       <c r="H424" s="11" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B425" s="5" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D425" s="1" t="s">
         <v>163</v>
@@ -11441,7 +11447,7 @@
     </row>
     <row r="428" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B428" s="5" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D428" s="1" t="s">
         <v>163</v>
@@ -11512,13 +11518,13 @@
     </row>
     <row r="431" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B431" s="5" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H431" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11526,7 +11532,7 @@
         <v>45</v>
       </c>
       <c r="H432" s="12" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="13.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11534,7 +11540,7 @@
         <v>45</v>
       </c>
       <c r="H433" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="13.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11542,15 +11548,15 @@
         <v>45</v>
       </c>
       <c r="H434" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D435" s="1" t="s">
         <v>64</v>
@@ -11574,7 +11580,7 @@
         <v>27</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F436" s="1" t="s">
         <v>84</v>
@@ -11591,7 +11597,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E437" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F437" s="1" t="s">
         <v>16</v>
@@ -11603,18 +11609,18 @@
         <v>17</v>
       </c>
       <c r="I437" s="6" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J437" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L437" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E438" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>123</v>
@@ -11623,7 +11629,7 @@
         <v>51</v>
       </c>
       <c r="H438" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K438" s="1" t="s">
         <v>125</v>
@@ -11631,7 +11637,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E439" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F439" s="1" t="s">
         <v>123</v>
@@ -11640,7 +11646,7 @@
         <v>51</v>
       </c>
       <c r="H439" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I439" s="17"/>
       <c r="K439" s="1" t="s">
@@ -11649,7 +11655,7 @@
     </row>
     <row r="440" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B440" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D440" s="1" t="s">
         <v>14</v>
@@ -11684,13 +11690,13 @@
         <v>17</v>
       </c>
       <c r="I441" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J441" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L441" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11704,7 +11710,7 @@
         <v>51</v>
       </c>
       <c r="H442" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K442" s="1" t="s">
         <v>125</v>
@@ -11762,7 +11768,7 @@
         <v>51</v>
       </c>
       <c r="H445" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K445" s="1" t="s">
         <v>41</v>
@@ -11779,12 +11785,12 @@
         <v>51</v>
       </c>
       <c r="H446" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B447" s="5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D447" s="1" t="s">
         <v>14</v>
@@ -11819,13 +11825,13 @@
         <v>17</v>
       </c>
       <c r="I448" s="6" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J448" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L448" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11883,7 +11889,7 @@
         <v>51</v>
       </c>
       <c r="H451" s="18" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K451" s="1" t="s">
         <v>41</v>
@@ -11900,12 +11906,12 @@
         <v>51</v>
       </c>
       <c r="H452" s="18" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B453" s="5" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D453" s="1" t="s">
         <v>14</v>
@@ -11940,13 +11946,13 @@
         <v>17</v>
       </c>
       <c r="I454" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J454" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L454" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12004,7 +12010,7 @@
         <v>51</v>
       </c>
       <c r="H457" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J457" s="1" t="s">
         <v>418</v>
@@ -12024,26 +12030,26 @@
         <v>51</v>
       </c>
       <c r="H458" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B459" s="5" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>51</v>
       </c>
       <c r="H459" s="19" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="4" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D460" s="1" t="s">
         <v>64</v>
@@ -12067,7 +12073,7 @@
         <v>27</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F461" s="1" t="s">
         <v>84</v>
@@ -12084,7 +12090,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E462" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>16</v>
@@ -12096,18 +12102,18 @@
         <v>17</v>
       </c>
       <c r="I462" s="6" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J462" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L462" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E463" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F463" s="1" t="s">
         <v>123</v>
@@ -12116,7 +12122,7 @@
         <v>51</v>
       </c>
       <c r="H463" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K463" s="1" t="s">
         <v>125</v>
@@ -12124,7 +12130,7 @@
     </row>
     <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E464" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F464" s="1" t="s">
         <v>123</v>
@@ -12133,7 +12139,7 @@
         <v>51</v>
       </c>
       <c r="H464" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I464" s="17"/>
       <c r="K464" s="1" t="s">
@@ -12142,7 +12148,7 @@
     </row>
     <row r="465" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B465" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D465" s="1" t="s">
         <v>14</v>
@@ -12177,13 +12183,13 @@
         <v>17</v>
       </c>
       <c r="I466" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J466" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L466" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12197,7 +12203,7 @@
         <v>51</v>
       </c>
       <c r="H467" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K467" s="1" t="s">
         <v>125</v>
@@ -12255,7 +12261,7 @@
         <v>51</v>
       </c>
       <c r="H470" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K470" s="1" t="s">
         <v>41</v>
@@ -12272,12 +12278,12 @@
         <v>51</v>
       </c>
       <c r="H471" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B472" s="5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D472" s="1" t="s">
         <v>14</v>
@@ -12312,13 +12318,13 @@
         <v>17</v>
       </c>
       <c r="I473" s="6" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J473" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L473" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12376,7 +12382,7 @@
         <v>51</v>
       </c>
       <c r="H476" s="18" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K476" s="1" t="s">
         <v>41</v>
@@ -12393,12 +12399,12 @@
         <v>51</v>
       </c>
       <c r="H477" s="18" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B478" s="5" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D478" s="1" t="s">
         <v>14</v>
@@ -12433,13 +12439,13 @@
         <v>17</v>
       </c>
       <c r="I479" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J479" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L479" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12497,7 +12503,7 @@
         <v>51</v>
       </c>
       <c r="H482" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J482" s="1" t="s">
         <v>418</v>
@@ -12517,12 +12523,12 @@
         <v>51</v>
       </c>
       <c r="H483" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B484" s="5" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D484" s="1" t="s">
         <v>163</v>
@@ -12593,10 +12599,10 @@
     </row>
     <row r="487" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="4" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B487" s="5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D487" s="1" t="s">
         <v>64</v>
@@ -12620,7 +12626,7 @@
         <v>27</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F488" s="1" t="s">
         <v>84</v>
@@ -12637,7 +12643,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E489" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F489" s="1" t="s">
         <v>16</v>
@@ -12649,18 +12655,18 @@
         <v>17</v>
       </c>
       <c r="I489" s="6" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J489" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L489" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E490" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F490" s="1" t="s">
         <v>123</v>
@@ -12669,7 +12675,7 @@
         <v>51</v>
       </c>
       <c r="H490" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K490" s="1" t="s">
         <v>125</v>
@@ -12677,7 +12683,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E491" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>123</v>
@@ -12686,7 +12692,7 @@
         <v>51</v>
       </c>
       <c r="H491" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I491" s="17"/>
       <c r="K491" s="1" t="s">
@@ -12695,7 +12701,7 @@
     </row>
     <row r="492" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B492" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D492" s="1" t="s">
         <v>14</v>
@@ -12730,13 +12736,13 @@
         <v>17</v>
       </c>
       <c r="I493" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J493" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L493" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12750,7 +12756,7 @@
         <v>51</v>
       </c>
       <c r="H494" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K494" s="1" t="s">
         <v>125</v>
@@ -12808,7 +12814,7 @@
         <v>51</v>
       </c>
       <c r="H497" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K497" s="1" t="s">
         <v>41</v>
@@ -12825,12 +12831,12 @@
         <v>51</v>
       </c>
       <c r="H498" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B499" s="5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D499" s="1" t="s">
         <v>14</v>
@@ -12865,13 +12871,13 @@
         <v>17</v>
       </c>
       <c r="I500" s="6" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J500" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L500" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12929,7 +12935,7 @@
         <v>51</v>
       </c>
       <c r="H503" s="18" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K503" s="1" t="s">
         <v>41</v>
@@ -12946,12 +12952,12 @@
         <v>51</v>
       </c>
       <c r="H504" s="18" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B505" s="5" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D505" s="1" t="s">
         <v>14</v>
@@ -12986,13 +12992,13 @@
         <v>17</v>
       </c>
       <c r="I506" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J506" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L506" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13050,7 +13056,7 @@
         <v>51</v>
       </c>
       <c r="H509" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J509" s="1" t="s">
         <v>418</v>
@@ -13070,12 +13076,12 @@
         <v>51</v>
       </c>
       <c r="H510" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B511" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D511" s="1" t="s">
         <v>163</v>
@@ -13146,7 +13152,7 @@
     </row>
     <row r="514" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D514" s="1" t="s">
         <v>64</v>
@@ -13158,17 +13164,20 @@
         <v>75</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H514" s="11" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I514" s="20"/>
+      <c r="K514" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="515" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="0"/>
       <c r="B515" s="5" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D515" s="1" t="s">
         <v>29</v>
@@ -13203,13 +13212,13 @@
         <v>17</v>
       </c>
       <c r="I516" s="6" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J516" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L516" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13220,10 +13229,10 @@
         <v>123</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H517" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K517" s="1" t="s">
         <v>125</v>
@@ -13237,10 +13246,10 @@
         <v>21</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H518" s="11" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="K518" s="1" t="s">
         <v>41</v>
@@ -13260,18 +13269,18 @@
         <v>17</v>
       </c>
       <c r="I519" s="6" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J519" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L519" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B520" s="5" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D520" s="1" t="s">
         <v>29</v>
@@ -13306,13 +13315,13 @@
         <v>17</v>
       </c>
       <c r="I521" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J521" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L521" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13323,10 +13332,10 @@
         <v>123</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H522" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K522" s="1" t="s">
         <v>125</v>
@@ -13340,10 +13349,10 @@
         <v>21</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H523" s="11" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K523" s="1" t="s">
         <v>41</v>
@@ -13363,18 +13372,18 @@
         <v>17</v>
       </c>
       <c r="I524" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J524" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L524" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B525" s="5" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D525" s="1" t="s">
         <v>29</v>
@@ -13409,13 +13418,13 @@
         <v>17</v>
       </c>
       <c r="I526" s="6" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J526" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L526" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13426,10 +13435,10 @@
         <v>123</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H527" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K527" s="1" t="s">
         <v>125</v>
@@ -13443,10 +13452,10 @@
         <v>21</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H528" s="11" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="K528" s="1" t="s">
         <v>41</v>
@@ -13466,18 +13475,18 @@
         <v>17</v>
       </c>
       <c r="I529" s="6" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J529" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L529" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B530" s="5" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D530" s="1" t="s">
         <v>29</v>
@@ -13512,13 +13521,13 @@
         <v>17</v>
       </c>
       <c r="I531" s="6" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J531" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L531" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13529,10 +13538,10 @@
         <v>123</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H532" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K532" s="1" t="s">
         <v>125</v>
@@ -13546,10 +13555,10 @@
         <v>89</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H533" s="11" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K533" s="1" t="s">
         <v>41</v>
@@ -13563,10 +13572,10 @@
         <v>21</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H534" s="11" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13583,18 +13592,18 @@
         <v>17</v>
       </c>
       <c r="I535" s="6" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J535" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L535" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B536" s="5" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D536" s="1" t="s">
         <v>29</v>
@@ -13635,7 +13644,7 @@
         <v>112</v>
       </c>
       <c r="L537" s="22" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13646,10 +13655,10 @@
         <v>123</v>
       </c>
       <c r="G538" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H538" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K538" s="1" t="s">
         <v>125</v>
@@ -13663,10 +13672,10 @@
         <v>89</v>
       </c>
       <c r="G539" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H539" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K539" s="1" t="s">
         <v>41</v>
@@ -13680,10 +13689,10 @@
         <v>21</v>
       </c>
       <c r="G540" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H540" s="11" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13700,18 +13709,18 @@
         <v>17</v>
       </c>
       <c r="I541" s="6" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J541" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L541" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B542" s="5" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D542" s="1" t="s">
         <v>29</v>
@@ -13746,13 +13755,13 @@
         <v>17</v>
       </c>
       <c r="I543" s="6" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="J543" s="1" t="s">
         <v>177</v>
       </c>
       <c r="L543" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13763,10 +13772,10 @@
         <v>123</v>
       </c>
       <c r="G544" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H544" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K544" s="1" t="s">
         <v>125</v>
@@ -13780,10 +13789,10 @@
         <v>89</v>
       </c>
       <c r="G545" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H545" s="11" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K545" s="1" t="s">
         <v>41</v>
@@ -13791,7 +13800,7 @@
     </row>
     <row r="546" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B546" s="5" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D546" s="1" t="s">
         <v>29</v>
@@ -13826,13 +13835,13 @@
         <v>17</v>
       </c>
       <c r="I547" s="6" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="J547" s="1" t="s">
         <v>177</v>
       </c>
       <c r="L547" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13843,10 +13852,10 @@
         <v>123</v>
       </c>
       <c r="G548" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H548" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K548" s="1" t="s">
         <v>125</v>
@@ -13860,10 +13869,10 @@
         <v>89</v>
       </c>
       <c r="G549" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H549" s="11" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K549" s="1" t="s">
         <v>41</v>
@@ -13871,7 +13880,7 @@
     </row>
     <row r="550" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B550" s="5" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D550" s="1" t="s">
         <v>14</v>
@@ -13906,13 +13915,13 @@
         <v>17</v>
       </c>
       <c r="I551" s="6" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J551" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L551" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13923,10 +13932,10 @@
         <v>123</v>
       </c>
       <c r="G552" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H552" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K552" s="1" t="s">
         <v>125</v>
@@ -13940,10 +13949,10 @@
         <v>89</v>
       </c>
       <c r="G553" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H553" s="11" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K553" s="1" t="s">
         <v>41</v>
@@ -13957,10 +13966,10 @@
         <v>21</v>
       </c>
       <c r="G554" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H554" s="11" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13977,18 +13986,18 @@
         <v>17</v>
       </c>
       <c r="I555" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J555" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L555" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B556" s="5" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D556" s="1" t="s">
         <v>14</v>
@@ -14023,13 +14032,13 @@
         <v>17</v>
       </c>
       <c r="I557" s="6" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J557" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L557" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14040,10 +14049,10 @@
         <v>123</v>
       </c>
       <c r="G558" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H558" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K558" s="1" t="s">
         <v>125</v>
@@ -14057,10 +14066,10 @@
         <v>89</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H559" s="11" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K559" s="1" t="s">
         <v>41</v>
@@ -14074,10 +14083,10 @@
         <v>21</v>
       </c>
       <c r="G560" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H560" s="11" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14100,15 +14109,15 @@
         <v>112</v>
       </c>
       <c r="L561" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="4" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B562" s="5" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D562" s="1" t="s">
         <v>29</v>
@@ -14149,7 +14158,7 @@
         <v>112</v>
       </c>
       <c r="L563" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14166,7 +14175,7 @@
         <v>17</v>
       </c>
       <c r="I564" s="8" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K564" s="1" t="s">
         <v>125</v>
@@ -14174,7 +14183,7 @@
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C565" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>115</v>
@@ -14183,10 +14192,10 @@
         <v>279</v>
       </c>
       <c r="G565" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H565" s="11" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K565" s="1" t="s">
         <v>41</v>
@@ -14194,7 +14203,7 @@
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C566" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>118</v>
@@ -14211,10 +14220,10 @@
     </row>
     <row r="567" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="4" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B567" s="5" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D567" s="1" t="s">
         <v>14</v>
@@ -14249,13 +14258,13 @@
         <v>17</v>
       </c>
       <c r="I568" s="6" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J568" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L568" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14266,10 +14275,10 @@
         <v>89</v>
       </c>
       <c r="G569" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H569" s="11" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14280,10 +14289,10 @@
         <v>21</v>
       </c>
       <c r="G570" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H570" s="11" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14291,7 +14300,7 @@
         <v>64</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F571" s="1" t="s">
         <v>292</v>
@@ -14309,7 +14318,7 @@
     </row>
     <row r="572" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B572" s="5" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D572" s="1" t="s">
         <v>14</v>
@@ -14344,13 +14353,13 @@
         <v>17</v>
       </c>
       <c r="I573" s="6" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J573" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L573" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14388,13 +14397,13 @@
         <v>17</v>
       </c>
       <c r="I575" s="6" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J575" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L575" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14405,10 +14414,10 @@
         <v>21</v>
       </c>
       <c r="G576" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H576" s="11" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="K576" s="1" t="s">
         <v>41</v>
@@ -14416,10 +14425,10 @@
     </row>
     <row r="577" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="4" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B577" s="5" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D577" s="1" t="s">
         <v>14</v>
@@ -14454,13 +14463,13 @@
         <v>17</v>
       </c>
       <c r="I578" s="6" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J578" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L578" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14477,7 +14486,7 @@
         <v>17</v>
       </c>
       <c r="I579" s="8" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14494,13 +14503,13 @@
         <v>17</v>
       </c>
       <c r="I580" s="6" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J580" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L580" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14511,10 +14520,10 @@
         <v>279</v>
       </c>
       <c r="G581" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H581" s="11" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14533,10 +14542,10 @@
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B583" s="5" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D583" s="1" t="s">
         <v>34</v>
@@ -14562,10 +14571,10 @@
         <v>141</v>
       </c>
       <c r="G584" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H584" s="11" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J584" s="1" t="s">
         <v>143</v>
@@ -14582,10 +14591,10 @@
         <v>21</v>
       </c>
       <c r="G585" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H585" s="11" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14593,13 +14602,13 @@
         <v>147</v>
       </c>
       <c r="F586" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="G586" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="G586" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="H586" s="11" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K586" s="1" t="s">
         <v>125</v>
@@ -14613,29 +14622,29 @@
         <v>89</v>
       </c>
       <c r="G587" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H587" s="11" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E588" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F588" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G588" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H588" s="11" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B589" s="5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D589" s="1" t="s">
         <v>29</v>
@@ -14681,10 +14690,10 @@
         <v>38</v>
       </c>
       <c r="G591" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="H591" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="H591" s="4" t="s">
-        <v>626</v>
       </c>
       <c r="I591" s="3" t="str">
         <f aca="false">$B$583</f>
@@ -14719,10 +14728,10 @@
         <v>89</v>
       </c>
       <c r="G593" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H593" s="11" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14733,32 +14742,32 @@
         <v>21</v>
       </c>
       <c r="G594" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H594" s="11" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="595" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B595" s="5" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C595" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G595" s="23" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H595" s="15" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G596" s="23" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H596" s="12" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14769,10 +14778,10 @@
     </row>
     <row r="601" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B601" s="5" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G601" s="23" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H601" s="12" t="s">
         <v>46</v>
@@ -14780,42 +14789,42 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G602" s="23" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H602" s="12" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G603" s="23" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H603" s="12" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G604" s="23" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H604" s="12" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G605" s="23" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H605" s="12" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G606" s="23" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H606" s="12" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -1770,21 +1770,21 @@
     <t xml:space="preserve">$.donors[].biomarkers[]</t>
   </si>
   <si>
+    <t xml:space="preserve">OMOP PSA Biomarker Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4272032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prostate specific antigen measurement</t>
+  </si>
+  <si>
     <t xml:space="preserve">Biomarker</t>
   </si>
   <si>
     <t xml:space="preserve">test_date</t>
   </si>
   <si>
-    <t xml:space="preserve">OMOP PSA Biomarker Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4272032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prostate specific antigen measurement</t>
-  </si>
-  <si>
     <t xml:space="preserve">psa_level</t>
   </si>
   <si>
@@ -1794,6 +1794,9 @@
     <t xml:space="preserve">ng/mL</t>
   </si>
   <si>
+    <t xml:space="preserve">{current_biomarker_date}</t>
+  </si>
+  <si>
     <t xml:space="preserve">OMOP CA125 Biomarker Measurement</t>
   </si>
   <si>
@@ -1917,16 +1920,13 @@
     <t xml:space="preserve">Human papillomavirus typing</t>
   </si>
   <si>
-    <t xml:space="preserve">{Biomarker.test_date}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biomarker – HPV strain (Code)</t>
+    <t xml:space="preserve">Biomarker - HPV strain (Code)</t>
   </si>
   <si>
     <t xml:space="preserve">hpv_strain</t>
   </si>
   <si>
-    <t xml:space="preserve">Biomarker – HPV strain (Text From Source)</t>
+    <t xml:space="preserve">Biomarker - HPV strain (Text From Source)</t>
   </si>
   <si>
     <t xml:space="preserve">$.donors[].exposures[]</t>
@@ -13150,137 +13150,136 @@
         <v>61</v>
       </c>
     </row>
-    <row r="514" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="4" t="s">
         <v>556</v>
       </c>
+      <c r="B514" s="5" t="s">
+        <v>557</v>
+      </c>
       <c r="D514" s="1" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="F514" s="1" t="s">
-        <v>75</v>
+        <v>277</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="H514" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H514" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K514" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E515" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F515" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G515" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H515" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I515" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="I514" s="20"/>
-      <c r="K514" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="515" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A515" s="0"/>
-      <c r="B515" s="5" t="s">
+      <c r="J515" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L515" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="D515" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E515" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F515" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G515" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H515" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K515" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E516" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H516" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I516" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="J516" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L516" s="1" t="s">
+      <c r="H516" s="18" t="s">
         <v>561</v>
+      </c>
+      <c r="K516" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E517" s="1" t="s">
-        <v>31</v>
+        <v>363</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="H517" s="18" t="s">
-        <v>558</v>
+        <v>560</v>
+      </c>
+      <c r="H517" s="11" t="s">
+        <v>562</v>
       </c>
       <c r="K517" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E518" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="H518" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="K518" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="H518" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I518" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="J518" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L518" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D519" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="E519" s="1" t="s">
-        <v>366</v>
+        <v>565</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H519" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I519" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="J519" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L519" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
+      </c>
+      <c r="H519" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="I519" s="20"/>
+      <c r="K519" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B520" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D520" s="1" t="s">
         <v>29</v>
@@ -13315,13 +13314,13 @@
         <v>17</v>
       </c>
       <c r="I521" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J521" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L521" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13332,10 +13331,10 @@
         <v>123</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H522" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K522" s="1" t="s">
         <v>125</v>
@@ -13349,10 +13348,10 @@
         <v>21</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H523" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K523" s="1" t="s">
         <v>41</v>
@@ -13372,18 +13371,18 @@
         <v>17</v>
       </c>
       <c r="I524" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J524" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L524" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B525" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D525" s="1" t="s">
         <v>29</v>
@@ -13418,13 +13417,13 @@
         <v>17</v>
       </c>
       <c r="I526" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="J526" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L526" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13435,10 +13434,10 @@
         <v>123</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H527" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K527" s="1" t="s">
         <v>125</v>
@@ -13452,10 +13451,10 @@
         <v>21</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H528" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K528" s="1" t="s">
         <v>41</v>
@@ -13486,7 +13485,7 @@
     </row>
     <row r="530" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B530" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D530" s="1" t="s">
         <v>29</v>
@@ -13521,13 +13520,13 @@
         <v>17</v>
       </c>
       <c r="I531" s="6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J531" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L531" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13538,10 +13537,10 @@
         <v>123</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H532" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K532" s="1" t="s">
         <v>125</v>
@@ -13555,10 +13554,10 @@
         <v>89</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H533" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K533" s="1" t="s">
         <v>41</v>
@@ -13572,10 +13571,10 @@
         <v>21</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H534" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13592,18 +13591,18 @@
         <v>17</v>
       </c>
       <c r="I535" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J535" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L535" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B536" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D536" s="1" t="s">
         <v>29</v>
@@ -13644,7 +13643,7 @@
         <v>112</v>
       </c>
       <c r="L537" s="22" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13655,10 +13654,10 @@
         <v>123</v>
       </c>
       <c r="G538" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H538" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K538" s="1" t="s">
         <v>125</v>
@@ -13672,10 +13671,10 @@
         <v>89</v>
       </c>
       <c r="G539" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H539" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="K539" s="1" t="s">
         <v>41</v>
@@ -13689,10 +13688,10 @@
         <v>21</v>
       </c>
       <c r="G540" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H540" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13709,18 +13708,18 @@
         <v>17</v>
       </c>
       <c r="I541" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J541" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L541" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B542" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D542" s="1" t="s">
         <v>29</v>
@@ -13755,13 +13754,13 @@
         <v>17</v>
       </c>
       <c r="I543" s="6" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J543" s="1" t="s">
         <v>177</v>
       </c>
       <c r="L543" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13772,10 +13771,10 @@
         <v>123</v>
       </c>
       <c r="G544" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H544" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K544" s="1" t="s">
         <v>125</v>
@@ -13789,10 +13788,10 @@
         <v>89</v>
       </c>
       <c r="G545" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H545" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K545" s="1" t="s">
         <v>41</v>
@@ -13800,7 +13799,7 @@
     </row>
     <row r="546" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B546" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D546" s="1" t="s">
         <v>29</v>
@@ -13835,13 +13834,13 @@
         <v>17</v>
       </c>
       <c r="I547" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J547" s="1" t="s">
         <v>177</v>
       </c>
       <c r="L547" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13852,10 +13851,10 @@
         <v>123</v>
       </c>
       <c r="G548" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H548" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K548" s="1" t="s">
         <v>125</v>
@@ -13869,10 +13868,10 @@
         <v>89</v>
       </c>
       <c r="G549" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H549" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K549" s="1" t="s">
         <v>41</v>
@@ -13880,7 +13879,7 @@
     </row>
     <row r="550" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B550" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D550" s="1" t="s">
         <v>14</v>
@@ -13915,13 +13914,13 @@
         <v>17</v>
       </c>
       <c r="I551" s="6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J551" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L551" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13932,10 +13931,10 @@
         <v>123</v>
       </c>
       <c r="G552" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H552" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K552" s="1" t="s">
         <v>125</v>
@@ -13949,10 +13948,10 @@
         <v>89</v>
       </c>
       <c r="G553" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H553" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K553" s="1" t="s">
         <v>41</v>
@@ -13966,10 +13965,10 @@
         <v>21</v>
       </c>
       <c r="G554" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H554" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13986,18 +13985,18 @@
         <v>17</v>
       </c>
       <c r="I555" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J555" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L555" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B556" s="5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D556" s="1" t="s">
         <v>14</v>
@@ -14032,13 +14031,13 @@
         <v>17</v>
       </c>
       <c r="I557" s="6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J557" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L557" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14049,10 +14048,10 @@
         <v>123</v>
       </c>
       <c r="G558" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H558" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K558" s="1" t="s">
         <v>125</v>
@@ -14066,10 +14065,10 @@
         <v>89</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H559" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K559" s="1" t="s">
         <v>41</v>
@@ -14083,10 +14082,10 @@
         <v>21</v>
       </c>
       <c r="G560" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H560" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14109,15 +14108,15 @@
         <v>112</v>
       </c>
       <c r="L561" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B562" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D562" s="1" t="s">
         <v>29</v>
@@ -14158,7 +14157,7 @@
         <v>112</v>
       </c>
       <c r="L563" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14175,7 +14174,7 @@
         <v>17</v>
       </c>
       <c r="I564" s="8" t="s">
-        <v>606</v>
+        <v>565</v>
       </c>
       <c r="K564" s="1" t="s">
         <v>125</v>
@@ -14192,7 +14191,7 @@
         <v>279</v>
       </c>
       <c r="G565" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H565" s="11" t="s">
         <v>608</v>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3535" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="649">
   <si>
     <t xml:space="preserve">Source JSON Level</t>
   </si>
@@ -1770,6 +1770,15 @@
     <t xml:space="preserve">$.donors[].biomarkers[]</t>
   </si>
   <si>
+    <t xml:space="preserve">{current_biomarker_date}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomarker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_date</t>
+  </si>
+  <si>
     <t xml:space="preserve">OMOP PSA Biomarker Measurement</t>
   </si>
   <si>
@@ -1779,12 +1788,6 @@
     <t xml:space="preserve">Prostate specific antigen measurement</t>
   </si>
   <si>
-    <t xml:space="preserve">Biomarker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_date</t>
-  </si>
-  <si>
     <t xml:space="preserve">psa_level</t>
   </si>
   <si>
@@ -1792,9 +1795,6 @@
   </si>
   <si>
     <t xml:space="preserve">ng/mL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{current_biomarker_date}</t>
   </si>
   <si>
     <t xml:space="preserve">OMOP CA125 Biomarker Measurement</t>
@@ -13150,131 +13150,135 @@
         <v>61</v>
       </c>
     </row>
-    <row r="514" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="B514" s="5" t="s">
+      <c r="B514" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E514" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="D514" s="1" t="s">
+      <c r="F514" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G514" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H514" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="I514" s="20"/>
+      <c r="K514" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="515" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A515" s="0"/>
+      <c r="B515" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="D515" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E514" s="1" t="s">
+      <c r="E515" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F514" s="1" t="s">
+      <c r="F515" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G514" s="1" t="s">
+      <c r="G515" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H514" s="4" t="s">
+      <c r="H515" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K514" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E515" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F515" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G515" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H515" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I515" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="J515" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L515" s="1" t="s">
-        <v>559</v>
+      <c r="K515" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E516" s="1" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="H516" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H516" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I516" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="K516" s="1" t="s">
-        <v>125</v>
+      <c r="J516" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L516" s="1" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E517" s="1" t="s">
-        <v>363</v>
+        <v>31</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="H517" s="11" t="s">
-        <v>562</v>
+        <v>558</v>
+      </c>
+      <c r="H517" s="18" t="s">
+        <v>559</v>
       </c>
       <c r="K517" s="1" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E518" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F518" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G518" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H518" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="K518" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E519" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F518" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G518" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H518" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I518" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="J518" s="1" t="s">
+      <c r="F519" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G519" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H519" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I519" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="J519" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L518" s="1" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="519" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D519" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E519" s="1" t="s">
+      <c r="L519" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="F519" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G519" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="H519" s="11" t="s">
-        <v>561</v>
-      </c>
-      <c r="I519" s="20"/>
-      <c r="K519" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13331,10 +13335,10 @@
         <v>123</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H522" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K522" s="1" t="s">
         <v>125</v>
@@ -13348,7 +13352,7 @@
         <v>21</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H523" s="11" t="s">
         <v>569</v>
@@ -13434,10 +13438,10 @@
         <v>123</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H527" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K527" s="1" t="s">
         <v>125</v>
@@ -13451,7 +13455,7 @@
         <v>21</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H528" s="11" t="s">
         <v>575</v>
@@ -13474,13 +13478,13 @@
         <v>17</v>
       </c>
       <c r="I529" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J529" s="1" t="s">
         <v>112</v>
       </c>
       <c r="L529" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13537,10 +13541,10 @@
         <v>123</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H532" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K532" s="1" t="s">
         <v>125</v>
@@ -13554,7 +13558,7 @@
         <v>89</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H533" s="11" t="s">
         <v>579</v>
@@ -13571,7 +13575,7 @@
         <v>21</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H534" s="11" t="s">
         <v>580</v>
@@ -13654,10 +13658,10 @@
         <v>123</v>
       </c>
       <c r="G538" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H538" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K538" s="1" t="s">
         <v>125</v>
@@ -13671,7 +13675,7 @@
         <v>89</v>
       </c>
       <c r="G539" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H539" s="11" t="s">
         <v>585</v>
@@ -13688,7 +13692,7 @@
         <v>21</v>
       </c>
       <c r="G540" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H540" s="11" t="s">
         <v>586</v>
@@ -13771,10 +13775,10 @@
         <v>123</v>
       </c>
       <c r="G544" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H544" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K544" s="1" t="s">
         <v>125</v>
@@ -13788,7 +13792,7 @@
         <v>89</v>
       </c>
       <c r="G545" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H545" s="11" t="s">
         <v>590</v>
@@ -13851,10 +13855,10 @@
         <v>123</v>
       </c>
       <c r="G548" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H548" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K548" s="1" t="s">
         <v>125</v>
@@ -13868,7 +13872,7 @@
         <v>89</v>
       </c>
       <c r="G549" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H549" s="11" t="s">
         <v>594</v>
@@ -13931,10 +13935,10 @@
         <v>123</v>
       </c>
       <c r="G552" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H552" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K552" s="1" t="s">
         <v>125</v>
@@ -13948,7 +13952,7 @@
         <v>89</v>
       </c>
       <c r="G553" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H553" s="11" t="s">
         <v>598</v>
@@ -13965,7 +13969,7 @@
         <v>21</v>
       </c>
       <c r="G554" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H554" s="11" t="s">
         <v>598</v>
@@ -14048,10 +14052,10 @@
         <v>123</v>
       </c>
       <c r="G558" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H558" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K558" s="1" t="s">
         <v>125</v>
@@ -14065,7 +14069,7 @@
         <v>89</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H559" s="11" t="s">
         <v>602</v>
@@ -14082,7 +14086,7 @@
         <v>21</v>
       </c>
       <c r="G560" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H560" s="11" t="s">
         <v>602</v>
@@ -14174,7 +14178,7 @@
         <v>17</v>
       </c>
       <c r="I564" s="8" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="K564" s="1" t="s">
         <v>125</v>
@@ -14191,7 +14195,7 @@
         <v>279</v>
       </c>
       <c r="G565" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H565" s="11" t="s">
         <v>608</v>

--- a/config/MOHCCN to OMOP CDM Map v0.5.xlsx
+++ b/config/MOHCCN to OMOP CDM Map v0.5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3529" uniqueCount="649">
   <si>
     <t xml:space="preserve">Source JSON Level</t>
   </si>
@@ -1770,154 +1770,154 @@
     <t xml:space="preserve">$.donors[].biomarkers[]</t>
   </si>
   <si>
+    <t xml:space="preserve">OMOP PSA Biomarker Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4272032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prostate specific antigen measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomarker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psa_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4120724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng/mL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP CA125 Biomarker Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4197913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA 125 measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4118305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U/mL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP CEA Biomarker Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4244721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carcinoembryonic antigen measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP Estrogen Receptor Biomarker Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4307360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estrogen receptor assay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">er_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">er_percent_positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4041099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP Progesterone Receptor Biomarker Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progesterone receptor assay measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pr_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pr_percent_positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP HER2 IHC Status Biomarker Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35918264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HER2 IHC Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">her2_ihc_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP HER2 ISH Status Biomarker Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35918706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HER2 ISH Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">her2_ish_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP HPV IHC Status Biomarker Observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45763689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human papillomavirus screening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hpv_ihc_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45769444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunohistochemistry technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP HPV PCR Status Biomarker Observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hpv_pcr_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymerase chain reaction technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$.donors[].biomarkers[].hpv_strain[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMOP HPV strain Biomarker Measurements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human papillomavirus typing</t>
+  </si>
+  <si>
     <t xml:space="preserve">{current_biomarker_date}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biomarker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP PSA Biomarker Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4272032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prostate specific antigen measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">psa_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4120724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ng/mL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP CA125 Biomarker Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4197913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA 125 measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4118305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U/mL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP CEA Biomarker Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4244721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carcinoembryonic antigen measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP Estrogen Receptor Biomarker Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4307360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estrogen receptor assay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">er_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">er_percent_positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4041099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP Progesterone Receptor Biomarker Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progesterone receptor assay measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pr_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pr_percent_positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP HER2 IHC Status Biomarker Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35918264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HER2 IHC Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">her2_ihc_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP HER2 ISH Status Biomarker Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35918706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HER2 ISH Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">her2_ish_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP HPV IHC Status Biomarker Observation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45763689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human papillomavirus screening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hpv_ihc_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45769444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunohistochemistry technique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP HPV PCR Status Biomarker Observation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hpv_pcr_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polymerase chain reaction technique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$.donors[].biomarkers[].hpv_strain[]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMOP HPV strain Biomarker Measurements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human papillomavirus typing</t>
   </si>
   <si>
     <t xml:space="preserve">Biomarker - HPV strain (Code)</t>
@@ -2155,7 +2155,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2234,10 +2234,6 @@
     </xf>
     <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -13150,1132 +13146,1121 @@
         <v>61</v>
       </c>
     </row>
-    <row r="514" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="B514" s="1" t="s">
-        <v>63</v>
+      <c r="B514" s="5" t="s">
+        <v>557</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>557</v>
+        <v>168</v>
       </c>
       <c r="F514" s="1" t="s">
-        <v>75</v>
+        <v>277</v>
       </c>
       <c r="G514" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H514" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K514" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E515" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F515" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G515" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H515" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I515" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="H514" s="11" t="s">
+      <c r="J515" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L515" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="I514" s="20"/>
-      <c r="K514" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="515" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A515" s="0"/>
-      <c r="B515" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="D515" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E515" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F515" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G515" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H515" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K515" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E516" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H516" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I516" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="H516" s="18" t="s">
         <v>561</v>
       </c>
-      <c r="J516" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L516" s="1" t="s">
-        <v>562</v>
+      <c r="K516" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E517" s="1" t="s">
-        <v>31</v>
+        <v>363</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H517" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H517" s="11" t="s">
+        <v>562</v>
       </c>
       <c r="K517" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E518" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H518" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H518" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I518" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="K518" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J518" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L518" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B519" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E519" s="1" t="s">
-        <v>366</v>
+        <v>168</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H519" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I519" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="J519" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K519" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E520" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F520" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G520" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H520" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I520" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="J520" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L519" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="520" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B520" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="D520" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E520" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F520" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G520" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H520" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K520" s="1" t="s">
-        <v>41</v>
+      <c r="L520" s="1" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E521" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H521" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I521" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="J521" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L521" s="1" t="s">
-        <v>568</v>
+        <v>560</v>
+      </c>
+      <c r="H521" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="K521" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E522" s="1" t="s">
-        <v>31</v>
+        <v>363</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H522" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H522" s="11" t="s">
+        <v>568</v>
       </c>
       <c r="K522" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E523" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H523" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H523" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I523" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="K523" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J523" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L523" s="1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="524" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B524" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E524" s="1" t="s">
-        <v>366</v>
+        <v>168</v>
       </c>
       <c r="F524" s="1" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G524" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H524" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I524" s="6" t="s">
-        <v>570</v>
-      </c>
-      <c r="J524" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K524" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E525" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F525" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G525" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H525" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I525" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="J525" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L524" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="525" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B525" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="D525" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E525" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F525" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G525" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H525" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K525" s="1" t="s">
-        <v>41</v>
+      <c r="L525" s="1" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E526" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F526" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H526" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I526" s="6" t="s">
-        <v>573</v>
-      </c>
-      <c r="J526" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L526" s="1" t="s">
-        <v>574</v>
+        <v>560</v>
+      </c>
+      <c r="H526" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="K526" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E527" s="1" t="s">
-        <v>31</v>
+        <v>363</v>
       </c>
       <c r="F527" s="1" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H527" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H527" s="11" t="s">
+        <v>574</v>
       </c>
       <c r="K527" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E528" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F528" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H528" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H528" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I528" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="J528" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L528" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="529" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B529" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="K528" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D529" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E529" s="1" t="s">
-        <v>366</v>
+        <v>168</v>
       </c>
       <c r="F529" s="1" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G529" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H529" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I529" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="J529" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K529" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E530" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F530" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G530" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H530" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I530" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="J530" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L529" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="530" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B530" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="D530" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E530" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F530" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G530" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H530" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K530" s="1" t="s">
-        <v>41</v>
+      <c r="L530" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E531" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F531" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G531" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H531" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I531" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="J531" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L531" s="1" t="s">
-        <v>578</v>
+        <v>560</v>
+      </c>
+      <c r="H531" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="K531" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E532" s="1" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F532" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H532" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H532" s="11" t="s">
+        <v>578</v>
       </c>
       <c r="K532" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E533" s="1" t="s">
-        <v>115</v>
+        <v>363</v>
       </c>
       <c r="F533" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H533" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="K533" s="1" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E534" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F534" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H534" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H534" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I534" s="6" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J534" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L534" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="535" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B535" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="D535" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E535" s="1" t="s">
-        <v>366</v>
+        <v>168</v>
       </c>
       <c r="F535" s="1" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G535" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H535" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I535" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="J535" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K535" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="536" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E536" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F536" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G536" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H536" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I536" s="20" t="n">
+        <v>4030384</v>
+      </c>
+      <c r="J536" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L535" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="536" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B536" s="5" t="s">
+      <c r="L536" s="21" t="s">
         <v>583</v>
       </c>
-      <c r="D536" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E536" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F536" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G536" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H536" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K536" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="537" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E537" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G537" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H537" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I537" s="21" t="n">
-        <v>4030384</v>
-      </c>
-      <c r="J537" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L537" s="22" t="s">
-        <v>584</v>
+        <v>560</v>
+      </c>
+      <c r="H537" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="K537" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E538" s="1" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F538" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G538" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H538" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H538" s="11" t="s">
+        <v>584</v>
       </c>
       <c r="K538" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E539" s="1" t="s">
-        <v>115</v>
+        <v>363</v>
       </c>
       <c r="F539" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="G539" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H539" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="K539" s="1" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E540" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F540" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G540" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H540" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H540" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I540" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="J540" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L540" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="541" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B541" s="5" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D541" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E541" s="1" t="s">
-        <v>366</v>
+        <v>168</v>
       </c>
       <c r="F541" s="1" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G541" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H541" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I541" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="J541" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L541" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="542" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B542" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K541" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E542" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F542" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G542" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H542" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I542" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="D542" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E542" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F542" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G542" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H542" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K542" s="1" t="s">
-        <v>41</v>
+      <c r="J542" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L542" s="1" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E543" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F543" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G543" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H543" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I543" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="J543" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L543" s="1" t="s">
-        <v>589</v>
+        <v>560</v>
+      </c>
+      <c r="H543" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="K543" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E544" s="1" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F544" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G544" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H544" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H544" s="11" t="s">
+        <v>589</v>
       </c>
       <c r="K544" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="545" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B545" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E545" s="1" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="F545" s="1" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="G545" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H545" s="11" t="s">
-        <v>590</v>
+        <v>39</v>
+      </c>
+      <c r="H545" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="K545" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="546" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B546" s="5" t="s">
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E546" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F546" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G546" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H546" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I546" s="6" t="s">
         <v>591</v>
       </c>
-      <c r="D546" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E546" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F546" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G546" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H546" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K546" s="1" t="s">
-        <v>41</v>
+      <c r="J546" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L546" s="1" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E547" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="F547" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G547" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H547" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I547" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="J547" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L547" s="1" t="s">
-        <v>593</v>
+        <v>560</v>
+      </c>
+      <c r="H547" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="K547" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E548" s="1" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F548" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G548" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H548" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H548" s="11" t="s">
+        <v>593</v>
       </c>
       <c r="K548" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="549" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B549" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E549" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F549" s="1" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="G549" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H549" s="11" t="s">
-        <v>594</v>
+        <v>39</v>
+      </c>
+      <c r="H549" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="K549" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="550" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B550" s="5" t="s">
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E550" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F550" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G550" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H550" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I550" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="D550" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E550" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F550" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G550" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H550" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K550" s="1" t="s">
-        <v>41</v>
+      <c r="J550" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L550" s="1" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E551" s="1" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="F551" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G551" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H551" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I551" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="J551" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L551" s="1" t="s">
-        <v>597</v>
+        <v>560</v>
+      </c>
+      <c r="H551" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="K551" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E552" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F552" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G552" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H552" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H552" s="11" t="s">
+        <v>597</v>
       </c>
       <c r="K552" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E553" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F553" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="G553" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H553" s="11" t="s">
-        <v>598</v>
-      </c>
-      <c r="K553" s="1" t="s">
-        <v>41</v>
+        <v>597</v>
       </c>
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E554" s="1" t="s">
-        <v>118</v>
+        <v>216</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G554" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H554" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H554" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I554" s="3" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J554" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L554" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="555" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B555" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="D555" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E555" s="1" t="s">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="F555" s="1" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G555" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H555" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I555" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="J555" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H555" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K555" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E556" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F556" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G556" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H556" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I556" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="J556" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L555" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="556" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B556" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="D556" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E556" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F556" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G556" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H556" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K556" s="1" t="s">
-        <v>41</v>
+      <c r="L556" s="1" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E557" s="1" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="F557" s="1" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G557" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H557" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I557" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="J557" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L557" s="1" t="s">
-        <v>597</v>
+        <v>560</v>
+      </c>
+      <c r="H557" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="K557" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E558" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F558" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G558" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H558" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="H558" s="11" t="s">
+        <v>601</v>
       </c>
       <c r="K558" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E559" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F559" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G559" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="H559" s="11" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E560" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F560" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G560" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H560" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I560" s="20" t="n">
+        <v>4120014</v>
+      </c>
+      <c r="J560" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L560" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="561" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A561" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B561" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="D561" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E561" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F561" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G561" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H561" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K561" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="562" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E562" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F562" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G562" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H562" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I562" s="20" t="n">
+        <v>4194639</v>
+      </c>
+      <c r="J562" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L562" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E563" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F563" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G563" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H563" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I563" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="K563" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C564" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E564" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F559" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G559" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H559" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="K559" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E560" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F560" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G560" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H560" s="11" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E561" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F561" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G561" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H561" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I561" s="21" t="n">
-        <v>4120014</v>
-      </c>
-      <c r="J561" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L561" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="562" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A562" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="B562" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="D562" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E562" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F562" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G562" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H562" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K562" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="563" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E563" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F563" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G563" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H563" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I563" s="21" t="n">
-        <v>4194639</v>
-      </c>
-      <c r="J563" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L563" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E564" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F564" s="1" t="s">
-        <v>123</v>
+        <v>279</v>
       </c>
       <c r="G564" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H564" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I564" s="8" t="s">
-        <v>557</v>
+        <v>560</v>
+      </c>
+      <c r="H564" s="11" t="s">
+        <v>608</v>
       </c>
       <c r="K564" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C565" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G565" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="H565" s="11" t="s">
-        <v>608</v>
-      </c>
-      <c r="K565" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C566" s="1" t="s">
-        <v>609</v>
+        <v>17</v>
+      </c>
+      <c r="H565" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="566" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A566" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B566" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="D566" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F566" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G566" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H566" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="567" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A567" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="B567" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="D567" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K566" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E567" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F567" s="1" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="G567" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H567" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K567" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I567" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="J567" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L567" s="1" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E568" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G568" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H568" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I568" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="J568" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L568" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
+      </c>
+      <c r="H568" s="11" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E569" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F569" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="G569" s="1" t="s">
         <v>614</v>
@@ -14285,28 +14270,38 @@
       </c>
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D570" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="E570" s="1" t="s">
-        <v>118</v>
+        <v>616</v>
       </c>
       <c r="F570" s="1" t="s">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="G570" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="H570" s="11" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="H570" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I570" s="3" t="str">
+        <f aca="false">$B$566</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
+    </row>
+    <row r="571" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B571" s="5" t="s">
+        <v>617</v>
+      </c>
       <c r="D571" s="1" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>616</v>
+        <v>110</v>
       </c>
       <c r="F571" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="G571" s="1" t="s">
         <v>39</v>
@@ -14314,264 +14309,260 @@
       <c r="H571" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I571" s="3" t="str">
-        <f aca="false">$B$567</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
-    </row>
-    <row r="572" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B572" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="D572" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="K571" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E572" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F572" s="1" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="G572" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H572" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K572" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I572" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="J572" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L572" s="1" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E573" s="1" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>16</v>
+        <v>292</v>
       </c>
       <c r="G573" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H573" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I573" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="J573" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L573" s="1" t="s">
-        <v>619</v>
+        <v>40</v>
+      </c>
+      <c r="I573" s="3" t="str">
+        <f aca="false">$B$566</f>
+        <v>OMOP Tobacco Smoking Status Observation</v>
+      </c>
+      <c r="K573" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E574" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F574" s="1" t="s">
-        <v>292</v>
+        <v>16</v>
       </c>
       <c r="G574" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H574" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I574" s="3" t="str">
-        <f aca="false">$B$567</f>
-        <v>OMOP Tobacco Smoking Status Observation</v>
-      </c>
-      <c r="K574" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I574" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="J574" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L574" s="1" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E575" s="1" t="s">
-        <v>190</v>
+        <v>363</v>
       </c>
       <c r="F575" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G575" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H575" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I575" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="J575" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L575" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>614</v>
+      </c>
+      <c r="H575" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="K575" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="576" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A576" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B576" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="D576" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E576" s="1" t="s">
-        <v>363</v>
+        <v>110</v>
       </c>
       <c r="F576" s="1" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="G576" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="H576" s="11" t="s">
-        <v>622</v>
+        <v>39</v>
+      </c>
+      <c r="H576" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="K576" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="577" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A577" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="B577" s="5" t="s">
-        <v>624</v>
-      </c>
-      <c r="D577" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E577" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F577" s="1" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="G577" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H577" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K577" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I577" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="J577" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L577" s="1" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E578" s="1" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="F578" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G578" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H578" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I578" s="6" t="s">
-        <v>625</v>
-      </c>
-      <c r="J578" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L578" s="1" t="s">
-        <v>626</v>
+      <c r="H578" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I578" s="8" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E579" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G579" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H579" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I579" s="8" t="s">
-        <v>616</v>
+      <c r="H579" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I579" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="J579" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L579" s="1" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E580" s="1" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="F580" s="1" t="s">
-        <v>16</v>
+        <v>279</v>
       </c>
       <c r="G580" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H580" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I580" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="J580" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L580" s="1" t="s">
-        <v>621</v>
+        <v>614</v>
+      </c>
+      <c r="H580" s="11" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E581" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F581" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G581" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="H581" s="11" t="s">
-        <v>627</v>
+        <v>17</v>
+      </c>
+      <c r="H581" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A582" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B582" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="D582" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E582" s="1" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G582" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H582" s="4" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A583" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="B583" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="D583" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E583" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F583" s="1" t="s">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="G583" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H583" s="4" t="s">
-        <v>40</v>
+        <v>630</v>
+      </c>
+      <c r="H583" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="J583" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K583" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E584" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="G584" s="1" t="s">
         <v>630</v>
@@ -14579,50 +14570,44 @@
       <c r="H584" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="J584" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K584" s="1" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E585" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F585" s="1" t="s">
-        <v>21</v>
+        <v>632</v>
       </c>
       <c r="G585" s="1" t="s">
         <v>630</v>
       </c>
       <c r="H585" s="11" t="s">
-        <v>631</v>
+        <v>633</v>
+      </c>
+      <c r="K585" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E586" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F586" s="1" t="s">
-        <v>632</v>
+        <v>89</v>
       </c>
       <c r="G586" s="1" t="s">
         <v>630</v>
       </c>
       <c r="H586" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="K586" s="1" t="s">
-        <v>125</v>
+        <v>634</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E587" s="1" t="s">
-        <v>149</v>
+        <v>635</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="G587" s="1" t="s">
         <v>630</v>
@@ -14631,104 +14616,104 @@
         <v>634</v>
       </c>
     </row>
-    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="588" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B588" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E588" s="1" t="s">
-        <v>635</v>
+        <v>168</v>
       </c>
       <c r="F588" s="1" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="G588" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="H588" s="11" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="589" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B589" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="D589" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="H588" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E589" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F589" s="1" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="G589" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H589" s="4" t="s">
-        <v>40</v>
+        <v>17</v>
+      </c>
+      <c r="I589" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J589" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E590" s="1" t="s">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="F590" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G590" s="1" t="s">
-        <v>17</v>
+        <v>630</v>
       </c>
       <c r="H590" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I590" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="J590" s="1" t="s">
-        <v>177</v>
+        <v>628</v>
+      </c>
+      <c r="I590" s="3" t="str">
+        <f aca="false">$B$582</f>
+        <v>OMOP Comorbidity Condition</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E591" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F591" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G591" s="1" t="s">
-        <v>630</v>
+        <v>17</v>
       </c>
       <c r="H591" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="I591" s="3" t="str">
-        <f aca="false">$B$583</f>
-        <v>OMOP Comorbidity Condition</v>
+        <v>17</v>
+      </c>
+      <c r="I591" s="3" t="n">
+        <v>1147127</v>
+      </c>
+      <c r="J591" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E592" s="1" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="F592" s="1" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G592" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H592" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I592" s="3" t="n">
-        <v>1147127</v>
-      </c>
-      <c r="J592" s="1" t="s">
-        <v>56</v>
+        <v>630</v>
+      </c>
+      <c r="H592" s="11" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E593" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F593" s="1" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="G593" s="1" t="s">
         <v>630</v>
@@ -14737,99 +14722,86 @@
         <v>637</v>
       </c>
     </row>
-    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E594" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F594" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G594" s="1" t="s">
+    <row r="594" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B594" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G594" s="22" t="s">
         <v>630</v>
       </c>
-      <c r="H594" s="11" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="595" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B595" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="G595" s="23" t="s">
+      <c r="H594" s="15" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G595" s="22" t="s">
         <v>630</v>
       </c>
-      <c r="H595" s="15" t="s">
-        <v>640</v>
+      <c r="H595" s="12" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G596" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="H596" s="12" t="s">
-        <v>641</v>
-      </c>
+      <c r="H596" s="11"/>
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H597" s="11"/>
     </row>
-    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H598" s="11"/>
-    </row>
-    <row r="601" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B601" s="5" t="s">
+    <row r="600" customFormat="false" ht="24.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B600" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="G601" s="23" t="s">
+      <c r="G600" s="22" t="s">
         <v>643</v>
       </c>
+      <c r="H600" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G601" s="22" t="s">
+        <v>643</v>
+      </c>
       <c r="H601" s="12" t="s">
-        <v>46</v>
+        <v>644</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G602" s="23" t="s">
+      <c r="G602" s="22" t="s">
         <v>643</v>
       </c>
       <c r="H602" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G603" s="23" t="s">
+      <c r="G603" s="22" t="s">
         <v>643</v>
       </c>
       <c r="H603" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G604" s="23" t="s">
+      <c r="G604" s="22" t="s">
         <v>643</v>
       </c>
       <c r="H604" s="12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G605" s="23" t="s">
+      <c r="G605" s="22" t="s">
         <v>643</v>
       </c>
       <c r="H605" s="12" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G606" s="23" t="s">
-        <v>643</v>
-      </c>
-      <c r="H606" s="12" t="s">
         <v>648</v>
       </c>
     </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
